--- a/Financial Analysis/IONQ.xlsx
+++ b/Financial Analysis/IONQ.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28526"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\antos\Desktop\Financial Analysis\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\antos\Documents\GitHub\FinanceModels\Financial Analysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DBF2C9FE-FA4D-4B77-A747-619F89820944}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{689CD8F5-9652-4EEE-B079-68FDEF6F9F10}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{054FC3C2-46E6-4A64-A90B-FD32B5955AC0}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="67">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="67">
   <si>
     <t>IONQ</t>
   </si>
@@ -376,14 +376,14 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>17</xdr:col>
-      <xdr:colOff>22860</xdr:colOff>
+      <xdr:col>19</xdr:col>
+      <xdr:colOff>30480</xdr:colOff>
       <xdr:row>0</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>17</xdr:col>
-      <xdr:colOff>22860</xdr:colOff>
+      <xdr:col>19</xdr:col>
+      <xdr:colOff>30480</xdr:colOff>
       <xdr:row>33</xdr:row>
       <xdr:rowOff>91440</xdr:rowOff>
     </xdr:to>
@@ -400,7 +400,7 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="11262360" y="0"/>
+          <a:off x="12489180" y="0"/>
           <a:ext cx="0" cy="6126480"/>
         </a:xfrm>
         <a:prstGeom prst="line">
@@ -749,14 +749,14 @@
         <v>1</v>
       </c>
       <c r="D3" s="4">
-        <v>22.57</v>
+        <v>47.13</v>
       </c>
       <c r="E3" s="3">
         <v>45729</v>
       </c>
       <c r="F3" s="3">
         <f ca="1">TODAY()</f>
-        <v>45745</v>
+        <v>45804</v>
       </c>
       <c r="G3" s="3">
         <v>45804</v>
@@ -767,8 +767,11 @@
         <v>2</v>
       </c>
       <c r="D4" s="5">
-        <f>217.9</f>
-        <v>217.9</v>
+        <f>247.8</f>
+        <v>247.8</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>63</v>
       </c>
     </row>
     <row r="5" spans="2:11" x14ac:dyDescent="0.3">
@@ -777,7 +780,7 @@
       </c>
       <c r="D5" s="5">
         <f>D3*D4</f>
-        <v>4918.0030000000006</v>
+        <v>11678.814</v>
       </c>
     </row>
     <row r="6" spans="2:11" x14ac:dyDescent="0.3">
@@ -785,8 +788,11 @@
         <v>4</v>
       </c>
       <c r="D6" s="5">
-        <f>54.9+285.9+23.5</f>
-        <v>364.29999999999995</v>
+        <f>159.7+428.6+108.9</f>
+        <v>697.19999999999993</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>63</v>
       </c>
     </row>
     <row r="7" spans="2:11" x14ac:dyDescent="0.3">
@@ -796,6 +802,9 @@
       <c r="D7" s="5">
         <v>0</v>
       </c>
+      <c r="E7" s="2" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="8" spans="2:11" x14ac:dyDescent="0.3">
       <c r="C8" t="s">
@@ -803,7 +812,7 @@
       </c>
       <c r="D8" s="5">
         <f>D6-D7</f>
-        <v>364.29999999999995</v>
+        <v>697.19999999999993</v>
       </c>
     </row>
     <row r="9" spans="2:11" x14ac:dyDescent="0.3">
@@ -812,7 +821,7 @@
       </c>
       <c r="D9" s="5">
         <f>D5-D8</f>
-        <v>4553.7030000000004</v>
+        <v>10981.614</v>
       </c>
     </row>
     <row r="10" spans="2:11" x14ac:dyDescent="0.3">
@@ -996,16 +1005,16 @@
         <v>11.7</v>
       </c>
       <c r="S3" s="8">
-        <v>7.5</v>
+        <v>7.6</v>
       </c>
       <c r="T3" s="8">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="U3" s="8">
         <v>24</v>
       </c>
       <c r="V3" s="8">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="W3" s="8"/>
       <c r="X3" s="8">
@@ -1025,48 +1034,48 @@
         <v>43.099999999999994</v>
       </c>
       <c r="AB3" s="8">
-        <f>AA3*1.95</f>
-        <v>84.044999999999987</v>
+        <f>SUM(S3:V3)</f>
+        <v>78.599999999999994</v>
       </c>
       <c r="AC3" s="8">
         <f>AB3*1.8</f>
-        <v>151.28099999999998</v>
+        <v>141.47999999999999</v>
       </c>
       <c r="AD3" s="8">
         <f>AC3*1.7</f>
-        <v>257.17769999999996</v>
+        <v>240.51599999999996</v>
       </c>
       <c r="AE3" s="8">
         <f>AD3*1.6</f>
-        <v>411.48431999999997</v>
+        <v>384.82559999999995</v>
       </c>
       <c r="AF3" s="8">
         <f>AE3*1.5</f>
-        <v>617.22647999999992</v>
+        <v>577.23839999999996</v>
       </c>
       <c r="AG3" s="8">
         <f>AF3*1.45</f>
-        <v>894.97839599999986</v>
+        <v>836.99567999999988</v>
       </c>
       <c r="AH3" s="8">
         <f>AG3*1.25</f>
-        <v>1118.7229949999999</v>
+        <v>1046.2445999999998</v>
       </c>
       <c r="AI3" s="8">
         <f>AH3*1.2</f>
-        <v>1342.4675939999997</v>
+        <v>1255.4935199999998</v>
       </c>
       <c r="AJ3" s="8">
         <f>AI3*1.15</f>
-        <v>1543.8377330999995</v>
+        <v>1443.8175479999995</v>
       </c>
       <c r="AK3" s="8">
         <f>AJ3*1.1</f>
-        <v>1698.2215064099996</v>
+        <v>1588.1993027999997</v>
       </c>
       <c r="AL3" s="8">
         <f>AK3*1.05</f>
-        <v>1783.1325817304996</v>
+        <v>1667.6092679399999</v>
       </c>
     </row>
     <row r="4" spans="2:38" x14ac:dyDescent="0.3">
@@ -1122,12 +1131,11 @@
         <v>5</v>
       </c>
       <c r="S4" s="5">
-        <f>S3-S5</f>
-        <v>3.5999999999999996</v>
+        <v>4.3</v>
       </c>
       <c r="T4" s="5">
         <f t="shared" ref="T4:V4" si="0">T3-T5</f>
-        <v>10.559999999999999</v>
+        <v>8.16</v>
       </c>
       <c r="U4" s="5">
         <f t="shared" si="0"/>
@@ -1135,7 +1143,7 @@
       </c>
       <c r="V4" s="5">
         <f t="shared" si="0"/>
-        <v>12.48</v>
+        <v>14.399999999999999</v>
       </c>
       <c r="X4" s="5">
         <f>SUM(C4:F4)</f>
@@ -1155,47 +1163,47 @@
       </c>
       <c r="AB4" s="5">
         <f>AB3-AB5</f>
-        <v>42.022499999999994</v>
+        <v>39.299999999999997</v>
       </c>
       <c r="AC4" s="5">
         <f t="shared" ref="AC4:AL4" si="1">AC3-AC5</f>
-        <v>74.127689999999987</v>
+        <v>69.325199999999995</v>
       </c>
       <c r="AD4" s="5">
         <f t="shared" si="1"/>
-        <v>123.44529599999998</v>
+        <v>115.44767999999998</v>
       </c>
       <c r="AE4" s="5">
         <f t="shared" si="1"/>
-        <v>197.51247359999996</v>
+        <v>184.71628799999996</v>
       </c>
       <c r="AF4" s="5">
         <f t="shared" si="1"/>
-        <v>283.92418079999993</v>
+        <v>265.52966399999997</v>
       </c>
       <c r="AG4" s="5">
         <f t="shared" si="1"/>
-        <v>393.79049423999987</v>
+        <v>368.27809919999993</v>
       </c>
       <c r="AH4" s="5">
         <f t="shared" si="1"/>
-        <v>469.86365790000002</v>
+        <v>439.422732</v>
       </c>
       <c r="AI4" s="5">
         <f t="shared" si="1"/>
-        <v>536.98703759999989</v>
+        <v>502.19740799999988</v>
       </c>
       <c r="AJ4" s="5">
         <f t="shared" si="1"/>
-        <v>586.65833857799976</v>
+        <v>548.65066823999985</v>
       </c>
       <c r="AK4" s="5">
         <f t="shared" si="1"/>
-        <v>628.34195737169989</v>
+        <v>587.63374203599983</v>
       </c>
       <c r="AL4" s="5">
         <f t="shared" si="1"/>
-        <v>641.92772942297984</v>
+        <v>600.33933645839988</v>
       </c>
     </row>
     <row r="5" spans="2:38" s="1" customFormat="1" x14ac:dyDescent="0.3">
@@ -1203,7 +1211,7 @@
         <v>25</v>
       </c>
       <c r="C5" s="8">
-        <f t="shared" ref="C5:R5" si="2">C3-C4</f>
+        <f t="shared" ref="C5:S5" si="2">C3-C4</f>
         <v>-0.1</v>
       </c>
       <c r="D5" s="8">
@@ -1267,12 +1275,12 @@
         <v>6.6999999999999993</v>
       </c>
       <c r="S5" s="8">
-        <f>S3*0.52</f>
-        <v>3.9000000000000004</v>
+        <f t="shared" si="2"/>
+        <v>3.3</v>
       </c>
       <c r="T5" s="8">
         <f t="shared" ref="T5:V5" si="3">T3*0.52</f>
-        <v>11.440000000000001</v>
+        <v>8.84</v>
       </c>
       <c r="U5" s="8">
         <f t="shared" si="3"/>
@@ -1280,7 +1288,7 @@
       </c>
       <c r="V5" s="8">
         <f t="shared" si="3"/>
-        <v>13.52</v>
+        <v>15.600000000000001</v>
       </c>
       <c r="X5" s="8">
         <f>X3-X4</f>
@@ -1300,47 +1308,47 @@
       </c>
       <c r="AB5" s="8">
         <f>AB3*0.5</f>
-        <v>42.022499999999994</v>
+        <v>39.299999999999997</v>
       </c>
       <c r="AC5" s="8">
         <f>AC3*0.51</f>
-        <v>77.153309999999991</v>
+        <v>72.154799999999994</v>
       </c>
       <c r="AD5" s="8">
         <f>AD3*0.52</f>
-        <v>133.73240399999997</v>
+        <v>125.06831999999999</v>
       </c>
       <c r="AE5" s="8">
         <f>AE3*0.52</f>
-        <v>213.9718464</v>
+        <v>200.10931199999999</v>
       </c>
       <c r="AF5" s="8">
         <f>AF3*0.54</f>
-        <v>333.30229919999999</v>
+        <v>311.70873599999999</v>
       </c>
       <c r="AG5" s="8">
         <f>AG3*0.56</f>
-        <v>501.18790175999999</v>
+        <v>468.71758079999995</v>
       </c>
       <c r="AH5" s="8">
         <f>AH3*0.58</f>
-        <v>648.85933709999983</v>
+        <v>606.82186799999977</v>
       </c>
       <c r="AI5" s="8">
         <f>AI3*0.6</f>
-        <v>805.48055639999984</v>
+        <v>753.29611199999988</v>
       </c>
       <c r="AJ5" s="8">
         <f>AJ3*0.62</f>
-        <v>957.17939452199971</v>
+        <v>895.16687975999969</v>
       </c>
       <c r="AK5" s="8">
         <f>AK3*0.63</f>
-        <v>1069.8795490382997</v>
+        <v>1000.5655607639999</v>
       </c>
       <c r="AL5" s="8">
         <f>AL3*0.64</f>
-        <v>1141.2048523075198</v>
+        <v>1067.2699314816</v>
       </c>
     </row>
     <row r="6" spans="2:38" x14ac:dyDescent="0.3">
@@ -1395,7 +1403,9 @@
       <c r="R6" s="5">
         <v>40.1</v>
       </c>
-      <c r="S6" s="5"/>
+      <c r="S6" s="5">
+        <v>40</v>
+      </c>
       <c r="T6" s="5"/>
       <c r="U6" s="5"/>
       <c r="V6" s="5"/>
@@ -1512,7 +1522,9 @@
       <c r="R7" s="5">
         <v>8.9</v>
       </c>
-      <c r="S7" s="5"/>
+      <c r="S7" s="5">
+        <v>8.6</v>
+      </c>
       <c r="T7" s="5"/>
       <c r="U7" s="5"/>
       <c r="V7" s="5"/>
@@ -1534,47 +1546,47 @@
       </c>
       <c r="AB7" s="5">
         <f>AB3*0.4</f>
-        <v>33.617999999999995</v>
+        <v>31.439999999999998</v>
       </c>
       <c r="AC7" s="5">
         <f>AC3*0.3</f>
-        <v>45.384299999999989</v>
+        <v>42.443999999999996</v>
       </c>
       <c r="AD7" s="5">
         <f>AD3*0.26</f>
-        <v>66.866201999999987</v>
+        <v>62.534159999999993</v>
       </c>
       <c r="AE7" s="5">
         <f>AE3*0.24</f>
-        <v>98.756236799999982</v>
+        <v>92.358143999999982</v>
       </c>
       <c r="AF7" s="5">
         <f>AF3*0.22</f>
-        <v>135.78982559999997</v>
+        <v>126.992448</v>
       </c>
       <c r="AG7" s="5">
         <f>AG3*0.2</f>
-        <v>178.99567919999998</v>
+        <v>167.399136</v>
       </c>
       <c r="AH7" s="5">
         <f>AH3*0.18</f>
-        <v>201.37013909999996</v>
+        <v>188.32402799999994</v>
       </c>
       <c r="AI7" s="5">
         <f>AI3*0.17</f>
-        <v>228.21949097999996</v>
+        <v>213.43389839999998</v>
       </c>
       <c r="AJ7" s="5">
         <f>AJ3*0.16</f>
-        <v>247.01403729599991</v>
+        <v>231.01080767999994</v>
       </c>
       <c r="AK7" s="5">
         <f>AK3*0.15</f>
-        <v>254.73322596149993</v>
+        <v>238.22989541999993</v>
       </c>
       <c r="AL7" s="5">
         <f>AL3*0.14</f>
-        <v>249.63856144226997</v>
+        <v>233.4652975116</v>
       </c>
     </row>
     <row r="8" spans="2:38" x14ac:dyDescent="0.3">
@@ -1629,7 +1641,9 @@
       <c r="R8" s="5">
         <v>29.7</v>
       </c>
-      <c r="S8" s="5"/>
+      <c r="S8" s="5">
+        <v>23.8</v>
+      </c>
       <c r="T8" s="5"/>
       <c r="U8" s="5"/>
       <c r="V8" s="5"/>
@@ -1746,7 +1760,9 @@
       <c r="R9" s="5">
         <v>5.5</v>
       </c>
-      <c r="S9" s="5"/>
+      <c r="S9" s="5">
+        <v>6.6</v>
+      </c>
       <c r="T9" s="5"/>
       <c r="U9" s="5"/>
       <c r="V9" s="5"/>
@@ -1879,7 +1895,10 @@
         <f t="shared" si="7"/>
         <v>84.2</v>
       </c>
-      <c r="S10" s="5"/>
+      <c r="S10" s="5">
+        <f t="shared" ref="S10" si="8">SUM(S6:S9)</f>
+        <v>79</v>
+      </c>
       <c r="T10" s="5"/>
       <c r="U10" s="5"/>
       <c r="V10" s="5"/>
@@ -1900,48 +1919,48 @@
         <v>255</v>
       </c>
       <c r="AB10" s="5">
-        <f t="shared" ref="AB10:AL10" si="8">SUM(AB6:AB9)</f>
-        <v>301.42</v>
+        <f t="shared" ref="AB10:AL10" si="9">SUM(AB6:AB9)</f>
+        <v>299.24200000000002</v>
       </c>
       <c r="AC10" s="5">
-        <f t="shared" si="8"/>
-        <v>345.84064000000001</v>
+        <f t="shared" si="9"/>
+        <v>342.90034000000003</v>
       </c>
       <c r="AD10" s="5">
-        <f t="shared" si="8"/>
-        <v>388.56169280000012</v>
+        <f t="shared" si="9"/>
+        <v>384.22965080000012</v>
       </c>
       <c r="AE10" s="5">
-        <f t="shared" si="8"/>
-        <v>436.41252906000011</v>
+        <f t="shared" si="9"/>
+        <v>430.01443626000014</v>
       </c>
       <c r="AF10" s="5">
-        <f t="shared" si="8"/>
-        <v>487.64123721660008</v>
+        <f t="shared" si="9"/>
+        <v>478.84385961660007</v>
       </c>
       <c r="AG10" s="5">
-        <f t="shared" si="8"/>
-        <v>544.71223842004213</v>
+        <f t="shared" si="9"/>
+        <v>533.11569522004208</v>
       </c>
       <c r="AH10" s="5">
-        <f t="shared" si="8"/>
-        <v>581.56205352023346</v>
+        <f t="shared" si="9"/>
+        <v>568.51594242023339</v>
       </c>
       <c r="AI10" s="5">
-        <f t="shared" si="8"/>
-        <v>623.52556254162698</v>
+        <f t="shared" si="9"/>
+        <v>608.73996996162691</v>
       </c>
       <c r="AJ10" s="5">
-        <f t="shared" si="8"/>
-        <v>658.10304602999861</v>
+        <f t="shared" si="9"/>
+        <v>642.09981641399861</v>
       </c>
       <c r="AK10" s="5">
-        <f t="shared" si="8"/>
-        <v>682.30538177224082</v>
+        <f t="shared" si="9"/>
+        <v>665.80205123074086</v>
       </c>
       <c r="AL10" s="5">
-        <f t="shared" si="8"/>
-        <v>694.42702730147312</v>
+        <f t="shared" si="9"/>
+        <v>678.2537633708032</v>
       </c>
     </row>
     <row r="11" spans="2:38" s="1" customFormat="1" x14ac:dyDescent="0.3">
@@ -1949,70 +1968,73 @@
         <v>31</v>
       </c>
       <c r="C11" s="8">
-        <f t="shared" ref="C11:R11" si="9">C5-C10</f>
+        <f t="shared" ref="C11:R11" si="10">C5-C10</f>
         <v>-7.4</v>
       </c>
       <c r="D11" s="8">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>-10</v>
       </c>
       <c r="E11" s="8">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>-10.6</v>
       </c>
       <c r="F11" s="8">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>-10.8</v>
       </c>
       <c r="G11" s="8">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>-18.3</v>
       </c>
       <c r="H11" s="8">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>-19</v>
       </c>
       <c r="I11" s="8">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>-24.799999999999997</v>
       </c>
       <c r="J11" s="8">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>-23.699999999999996</v>
       </c>
       <c r="K11" s="8">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>-28</v>
       </c>
       <c r="L11" s="8">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>-33.099999999999994</v>
       </c>
       <c r="M11" s="8">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>-42.1</v>
       </c>
       <c r="N11" s="8">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>-54.500000000000007</v>
       </c>
       <c r="O11" s="8">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>-52.900000000000006</v>
       </c>
       <c r="P11" s="8">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>-48.899999999999991</v>
       </c>
       <c r="Q11" s="8">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>-53.100000000000009</v>
       </c>
       <c r="R11" s="8">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>-77.5</v>
       </c>
-      <c r="S11" s="8"/>
+      <c r="S11" s="8">
+        <f t="shared" ref="S11" si="11">S5-S10</f>
+        <v>-75.7</v>
+      </c>
       <c r="T11" s="8"/>
       <c r="U11" s="8"/>
       <c r="V11" s="8"/>
@@ -2033,48 +2055,48 @@
         <v>-232.4</v>
       </c>
       <c r="AB11" s="8">
-        <f t="shared" ref="AB11:AL11" si="10">AB5-AB10</f>
-        <v>-259.39750000000004</v>
+        <f t="shared" ref="AB11:AL11" si="12">AB5-AB10</f>
+        <v>-259.94200000000001</v>
       </c>
       <c r="AC11" s="8">
-        <f t="shared" si="10"/>
-        <v>-268.68733000000003</v>
+        <f t="shared" si="12"/>
+        <v>-270.74554000000001</v>
       </c>
       <c r="AD11" s="8">
-        <f t="shared" si="10"/>
-        <v>-254.82928880000014</v>
+        <f t="shared" si="12"/>
+        <v>-259.16133080000014</v>
       </c>
       <c r="AE11" s="8">
-        <f t="shared" si="10"/>
-        <v>-222.44068266000011</v>
+        <f t="shared" si="12"/>
+        <v>-229.90512426000015</v>
       </c>
       <c r="AF11" s="8">
-        <f t="shared" si="10"/>
-        <v>-154.33893801660008</v>
+        <f t="shared" si="12"/>
+        <v>-167.13512361660008</v>
       </c>
       <c r="AG11" s="8">
-        <f t="shared" si="10"/>
-        <v>-43.524336660042138</v>
+        <f t="shared" si="12"/>
+        <v>-64.398114420042134</v>
       </c>
       <c r="AH11" s="8">
-        <f t="shared" si="10"/>
-        <v>67.297283579766372</v>
+        <f t="shared" si="12"/>
+        <v>38.305925579766381</v>
       </c>
       <c r="AI11" s="8">
-        <f t="shared" si="10"/>
-        <v>181.95499385837286</v>
+        <f t="shared" si="12"/>
+        <v>144.55614203837297</v>
       </c>
       <c r="AJ11" s="8">
-        <f t="shared" si="10"/>
-        <v>299.0763484920011</v>
+        <f t="shared" si="12"/>
+        <v>253.06706334600108</v>
       </c>
       <c r="AK11" s="8">
-        <f t="shared" si="10"/>
-        <v>387.57416726605891</v>
+        <f t="shared" si="12"/>
+        <v>334.76350953325903</v>
       </c>
       <c r="AL11" s="8">
-        <f t="shared" si="10"/>
-        <v>446.77782500604667</v>
+        <f t="shared" si="12"/>
+        <v>389.0161681107968</v>
       </c>
     </row>
     <row r="12" spans="2:38" x14ac:dyDescent="0.3">
@@ -2129,7 +2151,9 @@
       <c r="R12" s="5">
         <v>128.5</v>
       </c>
-      <c r="S12" s="5"/>
+      <c r="S12" s="5">
+        <v>-38.5</v>
+      </c>
       <c r="T12" s="5"/>
       <c r="U12" s="5"/>
       <c r="V12" s="5"/>
@@ -2235,7 +2259,9 @@
       <c r="R13" s="5">
         <v>-4.0999999999999996</v>
       </c>
-      <c r="S13" s="5"/>
+      <c r="S13" s="5">
+        <v>-4.9000000000000004</v>
+      </c>
       <c r="T13" s="5"/>
       <c r="U13" s="5"/>
       <c r="V13" s="5"/>
@@ -2260,43 +2286,43 @@
         <v>-18.745999999999999</v>
       </c>
       <c r="AC13" s="5">
-        <f t="shared" ref="AC13:AL13" si="11">AB13*1.03</f>
+        <f t="shared" ref="AC13:AL13" si="13">AB13*1.03</f>
         <v>-19.30838</v>
       </c>
       <c r="AD13" s="5">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>-19.8876314</v>
       </c>
       <c r="AE13" s="5">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>-20.484260341999999</v>
       </c>
       <c r="AF13" s="5">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>-21.098788152259999</v>
       </c>
       <c r="AG13" s="5">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>-21.731751796827801</v>
       </c>
       <c r="AH13" s="5">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>-22.383704350732636</v>
       </c>
       <c r="AI13" s="5">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>-23.055215481254617</v>
       </c>
       <c r="AJ13" s="5">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>-23.746871945692256</v>
       </c>
       <c r="AK13" s="5">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>-24.459278104063024</v>
       </c>
       <c r="AL13" s="5">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>-25.193056447184915</v>
       </c>
     </row>
@@ -2352,7 +2378,9 @@
       <c r="R14" s="5">
         <v>0.1</v>
       </c>
-      <c r="S14" s="5"/>
+      <c r="S14" s="5">
+        <v>-0.1</v>
+      </c>
       <c r="T14" s="5"/>
       <c r="U14" s="5"/>
       <c r="V14" s="5"/>
@@ -2411,70 +2439,73 @@
         <v>39</v>
       </c>
       <c r="C15" s="5">
-        <f t="shared" ref="C15:R15" si="12">SUM(C12:C14)</f>
+        <f t="shared" ref="C15:R15" si="14">SUM(C12:C14)</f>
         <v>0</v>
       </c>
       <c r="D15" s="5">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="E15" s="5">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>4.3</v>
       </c>
       <c r="F15" s="5">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>63.199999999999996</v>
       </c>
       <c r="G15" s="5">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>-14</v>
       </c>
       <c r="H15" s="5">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>-17.500000000000004</v>
       </c>
       <c r="I15" s="5">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>-0.90000000000000013</v>
       </c>
       <c r="J15" s="5">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>-5</v>
       </c>
       <c r="K15" s="5">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>-0.70000000000000007</v>
       </c>
       <c r="L15" s="5">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>10.6</v>
       </c>
       <c r="M15" s="5">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>2.4999999999999996</v>
       </c>
       <c r="N15" s="5">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>-12.600000000000001</v>
       </c>
       <c r="O15" s="5">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>-13.299999999999999</v>
       </c>
       <c r="P15" s="5">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>-11.299999999999999</v>
       </c>
       <c r="Q15" s="5">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>-0.60000000000000009</v>
       </c>
       <c r="R15" s="5">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>124.5</v>
       </c>
-      <c r="S15" s="5"/>
+      <c r="S15" s="5">
+        <f t="shared" ref="S15" si="15">SUM(S12:S14)</f>
+        <v>-43.5</v>
+      </c>
       <c r="T15" s="5"/>
       <c r="U15" s="5"/>
       <c r="V15" s="5"/>
@@ -2495,47 +2526,47 @@
         <v>99.3</v>
       </c>
       <c r="AB15" s="5">
-        <f t="shared" ref="AB15:AL15" si="13">SUM(AB12:AB14)</f>
+        <f t="shared" ref="AB15:AL15" si="16">SUM(AB12:AB14)</f>
         <v>-18.745999999999999</v>
       </c>
       <c r="AC15" s="5">
-        <f t="shared" si="13"/>
+        <f t="shared" si="16"/>
         <v>-19.30838</v>
       </c>
       <c r="AD15" s="5">
-        <f t="shared" si="13"/>
+        <f t="shared" si="16"/>
         <v>-19.8876314</v>
       </c>
       <c r="AE15" s="5">
-        <f t="shared" si="13"/>
+        <f t="shared" si="16"/>
         <v>-20.484260341999999</v>
       </c>
       <c r="AF15" s="5">
-        <f t="shared" si="13"/>
+        <f t="shared" si="16"/>
         <v>-21.098788152259999</v>
       </c>
       <c r="AG15" s="5">
-        <f t="shared" si="13"/>
+        <f t="shared" si="16"/>
         <v>-21.731751796827801</v>
       </c>
       <c r="AH15" s="5">
-        <f t="shared" si="13"/>
+        <f t="shared" si="16"/>
         <v>-22.383704350732636</v>
       </c>
       <c r="AI15" s="5">
-        <f t="shared" si="13"/>
+        <f t="shared" si="16"/>
         <v>-23.055215481254617</v>
       </c>
       <c r="AJ15" s="5">
-        <f t="shared" si="13"/>
+        <f t="shared" si="16"/>
         <v>-23.746871945692256</v>
       </c>
       <c r="AK15" s="5">
-        <f t="shared" si="13"/>
+        <f t="shared" si="16"/>
         <v>-24.459278104063024</v>
       </c>
       <c r="AL15" s="5">
-        <f t="shared" si="13"/>
+        <f t="shared" si="16"/>
         <v>-25.193056447184915</v>
       </c>
     </row>
@@ -2544,70 +2575,73 @@
         <v>35</v>
       </c>
       <c r="C16" s="8">
-        <f t="shared" ref="C16:R16" si="14">C11-C15</f>
+        <f t="shared" ref="C16:R16" si="17">C11-C15</f>
         <v>-7.4</v>
       </c>
       <c r="D16" s="8">
-        <f t="shared" si="14"/>
+        <f t="shared" si="17"/>
         <v>-10</v>
       </c>
       <c r="E16" s="8">
-        <f t="shared" si="14"/>
+        <f t="shared" si="17"/>
         <v>-14.899999999999999</v>
       </c>
       <c r="F16" s="8">
-        <f t="shared" si="14"/>
+        <f t="shared" si="17"/>
         <v>-74</v>
       </c>
       <c r="G16" s="8">
-        <f t="shared" si="14"/>
+        <f t="shared" si="17"/>
         <v>-4.3000000000000007</v>
       </c>
       <c r="H16" s="8">
-        <f t="shared" si="14"/>
+        <f t="shared" si="17"/>
         <v>-1.4999999999999964</v>
       </c>
       <c r="I16" s="8">
-        <f t="shared" si="14"/>
+        <f t="shared" si="17"/>
         <v>-23.9</v>
       </c>
       <c r="J16" s="8">
-        <f t="shared" si="14"/>
+        <f t="shared" si="17"/>
         <v>-18.699999999999996</v>
       </c>
       <c r="K16" s="8">
-        <f t="shared" si="14"/>
+        <f t="shared" si="17"/>
         <v>-27.3</v>
       </c>
       <c r="L16" s="8">
-        <f t="shared" si="14"/>
+        <f t="shared" si="17"/>
         <v>-43.699999999999996</v>
       </c>
       <c r="M16" s="8">
-        <f t="shared" si="14"/>
+        <f t="shared" si="17"/>
         <v>-44.6</v>
       </c>
       <c r="N16" s="8">
-        <f t="shared" si="14"/>
+        <f t="shared" si="17"/>
         <v>-41.900000000000006</v>
       </c>
       <c r="O16" s="8">
-        <f t="shared" si="14"/>
+        <f t="shared" si="17"/>
         <v>-39.600000000000009</v>
       </c>
       <c r="P16" s="8">
-        <f t="shared" si="14"/>
+        <f t="shared" si="17"/>
         <v>-37.599999999999994</v>
       </c>
       <c r="Q16" s="8">
-        <f t="shared" si="14"/>
+        <f t="shared" si="17"/>
         <v>-52.500000000000007</v>
       </c>
       <c r="R16" s="8">
-        <f t="shared" si="14"/>
+        <f t="shared" si="17"/>
         <v>-202</v>
       </c>
-      <c r="S16" s="8"/>
+      <c r="S16" s="8">
+        <f t="shared" ref="S16" si="18">S11-S15</f>
+        <v>-32.200000000000003</v>
+      </c>
       <c r="T16" s="8"/>
       <c r="U16" s="8"/>
       <c r="V16" s="8"/>
@@ -2628,48 +2662,48 @@
         <v>-331.7</v>
       </c>
       <c r="AB16" s="8">
-        <f t="shared" ref="AB16:AL16" si="15">AB11-AB15</f>
-        <v>-240.65150000000003</v>
+        <f t="shared" ref="AB16:AL16" si="19">AB11-AB15</f>
+        <v>-241.196</v>
       </c>
       <c r="AC16" s="8">
-        <f t="shared" si="15"/>
-        <v>-249.37895000000003</v>
+        <f t="shared" si="19"/>
+        <v>-251.43716000000001</v>
       </c>
       <c r="AD16" s="8">
-        <f t="shared" si="15"/>
-        <v>-234.94165740000014</v>
+        <f t="shared" si="19"/>
+        <v>-239.27369940000014</v>
       </c>
       <c r="AE16" s="8">
-        <f t="shared" si="15"/>
-        <v>-201.95642231800011</v>
+        <f t="shared" si="19"/>
+        <v>-209.42086391800015</v>
       </c>
       <c r="AF16" s="8">
-        <f t="shared" si="15"/>
-        <v>-133.24014986434008</v>
+        <f t="shared" si="19"/>
+        <v>-146.03633546434008</v>
       </c>
       <c r="AG16" s="8">
-        <f t="shared" si="15"/>
-        <v>-21.792584863214337</v>
+        <f t="shared" si="19"/>
+        <v>-42.666362623214333</v>
       </c>
       <c r="AH16" s="8">
-        <f t="shared" si="15"/>
-        <v>89.680987930499015</v>
+        <f t="shared" si="19"/>
+        <v>60.689629930499017</v>
       </c>
       <c r="AI16" s="8">
-        <f t="shared" si="15"/>
-        <v>205.01020933962747</v>
+        <f t="shared" si="19"/>
+        <v>167.61135751962757</v>
       </c>
       <c r="AJ16" s="8">
-        <f t="shared" si="15"/>
-        <v>322.82322043769335</v>
+        <f t="shared" si="19"/>
+        <v>276.81393529169333</v>
       </c>
       <c r="AK16" s="8">
-        <f t="shared" si="15"/>
-        <v>412.03344537012191</v>
+        <f t="shared" si="19"/>
+        <v>359.22278763732203</v>
       </c>
       <c r="AL16" s="8">
-        <f t="shared" si="15"/>
-        <v>471.97088145323158</v>
+        <f t="shared" si="19"/>
+        <v>414.20922455798171</v>
       </c>
     </row>
     <row r="17" spans="2:156" x14ac:dyDescent="0.3">
@@ -2724,7 +2758,9 @@
       <c r="R17" s="5">
         <v>0</v>
       </c>
-      <c r="S17" s="5"/>
+      <c r="S17" s="5">
+        <v>0</v>
+      </c>
       <c r="T17" s="5"/>
       <c r="U17" s="5"/>
       <c r="V17" s="5"/>
@@ -2783,70 +2819,73 @@
         <v>37</v>
       </c>
       <c r="C18" s="8">
-        <f t="shared" ref="C18:R18" si="16">C16-C17</f>
+        <f t="shared" ref="C18:R18" si="20">C16-C17</f>
         <v>-7.4</v>
       </c>
       <c r="D18" s="8">
-        <f t="shared" si="16"/>
+        <f t="shared" si="20"/>
         <v>-10</v>
       </c>
       <c r="E18" s="8">
-        <f t="shared" si="16"/>
+        <f t="shared" si="20"/>
         <v>-14.899999999999999</v>
       </c>
       <c r="F18" s="8">
-        <f t="shared" si="16"/>
+        <f t="shared" si="20"/>
         <v>-74</v>
       </c>
       <c r="G18" s="8">
-        <f t="shared" si="16"/>
+        <f t="shared" si="20"/>
         <v>-4.3000000000000007</v>
       </c>
       <c r="H18" s="8">
-        <f t="shared" si="16"/>
+        <f t="shared" si="20"/>
         <v>-1.4999999999999964</v>
       </c>
       <c r="I18" s="8">
-        <f t="shared" si="16"/>
+        <f t="shared" si="20"/>
         <v>-23.9</v>
       </c>
       <c r="J18" s="8">
-        <f t="shared" si="16"/>
+        <f t="shared" si="20"/>
         <v>-18.699999999999996</v>
       </c>
       <c r="K18" s="8">
-        <f t="shared" si="16"/>
+        <f t="shared" si="20"/>
         <v>-27.3</v>
       </c>
       <c r="L18" s="8">
-        <f t="shared" si="16"/>
+        <f t="shared" si="20"/>
         <v>-43.699999999999996</v>
       </c>
       <c r="M18" s="8">
-        <f t="shared" si="16"/>
+        <f t="shared" si="20"/>
         <v>-44.6</v>
       </c>
       <c r="N18" s="8">
-        <f t="shared" si="16"/>
+        <f t="shared" si="20"/>
         <v>-41.900000000000006</v>
       </c>
       <c r="O18" s="8">
-        <f t="shared" si="16"/>
+        <f t="shared" si="20"/>
         <v>-39.600000000000009</v>
       </c>
       <c r="P18" s="8">
-        <f t="shared" si="16"/>
+        <f t="shared" si="20"/>
         <v>-37.599999999999994</v>
       </c>
       <c r="Q18" s="8">
-        <f t="shared" si="16"/>
+        <f t="shared" si="20"/>
         <v>-52.500000000000007</v>
       </c>
       <c r="R18" s="8">
-        <f t="shared" si="16"/>
+        <f t="shared" si="20"/>
         <v>-202</v>
       </c>
-      <c r="S18" s="8"/>
+      <c r="S18" s="8">
+        <f t="shared" ref="S18" si="21">S16-S17</f>
+        <v>-32.200000000000003</v>
+      </c>
       <c r="T18" s="8"/>
       <c r="U18" s="8"/>
       <c r="V18" s="8"/>
@@ -2868,519 +2907,519 @@
       </c>
       <c r="AB18" s="8">
         <f>AB16-AB17</f>
-        <v>-240.65150000000003</v>
+        <v>-241.196</v>
       </c>
       <c r="AC18" s="8">
-        <f t="shared" ref="AC18:AL18" si="17">AC16-AC17</f>
-        <v>-249.37895000000003</v>
+        <f t="shared" ref="AC18:AL18" si="22">AC16-AC17</f>
+        <v>-251.43716000000001</v>
       </c>
       <c r="AD18" s="8">
-        <f t="shared" si="17"/>
-        <v>-234.94165740000014</v>
+        <f t="shared" si="22"/>
+        <v>-239.27369940000014</v>
       </c>
       <c r="AE18" s="8">
-        <f t="shared" si="17"/>
-        <v>-201.95642231800011</v>
+        <f t="shared" si="22"/>
+        <v>-209.42086391800015</v>
       </c>
       <c r="AF18" s="8">
-        <f t="shared" si="17"/>
-        <v>-133.24014986434008</v>
+        <f t="shared" si="22"/>
+        <v>-146.03633546434008</v>
       </c>
       <c r="AG18" s="8">
-        <f t="shared" si="17"/>
-        <v>-21.792584863214337</v>
+        <f t="shared" si="22"/>
+        <v>-42.666362623214333</v>
       </c>
       <c r="AH18" s="8">
-        <f t="shared" si="17"/>
-        <v>89.680987930499015</v>
+        <f t="shared" si="22"/>
+        <v>60.689629930499017</v>
       </c>
       <c r="AI18" s="8">
-        <f t="shared" si="17"/>
-        <v>205.01020933962747</v>
+        <f t="shared" si="22"/>
+        <v>167.61135751962757</v>
       </c>
       <c r="AJ18" s="8">
-        <f t="shared" si="17"/>
-        <v>322.82322043769335</v>
+        <f t="shared" si="22"/>
+        <v>276.81393529169333</v>
       </c>
       <c r="AK18" s="8">
-        <f t="shared" si="17"/>
-        <v>412.03344537012191</v>
+        <f t="shared" si="22"/>
+        <v>359.22278763732203</v>
       </c>
       <c r="AL18" s="8">
-        <f t="shared" si="17"/>
-        <v>471.97088145323158</v>
+        <f t="shared" si="22"/>
+        <v>414.20922455798171</v>
       </c>
       <c r="AM18" s="1">
         <f>AL18*(1+$AP$23)</f>
-        <v>467.25117263869924</v>
+        <v>410.0671323124019</v>
       </c>
       <c r="AN18" s="1">
-        <f t="shared" ref="AN18:CY18" si="18">AM18*(1+$AP$23)</f>
-        <v>462.57866091231227</v>
+        <f t="shared" ref="AN18:CY18" si="23">AM18*(1+$AP$23)</f>
+        <v>405.96646098927789</v>
       </c>
       <c r="AO18" s="1">
-        <f t="shared" si="18"/>
-        <v>457.95287430318916</v>
+        <f t="shared" si="23"/>
+        <v>401.90679637938513</v>
       </c>
       <c r="AP18" s="1">
-        <f t="shared" si="18"/>
-        <v>453.37334556015725</v>
+        <f t="shared" si="23"/>
+        <v>397.88772841559125</v>
       </c>
       <c r="AQ18" s="1">
-        <f t="shared" si="18"/>
-        <v>448.83961210455567</v>
+        <f t="shared" si="23"/>
+        <v>393.90885113143531</v>
       </c>
       <c r="AR18" s="1">
-        <f t="shared" si="18"/>
-        <v>444.35121598351009</v>
+        <f t="shared" si="23"/>
+        <v>389.96976262012095</v>
       </c>
       <c r="AS18" s="1">
-        <f t="shared" si="18"/>
-        <v>439.90770382367498</v>
+        <f t="shared" si="23"/>
+        <v>386.07006499391974</v>
       </c>
       <c r="AT18" s="1">
-        <f t="shared" si="18"/>
-        <v>435.50862678543825</v>
+        <f t="shared" si="23"/>
+        <v>382.20936434398055</v>
       </c>
       <c r="AU18" s="1">
-        <f t="shared" si="18"/>
-        <v>431.15354051758385</v>
+        <f t="shared" si="23"/>
+        <v>378.38727070054074</v>
       </c>
       <c r="AV18" s="1">
-        <f t="shared" si="18"/>
-        <v>426.842005112408</v>
+        <f t="shared" si="23"/>
+        <v>374.60339799353534</v>
       </c>
       <c r="AW18" s="1">
-        <f t="shared" si="18"/>
-        <v>422.57358506128389</v>
+        <f t="shared" si="23"/>
+        <v>370.85736401359998</v>
       </c>
       <c r="AX18" s="1">
-        <f t="shared" si="18"/>
-        <v>418.34784921067103</v>
+        <f t="shared" si="23"/>
+        <v>367.14879037346395</v>
       </c>
       <c r="AY18" s="1">
-        <f t="shared" si="18"/>
-        <v>414.16437071856433</v>
+        <f t="shared" si="23"/>
+        <v>363.4773024697293</v>
       </c>
       <c r="AZ18" s="1">
-        <f t="shared" si="18"/>
-        <v>410.02272701137866</v>
+        <f t="shared" si="23"/>
+        <v>359.84252944503197</v>
       </c>
       <c r="BA18" s="1">
-        <f t="shared" si="18"/>
-        <v>405.92249974126486</v>
+        <f t="shared" si="23"/>
+        <v>356.24410415058162</v>
       </c>
       <c r="BB18" s="1">
-        <f t="shared" si="18"/>
-        <v>401.86327474385223</v>
+        <f t="shared" si="23"/>
+        <v>352.68166310907583</v>
       </c>
       <c r="BC18" s="1">
-        <f t="shared" si="18"/>
-        <v>397.84464199641371</v>
+        <f t="shared" si="23"/>
+        <v>349.15484647798507</v>
       </c>
       <c r="BD18" s="1">
-        <f t="shared" si="18"/>
-        <v>393.86619557644957</v>
+        <f t="shared" si="23"/>
+        <v>345.66329801320524</v>
       </c>
       <c r="BE18" s="1">
-        <f t="shared" si="18"/>
-        <v>389.9275336206851</v>
+        <f t="shared" si="23"/>
+        <v>342.20666503307319</v>
       </c>
       <c r="BF18" s="1">
-        <f t="shared" si="18"/>
-        <v>386.02825828447823</v>
+        <f t="shared" si="23"/>
+        <v>338.78459838274244</v>
       </c>
       <c r="BG18" s="1">
-        <f t="shared" si="18"/>
-        <v>382.16797570163345</v>
+        <f t="shared" si="23"/>
+        <v>335.396752398915</v>
       </c>
       <c r="BH18" s="1">
-        <f t="shared" si="18"/>
-        <v>378.34629594461711</v>
+        <f t="shared" si="23"/>
+        <v>332.04278487492587</v>
       </c>
       <c r="BI18" s="1">
-        <f t="shared" si="18"/>
-        <v>374.56283298517093</v>
+        <f t="shared" si="23"/>
+        <v>328.72235702617661</v>
       </c>
       <c r="BJ18" s="1">
-        <f t="shared" si="18"/>
-        <v>370.81720465531919</v>
+        <f t="shared" si="23"/>
+        <v>325.43513345591487</v>
       </c>
       <c r="BK18" s="1">
-        <f t="shared" si="18"/>
-        <v>367.10903260876597</v>
+        <f t="shared" si="23"/>
+        <v>322.18078212135572</v>
       </c>
       <c r="BL18" s="1">
-        <f t="shared" si="18"/>
-        <v>363.43794228267831</v>
+        <f t="shared" si="23"/>
+        <v>318.95897430014213</v>
       </c>
       <c r="BM18" s="1">
-        <f t="shared" si="18"/>
-        <v>359.80356285985152</v>
+        <f t="shared" si="23"/>
+        <v>315.76938455714071</v>
       </c>
       <c r="BN18" s="1">
-        <f t="shared" si="18"/>
-        <v>356.20552723125303</v>
+        <f t="shared" si="23"/>
+        <v>312.61169071156928</v>
       </c>
       <c r="BO18" s="1">
-        <f t="shared" si="18"/>
-        <v>352.64347195894049</v>
+        <f t="shared" si="23"/>
+        <v>309.48557380445357</v>
       </c>
       <c r="BP18" s="1">
-        <f t="shared" si="18"/>
-        <v>349.11703723935108</v>
+        <f t="shared" si="23"/>
+        <v>306.39071806640902</v>
       </c>
       <c r="BQ18" s="1">
-        <f t="shared" si="18"/>
-        <v>345.62586686695755</v>
+        <f t="shared" si="23"/>
+        <v>303.32681088574492</v>
       </c>
       <c r="BR18" s="1">
-        <f t="shared" si="18"/>
-        <v>342.16960819828796</v>
+        <f t="shared" si="23"/>
+        <v>300.29354277688748</v>
       </c>
       <c r="BS18" s="1">
-        <f t="shared" si="18"/>
-        <v>338.74791211630509</v>
+        <f t="shared" si="23"/>
+        <v>297.2906073491186</v>
       </c>
       <c r="BT18" s="1">
-        <f t="shared" si="18"/>
-        <v>335.36043299514205</v>
+        <f t="shared" si="23"/>
+        <v>294.31770127562743</v>
       </c>
       <c r="BU18" s="1">
-        <f t="shared" si="18"/>
-        <v>332.0068286651906</v>
+        <f t="shared" si="23"/>
+        <v>291.37452426287115</v>
       </c>
       <c r="BV18" s="1">
-        <f t="shared" si="18"/>
-        <v>328.68676037853868</v>
+        <f t="shared" si="23"/>
+        <v>288.46077902024246</v>
       </c>
       <c r="BW18" s="1">
-        <f t="shared" si="18"/>
-        <v>325.39989277475331</v>
+        <f t="shared" si="23"/>
+        <v>285.57617123004002</v>
       </c>
       <c r="BX18" s="1">
-        <f t="shared" si="18"/>
-        <v>322.14589384700577</v>
+        <f t="shared" si="23"/>
+        <v>282.7204095177396</v>
       </c>
       <c r="BY18" s="1">
-        <f t="shared" si="18"/>
-        <v>318.92443490853572</v>
+        <f t="shared" si="23"/>
+        <v>279.89320542256218</v>
       </c>
       <c r="BZ18" s="1">
-        <f t="shared" si="18"/>
-        <v>315.73519055945036</v>
+        <f t="shared" si="23"/>
+        <v>277.09427336833653</v>
       </c>
       <c r="CA18" s="1">
-        <f t="shared" si="18"/>
-        <v>312.57783865385585</v>
+        <f t="shared" si="23"/>
+        <v>274.32333063465319</v>
       </c>
       <c r="CB18" s="1">
-        <f t="shared" si="18"/>
-        <v>309.45206026731728</v>
+        <f t="shared" si="23"/>
+        <v>271.58009732830664</v>
       </c>
       <c r="CC18" s="1">
-        <f t="shared" si="18"/>
-        <v>306.35753966464409</v>
+        <f t="shared" si="23"/>
+        <v>268.86429635502355</v>
       </c>
       <c r="CD18" s="1">
-        <f t="shared" si="18"/>
-        <v>303.29396426799764</v>
+        <f t="shared" si="23"/>
+        <v>266.1756533914733</v>
       </c>
       <c r="CE18" s="1">
-        <f t="shared" si="18"/>
-        <v>300.26102462531765</v>
+        <f t="shared" si="23"/>
+        <v>263.51389685755856</v>
       </c>
       <c r="CF18" s="1">
-        <f t="shared" si="18"/>
-        <v>297.25841437906445</v>
+        <f t="shared" si="23"/>
+        <v>260.87875788898299</v>
       </c>
       <c r="CG18" s="1">
-        <f t="shared" si="18"/>
-        <v>294.28583023527381</v>
+        <f t="shared" si="23"/>
+        <v>258.26997031009313</v>
       </c>
       <c r="CH18" s="1">
-        <f t="shared" si="18"/>
-        <v>291.34297193292105</v>
+        <f t="shared" si="23"/>
+        <v>255.6872706069922</v>
       </c>
       <c r="CI18" s="1">
-        <f t="shared" si="18"/>
-        <v>288.42954221359184</v>
+        <f t="shared" si="23"/>
+        <v>253.13039790092228</v>
       </c>
       <c r="CJ18" s="1">
-        <f t="shared" si="18"/>
-        <v>285.5452467914559</v>
+        <f t="shared" si="23"/>
+        <v>250.59909392191304</v>
       </c>
       <c r="CK18" s="1">
-        <f t="shared" si="18"/>
-        <v>282.68979432354132</v>
+        <f t="shared" si="23"/>
+        <v>248.09310298269389</v>
       </c>
       <c r="CL18" s="1">
-        <f t="shared" si="18"/>
-        <v>279.86289638030593</v>
+        <f t="shared" si="23"/>
+        <v>245.61217195286696</v>
       </c>
       <c r="CM18" s="1">
-        <f t="shared" si="18"/>
-        <v>277.06426741650284</v>
+        <f t="shared" si="23"/>
+        <v>243.15605023333828</v>
       </c>
       <c r="CN18" s="1">
-        <f t="shared" si="18"/>
-        <v>274.29362474233784</v>
+        <f t="shared" si="23"/>
+        <v>240.72448973100489</v>
       </c>
       <c r="CO18" s="1">
-        <f t="shared" si="18"/>
-        <v>271.55068849491448</v>
+        <f t="shared" si="23"/>
+        <v>238.31724483369484</v>
       </c>
       <c r="CP18" s="1">
-        <f t="shared" si="18"/>
-        <v>268.83518160996533</v>
+        <f t="shared" si="23"/>
+        <v>235.93407238535789</v>
       </c>
       <c r="CQ18" s="1">
-        <f t="shared" si="18"/>
-        <v>266.14682979386566</v>
+        <f t="shared" si="23"/>
+        <v>233.5747316615043</v>
       </c>
       <c r="CR18" s="1">
-        <f t="shared" si="18"/>
-        <v>263.48536149592701</v>
+        <f t="shared" si="23"/>
+        <v>231.23898434488925</v>
       </c>
       <c r="CS18" s="1">
-        <f t="shared" si="18"/>
-        <v>260.85050788096771</v>
+        <f t="shared" si="23"/>
+        <v>228.92659450144035</v>
       </c>
       <c r="CT18" s="1">
-        <f t="shared" si="18"/>
-        <v>258.24200280215803</v>
+        <f t="shared" si="23"/>
+        <v>226.63732855642596</v>
       </c>
       <c r="CU18" s="1">
-        <f t="shared" si="18"/>
-        <v>255.65958277413645</v>
+        <f t="shared" si="23"/>
+        <v>224.37095527086169</v>
       </c>
       <c r="CV18" s="1">
-        <f t="shared" si="18"/>
-        <v>253.10298694639508</v>
+        <f t="shared" si="23"/>
+        <v>222.12724571815306</v>
       </c>
       <c r="CW18" s="1">
-        <f t="shared" si="18"/>
-        <v>250.57195707693111</v>
+        <f t="shared" si="23"/>
+        <v>219.90597326097154</v>
       </c>
       <c r="CX18" s="1">
-        <f t="shared" si="18"/>
-        <v>248.0662375061618</v>
+        <f t="shared" si="23"/>
+        <v>217.70691352836181</v>
       </c>
       <c r="CY18" s="1">
-        <f t="shared" si="18"/>
-        <v>245.58557513110017</v>
+        <f t="shared" si="23"/>
+        <v>215.52984439307818</v>
       </c>
       <c r="CZ18" s="1">
-        <f t="shared" ref="CZ18:EZ18" si="19">CY18*(1+$AP$23)</f>
-        <v>243.12971937978918</v>
+        <f t="shared" ref="CZ18:EZ18" si="24">CY18*(1+$AP$23)</f>
+        <v>213.3745459491474</v>
       </c>
       <c r="DA18" s="1">
-        <f t="shared" si="19"/>
-        <v>240.69842218599129</v>
+        <f t="shared" si="24"/>
+        <v>211.24080048965592</v>
       </c>
       <c r="DB18" s="1">
-        <f t="shared" si="19"/>
-        <v>238.29143796413138</v>
+        <f t="shared" si="24"/>
+        <v>209.12839248475936</v>
       </c>
       <c r="DC18" s="1">
-        <f t="shared" si="19"/>
-        <v>235.90852358449007</v>
+        <f t="shared" si="24"/>
+        <v>207.03710855991176</v>
       </c>
       <c r="DD18" s="1">
-        <f t="shared" si="19"/>
-        <v>233.54943834864517</v>
+        <f t="shared" si="24"/>
+        <v>204.96673747431265</v>
       </c>
       <c r="DE18" s="1">
-        <f t="shared" si="19"/>
-        <v>231.21394396515871</v>
+        <f t="shared" si="24"/>
+        <v>202.91707009956951</v>
       </c>
       <c r="DF18" s="1">
-        <f t="shared" si="19"/>
-        <v>228.90180452550712</v>
+        <f t="shared" si="24"/>
+        <v>200.88789939857381</v>
       </c>
       <c r="DG18" s="1">
-        <f t="shared" si="19"/>
-        <v>226.61278648025205</v>
+        <f t="shared" si="24"/>
+        <v>198.87902040458806</v>
       </c>
       <c r="DH18" s="1">
-        <f t="shared" si="19"/>
-        <v>224.34665861544954</v>
+        <f t="shared" si="24"/>
+        <v>196.89023020054219</v>
       </c>
       <c r="DI18" s="1">
-        <f t="shared" si="19"/>
-        <v>222.10319202929503</v>
+        <f t="shared" si="24"/>
+        <v>194.92132789853676</v>
       </c>
       <c r="DJ18" s="1">
-        <f t="shared" si="19"/>
-        <v>219.88216010900209</v>
+        <f t="shared" si="24"/>
+        <v>192.97211461955138</v>
       </c>
       <c r="DK18" s="1">
-        <f t="shared" si="19"/>
-        <v>217.68333850791205</v>
+        <f t="shared" si="24"/>
+        <v>191.04239347335587</v>
       </c>
       <c r="DL18" s="1">
-        <f t="shared" si="19"/>
-        <v>215.50650512283292</v>
+        <f t="shared" si="24"/>
+        <v>189.13196953862231</v>
       </c>
       <c r="DM18" s="1">
-        <f t="shared" si="19"/>
-        <v>213.3514400716046</v>
+        <f t="shared" si="24"/>
+        <v>187.2406498432361</v>
       </c>
       <c r="DN18" s="1">
-        <f t="shared" si="19"/>
-        <v>211.21792567088855</v>
+        <f t="shared" si="24"/>
+        <v>185.36824334480374</v>
       </c>
       <c r="DO18" s="1">
-        <f t="shared" si="19"/>
-        <v>209.10574641417966</v>
+        <f t="shared" si="24"/>
+        <v>183.51456091135572</v>
       </c>
       <c r="DP18" s="1">
-        <f t="shared" si="19"/>
-        <v>207.01468895003785</v>
+        <f t="shared" si="24"/>
+        <v>181.67941530224215</v>
       </c>
       <c r="DQ18" s="1">
-        <f t="shared" si="19"/>
-        <v>204.94454206053746</v>
+        <f t="shared" si="24"/>
+        <v>179.86262114921973</v>
       </c>
       <c r="DR18" s="1">
-        <f t="shared" si="19"/>
-        <v>202.89509663993209</v>
+        <f t="shared" si="24"/>
+        <v>178.06399493772753</v>
       </c>
       <c r="DS18" s="1">
-        <f t="shared" si="19"/>
-        <v>200.86614567353277</v>
+        <f t="shared" si="24"/>
+        <v>176.28335498835025</v>
       </c>
       <c r="DT18" s="1">
-        <f t="shared" si="19"/>
-        <v>198.85748421679745</v>
+        <f t="shared" si="24"/>
+        <v>174.52052143846674</v>
       </c>
       <c r="DU18" s="1">
-        <f t="shared" si="19"/>
-        <v>196.86890937462948</v>
+        <f t="shared" si="24"/>
+        <v>172.77531622408208</v>
       </c>
       <c r="DV18" s="1">
-        <f t="shared" si="19"/>
-        <v>194.90022028088319</v>
+        <f t="shared" si="24"/>
+        <v>171.04756306184126</v>
       </c>
       <c r="DW18" s="1">
-        <f t="shared" si="19"/>
-        <v>192.95121807807436</v>
+        <f t="shared" si="24"/>
+        <v>169.33708743122284</v>
       </c>
       <c r="DX18" s="1">
-        <f t="shared" si="19"/>
-        <v>191.02170589729363</v>
+        <f t="shared" si="24"/>
+        <v>167.64371655691062</v>
       </c>
       <c r="DY18" s="1">
-        <f t="shared" si="19"/>
-        <v>189.1114888383207</v>
+        <f t="shared" si="24"/>
+        <v>165.96727939134152</v>
       </c>
       <c r="DZ18" s="1">
-        <f t="shared" si="19"/>
-        <v>187.22037394993748</v>
+        <f t="shared" si="24"/>
+        <v>164.30760659742811</v>
       </c>
       <c r="EA18" s="1">
-        <f t="shared" si="19"/>
-        <v>185.3481702104381</v>
+        <f t="shared" si="24"/>
+        <v>162.66453053145383</v>
       </c>
       <c r="EB18" s="1">
-        <f t="shared" si="19"/>
-        <v>183.49468850833372</v>
+        <f t="shared" si="24"/>
+        <v>161.03788522613928</v>
       </c>
       <c r="EC18" s="1">
-        <f t="shared" si="19"/>
-        <v>181.6597416232504</v>
+        <f t="shared" si="24"/>
+        <v>159.42750637387789</v>
       </c>
       <c r="ED18" s="1">
-        <f t="shared" si="19"/>
-        <v>179.8431442070179</v>
+        <f t="shared" si="24"/>
+        <v>157.8332313101391</v>
       </c>
       <c r="EE18" s="1">
-        <f t="shared" si="19"/>
-        <v>178.04471276494772</v>
+        <f t="shared" si="24"/>
+        <v>156.25489899703771</v>
       </c>
       <c r="EF18" s="1">
-        <f t="shared" si="19"/>
-        <v>176.26426563729825</v>
+        <f t="shared" si="24"/>
+        <v>154.69235000706735</v>
       </c>
       <c r="EG18" s="1">
-        <f t="shared" si="19"/>
-        <v>174.50162298092528</v>
+        <f t="shared" si="24"/>
+        <v>153.14542650699667</v>
       </c>
       <c r="EH18" s="1">
-        <f t="shared" si="19"/>
-        <v>172.75660675111601</v>
+        <f t="shared" si="24"/>
+        <v>151.61397224192669</v>
       </c>
       <c r="EI18" s="1">
-        <f t="shared" si="19"/>
-        <v>171.02904068360485</v>
+        <f t="shared" si="24"/>
+        <v>150.09783251950742</v>
       </c>
       <c r="EJ18" s="1">
-        <f t="shared" si="19"/>
-        <v>169.31875027676881</v>
+        <f t="shared" si="24"/>
+        <v>148.59685419431236</v>
       </c>
       <c r="EK18" s="1">
-        <f t="shared" si="19"/>
-        <v>167.62556277400111</v>
+        <f t="shared" si="24"/>
+        <v>147.11088565236923</v>
       </c>
       <c r="EL18" s="1">
-        <f t="shared" si="19"/>
-        <v>165.94930714626111</v>
+        <f t="shared" si="24"/>
+        <v>145.63977679584553</v>
       </c>
       <c r="EM18" s="1">
-        <f t="shared" si="19"/>
-        <v>164.2898140747985</v>
+        <f t="shared" si="24"/>
+        <v>144.18337902788707</v>
       </c>
       <c r="EN18" s="1">
-        <f t="shared" si="19"/>
-        <v>162.64691593405053</v>
+        <f t="shared" si="24"/>
+        <v>142.74154523760819</v>
       </c>
       <c r="EO18" s="1">
-        <f t="shared" si="19"/>
-        <v>161.02044677471002</v>
+        <f t="shared" si="24"/>
+        <v>141.3141297852321</v>
       </c>
       <c r="EP18" s="1">
-        <f t="shared" si="19"/>
-        <v>159.41024230696291</v>
+        <f t="shared" si="24"/>
+        <v>139.90098848737978</v>
       </c>
       <c r="EQ18" s="1">
-        <f t="shared" si="19"/>
-        <v>157.81613988389327</v>
+        <f t="shared" si="24"/>
+        <v>138.50197860250597</v>
       </c>
       <c r="ER18" s="1">
-        <f t="shared" si="19"/>
-        <v>156.23797848505433</v>
+        <f t="shared" si="24"/>
+        <v>137.11695881648092</v>
       </c>
       <c r="ES18" s="1">
-        <f t="shared" si="19"/>
-        <v>154.67559870020378</v>
+        <f t="shared" si="24"/>
+        <v>135.74578922831611</v>
       </c>
       <c r="ET18" s="1">
-        <f t="shared" si="19"/>
-        <v>153.12884271320175</v>
+        <f t="shared" si="24"/>
+        <v>134.38833133603296</v>
       </c>
       <c r="EU18" s="1">
-        <f t="shared" si="19"/>
-        <v>151.59755428606974</v>
+        <f t="shared" si="24"/>
+        <v>133.04444802267264</v>
       </c>
       <c r="EV18" s="1">
-        <f t="shared" si="19"/>
-        <v>150.08157874320904</v>
+        <f t="shared" si="24"/>
+        <v>131.71400354244591</v>
       </c>
       <c r="EW18" s="1">
-        <f t="shared" si="19"/>
-        <v>148.58076295577695</v>
+        <f t="shared" si="24"/>
+        <v>130.39686350702144</v>
       </c>
       <c r="EX18" s="1">
-        <f t="shared" si="19"/>
-        <v>147.09495532621918</v>
+        <f t="shared" si="24"/>
+        <v>129.09289487195122</v>
       </c>
       <c r="EY18" s="1">
-        <f t="shared" si="19"/>
-        <v>145.62400577295699</v>
+        <f t="shared" si="24"/>
+        <v>127.80196592323171</v>
       </c>
       <c r="EZ18" s="1">
-        <f t="shared" si="19"/>
-        <v>144.16776571522743</v>
+        <f t="shared" si="24"/>
+        <v>126.52394626399939</v>
       </c>
     </row>
     <row r="19" spans="2:156" x14ac:dyDescent="0.3">
@@ -3388,70 +3427,73 @@
         <v>2</v>
       </c>
       <c r="C19" s="5">
-        <f t="shared" ref="C19:R19" si="20">216.4</f>
+        <f t="shared" ref="C19:S19" si="25">216.4</f>
         <v>216.4</v>
       </c>
       <c r="D19" s="5">
-        <f t="shared" si="20"/>
+        <f t="shared" si="25"/>
         <v>216.4</v>
       </c>
       <c r="E19" s="5">
-        <f t="shared" si="20"/>
+        <f t="shared" si="25"/>
         <v>216.4</v>
       </c>
       <c r="F19" s="5">
-        <f t="shared" si="20"/>
+        <f t="shared" si="25"/>
         <v>216.4</v>
       </c>
       <c r="G19" s="5">
-        <f t="shared" si="20"/>
+        <f t="shared" si="25"/>
         <v>216.4</v>
       </c>
       <c r="H19" s="5">
-        <f t="shared" si="20"/>
+        <f t="shared" si="25"/>
         <v>216.4</v>
       </c>
       <c r="I19" s="5">
-        <f t="shared" si="20"/>
+        <f t="shared" si="25"/>
         <v>216.4</v>
       </c>
       <c r="J19" s="5">
-        <f t="shared" si="20"/>
+        <f t="shared" si="25"/>
         <v>216.4</v>
       </c>
       <c r="K19" s="5">
-        <f t="shared" si="20"/>
+        <f t="shared" si="25"/>
         <v>216.4</v>
       </c>
       <c r="L19" s="5">
-        <f t="shared" si="20"/>
+        <f t="shared" si="25"/>
         <v>216.4</v>
       </c>
       <c r="M19" s="5">
-        <f t="shared" si="20"/>
+        <f t="shared" si="25"/>
         <v>216.4</v>
       </c>
       <c r="N19" s="5">
-        <f t="shared" si="20"/>
+        <f t="shared" si="25"/>
         <v>216.4</v>
       </c>
       <c r="O19" s="5">
-        <f t="shared" si="20"/>
+        <f t="shared" si="25"/>
         <v>216.4</v>
       </c>
       <c r="P19" s="5">
-        <f t="shared" si="20"/>
+        <f t="shared" si="25"/>
         <v>216.4</v>
       </c>
       <c r="Q19" s="5">
-        <f t="shared" si="20"/>
+        <f t="shared" si="25"/>
         <v>216.4</v>
       </c>
       <c r="R19" s="5">
-        <f t="shared" si="20"/>
+        <f t="shared" si="25"/>
         <v>216.4</v>
       </c>
-      <c r="S19" s="5"/>
+      <c r="S19" s="5">
+        <f t="shared" si="25"/>
+        <v>216.4</v>
+      </c>
       <c r="T19" s="5"/>
       <c r="U19" s="5"/>
       <c r="V19" s="5"/>
@@ -3476,43 +3518,43 @@
         <v>216.4</v>
       </c>
       <c r="AC19" s="5">
-        <f t="shared" ref="AC19:AL19" si="21">216.4</f>
+        <f t="shared" ref="AC19:AL19" si="26">216.4</f>
         <v>216.4</v>
       </c>
       <c r="AD19" s="5">
-        <f t="shared" si="21"/>
+        <f t="shared" si="26"/>
         <v>216.4</v>
       </c>
       <c r="AE19" s="5">
-        <f t="shared" si="21"/>
+        <f t="shared" si="26"/>
         <v>216.4</v>
       </c>
       <c r="AF19" s="5">
-        <f t="shared" si="21"/>
+        <f t="shared" si="26"/>
         <v>216.4</v>
       </c>
       <c r="AG19" s="5">
-        <f t="shared" si="21"/>
+        <f t="shared" si="26"/>
         <v>216.4</v>
       </c>
       <c r="AH19" s="5">
-        <f t="shared" si="21"/>
+        <f t="shared" si="26"/>
         <v>216.4</v>
       </c>
       <c r="AI19" s="5">
-        <f t="shared" si="21"/>
+        <f t="shared" si="26"/>
         <v>216.4</v>
       </c>
       <c r="AJ19" s="5">
-        <f t="shared" si="21"/>
+        <f t="shared" si="26"/>
         <v>216.4</v>
       </c>
       <c r="AK19" s="5">
-        <f t="shared" si="21"/>
+        <f t="shared" si="26"/>
         <v>216.4</v>
       </c>
       <c r="AL19" s="5">
-        <f t="shared" si="21"/>
+        <f t="shared" si="26"/>
         <v>216.4</v>
       </c>
     </row>
@@ -3521,70 +3563,73 @@
         <v>38</v>
       </c>
       <c r="C20" s="7">
-        <f t="shared" ref="C20:R20" si="22">C18/C19</f>
+        <f t="shared" ref="C20:R20" si="27">C18/C19</f>
         <v>-3.4195933456561925E-2</v>
       </c>
       <c r="D20" s="7">
-        <f t="shared" si="22"/>
+        <f t="shared" si="27"/>
         <v>-4.6210720887245843E-2</v>
       </c>
       <c r="E20" s="7">
-        <f t="shared" si="22"/>
+        <f t="shared" si="27"/>
         <v>-6.88539741219963E-2</v>
       </c>
       <c r="F20" s="7">
-        <f t="shared" si="22"/>
+        <f t="shared" si="27"/>
         <v>-0.34195933456561922</v>
       </c>
       <c r="G20" s="7">
-        <f t="shared" si="22"/>
+        <f t="shared" si="27"/>
         <v>-1.9870609981515713E-2</v>
       </c>
       <c r="H20" s="7">
-        <f t="shared" si="22"/>
+        <f t="shared" si="27"/>
         <v>-6.9316081330868598E-3</v>
       </c>
       <c r="I20" s="7">
-        <f t="shared" si="22"/>
+        <f t="shared" si="27"/>
         <v>-0.11044362292051756</v>
       </c>
       <c r="J20" s="7">
-        <f t="shared" si="22"/>
+        <f t="shared" si="27"/>
         <v>-8.6414048059149706E-2</v>
       </c>
       <c r="K20" s="7">
-        <f t="shared" si="22"/>
+        <f t="shared" si="27"/>
         <v>-0.12615526802218113</v>
       </c>
       <c r="L20" s="7">
-        <f t="shared" si="22"/>
+        <f t="shared" si="27"/>
         <v>-0.2019408502772643</v>
       </c>
       <c r="M20" s="7">
-        <f t="shared" si="22"/>
+        <f t="shared" si="27"/>
         <v>-0.20609981515711645</v>
       </c>
       <c r="N20" s="7">
-        <f t="shared" si="22"/>
+        <f t="shared" si="27"/>
         <v>-0.19362292051756008</v>
       </c>
       <c r="O20" s="7">
-        <f t="shared" si="22"/>
+        <f t="shared" si="27"/>
         <v>-0.18299445471349357</v>
       </c>
       <c r="P20" s="7">
-        <f t="shared" si="22"/>
+        <f t="shared" si="27"/>
         <v>-0.17375231053604434</v>
       </c>
       <c r="Q20" s="7">
-        <f t="shared" si="22"/>
+        <f t="shared" si="27"/>
         <v>-0.24260628465804068</v>
       </c>
       <c r="R20" s="7">
-        <f t="shared" si="22"/>
+        <f t="shared" si="27"/>
         <v>-0.93345656192236592</v>
       </c>
-      <c r="S20" s="7"/>
+      <c r="S20" s="7">
+        <f t="shared" ref="S20" si="28">S18/S19</f>
+        <v>-0.1487985212569316</v>
+      </c>
       <c r="T20" s="7"/>
       <c r="U20" s="7"/>
       <c r="V20" s="7"/>
@@ -3606,47 +3651,47 @@
       </c>
       <c r="AB20" s="7">
         <f>AB18/AB19</f>
-        <v>-1.1120679297597043</v>
+        <v>-1.1145841035120148</v>
       </c>
       <c r="AC20" s="7">
-        <f t="shared" ref="AC20:AL20" si="23">AC18/AC19</f>
-        <v>-1.1523981053604437</v>
+        <f t="shared" ref="AC20:AL20" si="29">AC18/AC19</f>
+        <v>-1.1619092421441775</v>
       </c>
       <c r="AD20" s="7">
-        <f t="shared" si="23"/>
-        <v>-1.0856823354898342</v>
+        <f t="shared" si="29"/>
+        <v>-1.1057010138632168</v>
       </c>
       <c r="AE20" s="7">
-        <f t="shared" si="23"/>
-        <v>-0.93325518631238491</v>
+        <f t="shared" si="29"/>
+        <v>-0.96774890904805977</v>
       </c>
       <c r="AF20" s="7">
-        <f t="shared" si="23"/>
-        <v>-0.61571233763558264</v>
+        <f t="shared" si="29"/>
+        <v>-0.67484443375388203</v>
       </c>
       <c r="AG20" s="7">
-        <f t="shared" si="23"/>
-        <v>-0.10070510565256163</v>
+        <f t="shared" si="29"/>
+        <v>-0.19716433744553757</v>
       </c>
       <c r="AH20" s="7">
-        <f t="shared" si="23"/>
-        <v>0.4144223102148753</v>
+        <f t="shared" si="29"/>
+        <v>0.28045115494685313</v>
       </c>
       <c r="AI20" s="7">
-        <f t="shared" si="23"/>
-        <v>0.94736695628293655</v>
+        <f t="shared" si="29"/>
+        <v>0.77454416598718845</v>
       </c>
       <c r="AJ20" s="7">
-        <f t="shared" si="23"/>
-        <v>1.4917893735568084</v>
+        <f t="shared" si="29"/>
+        <v>1.2791771501464571</v>
       </c>
       <c r="AK20" s="7">
-        <f t="shared" si="23"/>
-        <v>1.9040362540208959</v>
+        <f t="shared" si="29"/>
+        <v>1.6599943975846674</v>
       </c>
       <c r="AL20" s="7">
-        <f t="shared" si="23"/>
-        <v>2.181011466974268</v>
+        <f t="shared" si="29"/>
+        <v>1.9140906864971428</v>
       </c>
     </row>
     <row r="22" spans="2:156" s="1" customFormat="1" x14ac:dyDescent="0.3">
@@ -3658,43 +3703,43 @@
       <c r="E22" s="9"/>
       <c r="F22" s="9"/>
       <c r="G22" s="9">
-        <f t="shared" ref="G22:P22" si="24">G3/C3-1</f>
+        <f t="shared" ref="G22:P22" si="30">G3/C3-1</f>
         <v>19</v>
       </c>
       <c r="H22" s="9">
-        <f t="shared" si="24"/>
+        <f t="shared" si="30"/>
         <v>25</v>
       </c>
       <c r="I22" s="9">
-        <f t="shared" si="24"/>
+        <f t="shared" si="30"/>
         <v>12.999999999999998</v>
       </c>
       <c r="J22" s="9">
-        <f t="shared" si="24"/>
+        <f t="shared" si="30"/>
         <v>1.3749999999999996</v>
       </c>
       <c r="K22" s="9">
-        <f t="shared" si="24"/>
+        <f t="shared" si="30"/>
         <v>1.1499999999999999</v>
       </c>
       <c r="L22" s="9">
-        <f t="shared" si="24"/>
+        <f t="shared" si="30"/>
         <v>1.1153846153846154</v>
       </c>
       <c r="M22" s="9">
-        <f t="shared" si="24"/>
+        <f t="shared" si="30"/>
         <v>1.1785714285714284</v>
       </c>
       <c r="N22" s="9">
-        <f t="shared" si="24"/>
+        <f t="shared" si="30"/>
         <v>0.60526315789473673</v>
       </c>
       <c r="O22" s="9">
-        <f t="shared" si="24"/>
+        <f t="shared" si="30"/>
         <v>0.76744186046511631</v>
       </c>
       <c r="P22" s="9">
-        <f t="shared" si="24"/>
+        <f t="shared" si="30"/>
         <v>1.0727272727272728</v>
       </c>
       <c r="Q22" s="9">
@@ -3706,20 +3751,20 @@
         <v>0.91803278688524581</v>
       </c>
       <c r="S22" s="9">
-        <f t="shared" ref="S22:V22" si="25">S3/O3-1</f>
-        <v>-1.3157894736842035E-2</v>
+        <f t="shared" ref="S22:V22" si="31">S3/O3-1</f>
+        <v>0</v>
       </c>
       <c r="T22" s="9">
-        <f t="shared" si="25"/>
-        <v>0.92982456140350878</v>
+        <f t="shared" si="31"/>
+        <v>0.49122807017543857</v>
       </c>
       <c r="U22" s="9">
-        <f t="shared" si="25"/>
+        <f t="shared" si="31"/>
         <v>0.93548387096774177</v>
       </c>
       <c r="V22" s="9">
-        <f t="shared" si="25"/>
-        <v>1.2222222222222223</v>
+        <f t="shared" si="31"/>
+        <v>1.5641025641025643</v>
       </c>
       <c r="X22" s="9"/>
       <c r="Y22" s="9">
@@ -3727,55 +3772,55 @@
         <v>4.5999999999999996</v>
       </c>
       <c r="Z22" s="9">
-        <f t="shared" ref="Z22:AL22" si="26">Z3/Y3-1</f>
+        <f t="shared" ref="Z22:AL22" si="32">Z3/Y3-1</f>
         <v>0.96428571428571441</v>
       </c>
       <c r="AA22" s="9">
-        <f t="shared" si="26"/>
+        <f t="shared" si="32"/>
         <v>0.95909090909090877</v>
       </c>
       <c r="AB22" s="9">
-        <f t="shared" si="26"/>
-        <v>0.95</v>
+        <f t="shared" si="32"/>
+        <v>0.82366589327146178</v>
       </c>
       <c r="AC22" s="9">
-        <f t="shared" si="26"/>
+        <f t="shared" si="32"/>
         <v>0.8</v>
       </c>
       <c r="AD22" s="9">
-        <f t="shared" si="26"/>
+        <f t="shared" si="32"/>
         <v>0.7</v>
       </c>
       <c r="AE22" s="9">
-        <f t="shared" si="26"/>
+        <f t="shared" si="32"/>
         <v>0.60000000000000009</v>
       </c>
       <c r="AF22" s="9">
-        <f t="shared" si="26"/>
+        <f t="shared" si="32"/>
         <v>0.5</v>
       </c>
       <c r="AG22" s="9">
-        <f t="shared" si="26"/>
+        <f t="shared" si="32"/>
         <v>0.44999999999999996</v>
       </c>
       <c r="AH22" s="9">
-        <f t="shared" si="26"/>
+        <f t="shared" si="32"/>
         <v>0.25</v>
       </c>
       <c r="AI22" s="9">
-        <f t="shared" si="26"/>
+        <f t="shared" si="32"/>
         <v>0.19999999999999996</v>
       </c>
       <c r="AJ22" s="9">
-        <f t="shared" si="26"/>
+        <f t="shared" si="32"/>
         <v>0.14999999999999991</v>
       </c>
       <c r="AK22" s="9">
-        <f t="shared" si="26"/>
+        <f t="shared" si="32"/>
         <v>0.10000000000000009</v>
       </c>
       <c r="AL22" s="9">
-        <f t="shared" si="26"/>
+        <f t="shared" si="32"/>
         <v>5.0000000000000044E-2</v>
       </c>
     </row>
@@ -3784,59 +3829,59 @@
         <v>45</v>
       </c>
       <c r="C23" s="10">
-        <f t="shared" ref="C23:P23" si="27">C5/C3</f>
+        <f t="shared" ref="C23:P23" si="33">C5/C3</f>
         <v>-1</v>
       </c>
       <c r="D23" s="10">
-        <f t="shared" si="27"/>
+        <f t="shared" si="33"/>
         <v>-1.9999999999999998</v>
       </c>
       <c r="E23" s="10">
-        <f t="shared" si="27"/>
+        <f t="shared" si="33"/>
         <v>0</v>
       </c>
       <c r="F23" s="10">
-        <f t="shared" si="27"/>
+        <f t="shared" si="33"/>
         <v>0.8125</v>
       </c>
       <c r="G23" s="10">
-        <f t="shared" si="27"/>
+        <f t="shared" si="33"/>
         <v>0.7</v>
       </c>
       <c r="H23" s="10">
-        <f t="shared" si="27"/>
+        <f t="shared" si="33"/>
         <v>0.73076923076923084</v>
       </c>
       <c r="I23" s="10">
-        <f t="shared" si="27"/>
+        <f t="shared" si="33"/>
         <v>0.74999999999999989</v>
       </c>
       <c r="J23" s="10">
-        <f t="shared" si="27"/>
+        <f t="shared" si="33"/>
         <v>0.76315789473684215</v>
       </c>
       <c r="K23" s="10">
-        <f t="shared" si="27"/>
+        <f t="shared" si="33"/>
         <v>0.76744186046511631</v>
       </c>
       <c r="L23" s="10">
-        <f t="shared" si="27"/>
+        <f t="shared" si="33"/>
         <v>0.65454545454545454</v>
       </c>
       <c r="M23" s="10">
-        <f t="shared" si="27"/>
+        <f t="shared" si="33"/>
         <v>0.67213114754098358</v>
       </c>
       <c r="N23" s="10">
-        <f t="shared" si="27"/>
+        <f t="shared" si="33"/>
         <v>0.47540983606557369</v>
       </c>
       <c r="O23" s="10">
-        <f t="shared" si="27"/>
+        <f t="shared" si="33"/>
         <v>0.55263157894736836</v>
       </c>
       <c r="P23" s="10">
-        <f t="shared" si="27"/>
+        <f t="shared" si="33"/>
         <v>0.50877192982456143</v>
       </c>
       <c r="Q23" s="10">
@@ -3848,23 +3893,23 @@
         <v>0.57264957264957261</v>
       </c>
       <c r="S23" s="10">
-        <f t="shared" ref="S23:V23" si="28">S5/S3</f>
+        <f t="shared" ref="S23:V23" si="34">S5/S3</f>
+        <v>0.43421052631578949</v>
+      </c>
+      <c r="T23" s="10">
+        <f t="shared" si="34"/>
         <v>0.52</v>
       </c>
-      <c r="T23" s="10">
-        <f t="shared" si="28"/>
+      <c r="U23" s="10">
+        <f t="shared" si="34"/>
         <v>0.52</v>
       </c>
-      <c r="U23" s="10">
-        <f t="shared" si="28"/>
+      <c r="V23" s="10">
+        <f t="shared" si="34"/>
         <v>0.52</v>
       </c>
-      <c r="V23" s="10">
-        <f t="shared" si="28"/>
-        <v>0.52</v>
-      </c>
       <c r="X23" s="10">
-        <f t="shared" ref="X23" si="29">X5/X3</f>
+        <f t="shared" ref="X23" si="35">X5/X3</f>
         <v>0.5</v>
       </c>
       <c r="Y23" s="10">
@@ -3872,55 +3917,55 @@
         <v>0.74107142857142849</v>
       </c>
       <c r="Z23" s="10">
-        <f t="shared" ref="Z23:AL23" si="30">Z5/Z3</f>
+        <f t="shared" ref="Z23:AL23" si="36">Z5/Z3</f>
         <v>0.63181818181818172</v>
       </c>
       <c r="AA23" s="10">
-        <f t="shared" si="30"/>
+        <f t="shared" si="36"/>
         <v>0.52436194895591637</v>
       </c>
       <c r="AB23" s="10">
-        <f t="shared" si="30"/>
+        <f t="shared" si="36"/>
         <v>0.5</v>
       </c>
       <c r="AC23" s="10">
-        <f t="shared" si="30"/>
+        <f t="shared" si="36"/>
         <v>0.51</v>
       </c>
       <c r="AD23" s="10">
-        <f t="shared" si="30"/>
+        <f t="shared" si="36"/>
         <v>0.52</v>
       </c>
       <c r="AE23" s="10">
-        <f t="shared" si="30"/>
+        <f t="shared" si="36"/>
         <v>0.52</v>
       </c>
       <c r="AF23" s="10">
-        <f t="shared" si="30"/>
+        <f t="shared" si="36"/>
         <v>0.54</v>
       </c>
       <c r="AG23" s="10">
-        <f t="shared" si="30"/>
+        <f t="shared" si="36"/>
         <v>0.56000000000000005</v>
       </c>
       <c r="AH23" s="10">
-        <f t="shared" si="30"/>
+        <f t="shared" si="36"/>
         <v>0.57999999999999996</v>
       </c>
       <c r="AI23" s="10">
-        <f t="shared" si="30"/>
+        <f t="shared" si="36"/>
         <v>0.6</v>
       </c>
       <c r="AJ23" s="10">
-        <f t="shared" si="30"/>
+        <f t="shared" si="36"/>
         <v>0.62</v>
       </c>
       <c r="AK23" s="10">
-        <f t="shared" si="30"/>
+        <f t="shared" si="36"/>
         <v>0.63</v>
       </c>
       <c r="AL23" s="10">
-        <f t="shared" si="30"/>
+        <f t="shared" si="36"/>
         <v>0.64</v>
       </c>
       <c r="AO23" t="s">
@@ -3939,43 +3984,43 @@
       <c r="E24" s="10"/>
       <c r="F24" s="10"/>
       <c r="G24" s="10">
-        <f t="shared" ref="G24:P24" si="31">G6/C6-1</f>
+        <f t="shared" ref="G24:P24" si="37">G6/C6-1</f>
         <v>0.9729729729729728</v>
       </c>
       <c r="H24" s="10">
-        <f t="shared" si="31"/>
+        <f t="shared" si="37"/>
         <v>0.76363636363636345</v>
       </c>
       <c r="I24" s="10">
-        <f t="shared" si="31"/>
+        <f t="shared" si="37"/>
         <v>1.1451612903225805</v>
       </c>
       <c r="J24" s="10">
-        <f t="shared" si="31"/>
+        <f t="shared" si="37"/>
         <v>1.7959183673469385</v>
       </c>
       <c r="K24" s="10">
-        <f t="shared" si="31"/>
+        <f t="shared" si="37"/>
         <v>1.2191780821917808</v>
       </c>
       <c r="L24" s="10">
-        <f t="shared" si="31"/>
+        <f t="shared" si="37"/>
         <v>1.0515463917525771</v>
       </c>
       <c r="M24" s="10">
-        <f t="shared" si="31"/>
+        <f t="shared" si="37"/>
         <v>0.84962406015037595</v>
       </c>
       <c r="N24" s="10">
-        <f t="shared" si="31"/>
+        <f t="shared" si="37"/>
         <v>1.3065693430656937</v>
       </c>
       <c r="O24" s="10">
-        <f t="shared" si="31"/>
+        <f t="shared" si="37"/>
         <v>1</v>
       </c>
       <c r="P24" s="10">
-        <f t="shared" si="31"/>
+        <f t="shared" si="37"/>
         <v>0.56783919597989962</v>
       </c>
       <c r="Q24" s="10">
@@ -3987,19 +4032,19 @@
         <v>0.26898734177215178</v>
       </c>
       <c r="S24" s="10">
-        <f t="shared" ref="S24:V24" si="32">S6/O6-1</f>
+        <f t="shared" ref="S24:V24" si="38">S6/O6-1</f>
+        <v>0.23456790123456805</v>
+      </c>
+      <c r="T24" s="10">
+        <f t="shared" si="38"/>
         <v>-1</v>
       </c>
-      <c r="T24" s="10">
-        <f t="shared" si="32"/>
+      <c r="U24" s="10">
+        <f t="shared" si="38"/>
         <v>-1</v>
       </c>
-      <c r="U24" s="10">
-        <f t="shared" si="32"/>
-        <v>-1</v>
-      </c>
       <c r="V24" s="10">
-        <f t="shared" si="32"/>
+        <f t="shared" si="38"/>
         <v>-1</v>
       </c>
       <c r="X24" s="10"/>
@@ -4008,55 +4053,55 @@
         <v>1.1674876847290645</v>
       </c>
       <c r="Z24" s="10">
-        <f t="shared" ref="Z24:AL24" si="33">Z6/Y6-1</f>
+        <f t="shared" ref="Z24:AL24" si="39">Z6/Y6-1</f>
         <v>1.0977272727272727</v>
       </c>
       <c r="AA24" s="10">
-        <f t="shared" si="33"/>
+        <f t="shared" si="39"/>
         <v>0.48320693391115932</v>
       </c>
       <c r="AB24" s="10">
-        <f t="shared" si="33"/>
+        <f t="shared" si="39"/>
         <v>0.17999999999999994</v>
       </c>
       <c r="AC24" s="10">
-        <f t="shared" si="33"/>
+        <f t="shared" si="39"/>
         <v>0.12000000000000011</v>
       </c>
       <c r="AD24" s="10">
-        <f t="shared" si="33"/>
+        <f t="shared" si="39"/>
         <v>7.0000000000000062E-2</v>
       </c>
       <c r="AE24" s="10">
-        <f t="shared" si="33"/>
+        <f t="shared" si="39"/>
         <v>5.0000000000000044E-2</v>
       </c>
       <c r="AF24" s="10">
-        <f t="shared" si="33"/>
+        <f t="shared" si="39"/>
         <v>5.0000000000000044E-2</v>
       </c>
       <c r="AG24" s="10">
-        <f t="shared" si="33"/>
+        <f t="shared" si="39"/>
         <v>5.0000000000000044E-2</v>
       </c>
       <c r="AH24" s="10">
-        <f t="shared" si="33"/>
+        <f t="shared" si="39"/>
         <v>5.0000000000000044E-2</v>
       </c>
       <c r="AI24" s="10">
-        <f t="shared" si="33"/>
+        <f t="shared" si="39"/>
         <v>5.0000000000000044E-2</v>
       </c>
       <c r="AJ24" s="10">
-        <f t="shared" si="33"/>
+        <f t="shared" si="39"/>
         <v>5.0000000000000044E-2</v>
       </c>
       <c r="AK24" s="10">
-        <f t="shared" si="33"/>
+        <f t="shared" si="39"/>
         <v>5.0000000000000044E-2</v>
       </c>
       <c r="AL24" s="10">
-        <f t="shared" si="33"/>
+        <f t="shared" si="39"/>
         <v>5.0000000000000044E-2</v>
       </c>
       <c r="AO24" t="s">
@@ -4071,59 +4116,59 @@
         <v>47</v>
       </c>
       <c r="C25" s="10">
-        <f t="shared" ref="C25:P25" si="34">C7/C3</f>
+        <f t="shared" ref="C25:P25" si="40">C7/C3</f>
         <v>2</v>
       </c>
       <c r="D25" s="10">
-        <f t="shared" si="34"/>
+        <f t="shared" si="40"/>
         <v>9</v>
       </c>
       <c r="E25" s="10">
-        <f t="shared" si="34"/>
+        <f t="shared" si="40"/>
         <v>6.5</v>
       </c>
       <c r="F25" s="10">
-        <f t="shared" si="34"/>
+        <f t="shared" si="40"/>
         <v>0.5</v>
       </c>
       <c r="G25" s="10">
-        <f t="shared" si="34"/>
+        <f t="shared" si="40"/>
         <v>0.95</v>
       </c>
       <c r="H25" s="10">
-        <f t="shared" si="34"/>
+        <f t="shared" si="40"/>
         <v>0.80769230769230771</v>
       </c>
       <c r="I25" s="10">
-        <f t="shared" si="34"/>
+        <f t="shared" si="40"/>
         <v>0.7142857142857143</v>
       </c>
       <c r="J25" s="10">
-        <f t="shared" si="34"/>
+        <f t="shared" si="40"/>
         <v>0.63157894736842102</v>
       </c>
       <c r="K25" s="10">
-        <f t="shared" si="34"/>
+        <f t="shared" si="40"/>
         <v>0.62790697674418616</v>
       </c>
       <c r="L25" s="10">
-        <f t="shared" si="34"/>
+        <f t="shared" si="40"/>
         <v>0.65454545454545454</v>
       </c>
       <c r="M25" s="10">
-        <f t="shared" si="34"/>
+        <f t="shared" si="40"/>
         <v>0.81967213114754101</v>
       </c>
       <c r="N25" s="10">
-        <f t="shared" si="34"/>
+        <f t="shared" si="40"/>
         <v>1.1475409836065575</v>
       </c>
       <c r="O25" s="10">
-        <f t="shared" si="34"/>
+        <f t="shared" si="40"/>
         <v>0.88157894736842113</v>
       </c>
       <c r="P25" s="10">
-        <f t="shared" si="34"/>
+        <f t="shared" si="40"/>
         <v>0.53508771929824561</v>
       </c>
       <c r="Q25" s="10">
@@ -4135,23 +4180,23 @@
         <v>0.76068376068376076</v>
       </c>
       <c r="S25" s="10">
-        <f t="shared" ref="S25:V25" si="35">S7/S3</f>
-        <v>0</v>
+        <f t="shared" ref="S25:V25" si="41">S7/S3</f>
+        <v>1.131578947368421</v>
       </c>
       <c r="T25" s="10">
-        <f t="shared" si="35"/>
+        <f t="shared" si="41"/>
         <v>0</v>
       </c>
       <c r="U25" s="10">
-        <f t="shared" si="35"/>
+        <f t="shared" si="41"/>
         <v>0</v>
       </c>
       <c r="V25" s="10">
-        <f t="shared" si="35"/>
+        <f t="shared" si="41"/>
         <v>0</v>
       </c>
       <c r="X25" s="10">
-        <f t="shared" ref="X25" si="36">X7/X3</f>
+        <f t="shared" ref="X25" si="42">X7/X3</f>
         <v>1.6</v>
       </c>
       <c r="Y25" s="10">
@@ -4159,55 +4204,55 @@
         <v>0.75000000000000011</v>
       </c>
       <c r="Z25" s="10">
-        <f t="shared" ref="Z25:AL25" si="37">Z7/Z3</f>
+        <f t="shared" ref="Z25:AL25" si="43">Z7/Z3</f>
         <v>0.8318181818181819</v>
       </c>
       <c r="AA25" s="10">
-        <f t="shared" si="37"/>
+        <f t="shared" si="43"/>
         <v>0.65661252900232026</v>
       </c>
       <c r="AB25" s="10">
-        <f t="shared" si="37"/>
+        <f t="shared" si="43"/>
         <v>0.4</v>
       </c>
       <c r="AC25" s="10">
-        <f t="shared" si="37"/>
+        <f t="shared" si="43"/>
         <v>0.3</v>
       </c>
       <c r="AD25" s="10">
-        <f t="shared" si="37"/>
+        <f t="shared" si="43"/>
         <v>0.26</v>
       </c>
       <c r="AE25" s="10">
-        <f t="shared" si="37"/>
-        <v>0.23999999999999996</v>
+        <f t="shared" si="43"/>
+        <v>0.24</v>
       </c>
       <c r="AF25" s="10">
-        <f t="shared" si="37"/>
-        <v>0.21999999999999997</v>
+        <f t="shared" si="43"/>
+        <v>0.22</v>
       </c>
       <c r="AG25" s="10">
-        <f t="shared" si="37"/>
-        <v>0.2</v>
+        <f t="shared" si="43"/>
+        <v>0.20000000000000004</v>
       </c>
       <c r="AH25" s="10">
-        <f t="shared" si="37"/>
+        <f t="shared" si="43"/>
         <v>0.18</v>
       </c>
       <c r="AI25" s="10">
-        <f t="shared" si="37"/>
+        <f t="shared" si="43"/>
         <v>0.17</v>
       </c>
       <c r="AJ25" s="10">
-        <f t="shared" si="37"/>
+        <f t="shared" si="43"/>
         <v>0.16</v>
       </c>
       <c r="AK25" s="10">
-        <f t="shared" si="37"/>
+        <f t="shared" si="43"/>
         <v>0.15</v>
       </c>
       <c r="AL25" s="10">
-        <f t="shared" si="37"/>
+        <f t="shared" si="43"/>
         <v>0.14000000000000001</v>
       </c>
       <c r="AO25" t="s">
@@ -4215,7 +4260,7 @@
       </c>
       <c r="AP25" s="5">
         <f>NPV(AP24,AA18:EZ18)</f>
-        <v>1175.969291418229</v>
+        <v>851.43980610094263</v>
       </c>
     </row>
     <row r="26" spans="2:156" x14ac:dyDescent="0.3">
@@ -4227,43 +4272,43 @@
       <c r="E26" s="10"/>
       <c r="F26" s="10"/>
       <c r="G26" s="10">
-        <f t="shared" ref="G26:P26" si="38">G8/C8-1</f>
+        <f t="shared" ref="G26:P26" si="44">G8/C8-1</f>
         <v>2.0666666666666664</v>
       </c>
       <c r="H26" s="10">
-        <f t="shared" si="38"/>
+        <f t="shared" si="44"/>
         <v>1.6206896551724137</v>
       </c>
       <c r="I26" s="10">
-        <f t="shared" si="38"/>
+        <f t="shared" si="44"/>
         <v>3.04</v>
       </c>
       <c r="J26" s="10">
-        <f t="shared" si="38"/>
+        <f t="shared" si="44"/>
         <v>0.68518518518518512</v>
       </c>
       <c r="K26" s="10">
-        <f t="shared" si="38"/>
+        <f t="shared" si="44"/>
         <v>0.15217391304347827</v>
       </c>
       <c r="L26" s="10">
-        <f t="shared" si="38"/>
+        <f t="shared" si="44"/>
         <v>0.4342105263157896</v>
       </c>
       <c r="M26" s="10">
-        <f t="shared" si="38"/>
+        <f t="shared" si="44"/>
         <v>0.37623762376237635</v>
       </c>
       <c r="N26" s="10">
-        <f t="shared" si="38"/>
+        <f t="shared" si="44"/>
         <v>0.68131868131868156</v>
       </c>
       <c r="O26" s="10">
-        <f t="shared" si="38"/>
+        <f t="shared" si="44"/>
         <v>0.32075471698113223</v>
       </c>
       <c r="P26" s="10">
-        <f t="shared" si="38"/>
+        <f t="shared" si="44"/>
         <v>0.201834862385321</v>
       </c>
       <c r="Q26" s="10">
@@ -4275,19 +4320,19 @@
         <v>0.94117647058823506</v>
       </c>
       <c r="S26" s="10">
-        <f t="shared" ref="S26:V26" si="39">S8/O8-1</f>
+        <f t="shared" ref="S26:V26" si="45">S8/O8-1</f>
+        <v>0.7</v>
+      </c>
+      <c r="T26" s="10">
+        <f t="shared" si="45"/>
         <v>-1</v>
       </c>
-      <c r="T26" s="10">
-        <f t="shared" si="39"/>
+      <c r="U26" s="10">
+        <f t="shared" si="45"/>
         <v>-1</v>
       </c>
-      <c r="U26" s="10">
-        <f t="shared" si="39"/>
-        <v>-1</v>
-      </c>
       <c r="V26" s="10">
-        <f t="shared" si="39"/>
+        <f t="shared" si="45"/>
         <v>-1</v>
       </c>
       <c r="X26" s="10"/>
@@ -4296,55 +4341,55 @@
         <v>1.6086956521739131</v>
       </c>
       <c r="Z26" s="10">
-        <f t="shared" ref="Z26:AL26" si="40">Z8/Y8-1</f>
+        <f t="shared" ref="Z26:AL26" si="46">Z8/Y8-1</f>
         <v>0.40833333333333344</v>
       </c>
       <c r="AA26" s="10">
-        <f t="shared" si="40"/>
+        <f t="shared" si="46"/>
         <v>0.4023668639053255</v>
       </c>
       <c r="AB26" s="10">
-        <f t="shared" si="40"/>
+        <f t="shared" si="46"/>
         <v>0.10000000000000009</v>
       </c>
       <c r="AC26" s="10">
-        <f t="shared" si="40"/>
+        <f t="shared" si="46"/>
         <v>8.0000000000000071E-2</v>
       </c>
       <c r="AD26" s="10">
-        <f t="shared" si="40"/>
+        <f t="shared" si="46"/>
         <v>6.0000000000000053E-2</v>
       </c>
       <c r="AE26" s="10">
-        <f t="shared" si="40"/>
+        <f t="shared" si="46"/>
         <v>4.0000000000000036E-2</v>
       </c>
       <c r="AF26" s="10">
-        <f t="shared" si="40"/>
+        <f t="shared" si="46"/>
         <v>3.0000000000000027E-2</v>
       </c>
       <c r="AG26" s="10">
-        <f t="shared" si="40"/>
+        <f t="shared" si="46"/>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="AH26" s="10">
-        <f t="shared" si="40"/>
+        <f t="shared" si="46"/>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="AI26" s="10">
-        <f t="shared" si="40"/>
+        <f t="shared" si="46"/>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="AJ26" s="10">
-        <f t="shared" si="40"/>
+        <f t="shared" si="46"/>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="AK26" s="10">
-        <f t="shared" si="40"/>
+        <f t="shared" si="46"/>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="AL26" s="10">
-        <f t="shared" si="40"/>
+        <f t="shared" si="46"/>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="AO26" t="s">
@@ -4352,7 +4397,7 @@
       </c>
       <c r="AP26" s="5">
         <f>Main!D8</f>
-        <v>364.29999999999995</v>
+        <v>697.19999999999993</v>
       </c>
     </row>
     <row r="27" spans="2:156" x14ac:dyDescent="0.3">
@@ -4364,43 +4409,43 @@
       <c r="E27" s="10"/>
       <c r="F27" s="10"/>
       <c r="G27" s="10">
-        <f t="shared" ref="G27:P27" si="41">G9/C9-1</f>
+        <f t="shared" ref="G27:P27" si="47">G9/C9-1</f>
         <v>2.25</v>
       </c>
       <c r="H27" s="10">
-        <f t="shared" si="41"/>
+        <f t="shared" si="47"/>
         <v>2</v>
       </c>
       <c r="I27" s="10">
-        <f t="shared" si="41"/>
+        <f t="shared" si="47"/>
         <v>1.5</v>
       </c>
       <c r="J27" s="10">
-        <f t="shared" si="41"/>
+        <f t="shared" si="47"/>
         <v>0.39999999999999991</v>
       </c>
       <c r="K27" s="10">
-        <f t="shared" si="41"/>
+        <f t="shared" si="47"/>
         <v>0.38461538461538458</v>
       </c>
       <c r="L27" s="10">
-        <f t="shared" si="41"/>
+        <f t="shared" si="47"/>
         <v>0.53333333333333321</v>
       </c>
       <c r="M27" s="10">
-        <f t="shared" si="41"/>
+        <f t="shared" si="47"/>
         <v>0.8</v>
       </c>
       <c r="N27" s="10">
-        <f t="shared" si="41"/>
+        <f t="shared" si="47"/>
         <v>1.5</v>
       </c>
       <c r="O27" s="10">
-        <f t="shared" si="41"/>
+        <f t="shared" si="47"/>
         <v>1.2222222222222223</v>
       </c>
       <c r="P27" s="10">
-        <f t="shared" si="41"/>
+        <f t="shared" si="47"/>
         <v>0.86956521739130443</v>
       </c>
       <c r="Q27" s="10">
@@ -4412,19 +4457,19 @@
         <v>0.5714285714285714</v>
       </c>
       <c r="S27" s="10">
-        <f t="shared" ref="S27:V27" si="42">S9/O9-1</f>
+        <f t="shared" ref="S27:V27" si="48">S9/O9-1</f>
+        <v>0.64999999999999991</v>
+      </c>
+      <c r="T27" s="10">
+        <f t="shared" si="48"/>
         <v>-1</v>
       </c>
-      <c r="T27" s="10">
-        <f t="shared" si="42"/>
+      <c r="U27" s="10">
+        <f t="shared" si="48"/>
         <v>-1</v>
       </c>
-      <c r="U27" s="10">
-        <f t="shared" si="42"/>
-        <v>-1</v>
-      </c>
       <c r="V27" s="10">
-        <f t="shared" si="42"/>
+        <f t="shared" si="48"/>
         <v>-1</v>
       </c>
       <c r="X27" s="10"/>
@@ -4433,55 +4478,55 @@
         <v>1.2799999999999998</v>
       </c>
       <c r="Z27" s="10">
-        <f t="shared" ref="Z27:AL27" si="43">Z9/Y9-1</f>
+        <f t="shared" ref="Z27:AL27" si="49">Z9/Y9-1</f>
         <v>0.80701754385964941</v>
       </c>
       <c r="AA27" s="10">
-        <f t="shared" si="43"/>
+        <f t="shared" si="49"/>
         <v>0.81553398058252435</v>
       </c>
       <c r="AB27" s="10">
-        <f t="shared" si="43"/>
+        <f t="shared" si="49"/>
         <v>0.5</v>
       </c>
       <c r="AC27" s="10">
-        <f t="shared" si="43"/>
+        <f t="shared" si="49"/>
         <v>0.25</v>
       </c>
       <c r="AD27" s="10">
-        <f t="shared" si="43"/>
+        <f t="shared" si="49"/>
         <v>0.10000000000000009</v>
       </c>
       <c r="AE27" s="10">
-        <f t="shared" si="43"/>
+        <f t="shared" si="49"/>
         <v>7.0000000000000062E-2</v>
       </c>
       <c r="AF27" s="10">
-        <f t="shared" si="43"/>
+        <f t="shared" si="49"/>
         <v>3.0000000000000027E-2</v>
       </c>
       <c r="AG27" s="10">
-        <f t="shared" si="43"/>
+        <f t="shared" si="49"/>
         <v>3.0000000000000027E-2</v>
       </c>
       <c r="AH27" s="10">
-        <f t="shared" si="43"/>
+        <f t="shared" si="49"/>
         <v>3.0000000000000027E-2</v>
       </c>
       <c r="AI27" s="10">
-        <f t="shared" si="43"/>
+        <f t="shared" si="49"/>
         <v>3.0000000000000027E-2</v>
       </c>
       <c r="AJ27" s="10">
-        <f t="shared" si="43"/>
+        <f t="shared" si="49"/>
         <v>3.0000000000000027E-2</v>
       </c>
       <c r="AK27" s="10">
-        <f t="shared" si="43"/>
+        <f t="shared" si="49"/>
         <v>3.0000000000000027E-2</v>
       </c>
       <c r="AL27" s="10">
-        <f t="shared" si="43"/>
+        <f t="shared" si="49"/>
         <v>3.0000000000000027E-2</v>
       </c>
       <c r="AO27" t="s">
@@ -4489,7 +4534,7 @@
       </c>
       <c r="AP27" s="5">
         <f>AP25+AP26</f>
-        <v>1540.2692914182289</v>
+        <v>1548.6398061009427</v>
       </c>
     </row>
     <row r="28" spans="2:156" x14ac:dyDescent="0.3">
@@ -4497,59 +4542,59 @@
         <v>50</v>
       </c>
       <c r="C28" s="10">
-        <f t="shared" ref="C28:P28" si="44">C11/C3</f>
+        <f t="shared" ref="C28:P28" si="50">C11/C3</f>
         <v>-74</v>
       </c>
       <c r="D28" s="10">
-        <f t="shared" si="44"/>
+        <f t="shared" si="50"/>
         <v>-100</v>
       </c>
       <c r="E28" s="10">
-        <f t="shared" si="44"/>
+        <f t="shared" si="50"/>
         <v>-52.999999999999993</v>
       </c>
       <c r="F28" s="10">
-        <f t="shared" si="44"/>
+        <f t="shared" si="50"/>
         <v>-6.75</v>
       </c>
       <c r="G28" s="10">
-        <f t="shared" si="44"/>
+        <f t="shared" si="50"/>
         <v>-9.15</v>
       </c>
       <c r="H28" s="10">
-        <f t="shared" si="44"/>
+        <f t="shared" si="50"/>
         <v>-7.3076923076923075</v>
       </c>
       <c r="I28" s="10">
-        <f t="shared" si="44"/>
+        <f t="shared" si="50"/>
         <v>-8.8571428571428559</v>
       </c>
       <c r="J28" s="10">
-        <f t="shared" si="44"/>
+        <f t="shared" si="50"/>
         <v>-6.2368421052631566</v>
       </c>
       <c r="K28" s="10">
-        <f t="shared" si="44"/>
+        <f t="shared" si="50"/>
         <v>-6.5116279069767442</v>
       </c>
       <c r="L28" s="10">
-        <f t="shared" si="44"/>
+        <f t="shared" si="50"/>
         <v>-6.0181818181818167</v>
       </c>
       <c r="M28" s="10">
-        <f t="shared" si="44"/>
+        <f t="shared" si="50"/>
         <v>-6.9016393442622954</v>
       </c>
       <c r="N28" s="10">
-        <f t="shared" si="44"/>
+        <f t="shared" si="50"/>
         <v>-8.9344262295081975</v>
       </c>
       <c r="O28" s="10">
-        <f t="shared" si="44"/>
+        <f t="shared" si="50"/>
         <v>-6.9605263157894743</v>
       </c>
       <c r="P28" s="10">
-        <f t="shared" si="44"/>
+        <f t="shared" si="50"/>
         <v>-4.2894736842105257</v>
       </c>
       <c r="Q28" s="10">
@@ -4561,23 +4606,23 @@
         <v>-6.6239316239316244</v>
       </c>
       <c r="S28" s="10">
-        <f t="shared" ref="S28:V28" si="45">S11/S3</f>
-        <v>0</v>
+        <f t="shared" ref="S28:V28" si="51">S11/S3</f>
+        <v>-9.9605263157894743</v>
       </c>
       <c r="T28" s="10">
-        <f t="shared" si="45"/>
+        <f t="shared" si="51"/>
         <v>0</v>
       </c>
       <c r="U28" s="10">
-        <f t="shared" si="45"/>
+        <f t="shared" si="51"/>
         <v>0</v>
       </c>
       <c r="V28" s="10">
-        <f t="shared" si="45"/>
+        <f t="shared" si="51"/>
         <v>0</v>
       </c>
       <c r="X28" s="10">
-        <f t="shared" ref="X28" si="46">X11/X3</f>
+        <f t="shared" ref="X28" si="52">X11/X3</f>
         <v>-19.399999999999999</v>
       </c>
       <c r="Y28" s="10">
@@ -4585,63 +4630,63 @@
         <v>-7.6607142857142874</v>
       </c>
       <c r="Z28" s="10">
-        <f t="shared" ref="Z28:AL28" si="47">Z11/Z3</f>
+        <f t="shared" ref="Z28:AL28" si="53">Z11/Z3</f>
         <v>-7.1681818181818189</v>
       </c>
       <c r="AA28" s="10">
-        <f t="shared" si="47"/>
+        <f t="shared" si="53"/>
         <v>-5.3921113689095135</v>
       </c>
       <c r="AB28" s="10">
-        <f t="shared" si="47"/>
-        <v>-3.0864120411684226</v>
+        <f t="shared" si="53"/>
+        <v>-3.3071501272264636</v>
       </c>
       <c r="AC28" s="10">
-        <f t="shared" si="47"/>
-        <v>-1.7760811337841504</v>
+        <f t="shared" si="53"/>
+        <v>-1.91366652530393</v>
       </c>
       <c r="AD28" s="10">
-        <f t="shared" si="47"/>
-        <v>-0.99086852709235751</v>
+        <f t="shared" si="53"/>
+        <v>-1.0775222055913127</v>
       </c>
       <c r="AE28" s="10">
-        <f t="shared" si="47"/>
-        <v>-0.54058118826982304</v>
+        <f t="shared" si="53"/>
+        <v>-0.59742679348775185</v>
       </c>
       <c r="AF28" s="10">
-        <f t="shared" si="47"/>
-        <v>-0.25005236006173959</v>
+        <f t="shared" si="53"/>
+        <v>-0.28954262851639823</v>
       </c>
       <c r="AG28" s="10">
-        <f t="shared" si="47"/>
-        <v>-4.8631717653262935E-2</v>
+        <f t="shared" si="53"/>
+        <v>-7.69396019105405E-2</v>
       </c>
       <c r="AH28" s="10">
-        <f t="shared" si="47"/>
-        <v>6.01554485610322E-2</v>
+        <f t="shared" si="53"/>
+        <v>3.6612782115928139E-2</v>
       </c>
       <c r="AI28" s="10">
-        <f t="shared" si="47"/>
-        <v>0.13553771776063661</v>
+        <f t="shared" si="53"/>
+        <v>0.11513889935359682</v>
       </c>
       <c r="AJ28" s="10">
-        <f t="shared" si="47"/>
-        <v>0.19372265755641363</v>
+        <f t="shared" si="53"/>
+        <v>0.17527634547492088</v>
       </c>
       <c r="AK28" s="10">
-        <f t="shared" si="47"/>
-        <v>0.22822356553791479</v>
+        <f t="shared" si="53"/>
+        <v>0.21078180108949177</v>
       </c>
       <c r="AL28" s="10">
-        <f t="shared" si="47"/>
-        <v>0.25055782704192214</v>
+        <f t="shared" si="53"/>
+        <v>0.23327776811371947</v>
       </c>
       <c r="AO28" t="s">
         <v>57</v>
       </c>
       <c r="AP28" s="4">
         <f>AP27/AL19</f>
-        <v>7.1176954316923702</v>
+        <v>7.1563761834609183</v>
       </c>
     </row>
     <row r="29" spans="2:156" x14ac:dyDescent="0.3">
@@ -4649,59 +4694,59 @@
         <v>36</v>
       </c>
       <c r="C29" s="10">
-        <f t="shared" ref="C29:P29" si="48">C17/C16</f>
+        <f t="shared" ref="C29:P29" si="54">C17/C16</f>
         <v>0</v>
       </c>
       <c r="D29" s="10">
-        <f t="shared" si="48"/>
+        <f t="shared" si="54"/>
         <v>0</v>
       </c>
       <c r="E29" s="10">
-        <f t="shared" si="48"/>
+        <f t="shared" si="54"/>
         <v>0</v>
       </c>
       <c r="F29" s="10">
-        <f t="shared" si="48"/>
+        <f t="shared" si="54"/>
         <v>0</v>
       </c>
       <c r="G29" s="10">
-        <f t="shared" si="48"/>
+        <f t="shared" si="54"/>
         <v>0</v>
       </c>
       <c r="H29" s="10">
-        <f t="shared" si="48"/>
+        <f t="shared" si="54"/>
         <v>0</v>
       </c>
       <c r="I29" s="10">
-        <f t="shared" si="48"/>
+        <f t="shared" si="54"/>
         <v>0</v>
       </c>
       <c r="J29" s="10">
-        <f t="shared" si="48"/>
+        <f t="shared" si="54"/>
         <v>0</v>
       </c>
       <c r="K29" s="10">
-        <f t="shared" si="48"/>
+        <f t="shared" si="54"/>
         <v>0</v>
       </c>
       <c r="L29" s="10">
-        <f t="shared" si="48"/>
+        <f t="shared" si="54"/>
         <v>0</v>
       </c>
       <c r="M29" s="10">
-        <f t="shared" si="48"/>
+        <f t="shared" si="54"/>
         <v>0</v>
       </c>
       <c r="N29" s="10">
-        <f t="shared" si="48"/>
+        <f t="shared" si="54"/>
         <v>0</v>
       </c>
       <c r="O29" s="10">
-        <f t="shared" si="48"/>
+        <f t="shared" si="54"/>
         <v>0</v>
       </c>
       <c r="P29" s="10">
-        <f t="shared" si="48"/>
+        <f t="shared" si="54"/>
         <v>0</v>
       </c>
       <c r="Q29" s="10">
@@ -4712,24 +4757,24 @@
         <f>R17/R16</f>
         <v>0</v>
       </c>
-      <c r="S29" s="10" t="e">
-        <f t="shared" ref="S29:V29" si="49">S17/S16</f>
+      <c r="S29" s="10">
+        <f t="shared" ref="S29:V29" si="55">S17/S16</f>
+        <v>0</v>
+      </c>
+      <c r="T29" s="10" t="e">
+        <f t="shared" si="55"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="T29" s="10" t="e">
-        <f t="shared" si="49"/>
+      <c r="U29" s="10" t="e">
+        <f t="shared" si="55"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="U29" s="10" t="e">
-        <f t="shared" si="49"/>
+      <c r="V29" s="10" t="e">
+        <f t="shared" si="55"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="V29" s="10" t="e">
-        <f t="shared" si="49"/>
-        <v>#DIV/0!</v>
-      </c>
       <c r="X29" s="10">
-        <f t="shared" ref="X29" si="50">X17/X16</f>
+        <f t="shared" ref="X29" si="56">X17/X16</f>
         <v>0</v>
       </c>
       <c r="Y29" s="10">
@@ -4737,55 +4782,55 @@
         <v>0</v>
       </c>
       <c r="Z29" s="10">
-        <f t="shared" ref="Z29:AL29" si="51">Z17/Z16</f>
+        <f t="shared" ref="Z29:AL29" si="57">Z17/Z16</f>
         <v>0</v>
       </c>
       <c r="AA29" s="10">
-        <f t="shared" si="51"/>
+        <f t="shared" si="57"/>
         <v>0</v>
       </c>
       <c r="AB29" s="10">
-        <f t="shared" si="51"/>
+        <f t="shared" si="57"/>
         <v>0</v>
       </c>
       <c r="AC29" s="10">
-        <f t="shared" si="51"/>
+        <f t="shared" si="57"/>
         <v>0</v>
       </c>
       <c r="AD29" s="10">
-        <f t="shared" si="51"/>
+        <f t="shared" si="57"/>
         <v>0</v>
       </c>
       <c r="AE29" s="10">
-        <f t="shared" si="51"/>
+        <f t="shared" si="57"/>
         <v>0</v>
       </c>
       <c r="AF29" s="10">
-        <f t="shared" si="51"/>
+        <f t="shared" si="57"/>
         <v>0</v>
       </c>
       <c r="AG29" s="10">
-        <f t="shared" si="51"/>
+        <f t="shared" si="57"/>
         <v>0</v>
       </c>
       <c r="AH29" s="10">
-        <f t="shared" si="51"/>
+        <f t="shared" si="57"/>
         <v>0</v>
       </c>
       <c r="AI29" s="10">
-        <f t="shared" si="51"/>
+        <f t="shared" si="57"/>
         <v>0</v>
       </c>
       <c r="AJ29" s="10">
-        <f t="shared" si="51"/>
+        <f t="shared" si="57"/>
         <v>0</v>
       </c>
       <c r="AK29" s="10">
-        <f t="shared" si="51"/>
+        <f t="shared" si="57"/>
         <v>0</v>
       </c>
       <c r="AL29" s="10">
-        <f t="shared" si="51"/>
+        <f t="shared" si="57"/>
         <v>0</v>
       </c>
       <c r="AO29" t="s">
@@ -4793,7 +4838,7 @@
       </c>
       <c r="AP29" s="4">
         <f>Main!D3</f>
-        <v>22.57</v>
+        <v>47.13</v>
       </c>
     </row>
     <row r="30" spans="2:156" x14ac:dyDescent="0.3">
@@ -4801,59 +4846,59 @@
         <v>51</v>
       </c>
       <c r="C30" s="10">
-        <f t="shared" ref="C30:P30" si="52">C18/C3</f>
+        <f t="shared" ref="C30:P30" si="58">C18/C3</f>
         <v>-74</v>
       </c>
       <c r="D30" s="10">
-        <f t="shared" si="52"/>
+        <f t="shared" si="58"/>
         <v>-100</v>
       </c>
       <c r="E30" s="10">
-        <f t="shared" si="52"/>
+        <f t="shared" si="58"/>
         <v>-74.499999999999986</v>
       </c>
       <c r="F30" s="10">
-        <f t="shared" si="52"/>
+        <f t="shared" si="58"/>
         <v>-46.25</v>
       </c>
       <c r="G30" s="10">
-        <f t="shared" si="52"/>
+        <f t="shared" si="58"/>
         <v>-2.1500000000000004</v>
       </c>
       <c r="H30" s="10">
-        <f t="shared" si="52"/>
+        <f t="shared" si="58"/>
         <v>-0.57692307692307554</v>
       </c>
       <c r="I30" s="10">
-        <f t="shared" si="52"/>
+        <f t="shared" si="58"/>
         <v>-8.5357142857142865</v>
       </c>
       <c r="J30" s="10">
-        <f t="shared" si="52"/>
+        <f t="shared" si="58"/>
         <v>-4.9210526315789469</v>
       </c>
       <c r="K30" s="10">
-        <f t="shared" si="52"/>
+        <f t="shared" si="58"/>
         <v>-6.3488372093023262</v>
       </c>
       <c r="L30" s="10">
-        <f t="shared" si="52"/>
+        <f t="shared" si="58"/>
         <v>-7.9454545454545444</v>
       </c>
       <c r="M30" s="10">
-        <f t="shared" si="52"/>
+        <f t="shared" si="58"/>
         <v>-7.3114754098360661</v>
       </c>
       <c r="N30" s="10">
-        <f t="shared" si="52"/>
+        <f t="shared" si="58"/>
         <v>-6.8688524590163951</v>
       </c>
       <c r="O30" s="10">
-        <f t="shared" si="52"/>
+        <f t="shared" si="58"/>
         <v>-5.2105263157894752</v>
       </c>
       <c r="P30" s="10">
-        <f t="shared" si="52"/>
+        <f t="shared" si="58"/>
         <v>-3.2982456140350873</v>
       </c>
       <c r="Q30" s="10">
@@ -4865,23 +4910,23 @@
         <v>-17.264957264957268</v>
       </c>
       <c r="S30" s="10">
-        <f t="shared" ref="S30:V30" si="53">S18/S3</f>
-        <v>0</v>
+        <f t="shared" ref="S30:V30" si="59">S18/S3</f>
+        <v>-4.2368421052631584</v>
       </c>
       <c r="T30" s="10">
-        <f t="shared" si="53"/>
+        <f t="shared" si="59"/>
         <v>0</v>
       </c>
       <c r="U30" s="10">
-        <f t="shared" si="53"/>
+        <f t="shared" si="59"/>
         <v>0</v>
       </c>
       <c r="V30" s="10">
-        <f t="shared" si="53"/>
+        <f t="shared" si="59"/>
         <v>0</v>
       </c>
       <c r="X30" s="10">
-        <f t="shared" ref="X30" si="54">X18/X3</f>
+        <f t="shared" ref="X30" si="60">X18/X3</f>
         <v>-53.15</v>
       </c>
       <c r="Y30" s="10">
@@ -4889,63 +4934,63 @@
         <v>-4.3214285714285721</v>
       </c>
       <c r="Z30" s="10">
-        <f t="shared" ref="Z30:AL30" si="55">Z18/Z3</f>
+        <f t="shared" ref="Z30:AL30" si="61">Z18/Z3</f>
         <v>-7.1590909090909101</v>
       </c>
       <c r="AA30" s="10">
-        <f t="shared" si="55"/>
+        <f t="shared" si="61"/>
         <v>-7.6960556844547572</v>
       </c>
       <c r="AB30" s="10">
-        <f t="shared" si="55"/>
-        <v>-2.8633648640609204</v>
+        <f t="shared" si="61"/>
+        <v>-3.0686513994910944</v>
       </c>
       <c r="AC30" s="10">
-        <f t="shared" si="55"/>
-        <v>-1.6484485824393023</v>
+        <f t="shared" si="61"/>
+        <v>-1.7771922533220246</v>
       </c>
       <c r="AD30" s="10">
-        <f t="shared" si="55"/>
-        <v>-0.91353821657165524</v>
+        <f t="shared" si="61"/>
+        <v>-0.99483485256698168</v>
       </c>
       <c r="AE30" s="10">
-        <f t="shared" si="55"/>
-        <v>-0.49079980087212099</v>
+        <f t="shared" si="61"/>
+        <v>-0.54419680997833875</v>
       </c>
       <c r="AF30" s="10">
-        <f t="shared" si="55"/>
-        <v>-0.21586914071531749</v>
+        <f t="shared" si="61"/>
+        <v>-0.25299137317326792</v>
       </c>
       <c r="AG30" s="10">
-        <f t="shared" si="55"/>
-        <v>-2.4349844600287246E-2</v>
+        <f t="shared" si="61"/>
+        <v>-5.0975606735765157E-2</v>
       </c>
       <c r="AH30" s="10">
-        <f t="shared" si="55"/>
-        <v>8.0163711956684175E-2</v>
+        <f t="shared" si="61"/>
+        <v>5.8007114139943021E-2</v>
       </c>
       <c r="AI30" s="10">
-        <f t="shared" si="55"/>
-        <v>0.15271147717523786</v>
+        <f t="shared" si="61"/>
+        <v>0.13350236767420959</v>
       </c>
       <c r="AJ30" s="10">
-        <f t="shared" si="55"/>
-        <v>0.20910437251036085</v>
+        <f t="shared" si="61"/>
+        <v>0.191723625796861</v>
       </c>
       <c r="AK30" s="10">
-        <f t="shared" si="55"/>
-        <v>0.24262644408570172</v>
+        <f t="shared" si="61"/>
+        <v>0.22618243630003568</v>
       </c>
       <c r="AL30" s="10">
-        <f t="shared" si="55"/>
-        <v>0.26468636504594173</v>
+        <f t="shared" si="61"/>
+        <v>0.24838505789168164</v>
       </c>
       <c r="AO30" s="1" t="s">
         <v>59</v>
       </c>
       <c r="AP30" s="9">
         <f>AP28/AP29-1</f>
-        <v>-0.68463910360246483</v>
+        <v>-0.84815666913938215</v>
       </c>
     </row>
     <row r="31" spans="2:156" x14ac:dyDescent="0.3">

--- a/Financial Analysis/IONQ.xlsx
+++ b/Financial Analysis/IONQ.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\antos\Documents\GitHub\FinanceModels\Financial Analysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{689CD8F5-9652-4EEE-B079-68FDEF6F9F10}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8D6AE02D-B86E-4A9B-928B-BC274672CF1A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{054FC3C2-46E6-4A64-A90B-FD32B5955AC0}"/>
   </bookViews>
@@ -326,14 +326,14 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>26</xdr:col>
-      <xdr:colOff>30480</xdr:colOff>
+      <xdr:col>27</xdr:col>
+      <xdr:colOff>38100</xdr:colOff>
       <xdr:row>0</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>26</xdr:col>
-      <xdr:colOff>30480</xdr:colOff>
+      <xdr:col>27</xdr:col>
+      <xdr:colOff>38100</xdr:colOff>
       <xdr:row>33</xdr:row>
       <xdr:rowOff>83820</xdr:rowOff>
     </xdr:to>
@@ -350,7 +350,7 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="14317980" y="0"/>
+          <a:off x="17373600" y="0"/>
           <a:ext cx="0" cy="6118860"/>
         </a:xfrm>
         <a:prstGeom prst="line">
@@ -376,13 +376,13 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>19</xdr:col>
+      <xdr:col>20</xdr:col>
       <xdr:colOff>30480</xdr:colOff>
       <xdr:row>0</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>19</xdr:col>
+      <xdr:col>20</xdr:col>
       <xdr:colOff>30480</xdr:colOff>
       <xdr:row>33</xdr:row>
       <xdr:rowOff>91440</xdr:rowOff>
@@ -400,7 +400,7 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="12489180" y="0"/>
+          <a:off x="13098780" y="0"/>
           <a:ext cx="0" cy="6126480"/>
         </a:xfrm>
         <a:prstGeom prst="line">
@@ -749,17 +749,17 @@
         <v>1</v>
       </c>
       <c r="D3" s="4">
-        <v>47.13</v>
+        <v>39.86</v>
       </c>
       <c r="E3" s="3">
-        <v>45729</v>
+        <v>45891</v>
       </c>
       <c r="F3" s="3">
         <f ca="1">TODAY()</f>
-        <v>45804</v>
+        <v>45894</v>
       </c>
       <c r="G3" s="3">
-        <v>45804</v>
+        <v>45965</v>
       </c>
     </row>
     <row r="4" spans="2:11" x14ac:dyDescent="0.3">
@@ -767,11 +767,11 @@
         <v>2</v>
       </c>
       <c r="D4" s="5">
-        <f>247.8</f>
-        <v>247.8</v>
+        <f>296.8</f>
+        <v>296.8</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="5" spans="2:11" x14ac:dyDescent="0.3">
@@ -780,7 +780,7 @@
       </c>
       <c r="D5" s="5">
         <f>D3*D4</f>
-        <v>11678.814</v>
+        <v>11830.448</v>
       </c>
     </row>
     <row r="6" spans="2:11" x14ac:dyDescent="0.3">
@@ -788,11 +788,11 @@
         <v>4</v>
       </c>
       <c r="D6" s="5">
-        <f>159.7+428.6+108.9</f>
-        <v>697.19999999999993</v>
+        <f>140.1+406.8+109</f>
+        <v>655.9</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="7" spans="2:11" x14ac:dyDescent="0.3">
@@ -803,7 +803,7 @@
         <v>0</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="8" spans="2:11" x14ac:dyDescent="0.3">
@@ -812,7 +812,7 @@
       </c>
       <c r="D8" s="5">
         <f>D6-D7</f>
-        <v>697.19999999999993</v>
+        <v>655.9</v>
       </c>
     </row>
     <row r="9" spans="2:11" x14ac:dyDescent="0.3">
@@ -821,7 +821,7 @@
       </c>
       <c r="D9" s="5">
         <f>D5-D8</f>
-        <v>10981.614</v>
+        <v>11174.548000000001</v>
       </c>
     </row>
     <row r="10" spans="2:11" x14ac:dyDescent="0.3">
@@ -1008,7 +1008,7 @@
         <v>7.6</v>
       </c>
       <c r="T3" s="8">
-        <v>17</v>
+        <v>20.7</v>
       </c>
       <c r="U3" s="8">
         <v>24</v>
@@ -1035,47 +1035,47 @@
       </c>
       <c r="AB3" s="8">
         <f>SUM(S3:V3)</f>
-        <v>78.599999999999994</v>
+        <v>82.3</v>
       </c>
       <c r="AC3" s="8">
         <f>AB3*1.8</f>
-        <v>141.47999999999999</v>
+        <v>148.13999999999999</v>
       </c>
       <c r="AD3" s="8">
         <f>AC3*1.7</f>
-        <v>240.51599999999996</v>
+        <v>251.83799999999997</v>
       </c>
       <c r="AE3" s="8">
         <f>AD3*1.6</f>
-        <v>384.82559999999995</v>
+        <v>402.94079999999997</v>
       </c>
       <c r="AF3" s="8">
         <f>AE3*1.5</f>
-        <v>577.23839999999996</v>
+        <v>604.41120000000001</v>
       </c>
       <c r="AG3" s="8">
         <f>AF3*1.45</f>
-        <v>836.99567999999988</v>
+        <v>876.39624000000003</v>
       </c>
       <c r="AH3" s="8">
         <f>AG3*1.25</f>
-        <v>1046.2445999999998</v>
+        <v>1095.4953</v>
       </c>
       <c r="AI3" s="8">
         <f>AH3*1.2</f>
-        <v>1255.4935199999998</v>
+        <v>1314.5943600000001</v>
       </c>
       <c r="AJ3" s="8">
         <f>AI3*1.15</f>
-        <v>1443.8175479999995</v>
+        <v>1511.783514</v>
       </c>
       <c r="AK3" s="8">
         <f>AJ3*1.1</f>
-        <v>1588.1993027999997</v>
+        <v>1662.9618654000001</v>
       </c>
       <c r="AL3" s="8">
         <f>AK3*1.05</f>
-        <v>1667.6092679399999</v>
+        <v>1746.1099586700002</v>
       </c>
     </row>
     <row r="4" spans="2:38" x14ac:dyDescent="0.3">
@@ -1134,11 +1134,10 @@
         <v>4.3</v>
       </c>
       <c r="T4" s="5">
-        <f t="shared" ref="T4:V4" si="0">T3-T5</f>
-        <v>8.16</v>
+        <v>8.3000000000000007</v>
       </c>
       <c r="U4" s="5">
-        <f t="shared" si="0"/>
+        <f t="shared" ref="U4:V4" si="0">U3-U5</f>
         <v>11.52</v>
       </c>
       <c r="V4" s="5">
@@ -1163,47 +1162,47 @@
       </c>
       <c r="AB4" s="5">
         <f>AB3-AB5</f>
-        <v>39.299999999999997</v>
+        <v>41.15</v>
       </c>
       <c r="AC4" s="5">
         <f t="shared" ref="AC4:AL4" si="1">AC3-AC5</f>
-        <v>69.325199999999995</v>
+        <v>72.588599999999985</v>
       </c>
       <c r="AD4" s="5">
         <f t="shared" si="1"/>
-        <v>115.44767999999998</v>
+        <v>120.88223999999997</v>
       </c>
       <c r="AE4" s="5">
         <f t="shared" si="1"/>
-        <v>184.71628799999996</v>
+        <v>193.41158399999998</v>
       </c>
       <c r="AF4" s="5">
         <f t="shared" si="1"/>
-        <v>265.52966399999997</v>
+        <v>278.02915200000001</v>
       </c>
       <c r="AG4" s="5">
         <f t="shared" si="1"/>
-        <v>368.27809919999993</v>
+        <v>385.61434559999998</v>
       </c>
       <c r="AH4" s="5">
         <f t="shared" si="1"/>
-        <v>439.422732</v>
+        <v>460.10802600000011</v>
       </c>
       <c r="AI4" s="5">
         <f t="shared" si="1"/>
-        <v>502.19740799999988</v>
+        <v>525.83774400000004</v>
       </c>
       <c r="AJ4" s="5">
         <f t="shared" si="1"/>
-        <v>548.65066823999985</v>
+        <v>574.47773531999997</v>
       </c>
       <c r="AK4" s="5">
         <f t="shared" si="1"/>
-        <v>587.63374203599983</v>
+        <v>615.29589019800005</v>
       </c>
       <c r="AL4" s="5">
         <f t="shared" si="1"/>
-        <v>600.33933645839988</v>
+        <v>628.59958512120011</v>
       </c>
     </row>
     <row r="5" spans="2:38" s="1" customFormat="1" x14ac:dyDescent="0.3">
@@ -1211,7 +1210,7 @@
         <v>25</v>
       </c>
       <c r="C5" s="8">
-        <f t="shared" ref="C5:S5" si="2">C3-C4</f>
+        <f t="shared" ref="C5:T5" si="2">C3-C4</f>
         <v>-0.1</v>
       </c>
       <c r="D5" s="8">
@@ -1279,11 +1278,11 @@
         <v>3.3</v>
       </c>
       <c r="T5" s="8">
-        <f t="shared" ref="T5:V5" si="3">T3*0.52</f>
-        <v>8.84</v>
+        <f t="shared" si="2"/>
+        <v>12.399999999999999</v>
       </c>
       <c r="U5" s="8">
-        <f t="shared" si="3"/>
+        <f t="shared" ref="U5:V5" si="3">U3*0.52</f>
         <v>12.48</v>
       </c>
       <c r="V5" s="8">
@@ -1308,47 +1307,47 @@
       </c>
       <c r="AB5" s="8">
         <f>AB3*0.5</f>
-        <v>39.299999999999997</v>
+        <v>41.15</v>
       </c>
       <c r="AC5" s="8">
         <f>AC3*0.51</f>
-        <v>72.154799999999994</v>
+        <v>75.551400000000001</v>
       </c>
       <c r="AD5" s="8">
         <f>AD3*0.52</f>
-        <v>125.06831999999999</v>
+        <v>130.95576</v>
       </c>
       <c r="AE5" s="8">
         <f>AE3*0.52</f>
-        <v>200.10931199999999</v>
+        <v>209.52921599999999</v>
       </c>
       <c r="AF5" s="8">
         <f>AF3*0.54</f>
-        <v>311.70873599999999</v>
+        <v>326.382048</v>
       </c>
       <c r="AG5" s="8">
         <f>AG3*0.56</f>
-        <v>468.71758079999995</v>
+        <v>490.78189440000006</v>
       </c>
       <c r="AH5" s="8">
         <f>AH3*0.58</f>
-        <v>606.82186799999977</v>
+        <v>635.38727399999993</v>
       </c>
       <c r="AI5" s="8">
         <f>AI3*0.6</f>
-        <v>753.29611199999988</v>
+        <v>788.75661600000001</v>
       </c>
       <c r="AJ5" s="8">
         <f>AJ3*0.62</f>
-        <v>895.16687975999969</v>
+        <v>937.30577868</v>
       </c>
       <c r="AK5" s="8">
         <f>AK3*0.63</f>
-        <v>1000.5655607639999</v>
+        <v>1047.665975202</v>
       </c>
       <c r="AL5" s="8">
         <f>AL3*0.64</f>
-        <v>1067.2699314816</v>
+        <v>1117.5103735488001</v>
       </c>
     </row>
     <row r="6" spans="2:38" x14ac:dyDescent="0.3">
@@ -1406,7 +1405,9 @@
       <c r="S6" s="5">
         <v>40</v>
       </c>
-      <c r="T6" s="5"/>
+      <c r="T6" s="5">
+        <v>103.4</v>
+      </c>
       <c r="U6" s="5"/>
       <c r="V6" s="5"/>
       <c r="X6" s="5">
@@ -1525,7 +1526,9 @@
       <c r="S7" s="5">
         <v>8.6</v>
       </c>
-      <c r="T7" s="5"/>
+      <c r="T7" s="5">
+        <v>10.9</v>
+      </c>
       <c r="U7" s="5"/>
       <c r="V7" s="5"/>
       <c r="X7" s="5">
@@ -1546,47 +1549,47 @@
       </c>
       <c r="AB7" s="5">
         <f>AB3*0.4</f>
-        <v>31.439999999999998</v>
+        <v>32.92</v>
       </c>
       <c r="AC7" s="5">
         <f>AC3*0.3</f>
-        <v>42.443999999999996</v>
+        <v>44.441999999999993</v>
       </c>
       <c r="AD7" s="5">
         <f>AD3*0.26</f>
-        <v>62.534159999999993</v>
+        <v>65.477879999999999</v>
       </c>
       <c r="AE7" s="5">
         <f>AE3*0.24</f>
-        <v>92.358143999999982</v>
+        <v>96.705791999999988</v>
       </c>
       <c r="AF7" s="5">
         <f>AF3*0.22</f>
-        <v>126.992448</v>
+        <v>132.97046399999999</v>
       </c>
       <c r="AG7" s="5">
         <f>AG3*0.2</f>
-        <v>167.399136</v>
+        <v>175.27924800000002</v>
       </c>
       <c r="AH7" s="5">
         <f>AH3*0.18</f>
-        <v>188.32402799999994</v>
+        <v>197.189154</v>
       </c>
       <c r="AI7" s="5">
         <f>AI3*0.17</f>
-        <v>213.43389839999998</v>
+        <v>223.48104120000002</v>
       </c>
       <c r="AJ7" s="5">
         <f>AJ3*0.16</f>
-        <v>231.01080767999994</v>
+        <v>241.88536224000001</v>
       </c>
       <c r="AK7" s="5">
         <f>AK3*0.15</f>
-        <v>238.22989541999993</v>
+        <v>249.44427981000001</v>
       </c>
       <c r="AL7" s="5">
         <f>AL3*0.14</f>
-        <v>233.4652975116</v>
+        <v>244.45539421380005</v>
       </c>
     </row>
     <row r="8" spans="2:38" x14ac:dyDescent="0.3">
@@ -1644,7 +1647,9 @@
       <c r="S8" s="5">
         <v>23.8</v>
       </c>
-      <c r="T8" s="5"/>
+      <c r="T8" s="5">
+        <v>48.1</v>
+      </c>
       <c r="U8" s="5"/>
       <c r="V8" s="5"/>
       <c r="X8" s="5">
@@ -1763,7 +1768,9 @@
       <c r="S9" s="5">
         <v>6.6</v>
       </c>
-      <c r="T9" s="5"/>
+      <c r="T9" s="5">
+        <v>10.6</v>
+      </c>
       <c r="U9" s="5"/>
       <c r="V9" s="5"/>
       <c r="X9" s="5">
@@ -1896,10 +1903,13 @@
         <v>84.2</v>
       </c>
       <c r="S10" s="5">
-        <f t="shared" ref="S10" si="8">SUM(S6:S9)</f>
+        <f t="shared" ref="S10:T10" si="8">SUM(S6:S9)</f>
         <v>79</v>
       </c>
-      <c r="T10" s="5"/>
+      <c r="T10" s="5">
+        <f t="shared" si="8"/>
+        <v>173</v>
+      </c>
       <c r="U10" s="5"/>
       <c r="V10" s="5"/>
       <c r="X10" s="5">
@@ -1920,47 +1930,47 @@
       </c>
       <c r="AB10" s="5">
         <f t="shared" ref="AB10:AL10" si="9">SUM(AB6:AB9)</f>
-        <v>299.24200000000002</v>
+        <v>300.72200000000004</v>
       </c>
       <c r="AC10" s="5">
         <f t="shared" si="9"/>
-        <v>342.90034000000003</v>
+        <v>344.89834000000002</v>
       </c>
       <c r="AD10" s="5">
         <f t="shared" si="9"/>
-        <v>384.22965080000012</v>
+        <v>387.1733708000001</v>
       </c>
       <c r="AE10" s="5">
         <f t="shared" si="9"/>
-        <v>430.01443626000014</v>
+        <v>434.36208426000007</v>
       </c>
       <c r="AF10" s="5">
         <f t="shared" si="9"/>
-        <v>478.84385961660007</v>
+        <v>484.8218756166001</v>
       </c>
       <c r="AG10" s="5">
         <f t="shared" si="9"/>
-        <v>533.11569522004208</v>
+        <v>540.99580722004214</v>
       </c>
       <c r="AH10" s="5">
         <f t="shared" si="9"/>
-        <v>568.51594242023339</v>
+        <v>577.38106842023353</v>
       </c>
       <c r="AI10" s="5">
         <f t="shared" si="9"/>
-        <v>608.73996996162691</v>
+        <v>618.78711276162699</v>
       </c>
       <c r="AJ10" s="5">
         <f t="shared" si="9"/>
-        <v>642.09981641399861</v>
+        <v>652.9743709739987</v>
       </c>
       <c r="AK10" s="5">
         <f t="shared" si="9"/>
-        <v>665.80205123074086</v>
+        <v>677.01643562074094</v>
       </c>
       <c r="AL10" s="5">
         <f t="shared" si="9"/>
-        <v>678.2537633708032</v>
+        <v>689.24386007300325</v>
       </c>
     </row>
     <row r="11" spans="2:38" s="1" customFormat="1" x14ac:dyDescent="0.3">
@@ -2032,10 +2042,13 @@
         <v>-77.5</v>
       </c>
       <c r="S11" s="8">
-        <f t="shared" ref="S11" si="11">S5-S10</f>
+        <f t="shared" ref="S11:T11" si="11">S5-S10</f>
         <v>-75.7</v>
       </c>
-      <c r="T11" s="8"/>
+      <c r="T11" s="8">
+        <f t="shared" si="11"/>
+        <v>-160.6</v>
+      </c>
       <c r="U11" s="8"/>
       <c r="V11" s="8"/>
       <c r="X11" s="8">
@@ -2056,47 +2069,47 @@
       </c>
       <c r="AB11" s="8">
         <f t="shared" ref="AB11:AL11" si="12">AB5-AB10</f>
-        <v>-259.94200000000001</v>
+        <v>-259.57200000000006</v>
       </c>
       <c r="AC11" s="8">
         <f t="shared" si="12"/>
-        <v>-270.74554000000001</v>
+        <v>-269.34694000000002</v>
       </c>
       <c r="AD11" s="8">
         <f t="shared" si="12"/>
-        <v>-259.16133080000014</v>
+        <v>-256.2176108000001</v>
       </c>
       <c r="AE11" s="8">
         <f t="shared" si="12"/>
-        <v>-229.90512426000015</v>
+        <v>-224.83286826000008</v>
       </c>
       <c r="AF11" s="8">
         <f t="shared" si="12"/>
-        <v>-167.13512361660008</v>
+        <v>-158.4398276166001</v>
       </c>
       <c r="AG11" s="8">
         <f t="shared" si="12"/>
-        <v>-64.398114420042134</v>
+        <v>-50.213912820042083</v>
       </c>
       <c r="AH11" s="8">
         <f t="shared" si="12"/>
-        <v>38.305925579766381</v>
+        <v>58.006205579766402</v>
       </c>
       <c r="AI11" s="8">
         <f t="shared" si="12"/>
-        <v>144.55614203837297</v>
+        <v>169.96950323837302</v>
       </c>
       <c r="AJ11" s="8">
         <f t="shared" si="12"/>
-        <v>253.06706334600108</v>
+        <v>284.3314077060013</v>
       </c>
       <c r="AK11" s="8">
         <f t="shared" si="12"/>
-        <v>334.76350953325903</v>
+        <v>370.64953958125909</v>
       </c>
       <c r="AL11" s="8">
         <f t="shared" si="12"/>
-        <v>389.0161681107968</v>
+        <v>428.26651347579684</v>
       </c>
     </row>
     <row r="12" spans="2:38" x14ac:dyDescent="0.3">
@@ -2154,7 +2167,9 @@
       <c r="S12" s="5">
         <v>-38.5</v>
       </c>
-      <c r="T12" s="5"/>
+      <c r="T12" s="5">
+        <v>39.6</v>
+      </c>
       <c r="U12" s="5"/>
       <c r="V12" s="5"/>
       <c r="X12" s="5">
@@ -2262,7 +2277,9 @@
       <c r="S13" s="5">
         <v>-4.9000000000000004</v>
       </c>
-      <c r="T13" s="5"/>
+      <c r="T13" s="5">
+        <v>-7.1</v>
+      </c>
       <c r="U13" s="5"/>
       <c r="V13" s="5"/>
       <c r="X13" s="5">
@@ -2381,7 +2398,9 @@
       <c r="S14" s="5">
         <v>-0.1</v>
       </c>
-      <c r="T14" s="5"/>
+      <c r="T14" s="5">
+        <v>-0.2</v>
+      </c>
       <c r="U14" s="5"/>
       <c r="V14" s="5"/>
       <c r="X14" s="5">
@@ -2503,10 +2522,13 @@
         <v>124.5</v>
       </c>
       <c r="S15" s="5">
-        <f t="shared" ref="S15" si="15">SUM(S12:S14)</f>
+        <f t="shared" ref="S15:T15" si="15">SUM(S12:S14)</f>
         <v>-43.5</v>
       </c>
-      <c r="T15" s="5"/>
+      <c r="T15" s="5">
+        <f t="shared" si="15"/>
+        <v>32.299999999999997</v>
+      </c>
       <c r="U15" s="5"/>
       <c r="V15" s="5"/>
       <c r="X15" s="5">
@@ -2639,10 +2661,13 @@
         <v>-202</v>
       </c>
       <c r="S16" s="8">
-        <f t="shared" ref="S16" si="18">S11-S15</f>
+        <f t="shared" ref="S16:T16" si="18">S11-S15</f>
         <v>-32.200000000000003</v>
       </c>
-      <c r="T16" s="8"/>
+      <c r="T16" s="8">
+        <f t="shared" si="18"/>
+        <v>-192.89999999999998</v>
+      </c>
       <c r="U16" s="8"/>
       <c r="V16" s="8"/>
       <c r="X16" s="8">
@@ -2663,47 +2688,47 @@
       </c>
       <c r="AB16" s="8">
         <f t="shared" ref="AB16:AL16" si="19">AB11-AB15</f>
-        <v>-241.196</v>
+        <v>-240.82600000000005</v>
       </c>
       <c r="AC16" s="8">
         <f t="shared" si="19"/>
-        <v>-251.43716000000001</v>
+        <v>-250.03856000000002</v>
       </c>
       <c r="AD16" s="8">
         <f t="shared" si="19"/>
-        <v>-239.27369940000014</v>
+        <v>-236.3299794000001</v>
       </c>
       <c r="AE16" s="8">
         <f t="shared" si="19"/>
-        <v>-209.42086391800015</v>
+        <v>-204.34860791800008</v>
       </c>
       <c r="AF16" s="8">
         <f t="shared" si="19"/>
-        <v>-146.03633546434008</v>
+        <v>-137.3410394643401</v>
       </c>
       <c r="AG16" s="8">
         <f t="shared" si="19"/>
-        <v>-42.666362623214333</v>
+        <v>-28.482161023214282</v>
       </c>
       <c r="AH16" s="8">
         <f t="shared" si="19"/>
-        <v>60.689629930499017</v>
+        <v>80.389909930499044</v>
       </c>
       <c r="AI16" s="8">
         <f t="shared" si="19"/>
-        <v>167.61135751962757</v>
+        <v>193.02471871962763</v>
       </c>
       <c r="AJ16" s="8">
         <f t="shared" si="19"/>
-        <v>276.81393529169333</v>
+        <v>308.07827965169355</v>
       </c>
       <c r="AK16" s="8">
         <f t="shared" si="19"/>
-        <v>359.22278763732203</v>
+        <v>395.10881768532209</v>
       </c>
       <c r="AL16" s="8">
         <f t="shared" si="19"/>
-        <v>414.20922455798171</v>
+        <v>453.45956992298176</v>
       </c>
     </row>
     <row r="17" spans="2:156" x14ac:dyDescent="0.3">
@@ -2761,7 +2786,9 @@
       <c r="S17" s="5">
         <v>0</v>
       </c>
-      <c r="T17" s="5"/>
+      <c r="T17" s="5">
+        <v>-15.3</v>
+      </c>
       <c r="U17" s="5"/>
       <c r="V17" s="5"/>
       <c r="X17" s="5">
@@ -2883,10 +2910,13 @@
         <v>-202</v>
       </c>
       <c r="S18" s="8">
-        <f t="shared" ref="S18" si="21">S16-S17</f>
+        <f t="shared" ref="S18:T18" si="21">S16-S17</f>
         <v>-32.200000000000003</v>
       </c>
-      <c r="T18" s="8"/>
+      <c r="T18" s="8">
+        <f t="shared" si="21"/>
+        <v>-177.59999999999997</v>
+      </c>
       <c r="U18" s="8"/>
       <c r="V18" s="8"/>
       <c r="X18" s="8">
@@ -2907,519 +2937,519 @@
       </c>
       <c r="AB18" s="8">
         <f>AB16-AB17</f>
-        <v>-241.196</v>
+        <v>-240.82600000000005</v>
       </c>
       <c r="AC18" s="8">
         <f t="shared" ref="AC18:AL18" si="22">AC16-AC17</f>
-        <v>-251.43716000000001</v>
+        <v>-250.03856000000002</v>
       </c>
       <c r="AD18" s="8">
         <f t="shared" si="22"/>
-        <v>-239.27369940000014</v>
+        <v>-236.3299794000001</v>
       </c>
       <c r="AE18" s="8">
         <f t="shared" si="22"/>
-        <v>-209.42086391800015</v>
+        <v>-204.34860791800008</v>
       </c>
       <c r="AF18" s="8">
         <f t="shared" si="22"/>
-        <v>-146.03633546434008</v>
+        <v>-137.3410394643401</v>
       </c>
       <c r="AG18" s="8">
         <f t="shared" si="22"/>
-        <v>-42.666362623214333</v>
+        <v>-28.482161023214282</v>
       </c>
       <c r="AH18" s="8">
         <f t="shared" si="22"/>
-        <v>60.689629930499017</v>
+        <v>80.389909930499044</v>
       </c>
       <c r="AI18" s="8">
         <f t="shared" si="22"/>
-        <v>167.61135751962757</v>
+        <v>193.02471871962763</v>
       </c>
       <c r="AJ18" s="8">
         <f t="shared" si="22"/>
-        <v>276.81393529169333</v>
+        <v>308.07827965169355</v>
       </c>
       <c r="AK18" s="8">
         <f t="shared" si="22"/>
-        <v>359.22278763732203</v>
+        <v>395.10881768532209</v>
       </c>
       <c r="AL18" s="8">
         <f t="shared" si="22"/>
-        <v>414.20922455798171</v>
+        <v>453.45956992298176</v>
       </c>
       <c r="AM18" s="1">
         <f>AL18*(1+$AP$23)</f>
-        <v>410.0671323124019</v>
+        <v>448.92497422375192</v>
       </c>
       <c r="AN18" s="1">
         <f t="shared" ref="AN18:CY18" si="23">AM18*(1+$AP$23)</f>
-        <v>405.96646098927789</v>
+        <v>444.4357244815144</v>
       </c>
       <c r="AO18" s="1">
         <f t="shared" si="23"/>
-        <v>401.90679637938513</v>
+        <v>439.99136723669926</v>
       </c>
       <c r="AP18" s="1">
         <f t="shared" si="23"/>
-        <v>397.88772841559125</v>
+        <v>435.59145356433226</v>
       </c>
       <c r="AQ18" s="1">
         <f t="shared" si="23"/>
-        <v>393.90885113143531</v>
+        <v>431.23553902868895</v>
       </c>
       <c r="AR18" s="1">
         <f t="shared" si="23"/>
-        <v>389.96976262012095</v>
+        <v>426.92318363840207</v>
       </c>
       <c r="AS18" s="1">
         <f t="shared" si="23"/>
-        <v>386.07006499391974</v>
+        <v>422.65395180201801</v>
       </c>
       <c r="AT18" s="1">
         <f t="shared" si="23"/>
-        <v>382.20936434398055</v>
+        <v>418.42741228399785</v>
       </c>
       <c r="AU18" s="1">
         <f t="shared" si="23"/>
-        <v>378.38727070054074</v>
+        <v>414.24313816115784</v>
       </c>
       <c r="AV18" s="1">
         <f t="shared" si="23"/>
-        <v>374.60339799353534</v>
+        <v>410.10070677954627</v>
       </c>
       <c r="AW18" s="1">
         <f t="shared" si="23"/>
-        <v>370.85736401359998</v>
+        <v>405.99969971175079</v>
       </c>
       <c r="AX18" s="1">
         <f t="shared" si="23"/>
-        <v>367.14879037346395</v>
+        <v>401.93970271463326</v>
       </c>
       <c r="AY18" s="1">
         <f t="shared" si="23"/>
-        <v>363.4773024697293</v>
+        <v>397.92030568748692</v>
       </c>
       <c r="AZ18" s="1">
         <f t="shared" si="23"/>
-        <v>359.84252944503197</v>
+        <v>393.94110263061202</v>
       </c>
       <c r="BA18" s="1">
         <f t="shared" si="23"/>
-        <v>356.24410415058162</v>
+        <v>390.0016916043059</v>
       </c>
       <c r="BB18" s="1">
         <f t="shared" si="23"/>
-        <v>352.68166310907583</v>
+        <v>386.10167468826285</v>
       </c>
       <c r="BC18" s="1">
         <f t="shared" si="23"/>
-        <v>349.15484647798507</v>
+        <v>382.24065794138022</v>
       </c>
       <c r="BD18" s="1">
         <f t="shared" si="23"/>
-        <v>345.66329801320524</v>
+        <v>378.41825136196644</v>
       </c>
       <c r="BE18" s="1">
         <f t="shared" si="23"/>
-        <v>342.20666503307319</v>
+        <v>374.63406884834677</v>
       </c>
       <c r="BF18" s="1">
         <f t="shared" si="23"/>
-        <v>338.78459838274244</v>
+        <v>370.88772815986329</v>
       </c>
       <c r="BG18" s="1">
         <f t="shared" si="23"/>
-        <v>335.396752398915</v>
+        <v>367.17885087826465</v>
       </c>
       <c r="BH18" s="1">
         <f t="shared" si="23"/>
-        <v>332.04278487492587</v>
+        <v>363.50706236948201</v>
       </c>
       <c r="BI18" s="1">
         <f t="shared" si="23"/>
-        <v>328.72235702617661</v>
+        <v>359.87199174578717</v>
       </c>
       <c r="BJ18" s="1">
         <f t="shared" si="23"/>
-        <v>325.43513345591487</v>
+        <v>356.27327182832931</v>
       </c>
       <c r="BK18" s="1">
         <f t="shared" si="23"/>
-        <v>322.18078212135572</v>
+        <v>352.710539110046</v>
       </c>
       <c r="BL18" s="1">
         <f t="shared" si="23"/>
-        <v>318.95897430014213</v>
+        <v>349.18343371894554</v>
       </c>
       <c r="BM18" s="1">
         <f t="shared" si="23"/>
-        <v>315.76938455714071</v>
+        <v>345.69159938175608</v>
       </c>
       <c r="BN18" s="1">
         <f t="shared" si="23"/>
-        <v>312.61169071156928</v>
+        <v>342.2346833879385</v>
       </c>
       <c r="BO18" s="1">
         <f t="shared" si="23"/>
-        <v>309.48557380445357</v>
+        <v>338.81233655405913</v>
       </c>
       <c r="BP18" s="1">
         <f t="shared" si="23"/>
-        <v>306.39071806640902</v>
+        <v>335.42421318851854</v>
       </c>
       <c r="BQ18" s="1">
         <f t="shared" si="23"/>
-        <v>303.32681088574492</v>
+        <v>332.06997105663334</v>
       </c>
       <c r="BR18" s="1">
         <f t="shared" si="23"/>
-        <v>300.29354277688748</v>
+        <v>328.74927134606702</v>
       </c>
       <c r="BS18" s="1">
         <f t="shared" si="23"/>
-        <v>297.2906073491186</v>
+        <v>325.46177863260635</v>
       </c>
       <c r="BT18" s="1">
         <f t="shared" si="23"/>
-        <v>294.31770127562743</v>
+        <v>322.20716084628026</v>
       </c>
       <c r="BU18" s="1">
         <f t="shared" si="23"/>
-        <v>291.37452426287115</v>
+        <v>318.98508923781748</v>
       </c>
       <c r="BV18" s="1">
         <f t="shared" si="23"/>
-        <v>288.46077902024246</v>
+        <v>315.79523834543932</v>
       </c>
       <c r="BW18" s="1">
         <f t="shared" si="23"/>
-        <v>285.57617123004002</v>
+        <v>312.6372859619849</v>
       </c>
       <c r="BX18" s="1">
         <f t="shared" si="23"/>
-        <v>282.7204095177396</v>
+        <v>309.51091310236507</v>
       </c>
       <c r="BY18" s="1">
         <f t="shared" si="23"/>
-        <v>279.89320542256218</v>
+        <v>306.4158039713414</v>
       </c>
       <c r="BZ18" s="1">
         <f t="shared" si="23"/>
-        <v>277.09427336833653</v>
+        <v>303.35164593162801</v>
       </c>
       <c r="CA18" s="1">
         <f t="shared" si="23"/>
-        <v>274.32333063465319</v>
+        <v>300.31812947231174</v>
       </c>
       <c r="CB18" s="1">
         <f t="shared" si="23"/>
-        <v>271.58009732830664</v>
+        <v>297.31494817758863</v>
       </c>
       <c r="CC18" s="1">
         <f t="shared" si="23"/>
-        <v>268.86429635502355</v>
+        <v>294.34179869581277</v>
       </c>
       <c r="CD18" s="1">
         <f t="shared" si="23"/>
-        <v>266.1756533914733</v>
+        <v>291.39838070885463</v>
       </c>
       <c r="CE18" s="1">
         <f t="shared" si="23"/>
-        <v>263.51389685755856</v>
+        <v>288.4843969017661</v>
       </c>
       <c r="CF18" s="1">
         <f t="shared" si="23"/>
-        <v>260.87875788898299</v>
+        <v>285.59955293274845</v>
       </c>
       <c r="CG18" s="1">
         <f t="shared" si="23"/>
-        <v>258.26997031009313</v>
+        <v>282.74355740342094</v>
       </c>
       <c r="CH18" s="1">
         <f t="shared" si="23"/>
-        <v>255.6872706069922</v>
+        <v>279.91612182938673</v>
       </c>
       <c r="CI18" s="1">
         <f t="shared" si="23"/>
-        <v>253.13039790092228</v>
+        <v>277.11696061109285</v>
       </c>
       <c r="CJ18" s="1">
         <f t="shared" si="23"/>
-        <v>250.59909392191304</v>
+        <v>274.34579100498189</v>
       </c>
       <c r="CK18" s="1">
         <f t="shared" si="23"/>
-        <v>248.09310298269389</v>
+        <v>271.60233309493208</v>
       </c>
       <c r="CL18" s="1">
         <f t="shared" si="23"/>
-        <v>245.61217195286696</v>
+        <v>268.88630976398275</v>
       </c>
       <c r="CM18" s="1">
         <f t="shared" si="23"/>
-        <v>243.15605023333828</v>
+        <v>266.1974466663429</v>
       </c>
       <c r="CN18" s="1">
         <f t="shared" si="23"/>
-        <v>240.72448973100489</v>
+        <v>263.53547219967948</v>
       </c>
       <c r="CO18" s="1">
         <f t="shared" si="23"/>
-        <v>238.31724483369484</v>
+        <v>260.90011747768267</v>
       </c>
       <c r="CP18" s="1">
         <f t="shared" si="23"/>
-        <v>235.93407238535789</v>
+        <v>258.29111630290583</v>
       </c>
       <c r="CQ18" s="1">
         <f t="shared" si="23"/>
-        <v>233.5747316615043</v>
+        <v>255.70820513987678</v>
       </c>
       <c r="CR18" s="1">
         <f t="shared" si="23"/>
-        <v>231.23898434488925</v>
+        <v>253.15112308847802</v>
       </c>
       <c r="CS18" s="1">
         <f t="shared" si="23"/>
-        <v>228.92659450144035</v>
+        <v>250.61961185759324</v>
       </c>
       <c r="CT18" s="1">
         <f t="shared" si="23"/>
-        <v>226.63732855642596</v>
+        <v>248.11341573901731</v>
       </c>
       <c r="CU18" s="1">
         <f t="shared" si="23"/>
-        <v>224.37095527086169</v>
+        <v>245.63228158162713</v>
       </c>
       <c r="CV18" s="1">
         <f t="shared" si="23"/>
-        <v>222.12724571815306</v>
+        <v>243.17595876581086</v>
       </c>
       <c r="CW18" s="1">
         <f t="shared" si="23"/>
-        <v>219.90597326097154</v>
+        <v>240.74419917815274</v>
       </c>
       <c r="CX18" s="1">
         <f t="shared" si="23"/>
-        <v>217.70691352836181</v>
+        <v>238.33675718637122</v>
       </c>
       <c r="CY18" s="1">
         <f t="shared" si="23"/>
-        <v>215.52984439307818</v>
+        <v>235.9533896145075</v>
       </c>
       <c r="CZ18" s="1">
         <f t="shared" ref="CZ18:EZ18" si="24">CY18*(1+$AP$23)</f>
-        <v>213.3745459491474</v>
+        <v>233.59385571836242</v>
       </c>
       <c r="DA18" s="1">
         <f t="shared" si="24"/>
-        <v>211.24080048965592</v>
+        <v>231.2579171611788</v>
       </c>
       <c r="DB18" s="1">
         <f t="shared" si="24"/>
-        <v>209.12839248475936</v>
+        <v>228.94533798956701</v>
       </c>
       <c r="DC18" s="1">
         <f t="shared" si="24"/>
-        <v>207.03710855991176</v>
+        <v>226.65588460967135</v>
       </c>
       <c r="DD18" s="1">
         <f t="shared" si="24"/>
-        <v>204.96673747431265</v>
+        <v>224.38932576357462</v>
       </c>
       <c r="DE18" s="1">
         <f t="shared" si="24"/>
-        <v>202.91707009956951</v>
+        <v>222.14543250593886</v>
       </c>
       <c r="DF18" s="1">
         <f t="shared" si="24"/>
-        <v>200.88789939857381</v>
+        <v>219.92397818087946</v>
       </c>
       <c r="DG18" s="1">
         <f t="shared" si="24"/>
-        <v>198.87902040458806</v>
+        <v>217.72473839907067</v>
       </c>
       <c r="DH18" s="1">
         <f t="shared" si="24"/>
-        <v>196.89023020054219</v>
+        <v>215.54749101507997</v>
       </c>
       <c r="DI18" s="1">
         <f t="shared" si="24"/>
-        <v>194.92132789853676</v>
+        <v>213.39201610492916</v>
       </c>
       <c r="DJ18" s="1">
         <f t="shared" si="24"/>
-        <v>192.97211461955138</v>
+        <v>211.25809594387985</v>
       </c>
       <c r="DK18" s="1">
         <f t="shared" si="24"/>
-        <v>191.04239347335587</v>
+        <v>209.14551498444106</v>
       </c>
       <c r="DL18" s="1">
         <f t="shared" si="24"/>
-        <v>189.13196953862231</v>
+        <v>207.05405983459664</v>
       </c>
       <c r="DM18" s="1">
         <f t="shared" si="24"/>
-        <v>187.2406498432361</v>
+        <v>204.98351923625069</v>
       </c>
       <c r="DN18" s="1">
         <f t="shared" si="24"/>
-        <v>185.36824334480374</v>
+        <v>202.93368404388818</v>
       </c>
       <c r="DO18" s="1">
         <f t="shared" si="24"/>
-        <v>183.51456091135572</v>
+        <v>200.9043472034493</v>
       </c>
       <c r="DP18" s="1">
         <f t="shared" si="24"/>
-        <v>181.67941530224215</v>
+        <v>198.8953037314148</v>
       </c>
       <c r="DQ18" s="1">
         <f t="shared" si="24"/>
-        <v>179.86262114921973</v>
+        <v>196.90635069410064</v>
       </c>
       <c r="DR18" s="1">
         <f t="shared" si="24"/>
-        <v>178.06399493772753</v>
+        <v>194.93728718715963</v>
       </c>
       <c r="DS18" s="1">
         <f t="shared" si="24"/>
-        <v>176.28335498835025</v>
+        <v>192.98791431528804</v>
       </c>
       <c r="DT18" s="1">
         <f t="shared" si="24"/>
-        <v>174.52052143846674</v>
+        <v>191.05803517213516</v>
       </c>
       <c r="DU18" s="1">
         <f t="shared" si="24"/>
-        <v>172.77531622408208</v>
+        <v>189.1474548204138</v>
       </c>
       <c r="DV18" s="1">
         <f t="shared" si="24"/>
-        <v>171.04756306184126</v>
+        <v>187.25598027220965</v>
       </c>
       <c r="DW18" s="1">
         <f t="shared" si="24"/>
-        <v>169.33708743122284</v>
+        <v>185.38342046948756</v>
       </c>
       <c r="DX18" s="1">
         <f t="shared" si="24"/>
-        <v>167.64371655691062</v>
+        <v>183.52958626479267</v>
       </c>
       <c r="DY18" s="1">
         <f t="shared" si="24"/>
-        <v>165.96727939134152</v>
+        <v>181.69429040214473</v>
       </c>
       <c r="DZ18" s="1">
         <f t="shared" si="24"/>
-        <v>164.30760659742811</v>
+        <v>179.87734749812327</v>
       </c>
       <c r="EA18" s="1">
         <f t="shared" si="24"/>
-        <v>162.66453053145383</v>
+        <v>178.07857402314204</v>
       </c>
       <c r="EB18" s="1">
         <f t="shared" si="24"/>
-        <v>161.03788522613928</v>
+        <v>176.29778828291063</v>
       </c>
       <c r="EC18" s="1">
         <f t="shared" si="24"/>
-        <v>159.42750637387789</v>
+        <v>174.53481040008151</v>
       </c>
       <c r="ED18" s="1">
         <f t="shared" si="24"/>
-        <v>157.8332313101391</v>
+        <v>172.7894622960807</v>
       </c>
       <c r="EE18" s="1">
         <f t="shared" si="24"/>
-        <v>156.25489899703771</v>
+        <v>171.0615676731199</v>
       </c>
       <c r="EF18" s="1">
         <f t="shared" si="24"/>
-        <v>154.69235000706735</v>
+        <v>169.35095199638869</v>
       </c>
       <c r="EG18" s="1">
         <f t="shared" si="24"/>
-        <v>153.14542650699667</v>
+        <v>167.65744247642479</v>
       </c>
       <c r="EH18" s="1">
         <f t="shared" si="24"/>
-        <v>151.61397224192669</v>
+        <v>165.98086805166054</v>
       </c>
       <c r="EI18" s="1">
         <f t="shared" si="24"/>
-        <v>150.09783251950742</v>
+        <v>164.32105937114392</v>
       </c>
       <c r="EJ18" s="1">
         <f t="shared" si="24"/>
-        <v>148.59685419431236</v>
+        <v>162.67784877743247</v>
       </c>
       <c r="EK18" s="1">
         <f t="shared" si="24"/>
-        <v>147.11088565236923</v>
+        <v>161.05107028965816</v>
       </c>
       <c r="EL18" s="1">
         <f t="shared" si="24"/>
-        <v>145.63977679584553</v>
+        <v>159.44055958676157</v>
       </c>
       <c r="EM18" s="1">
         <f t="shared" si="24"/>
-        <v>144.18337902788707</v>
+        <v>157.84615399089395</v>
       </c>
       <c r="EN18" s="1">
         <f t="shared" si="24"/>
-        <v>142.74154523760819</v>
+        <v>156.26769245098501</v>
       </c>
       <c r="EO18" s="1">
         <f t="shared" si="24"/>
-        <v>141.3141297852321</v>
+        <v>154.70501552647517</v>
       </c>
       <c r="EP18" s="1">
         <f t="shared" si="24"/>
-        <v>139.90098848737978</v>
+        <v>153.15796537121042</v>
       </c>
       <c r="EQ18" s="1">
         <f t="shared" si="24"/>
-        <v>138.50197860250597</v>
+        <v>151.62638571749832</v>
       </c>
       <c r="ER18" s="1">
         <f t="shared" si="24"/>
-        <v>137.11695881648092</v>
+        <v>150.11012186032335</v>
       </c>
       <c r="ES18" s="1">
         <f t="shared" si="24"/>
-        <v>135.74578922831611</v>
+        <v>148.60902064172012</v>
       </c>
       <c r="ET18" s="1">
         <f t="shared" si="24"/>
-        <v>134.38833133603296</v>
+        <v>147.12293043530292</v>
       </c>
       <c r="EU18" s="1">
         <f t="shared" si="24"/>
-        <v>133.04444802267264</v>
+        <v>145.6517011309499</v>
       </c>
       <c r="EV18" s="1">
         <f t="shared" si="24"/>
-        <v>131.71400354244591</v>
+        <v>144.1951841196404</v>
       </c>
       <c r="EW18" s="1">
         <f t="shared" si="24"/>
-        <v>130.39686350702144</v>
+        <v>142.75323227844399</v>
       </c>
       <c r="EX18" s="1">
         <f t="shared" si="24"/>
-        <v>129.09289487195122</v>
+        <v>141.32569995565956</v>
       </c>
       <c r="EY18" s="1">
         <f t="shared" si="24"/>
-        <v>127.80196592323171</v>
+        <v>139.91244295610295</v>
       </c>
       <c r="EZ18" s="1">
         <f t="shared" si="24"/>
-        <v>126.52394626399939</v>
+        <v>138.51331852654192</v>
       </c>
     </row>
     <row r="19" spans="2:156" x14ac:dyDescent="0.3">
@@ -3494,7 +3524,10 @@
         <f t="shared" si="25"/>
         <v>216.4</v>
       </c>
-      <c r="T19" s="5"/>
+      <c r="T19" s="5">
+        <f>296.8</f>
+        <v>296.8</v>
+      </c>
       <c r="U19" s="5"/>
       <c r="V19" s="5"/>
       <c r="X19" s="5">
@@ -3514,48 +3547,48 @@
         <v>216.4</v>
       </c>
       <c r="AB19" s="5">
-        <f>216.4</f>
-        <v>216.4</v>
+        <f t="shared" ref="AB19:AL19" si="26">296.8</f>
+        <v>296.8</v>
       </c>
       <c r="AC19" s="5">
-        <f t="shared" ref="AC19:AL19" si="26">216.4</f>
-        <v>216.4</v>
+        <f t="shared" si="26"/>
+        <v>296.8</v>
       </c>
       <c r="AD19" s="5">
         <f t="shared" si="26"/>
-        <v>216.4</v>
+        <v>296.8</v>
       </c>
       <c r="AE19" s="5">
         <f t="shared" si="26"/>
-        <v>216.4</v>
+        <v>296.8</v>
       </c>
       <c r="AF19" s="5">
         <f t="shared" si="26"/>
-        <v>216.4</v>
+        <v>296.8</v>
       </c>
       <c r="AG19" s="5">
         <f t="shared" si="26"/>
-        <v>216.4</v>
+        <v>296.8</v>
       </c>
       <c r="AH19" s="5">
         <f t="shared" si="26"/>
-        <v>216.4</v>
+        <v>296.8</v>
       </c>
       <c r="AI19" s="5">
         <f t="shared" si="26"/>
-        <v>216.4</v>
+        <v>296.8</v>
       </c>
       <c r="AJ19" s="5">
         <f t="shared" si="26"/>
-        <v>216.4</v>
+        <v>296.8</v>
       </c>
       <c r="AK19" s="5">
         <f t="shared" si="26"/>
-        <v>216.4</v>
+        <v>296.8</v>
       </c>
       <c r="AL19" s="5">
         <f t="shared" si="26"/>
-        <v>216.4</v>
+        <v>296.8</v>
       </c>
     </row>
     <row r="20" spans="2:156" x14ac:dyDescent="0.3">
@@ -3627,10 +3660,13 @@
         <v>-0.93345656192236592</v>
       </c>
       <c r="S20" s="7">
-        <f t="shared" ref="S20" si="28">S18/S19</f>
+        <f t="shared" ref="S20:T20" si="28">S18/S19</f>
         <v>-0.1487985212569316</v>
       </c>
-      <c r="T20" s="7"/>
+      <c r="T20" s="7">
+        <f t="shared" si="28"/>
+        <v>-0.59838274932614544</v>
+      </c>
       <c r="U20" s="7"/>
       <c r="V20" s="7"/>
       <c r="X20" s="7">
@@ -3651,47 +3687,47 @@
       </c>
       <c r="AB20" s="7">
         <f>AB18/AB19</f>
-        <v>-1.1145841035120148</v>
+        <v>-0.81140835579514836</v>
       </c>
       <c r="AC20" s="7">
         <f t="shared" ref="AC20:AL20" si="29">AC18/AC19</f>
-        <v>-1.1619092421441775</v>
+        <v>-0.84244797843665775</v>
       </c>
       <c r="AD20" s="7">
         <f t="shared" si="29"/>
-        <v>-1.1057010138632168</v>
+        <v>-0.79626003840970383</v>
       </c>
       <c r="AE20" s="7">
         <f t="shared" si="29"/>
-        <v>-0.96774890904805977</v>
+        <v>-0.68850609136792473</v>
       </c>
       <c r="AF20" s="7">
         <f t="shared" si="29"/>
-        <v>-0.67484443375388203</v>
+        <v>-0.46273935129494642</v>
       </c>
       <c r="AG20" s="7">
         <f t="shared" si="29"/>
-        <v>-0.19716433744553757</v>
+        <v>-9.5964154390883696E-2</v>
       </c>
       <c r="AH20" s="7">
         <f t="shared" si="29"/>
-        <v>0.28045115494685313</v>
+        <v>0.27085549167957895</v>
       </c>
       <c r="AI20" s="7">
         <f t="shared" si="29"/>
-        <v>0.77454416598718845</v>
+        <v>0.65035282587475618</v>
       </c>
       <c r="AJ20" s="7">
         <f t="shared" si="29"/>
-        <v>1.2791771501464571</v>
+        <v>1.0379995945137923</v>
       </c>
       <c r="AK20" s="7">
         <f t="shared" si="29"/>
-        <v>1.6599943975846674</v>
+        <v>1.3312291700987942</v>
       </c>
       <c r="AL20" s="7">
         <f t="shared" si="29"/>
-        <v>1.9140906864971428</v>
+        <v>1.5278287396326877</v>
       </c>
     </row>
     <row r="22" spans="2:156" s="1" customFormat="1" x14ac:dyDescent="0.3">
@@ -3756,7 +3792,7 @@
       </c>
       <c r="T22" s="9">
         <f t="shared" si="31"/>
-        <v>0.49122807017543857</v>
+        <v>0.8157894736842104</v>
       </c>
       <c r="U22" s="9">
         <f t="shared" si="31"/>
@@ -3781,11 +3817,11 @@
       </c>
       <c r="AB22" s="9">
         <f t="shared" si="32"/>
-        <v>0.82366589327146178</v>
+        <v>0.90951276102088197</v>
       </c>
       <c r="AC22" s="9">
         <f t="shared" si="32"/>
-        <v>0.8</v>
+        <v>0.79999999999999982</v>
       </c>
       <c r="AD22" s="9">
         <f t="shared" si="32"/>
@@ -3797,7 +3833,7 @@
       </c>
       <c r="AF22" s="9">
         <f t="shared" si="32"/>
-        <v>0.5</v>
+        <v>0.50000000000000022</v>
       </c>
       <c r="AG22" s="9">
         <f t="shared" si="32"/>
@@ -3898,7 +3934,7 @@
       </c>
       <c r="T23" s="10">
         <f t="shared" si="34"/>
-        <v>0.52</v>
+        <v>0.59903381642512077</v>
       </c>
       <c r="U23" s="10">
         <f t="shared" si="34"/>
@@ -4037,7 +4073,7 @@
       </c>
       <c r="T24" s="10">
         <f t="shared" si="38"/>
-        <v>-1</v>
+        <v>2.3141025641025643</v>
       </c>
       <c r="U24" s="10">
         <f t="shared" si="38"/>
@@ -4185,7 +4221,7 @@
       </c>
       <c r="T25" s="10">
         <f t="shared" si="41"/>
-        <v>0</v>
+        <v>0.52657004830917875</v>
       </c>
       <c r="U25" s="10">
         <f t="shared" si="41"/>
@@ -4229,11 +4265,11 @@
       </c>
       <c r="AF25" s="10">
         <f t="shared" si="43"/>
-        <v>0.22</v>
+        <v>0.21999999999999997</v>
       </c>
       <c r="AG25" s="10">
         <f t="shared" si="43"/>
-        <v>0.20000000000000004</v>
+        <v>0.2</v>
       </c>
       <c r="AH25" s="10">
         <f t="shared" si="43"/>
@@ -4260,7 +4296,7 @@
       </c>
       <c r="AP25" s="5">
         <f>NPV(AP24,AA18:EZ18)</f>
-        <v>851.43980610094263</v>
+        <v>1071.9648925424406</v>
       </c>
     </row>
     <row r="26" spans="2:156" x14ac:dyDescent="0.3">
@@ -4325,7 +4361,7 @@
       </c>
       <c r="T26" s="10">
         <f t="shared" si="45"/>
-        <v>-1</v>
+        <v>2.6717557251908399</v>
       </c>
       <c r="U26" s="10">
         <f t="shared" si="45"/>
@@ -4397,7 +4433,7 @@
       </c>
       <c r="AP26" s="5">
         <f>Main!D8</f>
-        <v>697.19999999999993</v>
+        <v>655.9</v>
       </c>
     </row>
     <row r="27" spans="2:156" x14ac:dyDescent="0.3">
@@ -4462,7 +4498,7 @@
       </c>
       <c r="T27" s="10">
         <f t="shared" si="48"/>
-        <v>-1</v>
+        <v>1.4651162790697674</v>
       </c>
       <c r="U27" s="10">
         <f t="shared" si="48"/>
@@ -4534,7 +4570,7 @@
       </c>
       <c r="AP27" s="5">
         <f>AP25+AP26</f>
-        <v>1548.6398061009427</v>
+        <v>1727.8648925424404</v>
       </c>
     </row>
     <row r="28" spans="2:156" x14ac:dyDescent="0.3">
@@ -4611,7 +4647,7 @@
       </c>
       <c r="T28" s="10">
         <f t="shared" si="51"/>
-        <v>0</v>
+        <v>-7.7584541062801931</v>
       </c>
       <c r="U28" s="10">
         <f t="shared" si="51"/>
@@ -4639,54 +4675,54 @@
       </c>
       <c r="AB28" s="10">
         <f t="shared" si="53"/>
-        <v>-3.3071501272264636</v>
+        <v>-3.1539732685297701</v>
       </c>
       <c r="AC28" s="10">
         <f t="shared" si="53"/>
-        <v>-1.91366652530393</v>
+        <v>-1.8181918455515056</v>
       </c>
       <c r="AD28" s="10">
         <f t="shared" si="53"/>
-        <v>-1.0775222055913127</v>
+        <v>-1.0173905875999656</v>
       </c>
       <c r="AE28" s="10">
         <f t="shared" si="53"/>
-        <v>-0.59742679348775185</v>
+        <v>-0.55797990240750028</v>
       </c>
       <c r="AF28" s="10">
         <f t="shared" si="53"/>
-        <v>-0.28954262851639823</v>
+        <v>-0.26213913245916043</v>
       </c>
       <c r="AG28" s="10">
         <f t="shared" si="53"/>
-        <v>-7.69396019105405E-2</v>
+        <v>-5.7295901703140674E-2</v>
       </c>
       <c r="AH28" s="10">
         <f t="shared" si="53"/>
-        <v>3.6612782115928139E-2</v>
+        <v>5.2949753029306837E-2</v>
       </c>
       <c r="AI28" s="10">
         <f t="shared" si="53"/>
-        <v>0.11513889935359682</v>
+        <v>0.12929425867791872</v>
       </c>
       <c r="AJ28" s="10">
         <f t="shared" si="53"/>
-        <v>0.17527634547492088</v>
+        <v>0.18807680138917118</v>
       </c>
       <c r="AK28" s="10">
         <f t="shared" si="53"/>
-        <v>0.21078180108949177</v>
+        <v>0.22288517090685361</v>
       </c>
       <c r="AL28" s="10">
         <f t="shared" si="53"/>
-        <v>0.23327776811371947</v>
+        <v>0.24526892556182686</v>
       </c>
       <c r="AO28" t="s">
         <v>57</v>
       </c>
       <c r="AP28" s="4">
         <f>AP27/AL19</f>
-        <v>7.1563761834609183</v>
+        <v>5.821647212070217</v>
       </c>
     </row>
     <row r="29" spans="2:156" x14ac:dyDescent="0.3">
@@ -4761,9 +4797,9 @@
         <f t="shared" ref="S29:V29" si="55">S17/S16</f>
         <v>0</v>
       </c>
-      <c r="T29" s="10" t="e">
+      <c r="T29" s="10">
         <f t="shared" si="55"/>
-        <v>#DIV/0!</v>
+        <v>7.931570762052878E-2</v>
       </c>
       <c r="U29" s="10" t="e">
         <f t="shared" si="55"/>
@@ -4838,7 +4874,7 @@
       </c>
       <c r="AP29" s="4">
         <f>Main!D3</f>
-        <v>47.13</v>
+        <v>39.86</v>
       </c>
     </row>
     <row r="30" spans="2:156" x14ac:dyDescent="0.3">
@@ -4915,7 +4951,7 @@
       </c>
       <c r="T30" s="10">
         <f t="shared" si="59"/>
-        <v>0</v>
+        <v>-8.5797101449275353</v>
       </c>
       <c r="U30" s="10">
         <f t="shared" si="59"/>
@@ -4943,54 +4979,54 @@
       </c>
       <c r="AB30" s="10">
         <f t="shared" si="61"/>
-        <v>-3.0686513994910944</v>
+        <v>-2.926196840826246</v>
       </c>
       <c r="AC30" s="10">
         <f t="shared" si="61"/>
-        <v>-1.7771922533220246</v>
+        <v>-1.6878531119211559</v>
       </c>
       <c r="AD30" s="10">
         <f t="shared" si="61"/>
-        <v>-0.99483485256698168</v>
+        <v>-0.93842064898863609</v>
       </c>
       <c r="AE30" s="10">
         <f t="shared" si="61"/>
-        <v>-0.54419680997833875</v>
+        <v>-0.50714300442645699</v>
       </c>
       <c r="AF30" s="10">
         <f t="shared" si="61"/>
-        <v>-0.25299137317326792</v>
+        <v>-0.22723112917884397</v>
       </c>
       <c r="AG30" s="10">
         <f t="shared" si="61"/>
-        <v>-5.0975606735765157E-2</v>
+        <v>-3.249918213160554E-2</v>
       </c>
       <c r="AH30" s="10">
         <f t="shared" si="61"/>
-        <v>5.8007114139943021E-2</v>
+        <v>7.3382249956251783E-2</v>
       </c>
       <c r="AI30" s="10">
         <f t="shared" si="61"/>
-        <v>0.13350236767420959</v>
+        <v>0.14683215187354648</v>
       </c>
       <c r="AJ30" s="10">
         <f t="shared" si="61"/>
-        <v>0.191723625796861</v>
+        <v>0.20378465355568995</v>
       </c>
       <c r="AK30" s="10">
         <f t="shared" si="61"/>
-        <v>0.22618243630003568</v>
+        <v>0.23759343248095752</v>
       </c>
       <c r="AL30" s="10">
         <f t="shared" si="61"/>
-        <v>0.24838505789168164</v>
+        <v>0.25969702977261455</v>
       </c>
       <c r="AO30" s="1" t="s">
         <v>59</v>
       </c>
       <c r="AP30" s="9">
         <f>AP28/AP29-1</f>
-        <v>-0.84815666913938215</v>
+        <v>-0.85394763642573468</v>
       </c>
     </row>
     <row r="31" spans="2:156" x14ac:dyDescent="0.3">

--- a/Financial Analysis/IONQ.xlsx
+++ b/Financial Analysis/IONQ.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\antos\Documents\GitHub\FinanceModels\Financial Analysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8D6AE02D-B86E-4A9B-928B-BC274672CF1A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{23D3E308-2462-4805-BB64-901D9BEC98E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{054FC3C2-46E6-4A64-A90B-FD32B5955AC0}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{054FC3C2-46E6-4A64-A90B-FD32B5955AC0}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>
@@ -749,14 +749,14 @@
         <v>1</v>
       </c>
       <c r="D3" s="4">
-        <v>39.86</v>
+        <v>75.069999999999993</v>
       </c>
       <c r="E3" s="3">
-        <v>45891</v>
+        <v>45939</v>
       </c>
       <c r="F3" s="3">
         <f ca="1">TODAY()</f>
-        <v>45894</v>
+        <v>45939</v>
       </c>
       <c r="G3" s="3">
         <v>45965</v>
@@ -780,7 +780,7 @@
       </c>
       <c r="D5" s="5">
         <f>D3*D4</f>
-        <v>11830.448</v>
+        <v>22280.775999999998</v>
       </c>
     </row>
     <row r="6" spans="2:11" x14ac:dyDescent="0.3">
@@ -821,7 +821,7 @@
       </c>
       <c r="D9" s="5">
         <f>D5-D8</f>
-        <v>11174.548000000001</v>
+        <v>21624.875999999997</v>
       </c>
     </row>
     <row r="10" spans="2:11" x14ac:dyDescent="0.3">
@@ -4874,7 +4874,7 @@
       </c>
       <c r="AP29" s="4">
         <f>Main!D3</f>
-        <v>39.86</v>
+        <v>75.069999999999993</v>
       </c>
     </row>
     <row r="30" spans="2:156" x14ac:dyDescent="0.3">
@@ -5026,7 +5026,7 @@
       </c>
       <c r="AP30" s="9">
         <f>AP28/AP29-1</f>
-        <v>-0.85394763642573468</v>
+        <v>-0.92245041678339923</v>
       </c>
     </row>
     <row r="31" spans="2:156" x14ac:dyDescent="0.3">

--- a/Financial Analysis/IONQ.xlsx
+++ b/Financial Analysis/IONQ.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\antos\Documents\GitHub\FinanceModels\Financial Analysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{23D3E308-2462-4805-BB64-901D9BEC98E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3A62E678-3586-499E-BB3F-A412B97D508D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{054FC3C2-46E6-4A64-A90B-FD32B5955AC0}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{054FC3C2-46E6-4A64-A90B-FD32B5955AC0}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>
@@ -376,13 +376,13 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>20</xdr:col>
+      <xdr:col>21</xdr:col>
       <xdr:colOff>30480</xdr:colOff>
       <xdr:row>0</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>20</xdr:col>
+      <xdr:col>21</xdr:col>
       <xdr:colOff>30480</xdr:colOff>
       <xdr:row>33</xdr:row>
       <xdr:rowOff>91440</xdr:rowOff>
@@ -400,7 +400,7 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="13098780" y="0"/>
+          <a:off x="13708380" y="0"/>
           <a:ext cx="0" cy="6126480"/>
         </a:xfrm>
         <a:prstGeom prst="line">
@@ -749,17 +749,17 @@
         <v>1</v>
       </c>
       <c r="D3" s="4">
-        <v>75.069999999999993</v>
+        <v>57.7</v>
       </c>
       <c r="E3" s="3">
-        <v>45939</v>
+        <v>45967</v>
       </c>
       <c r="F3" s="3">
         <f ca="1">TODAY()</f>
-        <v>45939</v>
+        <v>45967</v>
       </c>
       <c r="G3" s="3">
-        <v>45965</v>
+        <v>46026</v>
       </c>
     </row>
     <row r="4" spans="2:11" x14ac:dyDescent="0.3">
@@ -767,11 +767,11 @@
         <v>2</v>
       </c>
       <c r="D4" s="5">
-        <f>296.8</f>
-        <v>296.8</v>
+        <f>354.3</f>
+        <v>354.3</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="5" spans="2:11" x14ac:dyDescent="0.3">
@@ -780,7 +780,7 @@
       </c>
       <c r="D5" s="5">
         <f>D3*D4</f>
-        <v>22280.775999999998</v>
+        <v>20443.11</v>
       </c>
     </row>
     <row r="6" spans="2:11" x14ac:dyDescent="0.3">
@@ -788,11 +788,11 @@
         <v>4</v>
       </c>
       <c r="D6" s="5">
-        <f>140.1+406.8+109</f>
-        <v>655.9</v>
+        <f>346+736.3+402.6</f>
+        <v>1484.9</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="7" spans="2:11" x14ac:dyDescent="0.3">
@@ -800,10 +800,11 @@
         <v>5</v>
       </c>
       <c r="D7" s="5">
-        <v>0</v>
+        <f>1768.2</f>
+        <v>1768.2</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="8" spans="2:11" x14ac:dyDescent="0.3">
@@ -812,7 +813,7 @@
       </c>
       <c r="D8" s="5">
         <f>D6-D7</f>
-        <v>655.9</v>
+        <v>-283.29999999999995</v>
       </c>
     </row>
     <row r="9" spans="2:11" x14ac:dyDescent="0.3">
@@ -821,7 +822,7 @@
       </c>
       <c r="D9" s="5">
         <f>D5-D8</f>
-        <v>21624.875999999997</v>
+        <v>20726.41</v>
       </c>
     </row>
     <row r="10" spans="2:11" x14ac:dyDescent="0.3">
@@ -1011,10 +1012,10 @@
         <v>20.7</v>
       </c>
       <c r="U3" s="8">
-        <v>24</v>
+        <v>39.9</v>
       </c>
       <c r="V3" s="8">
-        <v>30</v>
+        <v>43</v>
       </c>
       <c r="W3" s="8"/>
       <c r="X3" s="8">
@@ -1035,47 +1036,47 @@
       </c>
       <c r="AB3" s="8">
         <f>SUM(S3:V3)</f>
-        <v>82.3</v>
+        <v>111.19999999999999</v>
       </c>
       <c r="AC3" s="8">
-        <f>AB3*1.8</f>
-        <v>148.13999999999999</v>
+        <f>AB3*1.9</f>
+        <v>211.27999999999997</v>
       </c>
       <c r="AD3" s="8">
-        <f>AC3*1.7</f>
-        <v>251.83799999999997</v>
+        <f>AC3*1.75</f>
+        <v>369.73999999999995</v>
       </c>
       <c r="AE3" s="8">
         <f>AD3*1.6</f>
-        <v>402.94079999999997</v>
+        <v>591.58399999999995</v>
       </c>
       <c r="AF3" s="8">
         <f>AE3*1.5</f>
-        <v>604.41120000000001</v>
+        <v>887.37599999999998</v>
       </c>
       <c r="AG3" s="8">
         <f>AF3*1.45</f>
-        <v>876.39624000000003</v>
+        <v>1286.6951999999999</v>
       </c>
       <c r="AH3" s="8">
         <f>AG3*1.25</f>
-        <v>1095.4953</v>
+        <v>1608.3689999999999</v>
       </c>
       <c r="AI3" s="8">
         <f>AH3*1.2</f>
-        <v>1314.5943600000001</v>
+        <v>1930.0427999999997</v>
       </c>
       <c r="AJ3" s="8">
         <f>AI3*1.15</f>
-        <v>1511.783514</v>
+        <v>2219.5492199999994</v>
       </c>
       <c r="AK3" s="8">
         <f>AJ3*1.1</f>
-        <v>1662.9618654000001</v>
+        <v>2441.5041419999998</v>
       </c>
       <c r="AL3" s="8">
         <f>AK3*1.05</f>
-        <v>1746.1099586700002</v>
+        <v>2563.5793490999999</v>
       </c>
     </row>
     <row r="4" spans="2:38" x14ac:dyDescent="0.3">
@@ -1137,12 +1138,11 @@
         <v>8.3000000000000007</v>
       </c>
       <c r="U4" s="5">
-        <f t="shared" ref="U4:V4" si="0">U3-U5</f>
-        <v>11.52</v>
+        <v>21.3</v>
       </c>
       <c r="V4" s="5">
-        <f t="shared" si="0"/>
-        <v>14.399999999999999</v>
+        <f t="shared" ref="V4" si="0">V3-V5</f>
+        <v>21.93</v>
       </c>
       <c r="X4" s="5">
         <f>SUM(C4:F4)</f>
@@ -1162,47 +1162,47 @@
       </c>
       <c r="AB4" s="5">
         <f>AB3-AB5</f>
-        <v>41.15</v>
+        <v>55.599999999999994</v>
       </c>
       <c r="AC4" s="5">
         <f t="shared" ref="AC4:AL4" si="1">AC3-AC5</f>
-        <v>72.588599999999985</v>
+        <v>103.52719999999998</v>
       </c>
       <c r="AD4" s="5">
         <f t="shared" si="1"/>
-        <v>120.88223999999997</v>
+        <v>177.47519999999997</v>
       </c>
       <c r="AE4" s="5">
         <f t="shared" si="1"/>
-        <v>193.41158399999998</v>
+        <v>283.96031999999997</v>
       </c>
       <c r="AF4" s="5">
         <f t="shared" si="1"/>
-        <v>278.02915200000001</v>
+        <v>408.19295999999997</v>
       </c>
       <c r="AG4" s="5">
         <f t="shared" si="1"/>
-        <v>385.61434559999998</v>
+        <v>566.1458879999999</v>
       </c>
       <c r="AH4" s="5">
         <f t="shared" si="1"/>
-        <v>460.10802600000011</v>
+        <v>675.51498000000004</v>
       </c>
       <c r="AI4" s="5">
         <f t="shared" si="1"/>
-        <v>525.83774400000004</v>
+        <v>772.01711999999998</v>
       </c>
       <c r="AJ4" s="5">
         <f t="shared" si="1"/>
-        <v>574.47773531999997</v>
+        <v>865.62419579999982</v>
       </c>
       <c r="AK4" s="5">
         <f t="shared" si="1"/>
-        <v>615.29589019800005</v>
+        <v>927.77157395999984</v>
       </c>
       <c r="AL4" s="5">
         <f t="shared" si="1"/>
-        <v>628.59958512120011</v>
+        <v>974.16015265800002</v>
       </c>
     </row>
     <row r="5" spans="2:38" s="1" customFormat="1" x14ac:dyDescent="0.3">
@@ -1210,7 +1210,7 @@
         <v>25</v>
       </c>
       <c r="C5" s="8">
-        <f t="shared" ref="C5:T5" si="2">C3-C4</f>
+        <f t="shared" ref="C5:U5" si="2">C3-C4</f>
         <v>-0.1</v>
       </c>
       <c r="D5" s="8">
@@ -1282,12 +1282,12 @@
         <v>12.399999999999999</v>
       </c>
       <c r="U5" s="8">
-        <f t="shared" ref="U5:V5" si="3">U3*0.52</f>
-        <v>12.48</v>
+        <f t="shared" si="2"/>
+        <v>18.599999999999998</v>
       </c>
       <c r="V5" s="8">
-        <f t="shared" si="3"/>
-        <v>15.600000000000001</v>
+        <f>V3*0.49</f>
+        <v>21.07</v>
       </c>
       <c r="X5" s="8">
         <f>X3-X4</f>
@@ -1307,47 +1307,47 @@
       </c>
       <c r="AB5" s="8">
         <f>AB3*0.5</f>
-        <v>41.15</v>
+        <v>55.599999999999994</v>
       </c>
       <c r="AC5" s="8">
         <f>AC3*0.51</f>
-        <v>75.551400000000001</v>
+        <v>107.75279999999999</v>
       </c>
       <c r="AD5" s="8">
         <f>AD3*0.52</f>
-        <v>130.95576</v>
+        <v>192.26479999999998</v>
       </c>
       <c r="AE5" s="8">
         <f>AE3*0.52</f>
-        <v>209.52921599999999</v>
+        <v>307.62367999999998</v>
       </c>
       <c r="AF5" s="8">
         <f>AF3*0.54</f>
-        <v>326.382048</v>
+        <v>479.18304000000001</v>
       </c>
       <c r="AG5" s="8">
         <f>AG3*0.56</f>
-        <v>490.78189440000006</v>
+        <v>720.54931199999999</v>
       </c>
       <c r="AH5" s="8">
         <f>AH3*0.58</f>
-        <v>635.38727399999993</v>
+        <v>932.85401999999988</v>
       </c>
       <c r="AI5" s="8">
         <f>AI3*0.6</f>
-        <v>788.75661600000001</v>
+        <v>1158.0256799999997</v>
       </c>
       <c r="AJ5" s="8">
-        <f>AJ3*0.62</f>
-        <v>937.30577868</v>
+        <f>AJ3*0.61</f>
+        <v>1353.9250241999996</v>
       </c>
       <c r="AK5" s="8">
-        <f>AK3*0.63</f>
-        <v>1047.665975202</v>
+        <f>AK3*0.62</f>
+        <v>1513.7325680399999</v>
       </c>
       <c r="AL5" s="8">
-        <f>AL3*0.64</f>
-        <v>1117.5103735488001</v>
+        <f>AL3*0.62</f>
+        <v>1589.4191964419999</v>
       </c>
     </row>
     <row r="6" spans="2:38" x14ac:dyDescent="0.3">
@@ -1408,8 +1408,12 @@
       <c r="T6" s="5">
         <v>103.4</v>
       </c>
-      <c r="U6" s="5"/>
-      <c r="V6" s="5"/>
+      <c r="U6" s="5">
+        <v>66.3</v>
+      </c>
+      <c r="V6" s="5">
+        <v>80</v>
+      </c>
       <c r="X6" s="5">
         <f>SUM(C6:F6)</f>
         <v>20.299999999999997</v>
@@ -1443,31 +1447,31 @@
         <v>203.27152944000002</v>
       </c>
       <c r="AF6" s="5">
-        <f t="shared" ref="AF6:AL6" si="4">AE6*1.05</f>
+        <f t="shared" ref="AF6:AL6" si="3">AE6*1.05</f>
         <v>213.43510591200004</v>
       </c>
       <c r="AG6" s="5">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>224.10686120760005</v>
       </c>
       <c r="AH6" s="5">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>235.31220426798006</v>
       </c>
       <c r="AI6" s="5">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>247.07781448137908</v>
       </c>
       <c r="AJ6" s="5">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>259.43170520544805</v>
       </c>
       <c r="AK6" s="5">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>272.40329046572049</v>
       </c>
       <c r="AL6" s="5">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>286.02345498900655</v>
       </c>
     </row>
@@ -1529,8 +1533,13 @@
       <c r="T7" s="5">
         <v>10.9</v>
       </c>
-      <c r="U7" s="5"/>
-      <c r="V7" s="5"/>
+      <c r="U7" s="5">
+        <v>14.4</v>
+      </c>
+      <c r="V7" s="5">
+        <f>V3*0.4</f>
+        <v>17.2</v>
+      </c>
       <c r="X7" s="5">
         <f>SUM(C7:F7)</f>
         <v>3.2</v>
@@ -1549,47 +1558,47 @@
       </c>
       <c r="AB7" s="5">
         <f>AB3*0.4</f>
-        <v>32.92</v>
+        <v>44.48</v>
       </c>
       <c r="AC7" s="5">
         <f>AC3*0.3</f>
-        <v>44.441999999999993</v>
+        <v>63.383999999999986</v>
       </c>
       <c r="AD7" s="5">
         <f>AD3*0.26</f>
-        <v>65.477879999999999</v>
+        <v>96.13239999999999</v>
       </c>
       <c r="AE7" s="5">
         <f>AE3*0.24</f>
-        <v>96.705791999999988</v>
+        <v>141.98015999999998</v>
       </c>
       <c r="AF7" s="5">
         <f>AF3*0.22</f>
-        <v>132.97046399999999</v>
+        <v>195.22272000000001</v>
       </c>
       <c r="AG7" s="5">
         <f>AG3*0.2</f>
-        <v>175.27924800000002</v>
+        <v>257.33904000000001</v>
       </c>
       <c r="AH7" s="5">
         <f>AH3*0.18</f>
-        <v>197.189154</v>
+        <v>289.50641999999999</v>
       </c>
       <c r="AI7" s="5">
         <f>AI3*0.17</f>
-        <v>223.48104120000002</v>
+        <v>328.10727599999996</v>
       </c>
       <c r="AJ7" s="5">
         <f>AJ3*0.16</f>
-        <v>241.88536224000001</v>
+        <v>355.12787519999989</v>
       </c>
       <c r="AK7" s="5">
         <f>AK3*0.15</f>
-        <v>249.44427981000001</v>
+        <v>366.22562129999994</v>
       </c>
       <c r="AL7" s="5">
         <f>AL3*0.14</f>
-        <v>244.45539421380005</v>
+        <v>358.90110887400004</v>
       </c>
     </row>
     <row r="8" spans="2:38" x14ac:dyDescent="0.3">
@@ -1650,8 +1659,12 @@
       <c r="T8" s="5">
         <v>48.1</v>
       </c>
-      <c r="U8" s="5"/>
-      <c r="V8" s="5"/>
+      <c r="U8" s="5">
+        <v>82.5</v>
+      </c>
+      <c r="V8" s="5">
+        <v>100</v>
+      </c>
       <c r="X8" s="5">
         <f>SUM(C8:F8)</f>
         <v>13.8</v>
@@ -1693,23 +1706,23 @@
         <v>97.827880056192058</v>
       </c>
       <c r="AH8" s="5">
-        <f t="shared" ref="AH8:AL8" si="5">AG8*1.02</f>
+        <f t="shared" ref="AH8:AL8" si="4">AG8*1.02</f>
         <v>99.784437657315905</v>
       </c>
       <c r="AI8" s="5">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>101.78012641046223</v>
       </c>
       <c r="AJ8" s="5">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>103.81572893867148</v>
       </c>
       <c r="AK8" s="5">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>105.89204351744492</v>
       </c>
       <c r="AL8" s="5">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>108.00988438779382</v>
       </c>
     </row>
@@ -1771,8 +1784,12 @@
       <c r="T9" s="5">
         <v>10.6</v>
       </c>
-      <c r="U9" s="5"/>
-      <c r="V9" s="5"/>
+      <c r="U9" s="5">
+        <v>24.2</v>
+      </c>
+      <c r="V9" s="5">
+        <v>30</v>
+      </c>
       <c r="X9" s="5">
         <f>SUM(C9:F9)</f>
         <v>2.5</v>
@@ -1810,27 +1827,27 @@
         <v>42.506619375000007</v>
       </c>
       <c r="AG9" s="5">
-        <f t="shared" ref="AG9:AL9" si="6">AF9*1.03</f>
+        <f t="shared" ref="AG9:AL9" si="5">AF9*1.03</f>
         <v>43.781817956250009</v>
       </c>
       <c r="AH9" s="5">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>45.095272494937511</v>
       </c>
       <c r="AI9" s="5">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>46.448130669785634</v>
       </c>
       <c r="AJ9" s="5">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>47.841574589879201</v>
       </c>
       <c r="AK9" s="5">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>49.276821827575581</v>
       </c>
       <c r="AL9" s="5">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>50.755126482402851</v>
       </c>
     </row>
@@ -1839,79 +1856,85 @@
         <v>30</v>
       </c>
       <c r="C10" s="5">
-        <f t="shared" ref="C10:R10" si="7">SUM(C6:C9)</f>
+        <f t="shared" ref="C10:R10" si="6">SUM(C6:C9)</f>
         <v>7.3000000000000007</v>
       </c>
       <c r="D10" s="5">
+        <f t="shared" si="6"/>
+        <v>9.8000000000000007</v>
+      </c>
+      <c r="E10" s="5">
+        <f t="shared" si="6"/>
+        <v>10.6</v>
+      </c>
+      <c r="F10" s="5">
+        <f t="shared" si="6"/>
+        <v>12.100000000000001</v>
+      </c>
+      <c r="G10" s="5">
+        <f t="shared" si="6"/>
+        <v>19.7</v>
+      </c>
+      <c r="H10" s="5">
+        <f t="shared" si="6"/>
+        <v>20.9</v>
+      </c>
+      <c r="I10" s="5">
+        <f t="shared" si="6"/>
+        <v>26.9</v>
+      </c>
+      <c r="J10" s="5">
+        <f t="shared" si="6"/>
+        <v>26.599999999999994</v>
+      </c>
+      <c r="K10" s="5">
+        <f t="shared" si="6"/>
+        <v>31.3</v>
+      </c>
+      <c r="L10" s="5">
+        <f t="shared" si="6"/>
+        <v>36.699999999999996</v>
+      </c>
+      <c r="M10" s="5">
+        <f t="shared" si="6"/>
+        <v>46.2</v>
+      </c>
+      <c r="N10" s="5">
+        <f t="shared" si="6"/>
+        <v>57.400000000000006</v>
+      </c>
+      <c r="O10" s="5">
+        <f t="shared" si="6"/>
+        <v>57.1</v>
+      </c>
+      <c r="P10" s="5">
+        <f t="shared" si="6"/>
+        <v>54.699999999999996</v>
+      </c>
+      <c r="Q10" s="5">
+        <f t="shared" si="6"/>
+        <v>59.000000000000007</v>
+      </c>
+      <c r="R10" s="5">
+        <f t="shared" si="6"/>
+        <v>84.2</v>
+      </c>
+      <c r="S10" s="5">
+        <f t="shared" ref="S10:T10" si="7">SUM(S6:S9)</f>
+        <v>79</v>
+      </c>
+      <c r="T10" s="5">
         <f t="shared" si="7"/>
-        <v>9.8000000000000007</v>
-      </c>
-      <c r="E10" s="5">
-        <f t="shared" si="7"/>
-        <v>10.6</v>
-      </c>
-      <c r="F10" s="5">
-        <f t="shared" si="7"/>
-        <v>12.100000000000001</v>
-      </c>
-      <c r="G10" s="5">
-        <f t="shared" si="7"/>
-        <v>19.7</v>
-      </c>
-      <c r="H10" s="5">
-        <f t="shared" si="7"/>
-        <v>20.9</v>
-      </c>
-      <c r="I10" s="5">
-        <f t="shared" si="7"/>
-        <v>26.9</v>
-      </c>
-      <c r="J10" s="5">
-        <f t="shared" si="7"/>
-        <v>26.599999999999994</v>
-      </c>
-      <c r="K10" s="5">
-        <f t="shared" si="7"/>
-        <v>31.3</v>
-      </c>
-      <c r="L10" s="5">
-        <f t="shared" si="7"/>
-        <v>36.699999999999996</v>
-      </c>
-      <c r="M10" s="5">
-        <f t="shared" si="7"/>
-        <v>46.2</v>
-      </c>
-      <c r="N10" s="5">
-        <f t="shared" si="7"/>
-        <v>57.400000000000006</v>
-      </c>
-      <c r="O10" s="5">
-        <f t="shared" si="7"/>
-        <v>57.1</v>
-      </c>
-      <c r="P10" s="5">
-        <f t="shared" si="7"/>
-        <v>54.699999999999996</v>
-      </c>
-      <c r="Q10" s="5">
-        <f t="shared" si="7"/>
-        <v>59.000000000000007</v>
-      </c>
-      <c r="R10" s="5">
-        <f t="shared" si="7"/>
-        <v>84.2</v>
-      </c>
-      <c r="S10" s="5">
-        <f t="shared" ref="S10:T10" si="8">SUM(S6:S9)</f>
-        <v>79</v>
-      </c>
-      <c r="T10" s="5">
+        <v>173</v>
+      </c>
+      <c r="U10" s="5">
+        <f t="shared" ref="U10:V10" si="8">SUM(U6:U9)</f>
+        <v>187.39999999999998</v>
+      </c>
+      <c r="V10" s="5">
         <f t="shared" si="8"/>
-        <v>173</v>
-      </c>
-      <c r="U10" s="5"/>
-      <c r="V10" s="5"/>
+        <v>227.2</v>
+      </c>
       <c r="X10" s="5">
         <f>SUM(X6:X9)</f>
         <v>39.799999999999997</v>
@@ -1930,47 +1953,47 @@
       </c>
       <c r="AB10" s="5">
         <f t="shared" ref="AB10:AL10" si="9">SUM(AB6:AB9)</f>
-        <v>300.72200000000004</v>
+        <v>312.28200000000004</v>
       </c>
       <c r="AC10" s="5">
         <f t="shared" si="9"/>
-        <v>344.89834000000002</v>
+        <v>363.84034000000003</v>
       </c>
       <c r="AD10" s="5">
         <f t="shared" si="9"/>
-        <v>387.1733708000001</v>
+        <v>417.82789080000009</v>
       </c>
       <c r="AE10" s="5">
         <f t="shared" si="9"/>
-        <v>434.36208426000007</v>
+        <v>479.63645226000006</v>
       </c>
       <c r="AF10" s="5">
         <f t="shared" si="9"/>
-        <v>484.8218756166001</v>
+        <v>547.07413161660008</v>
       </c>
       <c r="AG10" s="5">
         <f t="shared" si="9"/>
-        <v>540.99580722004214</v>
+        <v>623.05559922004215</v>
       </c>
       <c r="AH10" s="5">
         <f t="shared" si="9"/>
-        <v>577.38106842023353</v>
+        <v>669.69833442023355</v>
       </c>
       <c r="AI10" s="5">
         <f t="shared" si="9"/>
-        <v>618.78711276162699</v>
+        <v>723.41334756162689</v>
       </c>
       <c r="AJ10" s="5">
         <f t="shared" si="9"/>
-        <v>652.9743709739987</v>
+        <v>766.21688393399859</v>
       </c>
       <c r="AK10" s="5">
         <f t="shared" si="9"/>
-        <v>677.01643562074094</v>
+        <v>793.79777711074087</v>
       </c>
       <c r="AL10" s="5">
         <f t="shared" si="9"/>
-        <v>689.24386007300325</v>
+        <v>803.68957473320324</v>
       </c>
     </row>
     <row r="11" spans="2:38" s="1" customFormat="1" x14ac:dyDescent="0.3">
@@ -2049,8 +2072,14 @@
         <f t="shared" si="11"/>
         <v>-160.6</v>
       </c>
-      <c r="U11" s="8"/>
-      <c r="V11" s="8"/>
+      <c r="U11" s="8">
+        <f t="shared" ref="U11:V11" si="12">U5-U10</f>
+        <v>-168.79999999999998</v>
+      </c>
+      <c r="V11" s="8">
+        <f t="shared" si="12"/>
+        <v>-206.13</v>
+      </c>
       <c r="X11" s="8">
         <f>X5-X10</f>
         <v>-38.799999999999997</v>
@@ -2068,48 +2097,48 @@
         <v>-232.4</v>
       </c>
       <c r="AB11" s="8">
-        <f t="shared" ref="AB11:AL11" si="12">AB5-AB10</f>
-        <v>-259.57200000000006</v>
+        <f t="shared" ref="AB11:AL11" si="13">AB5-AB10</f>
+        <v>-256.68200000000002</v>
       </c>
       <c r="AC11" s="8">
-        <f t="shared" si="12"/>
-        <v>-269.34694000000002</v>
+        <f t="shared" si="13"/>
+        <v>-256.08754000000005</v>
       </c>
       <c r="AD11" s="8">
-        <f t="shared" si="12"/>
-        <v>-256.2176108000001</v>
+        <f t="shared" si="13"/>
+        <v>-225.56309080000011</v>
       </c>
       <c r="AE11" s="8">
-        <f t="shared" si="12"/>
-        <v>-224.83286826000008</v>
+        <f t="shared" si="13"/>
+        <v>-172.01277226000008</v>
       </c>
       <c r="AF11" s="8">
-        <f t="shared" si="12"/>
-        <v>-158.4398276166001</v>
+        <f t="shared" si="13"/>
+        <v>-67.891091616600079</v>
       </c>
       <c r="AG11" s="8">
-        <f t="shared" si="12"/>
-        <v>-50.213912820042083</v>
+        <f t="shared" si="13"/>
+        <v>97.493712779957832</v>
       </c>
       <c r="AH11" s="8">
-        <f t="shared" si="12"/>
-        <v>58.006205579766402</v>
+        <f t="shared" si="13"/>
+        <v>263.15568557976633</v>
       </c>
       <c r="AI11" s="8">
-        <f t="shared" si="12"/>
-        <v>169.96950323837302</v>
+        <f t="shared" si="13"/>
+        <v>434.61233243837285</v>
       </c>
       <c r="AJ11" s="8">
-        <f t="shared" si="12"/>
-        <v>284.3314077060013</v>
+        <f t="shared" si="13"/>
+        <v>587.70814026600101</v>
       </c>
       <c r="AK11" s="8">
-        <f t="shared" si="12"/>
-        <v>370.64953958125909</v>
+        <f t="shared" si="13"/>
+        <v>719.93479092925907</v>
       </c>
       <c r="AL11" s="8">
-        <f t="shared" si="12"/>
-        <v>428.26651347579684</v>
+        <f t="shared" si="13"/>
+        <v>785.72962170879669</v>
       </c>
     </row>
     <row r="12" spans="2:38" x14ac:dyDescent="0.3">
@@ -2170,8 +2199,12 @@
       <c r="T12" s="5">
         <v>39.6</v>
       </c>
-      <c r="U12" s="5"/>
-      <c r="V12" s="5"/>
+      <c r="U12" s="5">
+        <v>881.8</v>
+      </c>
+      <c r="V12" s="5">
+        <v>100</v>
+      </c>
       <c r="X12" s="5">
         <f>SUM(C12:F12)</f>
         <v>63.3</v>
@@ -2280,8 +2313,12 @@
       <c r="T13" s="5">
         <v>-7.1</v>
       </c>
-      <c r="U13" s="5"/>
-      <c r="V13" s="5"/>
+      <c r="U13" s="5">
+        <v>-14.4</v>
+      </c>
+      <c r="V13" s="5">
+        <v>-18</v>
+      </c>
       <c r="X13" s="5">
         <f>SUM(C13:F13)</f>
         <v>-0.1</v>
@@ -2303,43 +2340,43 @@
         <v>-18.745999999999999</v>
       </c>
       <c r="AC13" s="5">
-        <f t="shared" ref="AC13:AL13" si="13">AB13*1.03</f>
+        <f t="shared" ref="AC13:AL13" si="14">AB13*1.03</f>
         <v>-19.30838</v>
       </c>
       <c r="AD13" s="5">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>-19.8876314</v>
       </c>
       <c r="AE13" s="5">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>-20.484260341999999</v>
       </c>
       <c r="AF13" s="5">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>-21.098788152259999</v>
       </c>
       <c r="AG13" s="5">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>-21.731751796827801</v>
       </c>
       <c r="AH13" s="5">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>-22.383704350732636</v>
       </c>
       <c r="AI13" s="5">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>-23.055215481254617</v>
       </c>
       <c r="AJ13" s="5">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>-23.746871945692256</v>
       </c>
       <c r="AK13" s="5">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>-24.459278104063024</v>
       </c>
       <c r="AL13" s="5">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>-25.193056447184915</v>
       </c>
     </row>
@@ -2401,8 +2438,13 @@
       <c r="T14" s="5">
         <v>-0.2</v>
       </c>
-      <c r="U14" s="5"/>
-      <c r="V14" s="5"/>
+      <c r="U14" s="5">
+        <f>22.8+1</f>
+        <v>23.8</v>
+      </c>
+      <c r="V14" s="5">
+        <v>0</v>
+      </c>
       <c r="X14" s="5">
         <f>SUM(C14:F14)</f>
         <v>4.3</v>
@@ -2458,79 +2500,85 @@
         <v>39</v>
       </c>
       <c r="C15" s="5">
-        <f t="shared" ref="C15:R15" si="14">SUM(C12:C14)</f>
+        <f t="shared" ref="C15:R15" si="15">SUM(C12:C14)</f>
         <v>0</v>
       </c>
       <c r="D15" s="5">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="E15" s="5">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>4.3</v>
       </c>
       <c r="F15" s="5">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>63.199999999999996</v>
       </c>
       <c r="G15" s="5">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>-14</v>
       </c>
       <c r="H15" s="5">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>-17.500000000000004</v>
       </c>
       <c r="I15" s="5">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>-0.90000000000000013</v>
       </c>
       <c r="J15" s="5">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>-5</v>
       </c>
       <c r="K15" s="5">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>-0.70000000000000007</v>
       </c>
       <c r="L15" s="5">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>10.6</v>
       </c>
       <c r="M15" s="5">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>2.4999999999999996</v>
       </c>
       <c r="N15" s="5">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>-12.600000000000001</v>
       </c>
       <c r="O15" s="5">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>-13.299999999999999</v>
       </c>
       <c r="P15" s="5">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>-11.299999999999999</v>
       </c>
       <c r="Q15" s="5">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>-0.60000000000000009</v>
       </c>
       <c r="R15" s="5">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>124.5</v>
       </c>
       <c r="S15" s="5">
-        <f t="shared" ref="S15:T15" si="15">SUM(S12:S14)</f>
+        <f t="shared" ref="S15:T15" si="16">SUM(S12:S14)</f>
         <v>-43.5</v>
       </c>
       <c r="T15" s="5">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>32.299999999999997</v>
       </c>
-      <c r="U15" s="5"/>
-      <c r="V15" s="5"/>
+      <c r="U15" s="5">
+        <f t="shared" ref="U15:V15" si="17">SUM(U12:U14)</f>
+        <v>891.19999999999993</v>
+      </c>
+      <c r="V15" s="5">
+        <f t="shared" si="17"/>
+        <v>82</v>
+      </c>
       <c r="X15" s="5">
         <f>SUM(X12:X14)</f>
         <v>67.5</v>
@@ -2548,47 +2596,47 @@
         <v>99.3</v>
       </c>
       <c r="AB15" s="5">
-        <f t="shared" ref="AB15:AL15" si="16">SUM(AB12:AB14)</f>
+        <f t="shared" ref="AB15:AL15" si="18">SUM(AB12:AB14)</f>
         <v>-18.745999999999999</v>
       </c>
       <c r="AC15" s="5">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>-19.30838</v>
       </c>
       <c r="AD15" s="5">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>-19.8876314</v>
       </c>
       <c r="AE15" s="5">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>-20.484260341999999</v>
       </c>
       <c r="AF15" s="5">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>-21.098788152259999</v>
       </c>
       <c r="AG15" s="5">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>-21.731751796827801</v>
       </c>
       <c r="AH15" s="5">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>-22.383704350732636</v>
       </c>
       <c r="AI15" s="5">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>-23.055215481254617</v>
       </c>
       <c r="AJ15" s="5">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>-23.746871945692256</v>
       </c>
       <c r="AK15" s="5">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>-24.459278104063024</v>
       </c>
       <c r="AL15" s="5">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>-25.193056447184915</v>
       </c>
     </row>
@@ -2597,79 +2645,85 @@
         <v>35</v>
       </c>
       <c r="C16" s="8">
-        <f t="shared" ref="C16:R16" si="17">C11-C15</f>
+        <f t="shared" ref="C16:R16" si="19">C11-C15</f>
         <v>-7.4</v>
       </c>
       <c r="D16" s="8">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>-10</v>
       </c>
       <c r="E16" s="8">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>-14.899999999999999</v>
       </c>
       <c r="F16" s="8">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>-74</v>
       </c>
       <c r="G16" s="8">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>-4.3000000000000007</v>
       </c>
       <c r="H16" s="8">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>-1.4999999999999964</v>
       </c>
       <c r="I16" s="8">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>-23.9</v>
       </c>
       <c r="J16" s="8">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>-18.699999999999996</v>
       </c>
       <c r="K16" s="8">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>-27.3</v>
       </c>
       <c r="L16" s="8">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>-43.699999999999996</v>
       </c>
       <c r="M16" s="8">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>-44.6</v>
       </c>
       <c r="N16" s="8">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>-41.900000000000006</v>
       </c>
       <c r="O16" s="8">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>-39.600000000000009</v>
       </c>
       <c r="P16" s="8">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>-37.599999999999994</v>
       </c>
       <c r="Q16" s="8">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>-52.500000000000007</v>
       </c>
       <c r="R16" s="8">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>-202</v>
       </c>
       <c r="S16" s="8">
-        <f t="shared" ref="S16:T16" si="18">S11-S15</f>
+        <f t="shared" ref="S16:T16" si="20">S11-S15</f>
         <v>-32.200000000000003</v>
       </c>
       <c r="T16" s="8">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>-192.89999999999998</v>
       </c>
-      <c r="U16" s="8"/>
-      <c r="V16" s="8"/>
+      <c r="U16" s="8">
+        <f t="shared" ref="U16:V16" si="21">U11-U15</f>
+        <v>-1060</v>
+      </c>
+      <c r="V16" s="8">
+        <f t="shared" si="21"/>
+        <v>-288.13</v>
+      </c>
       <c r="X16" s="8">
         <f>X11-X15</f>
         <v>-106.3</v>
@@ -2687,48 +2741,48 @@
         <v>-331.7</v>
       </c>
       <c r="AB16" s="8">
-        <f t="shared" ref="AB16:AL16" si="19">AB11-AB15</f>
-        <v>-240.82600000000005</v>
+        <f t="shared" ref="AB16:AL16" si="22">AB11-AB15</f>
+        <v>-237.93600000000001</v>
       </c>
       <c r="AC16" s="8">
-        <f t="shared" si="19"/>
-        <v>-250.03856000000002</v>
+        <f t="shared" si="22"/>
+        <v>-236.77916000000005</v>
       </c>
       <c r="AD16" s="8">
-        <f t="shared" si="19"/>
-        <v>-236.3299794000001</v>
+        <f t="shared" si="22"/>
+        <v>-205.67545940000011</v>
       </c>
       <c r="AE16" s="8">
-        <f t="shared" si="19"/>
-        <v>-204.34860791800008</v>
+        <f t="shared" si="22"/>
+        <v>-151.52851191800008</v>
       </c>
       <c r="AF16" s="8">
-        <f t="shared" si="19"/>
-        <v>-137.3410394643401</v>
+        <f t="shared" si="22"/>
+        <v>-46.79230346434008</v>
       </c>
       <c r="AG16" s="8">
-        <f t="shared" si="19"/>
-        <v>-28.482161023214282</v>
+        <f t="shared" si="22"/>
+        <v>119.22546457678564</v>
       </c>
       <c r="AH16" s="8">
-        <f t="shared" si="19"/>
-        <v>80.389909930499044</v>
+        <f t="shared" si="22"/>
+        <v>285.53938993049894</v>
       </c>
       <c r="AI16" s="8">
-        <f t="shared" si="19"/>
-        <v>193.02471871962763</v>
+        <f t="shared" si="22"/>
+        <v>457.66754791962745</v>
       </c>
       <c r="AJ16" s="8">
-        <f t="shared" si="19"/>
-        <v>308.07827965169355</v>
+        <f t="shared" si="22"/>
+        <v>611.45501221169332</v>
       </c>
       <c r="AK16" s="8">
-        <f t="shared" si="19"/>
-        <v>395.10881768532209</v>
+        <f t="shared" si="22"/>
+        <v>744.39406903332213</v>
       </c>
       <c r="AL16" s="8">
-        <f t="shared" si="19"/>
-        <v>453.45956992298176</v>
+        <f t="shared" si="22"/>
+        <v>810.92267815598166</v>
       </c>
     </row>
     <row r="17" spans="2:156" x14ac:dyDescent="0.3">
@@ -2789,8 +2843,13 @@
       <c r="T17" s="5">
         <v>-15.3</v>
       </c>
-      <c r="U17" s="5"/>
-      <c r="V17" s="5"/>
+      <c r="U17" s="5">
+        <v>-4.4000000000000004</v>
+      </c>
+      <c r="V17" s="5">
+        <f>V16*0.05</f>
+        <v>-14.406500000000001</v>
+      </c>
       <c r="X17" s="5">
         <f>SUM(C17:F17)</f>
         <v>0</v>
@@ -2846,79 +2905,85 @@
         <v>37</v>
       </c>
       <c r="C18" s="8">
-        <f t="shared" ref="C18:R18" si="20">C16-C17</f>
+        <f t="shared" ref="C18:R18" si="23">C16-C17</f>
         <v>-7.4</v>
       </c>
       <c r="D18" s="8">
-        <f t="shared" si="20"/>
+        <f t="shared" si="23"/>
         <v>-10</v>
       </c>
       <c r="E18" s="8">
-        <f t="shared" si="20"/>
+        <f t="shared" si="23"/>
         <v>-14.899999999999999</v>
       </c>
       <c r="F18" s="8">
-        <f t="shared" si="20"/>
+        <f t="shared" si="23"/>
         <v>-74</v>
       </c>
       <c r="G18" s="8">
-        <f t="shared" si="20"/>
+        <f t="shared" si="23"/>
         <v>-4.3000000000000007</v>
       </c>
       <c r="H18" s="8">
-        <f t="shared" si="20"/>
+        <f t="shared" si="23"/>
         <v>-1.4999999999999964</v>
       </c>
       <c r="I18" s="8">
-        <f t="shared" si="20"/>
+        <f t="shared" si="23"/>
         <v>-23.9</v>
       </c>
       <c r="J18" s="8">
-        <f t="shared" si="20"/>
+        <f t="shared" si="23"/>
         <v>-18.699999999999996</v>
       </c>
       <c r="K18" s="8">
-        <f t="shared" si="20"/>
+        <f t="shared" si="23"/>
         <v>-27.3</v>
       </c>
       <c r="L18" s="8">
-        <f t="shared" si="20"/>
+        <f t="shared" si="23"/>
         <v>-43.699999999999996</v>
       </c>
       <c r="M18" s="8">
-        <f t="shared" si="20"/>
+        <f t="shared" si="23"/>
         <v>-44.6</v>
       </c>
       <c r="N18" s="8">
-        <f t="shared" si="20"/>
+        <f t="shared" si="23"/>
         <v>-41.900000000000006</v>
       </c>
       <c r="O18" s="8">
-        <f t="shared" si="20"/>
+        <f t="shared" si="23"/>
         <v>-39.600000000000009</v>
       </c>
       <c r="P18" s="8">
-        <f t="shared" si="20"/>
+        <f t="shared" si="23"/>
         <v>-37.599999999999994</v>
       </c>
       <c r="Q18" s="8">
-        <f t="shared" si="20"/>
+        <f t="shared" si="23"/>
         <v>-52.500000000000007</v>
       </c>
       <c r="R18" s="8">
-        <f t="shared" si="20"/>
+        <f t="shared" si="23"/>
         <v>-202</v>
       </c>
       <c r="S18" s="8">
-        <f t="shared" ref="S18:T18" si="21">S16-S17</f>
+        <f t="shared" ref="S18:V18" si="24">S16-S17</f>
         <v>-32.200000000000003</v>
       </c>
       <c r="T18" s="8">
-        <f t="shared" si="21"/>
+        <f t="shared" si="24"/>
         <v>-177.59999999999997</v>
       </c>
-      <c r="U18" s="8"/>
-      <c r="V18" s="8"/>
+      <c r="U18" s="8">
+        <f t="shared" si="24"/>
+        <v>-1055.5999999999999</v>
+      </c>
+      <c r="V18" s="8">
+        <f t="shared" si="24"/>
+        <v>-273.7235</v>
+      </c>
       <c r="X18" s="8">
         <f>X16-X17</f>
         <v>-106.3</v>
@@ -2937,519 +3002,519 @@
       </c>
       <c r="AB18" s="8">
         <f>AB16-AB17</f>
-        <v>-240.82600000000005</v>
+        <v>-237.93600000000001</v>
       </c>
       <c r="AC18" s="8">
-        <f t="shared" ref="AC18:AL18" si="22">AC16-AC17</f>
-        <v>-250.03856000000002</v>
+        <f t="shared" ref="AC18:AL18" si="25">AC16-AC17</f>
+        <v>-236.77916000000005</v>
       </c>
       <c r="AD18" s="8">
-        <f t="shared" si="22"/>
-        <v>-236.3299794000001</v>
+        <f t="shared" si="25"/>
+        <v>-205.67545940000011</v>
       </c>
       <c r="AE18" s="8">
-        <f t="shared" si="22"/>
-        <v>-204.34860791800008</v>
+        <f t="shared" si="25"/>
+        <v>-151.52851191800008</v>
       </c>
       <c r="AF18" s="8">
-        <f t="shared" si="22"/>
-        <v>-137.3410394643401</v>
+        <f t="shared" si="25"/>
+        <v>-46.79230346434008</v>
       </c>
       <c r="AG18" s="8">
-        <f t="shared" si="22"/>
-        <v>-28.482161023214282</v>
+        <f t="shared" si="25"/>
+        <v>119.22546457678564</v>
       </c>
       <c r="AH18" s="8">
-        <f t="shared" si="22"/>
-        <v>80.389909930499044</v>
+        <f t="shared" si="25"/>
+        <v>285.53938993049894</v>
       </c>
       <c r="AI18" s="8">
-        <f t="shared" si="22"/>
-        <v>193.02471871962763</v>
+        <f t="shared" si="25"/>
+        <v>457.66754791962745</v>
       </c>
       <c r="AJ18" s="8">
-        <f t="shared" si="22"/>
-        <v>308.07827965169355</v>
+        <f t="shared" si="25"/>
+        <v>611.45501221169332</v>
       </c>
       <c r="AK18" s="8">
-        <f t="shared" si="22"/>
-        <v>395.10881768532209</v>
+        <f t="shared" si="25"/>
+        <v>744.39406903332213</v>
       </c>
       <c r="AL18" s="8">
-        <f t="shared" si="22"/>
-        <v>453.45956992298176</v>
+        <f t="shared" si="25"/>
+        <v>810.92267815598166</v>
       </c>
       <c r="AM18" s="1">
         <f>AL18*(1+$AP$23)</f>
-        <v>448.92497422375192</v>
+        <v>802.81345137442179</v>
       </c>
       <c r="AN18" s="1">
-        <f t="shared" ref="AN18:CY18" si="23">AM18*(1+$AP$23)</f>
-        <v>444.4357244815144</v>
+        <f t="shared" ref="AN18:CY18" si="26">AM18*(1+$AP$23)</f>
+        <v>794.78531686067754</v>
       </c>
       <c r="AO18" s="1">
-        <f t="shared" si="23"/>
-        <v>439.99136723669926</v>
+        <f t="shared" si="26"/>
+        <v>786.83746369207074</v>
       </c>
       <c r="AP18" s="1">
-        <f t="shared" si="23"/>
-        <v>435.59145356433226</v>
+        <f t="shared" si="26"/>
+        <v>778.96908905514999</v>
       </c>
       <c r="AQ18" s="1">
-        <f t="shared" si="23"/>
-        <v>431.23553902868895</v>
+        <f t="shared" si="26"/>
+        <v>771.17939816459852</v>
       </c>
       <c r="AR18" s="1">
-        <f t="shared" si="23"/>
-        <v>426.92318363840207</v>
+        <f t="shared" si="26"/>
+        <v>763.46760418295253</v>
       </c>
       <c r="AS18" s="1">
-        <f t="shared" si="23"/>
-        <v>422.65395180201801</v>
+        <f t="shared" si="26"/>
+        <v>755.83292814112303</v>
       </c>
       <c r="AT18" s="1">
-        <f t="shared" si="23"/>
-        <v>418.42741228399785</v>
+        <f t="shared" si="26"/>
+        <v>748.27459885971177</v>
       </c>
       <c r="AU18" s="1">
-        <f t="shared" si="23"/>
-        <v>414.24313816115784</v>
+        <f t="shared" si="26"/>
+        <v>740.79185287111466</v>
       </c>
       <c r="AV18" s="1">
-        <f t="shared" si="23"/>
-        <v>410.10070677954627</v>
+        <f t="shared" si="26"/>
+        <v>733.38393434240345</v>
       </c>
       <c r="AW18" s="1">
-        <f t="shared" si="23"/>
-        <v>405.99969971175079</v>
+        <f t="shared" si="26"/>
+        <v>726.05009499897938</v>
       </c>
       <c r="AX18" s="1">
-        <f t="shared" si="23"/>
-        <v>401.93970271463326</v>
+        <f t="shared" si="26"/>
+        <v>718.78959404898956</v>
       </c>
       <c r="AY18" s="1">
-        <f t="shared" si="23"/>
-        <v>397.92030568748692</v>
+        <f t="shared" si="26"/>
+        <v>711.6016981084997</v>
       </c>
       <c r="AZ18" s="1">
-        <f t="shared" si="23"/>
-        <v>393.94110263061202</v>
+        <f t="shared" si="26"/>
+        <v>704.48568112741475</v>
       </c>
       <c r="BA18" s="1">
-        <f t="shared" si="23"/>
-        <v>390.0016916043059</v>
+        <f t="shared" si="26"/>
+        <v>697.44082431614061</v>
       </c>
       <c r="BB18" s="1">
-        <f t="shared" si="23"/>
-        <v>386.10167468826285</v>
+        <f t="shared" si="26"/>
+        <v>690.4664160729792</v>
       </c>
       <c r="BC18" s="1">
-        <f t="shared" si="23"/>
-        <v>382.24065794138022</v>
+        <f t="shared" si="26"/>
+        <v>683.56175191224941</v>
       </c>
       <c r="BD18" s="1">
-        <f t="shared" si="23"/>
-        <v>378.41825136196644</v>
+        <f t="shared" si="26"/>
+        <v>676.72613439312693</v>
       </c>
       <c r="BE18" s="1">
-        <f t="shared" si="23"/>
-        <v>374.63406884834677</v>
+        <f t="shared" si="26"/>
+        <v>669.95887304919563</v>
       </c>
       <c r="BF18" s="1">
-        <f t="shared" si="23"/>
-        <v>370.88772815986329</v>
+        <f t="shared" si="26"/>
+        <v>663.25928431870364</v>
       </c>
       <c r="BG18" s="1">
-        <f t="shared" si="23"/>
-        <v>367.17885087826465</v>
+        <f t="shared" si="26"/>
+        <v>656.62669147551662</v>
       </c>
       <c r="BH18" s="1">
-        <f t="shared" si="23"/>
-        <v>363.50706236948201</v>
+        <f t="shared" si="26"/>
+        <v>650.06042456076148</v>
       </c>
       <c r="BI18" s="1">
-        <f t="shared" si="23"/>
-        <v>359.87199174578717</v>
+        <f t="shared" si="26"/>
+        <v>643.55982031515384</v>
       </c>
       <c r="BJ18" s="1">
-        <f t="shared" si="23"/>
-        <v>356.27327182832931</v>
+        <f t="shared" si="26"/>
+        <v>637.12422211200226</v>
       </c>
       <c r="BK18" s="1">
-        <f t="shared" si="23"/>
-        <v>352.710539110046</v>
+        <f t="shared" si="26"/>
+        <v>630.75297989088222</v>
       </c>
       <c r="BL18" s="1">
-        <f t="shared" si="23"/>
-        <v>349.18343371894554</v>
+        <f t="shared" si="26"/>
+        <v>624.44545009197338</v>
       </c>
       <c r="BM18" s="1">
-        <f t="shared" si="23"/>
-        <v>345.69159938175608</v>
+        <f t="shared" si="26"/>
+        <v>618.2009955910537</v>
       </c>
       <c r="BN18" s="1">
-        <f t="shared" si="23"/>
-        <v>342.2346833879385</v>
+        <f t="shared" si="26"/>
+        <v>612.01898563514317</v>
       </c>
       <c r="BO18" s="1">
-        <f t="shared" si="23"/>
-        <v>338.81233655405913</v>
+        <f t="shared" si="26"/>
+        <v>605.89879577879174</v>
       </c>
       <c r="BP18" s="1">
-        <f t="shared" si="23"/>
-        <v>335.42421318851854</v>
+        <f t="shared" si="26"/>
+        <v>599.83980782100377</v>
       </c>
       <c r="BQ18" s="1">
-        <f t="shared" si="23"/>
-        <v>332.06997105663334</v>
+        <f t="shared" si="26"/>
+        <v>593.84140974279376</v>
       </c>
       <c r="BR18" s="1">
-        <f t="shared" si="23"/>
-        <v>328.74927134606702</v>
+        <f t="shared" si="26"/>
+        <v>587.90299564536576</v>
       </c>
       <c r="BS18" s="1">
-        <f t="shared" si="23"/>
-        <v>325.46177863260635</v>
+        <f t="shared" si="26"/>
+        <v>582.02396568891209</v>
       </c>
       <c r="BT18" s="1">
-        <f t="shared" si="23"/>
-        <v>322.20716084628026</v>
+        <f t="shared" si="26"/>
+        <v>576.20372603202293</v>
       </c>
       <c r="BU18" s="1">
-        <f t="shared" si="23"/>
-        <v>318.98508923781748</v>
+        <f t="shared" si="26"/>
+        <v>570.44168877170273</v>
       </c>
       <c r="BV18" s="1">
-        <f t="shared" si="23"/>
-        <v>315.79523834543932</v>
+        <f t="shared" si="26"/>
+        <v>564.73727188398573</v>
       </c>
       <c r="BW18" s="1">
-        <f t="shared" si="23"/>
-        <v>312.6372859619849</v>
+        <f t="shared" si="26"/>
+        <v>559.08989916514588</v>
       </c>
       <c r="BX18" s="1">
-        <f t="shared" si="23"/>
-        <v>309.51091310236507</v>
+        <f t="shared" si="26"/>
+        <v>553.49900017349444</v>
       </c>
       <c r="BY18" s="1">
-        <f t="shared" si="23"/>
-        <v>306.4158039713414</v>
+        <f t="shared" si="26"/>
+        <v>547.96401017175947</v>
       </c>
       <c r="BZ18" s="1">
-        <f t="shared" si="23"/>
-        <v>303.35164593162801</v>
+        <f t="shared" si="26"/>
+        <v>542.4843700700419</v>
       </c>
       <c r="CA18" s="1">
-        <f t="shared" si="23"/>
-        <v>300.31812947231174</v>
+        <f t="shared" si="26"/>
+        <v>537.05952636934148</v>
       </c>
       <c r="CB18" s="1">
-        <f t="shared" si="23"/>
-        <v>297.31494817758863</v>
+        <f t="shared" si="26"/>
+        <v>531.68893110564807</v>
       </c>
       <c r="CC18" s="1">
-        <f t="shared" si="23"/>
-        <v>294.34179869581277</v>
+        <f t="shared" si="26"/>
+        <v>526.37204179459161</v>
       </c>
       <c r="CD18" s="1">
-        <f t="shared" si="23"/>
-        <v>291.39838070885463</v>
+        <f t="shared" si="26"/>
+        <v>521.10832137664568</v>
       </c>
       <c r="CE18" s="1">
-        <f t="shared" si="23"/>
-        <v>288.4843969017661</v>
+        <f t="shared" si="26"/>
+        <v>515.89723816287926</v>
       </c>
       <c r="CF18" s="1">
-        <f t="shared" si="23"/>
-        <v>285.59955293274845</v>
+        <f t="shared" si="26"/>
+        <v>510.73826578125045</v>
       </c>
       <c r="CG18" s="1">
-        <f t="shared" si="23"/>
-        <v>282.74355740342094</v>
+        <f t="shared" si="26"/>
+        <v>505.63088312343791</v>
       </c>
       <c r="CH18" s="1">
-        <f t="shared" si="23"/>
-        <v>279.91612182938673</v>
+        <f t="shared" si="26"/>
+        <v>500.57457429220352</v>
       </c>
       <c r="CI18" s="1">
-        <f t="shared" si="23"/>
-        <v>277.11696061109285</v>
+        <f t="shared" si="26"/>
+        <v>495.56882854928148</v>
       </c>
       <c r="CJ18" s="1">
-        <f t="shared" si="23"/>
-        <v>274.34579100498189</v>
+        <f t="shared" si="26"/>
+        <v>490.61314026378864</v>
       </c>
       <c r="CK18" s="1">
-        <f t="shared" si="23"/>
-        <v>271.60233309493208</v>
+        <f t="shared" si="26"/>
+        <v>485.70700886115077</v>
       </c>
       <c r="CL18" s="1">
-        <f t="shared" si="23"/>
-        <v>268.88630976398275</v>
+        <f t="shared" si="26"/>
+        <v>480.84993877253925</v>
       </c>
       <c r="CM18" s="1">
-        <f t="shared" si="23"/>
-        <v>266.1974466663429</v>
+        <f t="shared" si="26"/>
+        <v>476.04143938481383</v>
       </c>
       <c r="CN18" s="1">
-        <f t="shared" si="23"/>
-        <v>263.53547219967948</v>
+        <f t="shared" si="26"/>
+        <v>471.2810249909657</v>
       </c>
       <c r="CO18" s="1">
-        <f t="shared" si="23"/>
-        <v>260.90011747768267</v>
+        <f t="shared" si="26"/>
+        <v>466.56821474105607</v>
       </c>
       <c r="CP18" s="1">
-        <f t="shared" si="23"/>
-        <v>258.29111630290583</v>
+        <f t="shared" si="26"/>
+        <v>461.9025325936455</v>
       </c>
       <c r="CQ18" s="1">
-        <f t="shared" si="23"/>
-        <v>255.70820513987678</v>
+        <f t="shared" si="26"/>
+        <v>457.28350726770907</v>
       </c>
       <c r="CR18" s="1">
-        <f t="shared" si="23"/>
-        <v>253.15112308847802</v>
+        <f t="shared" si="26"/>
+        <v>452.71067219503198</v>
       </c>
       <c r="CS18" s="1">
-        <f t="shared" si="23"/>
-        <v>250.61961185759324</v>
+        <f t="shared" si="26"/>
+        <v>448.18356547308167</v>
       </c>
       <c r="CT18" s="1">
-        <f t="shared" si="23"/>
-        <v>248.11341573901731</v>
+        <f t="shared" si="26"/>
+        <v>443.70172981835083</v>
       </c>
       <c r="CU18" s="1">
-        <f t="shared" si="23"/>
-        <v>245.63228158162713</v>
+        <f t="shared" si="26"/>
+        <v>439.26471252016734</v>
       </c>
       <c r="CV18" s="1">
-        <f t="shared" si="23"/>
-        <v>243.17595876581086</v>
+        <f t="shared" si="26"/>
+        <v>434.87206539496566</v>
       </c>
       <c r="CW18" s="1">
-        <f t="shared" si="23"/>
-        <v>240.74419917815274</v>
+        <f t="shared" si="26"/>
+        <v>430.52334474101599</v>
       </c>
       <c r="CX18" s="1">
-        <f t="shared" si="23"/>
-        <v>238.33675718637122</v>
+        <f t="shared" si="26"/>
+        <v>426.21811129360583</v>
       </c>
       <c r="CY18" s="1">
-        <f t="shared" si="23"/>
-        <v>235.9533896145075</v>
+        <f t="shared" si="26"/>
+        <v>421.95593018066978</v>
       </c>
       <c r="CZ18" s="1">
-        <f t="shared" ref="CZ18:EZ18" si="24">CY18*(1+$AP$23)</f>
-        <v>233.59385571836242</v>
+        <f t="shared" ref="CZ18:EZ18" si="27">CY18*(1+$AP$23)</f>
+        <v>417.73637087886306</v>
       </c>
       <c r="DA18" s="1">
-        <f t="shared" si="24"/>
-        <v>231.2579171611788</v>
+        <f t="shared" si="27"/>
+        <v>413.55900717007444</v>
       </c>
       <c r="DB18" s="1">
-        <f t="shared" si="24"/>
-        <v>228.94533798956701</v>
+        <f t="shared" si="27"/>
+        <v>409.4234170983737</v>
       </c>
       <c r="DC18" s="1">
-        <f t="shared" si="24"/>
-        <v>226.65588460967135</v>
+        <f t="shared" si="27"/>
+        <v>405.32918292738998</v>
       </c>
       <c r="DD18" s="1">
-        <f t="shared" si="24"/>
-        <v>224.38932576357462</v>
+        <f t="shared" si="27"/>
+        <v>401.27589109811606</v>
       </c>
       <c r="DE18" s="1">
-        <f t="shared" si="24"/>
-        <v>222.14543250593886</v>
+        <f t="shared" si="27"/>
+        <v>397.26313218713489</v>
       </c>
       <c r="DF18" s="1">
-        <f t="shared" si="24"/>
-        <v>219.92397818087946</v>
+        <f t="shared" si="27"/>
+        <v>393.29050086526354</v>
       </c>
       <c r="DG18" s="1">
-        <f t="shared" si="24"/>
-        <v>217.72473839907067</v>
+        <f t="shared" si="27"/>
+        <v>389.35759585661089</v>
       </c>
       <c r="DH18" s="1">
-        <f t="shared" si="24"/>
-        <v>215.54749101507997</v>
+        <f t="shared" si="27"/>
+        <v>385.4640198980448</v>
       </c>
       <c r="DI18" s="1">
-        <f t="shared" si="24"/>
-        <v>213.39201610492916</v>
+        <f t="shared" si="27"/>
+        <v>381.60937969906433</v>
       </c>
       <c r="DJ18" s="1">
-        <f t="shared" si="24"/>
-        <v>211.25809594387985</v>
+        <f t="shared" si="27"/>
+        <v>377.79328590207371</v>
       </c>
       <c r="DK18" s="1">
-        <f t="shared" si="24"/>
-        <v>209.14551498444106</v>
+        <f t="shared" si="27"/>
+        <v>374.01535304305298</v>
       </c>
       <c r="DL18" s="1">
-        <f t="shared" si="24"/>
-        <v>207.05405983459664</v>
+        <f t="shared" si="27"/>
+        <v>370.27519951262246</v>
       </c>
       <c r="DM18" s="1">
-        <f t="shared" si="24"/>
-        <v>204.98351923625069</v>
+        <f t="shared" si="27"/>
+        <v>366.57244751749624</v>
       </c>
       <c r="DN18" s="1">
-        <f t="shared" si="24"/>
-        <v>202.93368404388818</v>
+        <f t="shared" si="27"/>
+        <v>362.90672304232129</v>
       </c>
       <c r="DO18" s="1">
-        <f t="shared" si="24"/>
-        <v>200.9043472034493</v>
+        <f t="shared" si="27"/>
+        <v>359.27765581189806</v>
       </c>
       <c r="DP18" s="1">
-        <f t="shared" si="24"/>
-        <v>198.8953037314148</v>
+        <f t="shared" si="27"/>
+        <v>355.68487925377906</v>
       </c>
       <c r="DQ18" s="1">
-        <f t="shared" si="24"/>
-        <v>196.90635069410064</v>
+        <f t="shared" si="27"/>
+        <v>352.12803046124128</v>
       </c>
       <c r="DR18" s="1">
-        <f t="shared" si="24"/>
-        <v>194.93728718715963</v>
+        <f t="shared" si="27"/>
+        <v>348.60675015662889</v>
       </c>
       <c r="DS18" s="1">
-        <f t="shared" si="24"/>
-        <v>192.98791431528804</v>
+        <f t="shared" si="27"/>
+        <v>345.12068265506258</v>
       </c>
       <c r="DT18" s="1">
-        <f t="shared" si="24"/>
-        <v>191.05803517213516</v>
+        <f t="shared" si="27"/>
+        <v>341.66947582851196</v>
       </c>
       <c r="DU18" s="1">
-        <f t="shared" si="24"/>
-        <v>189.1474548204138</v>
+        <f t="shared" si="27"/>
+        <v>338.25278107022683</v>
       </c>
       <c r="DV18" s="1">
-        <f t="shared" si="24"/>
-        <v>187.25598027220965</v>
+        <f t="shared" si="27"/>
+        <v>334.87025325952453</v>
       </c>
       <c r="DW18" s="1">
-        <f t="shared" si="24"/>
-        <v>185.38342046948756</v>
+        <f t="shared" si="27"/>
+        <v>331.52155072692926</v>
       </c>
       <c r="DX18" s="1">
-        <f t="shared" si="24"/>
-        <v>183.52958626479267</v>
+        <f t="shared" si="27"/>
+        <v>328.20633521965999</v>
       </c>
       <c r="DY18" s="1">
-        <f t="shared" si="24"/>
-        <v>181.69429040214473</v>
+        <f t="shared" si="27"/>
+        <v>324.9242718674634</v>
       </c>
       <c r="DZ18" s="1">
-        <f t="shared" si="24"/>
-        <v>179.87734749812327</v>
+        <f t="shared" si="27"/>
+        <v>321.67502914878878</v>
       </c>
       <c r="EA18" s="1">
-        <f t="shared" si="24"/>
-        <v>178.07857402314204</v>
+        <f t="shared" si="27"/>
+        <v>318.45827885730091</v>
       </c>
       <c r="EB18" s="1">
-        <f t="shared" si="24"/>
-        <v>176.29778828291063</v>
+        <f t="shared" si="27"/>
+        <v>315.27369606872787</v>
       </c>
       <c r="EC18" s="1">
-        <f t="shared" si="24"/>
-        <v>174.53481040008151</v>
+        <f t="shared" si="27"/>
+        <v>312.12095910804061</v>
       </c>
       <c r="ED18" s="1">
-        <f t="shared" si="24"/>
-        <v>172.7894622960807</v>
+        <f t="shared" si="27"/>
+        <v>308.99974951696021</v>
       </c>
       <c r="EE18" s="1">
-        <f t="shared" si="24"/>
-        <v>171.0615676731199</v>
+        <f t="shared" si="27"/>
+        <v>305.90975202179061</v>
       </c>
       <c r="EF18" s="1">
-        <f t="shared" si="24"/>
-        <v>169.35095199638869</v>
+        <f t="shared" si="27"/>
+        <v>302.85065450157271</v>
       </c>
       <c r="EG18" s="1">
-        <f t="shared" si="24"/>
-        <v>167.65744247642479</v>
+        <f t="shared" si="27"/>
+        <v>299.82214795655699</v>
       </c>
       <c r="EH18" s="1">
-        <f t="shared" si="24"/>
-        <v>165.98086805166054</v>
+        <f t="shared" si="27"/>
+        <v>296.8239264769914</v>
       </c>
       <c r="EI18" s="1">
-        <f t="shared" si="24"/>
-        <v>164.32105937114392</v>
+        <f t="shared" si="27"/>
+        <v>293.85568721222148</v>
       </c>
       <c r="EJ18" s="1">
-        <f t="shared" si="24"/>
-        <v>162.67784877743247</v>
+        <f t="shared" si="27"/>
+        <v>290.91713034009928</v>
       </c>
       <c r="EK18" s="1">
-        <f t="shared" si="24"/>
-        <v>161.05107028965816</v>
+        <f t="shared" si="27"/>
+        <v>288.00795903669831</v>
       </c>
       <c r="EL18" s="1">
-        <f t="shared" si="24"/>
-        <v>159.44055958676157</v>
+        <f t="shared" si="27"/>
+        <v>285.12787944633135</v>
       </c>
       <c r="EM18" s="1">
-        <f t="shared" si="24"/>
-        <v>157.84615399089395</v>
+        <f t="shared" si="27"/>
+        <v>282.27660065186802</v>
       </c>
       <c r="EN18" s="1">
-        <f t="shared" si="24"/>
-        <v>156.26769245098501</v>
+        <f t="shared" si="27"/>
+        <v>279.45383464534933</v>
       </c>
       <c r="EO18" s="1">
-        <f t="shared" si="24"/>
-        <v>154.70501552647517</v>
+        <f t="shared" si="27"/>
+        <v>276.65929629889581</v>
       </c>
       <c r="EP18" s="1">
-        <f t="shared" si="24"/>
-        <v>153.15796537121042</v>
+        <f t="shared" si="27"/>
+        <v>273.89270333590684</v>
       </c>
       <c r="EQ18" s="1">
-        <f t="shared" si="24"/>
-        <v>151.62638571749832</v>
+        <f t="shared" si="27"/>
+        <v>271.15377630254778</v>
       </c>
       <c r="ER18" s="1">
-        <f t="shared" si="24"/>
-        <v>150.11012186032335</v>
+        <f t="shared" si="27"/>
+        <v>268.44223853952229</v>
       </c>
       <c r="ES18" s="1">
-        <f t="shared" si="24"/>
-        <v>148.60902064172012</v>
+        <f t="shared" si="27"/>
+        <v>265.75781615412706</v>
       </c>
       <c r="ET18" s="1">
-        <f t="shared" si="24"/>
-        <v>147.12293043530292</v>
+        <f t="shared" si="27"/>
+        <v>263.10023799258579</v>
       </c>
       <c r="EU18" s="1">
-        <f t="shared" si="24"/>
-        <v>145.6517011309499</v>
+        <f t="shared" si="27"/>
+        <v>260.46923561265993</v>
       </c>
       <c r="EV18" s="1">
-        <f t="shared" si="24"/>
-        <v>144.1951841196404</v>
+        <f t="shared" si="27"/>
+        <v>257.86454325653335</v>
       </c>
       <c r="EW18" s="1">
-        <f t="shared" si="24"/>
-        <v>142.75323227844399</v>
+        <f t="shared" si="27"/>
+        <v>255.28589782396801</v>
       </c>
       <c r="EX18" s="1">
-        <f t="shared" si="24"/>
-        <v>141.32569995565956</v>
+        <f t="shared" si="27"/>
+        <v>252.73303884572834</v>
       </c>
       <c r="EY18" s="1">
-        <f t="shared" si="24"/>
-        <v>139.91244295610295</v>
+        <f t="shared" si="27"/>
+        <v>250.20570845727107</v>
       </c>
       <c r="EZ18" s="1">
-        <f t="shared" si="24"/>
-        <v>138.51331852654192</v>
+        <f t="shared" si="27"/>
+        <v>247.70365137269835</v>
       </c>
     </row>
     <row r="19" spans="2:156" x14ac:dyDescent="0.3">
@@ -3457,79 +3522,85 @@
         <v>2</v>
       </c>
       <c r="C19" s="5">
-        <f t="shared" ref="C19:S19" si="25">216.4</f>
+        <f t="shared" ref="C19:S19" si="28">216.4</f>
         <v>216.4</v>
       </c>
       <c r="D19" s="5">
-        <f t="shared" si="25"/>
+        <f t="shared" si="28"/>
         <v>216.4</v>
       </c>
       <c r="E19" s="5">
-        <f t="shared" si="25"/>
+        <f t="shared" si="28"/>
         <v>216.4</v>
       </c>
       <c r="F19" s="5">
-        <f t="shared" si="25"/>
+        <f t="shared" si="28"/>
         <v>216.4</v>
       </c>
       <c r="G19" s="5">
-        <f t="shared" si="25"/>
+        <f t="shared" si="28"/>
         <v>216.4</v>
       </c>
       <c r="H19" s="5">
-        <f t="shared" si="25"/>
+        <f t="shared" si="28"/>
         <v>216.4</v>
       </c>
       <c r="I19" s="5">
-        <f t="shared" si="25"/>
+        <f t="shared" si="28"/>
         <v>216.4</v>
       </c>
       <c r="J19" s="5">
-        <f t="shared" si="25"/>
+        <f t="shared" si="28"/>
         <v>216.4</v>
       </c>
       <c r="K19" s="5">
-        <f t="shared" si="25"/>
+        <f t="shared" si="28"/>
         <v>216.4</v>
       </c>
       <c r="L19" s="5">
-        <f t="shared" si="25"/>
+        <f t="shared" si="28"/>
         <v>216.4</v>
       </c>
       <c r="M19" s="5">
-        <f t="shared" si="25"/>
+        <f t="shared" si="28"/>
         <v>216.4</v>
       </c>
       <c r="N19" s="5">
-        <f t="shared" si="25"/>
+        <f t="shared" si="28"/>
         <v>216.4</v>
       </c>
       <c r="O19" s="5">
-        <f t="shared" si="25"/>
+        <f t="shared" si="28"/>
         <v>216.4</v>
       </c>
       <c r="P19" s="5">
-        <f t="shared" si="25"/>
+        <f t="shared" si="28"/>
         <v>216.4</v>
       </c>
       <c r="Q19" s="5">
-        <f t="shared" si="25"/>
+        <f t="shared" si="28"/>
         <v>216.4</v>
       </c>
       <c r="R19" s="5">
-        <f t="shared" si="25"/>
+        <f t="shared" si="28"/>
         <v>216.4</v>
       </c>
       <c r="S19" s="5">
-        <f t="shared" si="25"/>
+        <f t="shared" si="28"/>
         <v>216.4</v>
       </c>
       <c r="T19" s="5">
         <f>296.8</f>
         <v>296.8</v>
       </c>
-      <c r="U19" s="5"/>
-      <c r="V19" s="5"/>
+      <c r="U19" s="5">
+        <f>354.3</f>
+        <v>354.3</v>
+      </c>
+      <c r="V19" s="5">
+        <f>354.3</f>
+        <v>354.3</v>
+      </c>
       <c r="X19" s="5">
         <f>216.4</f>
         <v>216.4</v>
@@ -3547,48 +3618,48 @@
         <v>216.4</v>
       </c>
       <c r="AB19" s="5">
-        <f t="shared" ref="AB19:AL19" si="26">296.8</f>
-        <v>296.8</v>
+        <f t="shared" ref="AB19:AL19" si="29">354.3</f>
+        <v>354.3</v>
       </c>
       <c r="AC19" s="5">
-        <f t="shared" si="26"/>
-        <v>296.8</v>
+        <f t="shared" si="29"/>
+        <v>354.3</v>
       </c>
       <c r="AD19" s="5">
-        <f t="shared" si="26"/>
-        <v>296.8</v>
+        <f t="shared" si="29"/>
+        <v>354.3</v>
       </c>
       <c r="AE19" s="5">
-        <f t="shared" si="26"/>
-        <v>296.8</v>
+        <f t="shared" si="29"/>
+        <v>354.3</v>
       </c>
       <c r="AF19" s="5">
-        <f t="shared" si="26"/>
-        <v>296.8</v>
+        <f t="shared" si="29"/>
+        <v>354.3</v>
       </c>
       <c r="AG19" s="5">
-        <f t="shared" si="26"/>
-        <v>296.8</v>
+        <f t="shared" si="29"/>
+        <v>354.3</v>
       </c>
       <c r="AH19" s="5">
-        <f t="shared" si="26"/>
-        <v>296.8</v>
+        <f t="shared" si="29"/>
+        <v>354.3</v>
       </c>
       <c r="AI19" s="5">
-        <f t="shared" si="26"/>
-        <v>296.8</v>
+        <f t="shared" si="29"/>
+        <v>354.3</v>
       </c>
       <c r="AJ19" s="5">
-        <f t="shared" si="26"/>
-        <v>296.8</v>
+        <f t="shared" si="29"/>
+        <v>354.3</v>
       </c>
       <c r="AK19" s="5">
-        <f t="shared" si="26"/>
-        <v>296.8</v>
+        <f t="shared" si="29"/>
+        <v>354.3</v>
       </c>
       <c r="AL19" s="5">
-        <f t="shared" si="26"/>
-        <v>296.8</v>
+        <f t="shared" si="29"/>
+        <v>354.3</v>
       </c>
     </row>
     <row r="20" spans="2:156" x14ac:dyDescent="0.3">
@@ -3596,79 +3667,85 @@
         <v>38</v>
       </c>
       <c r="C20" s="7">
-        <f t="shared" ref="C20:R20" si="27">C18/C19</f>
+        <f t="shared" ref="C20:R20" si="30">C18/C19</f>
         <v>-3.4195933456561925E-2</v>
       </c>
       <c r="D20" s="7">
-        <f t="shared" si="27"/>
+        <f t="shared" si="30"/>
         <v>-4.6210720887245843E-2</v>
       </c>
       <c r="E20" s="7">
-        <f t="shared" si="27"/>
+        <f t="shared" si="30"/>
         <v>-6.88539741219963E-2</v>
       </c>
       <c r="F20" s="7">
-        <f t="shared" si="27"/>
+        <f t="shared" si="30"/>
         <v>-0.34195933456561922</v>
       </c>
       <c r="G20" s="7">
-        <f t="shared" si="27"/>
+        <f t="shared" si="30"/>
         <v>-1.9870609981515713E-2</v>
       </c>
       <c r="H20" s="7">
-        <f t="shared" si="27"/>
+        <f t="shared" si="30"/>
         <v>-6.9316081330868598E-3</v>
       </c>
       <c r="I20" s="7">
-        <f t="shared" si="27"/>
+        <f t="shared" si="30"/>
         <v>-0.11044362292051756</v>
       </c>
       <c r="J20" s="7">
-        <f t="shared" si="27"/>
+        <f t="shared" si="30"/>
         <v>-8.6414048059149706E-2</v>
       </c>
       <c r="K20" s="7">
-        <f t="shared" si="27"/>
+        <f t="shared" si="30"/>
         <v>-0.12615526802218113</v>
       </c>
       <c r="L20" s="7">
-        <f t="shared" si="27"/>
+        <f t="shared" si="30"/>
         <v>-0.2019408502772643</v>
       </c>
       <c r="M20" s="7">
-        <f t="shared" si="27"/>
+        <f t="shared" si="30"/>
         <v>-0.20609981515711645</v>
       </c>
       <c r="N20" s="7">
-        <f t="shared" si="27"/>
+        <f t="shared" si="30"/>
         <v>-0.19362292051756008</v>
       </c>
       <c r="O20" s="7">
-        <f t="shared" si="27"/>
+        <f t="shared" si="30"/>
         <v>-0.18299445471349357</v>
       </c>
       <c r="P20" s="7">
-        <f t="shared" si="27"/>
+        <f t="shared" si="30"/>
         <v>-0.17375231053604434</v>
       </c>
       <c r="Q20" s="7">
-        <f t="shared" si="27"/>
+        <f t="shared" si="30"/>
         <v>-0.24260628465804068</v>
       </c>
       <c r="R20" s="7">
-        <f t="shared" si="27"/>
+        <f t="shared" si="30"/>
         <v>-0.93345656192236592</v>
       </c>
       <c r="S20" s="7">
-        <f t="shared" ref="S20:T20" si="28">S18/S19</f>
+        <f t="shared" ref="S20:V20" si="31">S18/S19</f>
         <v>-0.1487985212569316</v>
       </c>
       <c r="T20" s="7">
-        <f t="shared" si="28"/>
+        <f t="shared" si="31"/>
         <v>-0.59838274932614544</v>
       </c>
-      <c r="U20" s="7"/>
-      <c r="V20" s="7"/>
+      <c r="U20" s="7">
+        <f t="shared" si="31"/>
+        <v>-2.9793959920970927</v>
+      </c>
+      <c r="V20" s="7">
+        <f t="shared" si="31"/>
+        <v>-0.77257550098786332</v>
+      </c>
       <c r="X20" s="7">
         <f>X18/X19</f>
         <v>-0.49121996303142329</v>
@@ -3687,47 +3764,47 @@
       </c>
       <c r="AB20" s="7">
         <f>AB18/AB19</f>
-        <v>-0.81140835579514836</v>
+        <v>-0.67156646909398809</v>
       </c>
       <c r="AC20" s="7">
-        <f t="shared" ref="AC20:AL20" si="29">AC18/AC19</f>
-        <v>-0.84244797843665775</v>
+        <f t="shared" ref="AC20:AL20" si="32">AC18/AC19</f>
+        <v>-0.66830132655941299</v>
       </c>
       <c r="AD20" s="7">
-        <f t="shared" si="29"/>
-        <v>-0.79626003840970383</v>
+        <f t="shared" si="32"/>
+        <v>-0.58051216313858345</v>
       </c>
       <c r="AE20" s="7">
-        <f t="shared" si="29"/>
-        <v>-0.68850609136792473</v>
+        <f t="shared" si="32"/>
+        <v>-0.42768419959920989</v>
       </c>
       <c r="AF20" s="7">
-        <f t="shared" si="29"/>
-        <v>-0.46273935129494642</v>
+        <f t="shared" si="32"/>
+        <v>-0.13206972470883455</v>
       </c>
       <c r="AG20" s="7">
-        <f t="shared" si="29"/>
-        <v>-9.5964154390883696E-2</v>
+        <f t="shared" si="32"/>
+        <v>0.33650991977642009</v>
       </c>
       <c r="AH20" s="7">
-        <f t="shared" si="29"/>
-        <v>0.27085549167957895</v>
+        <f t="shared" si="32"/>
+        <v>0.80592545845469643</v>
       </c>
       <c r="AI20" s="7">
-        <f t="shared" si="29"/>
-        <v>0.65035282587475618</v>
+        <f t="shared" si="32"/>
+        <v>1.2917514759233064</v>
       </c>
       <c r="AJ20" s="7">
-        <f t="shared" si="29"/>
-        <v>1.0379995945137923</v>
+        <f t="shared" si="32"/>
+        <v>1.7258114936824536</v>
       </c>
       <c r="AK20" s="7">
-        <f t="shared" si="29"/>
-        <v>1.3312291700987942</v>
+        <f t="shared" si="32"/>
+        <v>2.1010275727725714</v>
       </c>
       <c r="AL20" s="7">
-        <f t="shared" si="29"/>
-        <v>1.5278287396326877</v>
+        <f t="shared" si="32"/>
+        <v>2.2888023656674616</v>
       </c>
     </row>
     <row r="22" spans="2:156" s="1" customFormat="1" x14ac:dyDescent="0.3">
@@ -3739,43 +3816,43 @@
       <c r="E22" s="9"/>
       <c r="F22" s="9"/>
       <c r="G22" s="9">
-        <f t="shared" ref="G22:P22" si="30">G3/C3-1</f>
+        <f t="shared" ref="G22:P22" si="33">G3/C3-1</f>
         <v>19</v>
       </c>
       <c r="H22" s="9">
-        <f t="shared" si="30"/>
+        <f t="shared" si="33"/>
         <v>25</v>
       </c>
       <c r="I22" s="9">
-        <f t="shared" si="30"/>
+        <f t="shared" si="33"/>
         <v>12.999999999999998</v>
       </c>
       <c r="J22" s="9">
-        <f t="shared" si="30"/>
+        <f t="shared" si="33"/>
         <v>1.3749999999999996</v>
       </c>
       <c r="K22" s="9">
-        <f t="shared" si="30"/>
+        <f t="shared" si="33"/>
         <v>1.1499999999999999</v>
       </c>
       <c r="L22" s="9">
-        <f t="shared" si="30"/>
+        <f t="shared" si="33"/>
         <v>1.1153846153846154</v>
       </c>
       <c r="M22" s="9">
-        <f t="shared" si="30"/>
+        <f t="shared" si="33"/>
         <v>1.1785714285714284</v>
       </c>
       <c r="N22" s="9">
-        <f t="shared" si="30"/>
+        <f t="shared" si="33"/>
         <v>0.60526315789473673</v>
       </c>
       <c r="O22" s="9">
-        <f t="shared" si="30"/>
+        <f t="shared" si="33"/>
         <v>0.76744186046511631</v>
       </c>
       <c r="P22" s="9">
-        <f t="shared" si="30"/>
+        <f t="shared" si="33"/>
         <v>1.0727272727272728</v>
       </c>
       <c r="Q22" s="9">
@@ -3787,20 +3864,20 @@
         <v>0.91803278688524581</v>
       </c>
       <c r="S22" s="9">
-        <f t="shared" ref="S22:V22" si="31">S3/O3-1</f>
+        <f t="shared" ref="S22:V22" si="34">S3/O3-1</f>
         <v>0</v>
       </c>
       <c r="T22" s="9">
-        <f t="shared" si="31"/>
+        <f t="shared" si="34"/>
         <v>0.8157894736842104</v>
       </c>
       <c r="U22" s="9">
-        <f t="shared" si="31"/>
-        <v>0.93548387096774177</v>
+        <f t="shared" si="34"/>
+        <v>2.2177419354838706</v>
       </c>
       <c r="V22" s="9">
-        <f t="shared" si="31"/>
-        <v>1.5641025641025643</v>
+        <f t="shared" si="34"/>
+        <v>2.6752136752136755</v>
       </c>
       <c r="X22" s="9"/>
       <c r="Y22" s="9">
@@ -3808,55 +3885,55 @@
         <v>4.5999999999999996</v>
       </c>
       <c r="Z22" s="9">
-        <f t="shared" ref="Z22:AL22" si="32">Z3/Y3-1</f>
+        <f t="shared" ref="Z22:AL22" si="35">Z3/Y3-1</f>
         <v>0.96428571428571441</v>
       </c>
       <c r="AA22" s="9">
-        <f t="shared" si="32"/>
+        <f t="shared" si="35"/>
         <v>0.95909090909090877</v>
       </c>
       <c r="AB22" s="9">
-        <f t="shared" si="32"/>
-        <v>0.90951276102088197</v>
+        <f t="shared" si="35"/>
+        <v>1.5800464037122972</v>
       </c>
       <c r="AC22" s="9">
-        <f t="shared" si="32"/>
-        <v>0.79999999999999982</v>
+        <f t="shared" si="35"/>
+        <v>0.89999999999999991</v>
       </c>
       <c r="AD22" s="9">
-        <f t="shared" si="32"/>
-        <v>0.7</v>
+        <f t="shared" si="35"/>
+        <v>0.75</v>
       </c>
       <c r="AE22" s="9">
-        <f t="shared" si="32"/>
+        <f t="shared" si="35"/>
         <v>0.60000000000000009</v>
       </c>
       <c r="AF22" s="9">
-        <f t="shared" si="32"/>
-        <v>0.50000000000000022</v>
+        <f t="shared" si="35"/>
+        <v>0.5</v>
       </c>
       <c r="AG22" s="9">
-        <f t="shared" si="32"/>
+        <f t="shared" si="35"/>
         <v>0.44999999999999996</v>
       </c>
       <c r="AH22" s="9">
-        <f t="shared" si="32"/>
+        <f t="shared" si="35"/>
         <v>0.25</v>
       </c>
       <c r="AI22" s="9">
-        <f t="shared" si="32"/>
+        <f t="shared" si="35"/>
         <v>0.19999999999999996</v>
       </c>
       <c r="AJ22" s="9">
-        <f t="shared" si="32"/>
+        <f t="shared" si="35"/>
         <v>0.14999999999999991</v>
       </c>
       <c r="AK22" s="9">
-        <f t="shared" si="32"/>
+        <f t="shared" si="35"/>
         <v>0.10000000000000009</v>
       </c>
       <c r="AL22" s="9">
-        <f t="shared" si="32"/>
+        <f t="shared" si="35"/>
         <v>5.0000000000000044E-2</v>
       </c>
     </row>
@@ -3865,59 +3942,59 @@
         <v>45</v>
       </c>
       <c r="C23" s="10">
-        <f t="shared" ref="C23:P23" si="33">C5/C3</f>
+        <f t="shared" ref="C23:P23" si="36">C5/C3</f>
         <v>-1</v>
       </c>
       <c r="D23" s="10">
-        <f t="shared" si="33"/>
+        <f t="shared" si="36"/>
         <v>-1.9999999999999998</v>
       </c>
       <c r="E23" s="10">
-        <f t="shared" si="33"/>
+        <f t="shared" si="36"/>
         <v>0</v>
       </c>
       <c r="F23" s="10">
-        <f t="shared" si="33"/>
+        <f t="shared" si="36"/>
         <v>0.8125</v>
       </c>
       <c r="G23" s="10">
-        <f t="shared" si="33"/>
+        <f t="shared" si="36"/>
         <v>0.7</v>
       </c>
       <c r="H23" s="10">
-        <f t="shared" si="33"/>
+        <f t="shared" si="36"/>
         <v>0.73076923076923084</v>
       </c>
       <c r="I23" s="10">
-        <f t="shared" si="33"/>
+        <f t="shared" si="36"/>
         <v>0.74999999999999989</v>
       </c>
       <c r="J23" s="10">
-        <f t="shared" si="33"/>
+        <f t="shared" si="36"/>
         <v>0.76315789473684215</v>
       </c>
       <c r="K23" s="10">
-        <f t="shared" si="33"/>
+        <f t="shared" si="36"/>
         <v>0.76744186046511631</v>
       </c>
       <c r="L23" s="10">
-        <f t="shared" si="33"/>
+        <f t="shared" si="36"/>
         <v>0.65454545454545454</v>
       </c>
       <c r="M23" s="10">
-        <f t="shared" si="33"/>
+        <f t="shared" si="36"/>
         <v>0.67213114754098358</v>
       </c>
       <c r="N23" s="10">
-        <f t="shared" si="33"/>
+        <f t="shared" si="36"/>
         <v>0.47540983606557369</v>
       </c>
       <c r="O23" s="10">
-        <f t="shared" si="33"/>
+        <f t="shared" si="36"/>
         <v>0.55263157894736836</v>
       </c>
       <c r="P23" s="10">
-        <f t="shared" si="33"/>
+        <f t="shared" si="36"/>
         <v>0.50877192982456143</v>
       </c>
       <c r="Q23" s="10">
@@ -3929,23 +4006,23 @@
         <v>0.57264957264957261</v>
       </c>
       <c r="S23" s="10">
-        <f t="shared" ref="S23:V23" si="34">S5/S3</f>
+        <f t="shared" ref="S23:V23" si="37">S5/S3</f>
         <v>0.43421052631578949</v>
       </c>
       <c r="T23" s="10">
-        <f t="shared" si="34"/>
+        <f t="shared" si="37"/>
         <v>0.59903381642512077</v>
       </c>
       <c r="U23" s="10">
-        <f t="shared" si="34"/>
-        <v>0.52</v>
+        <f t="shared" si="37"/>
+        <v>0.46616541353383456</v>
       </c>
       <c r="V23" s="10">
-        <f t="shared" si="34"/>
-        <v>0.52</v>
+        <f t="shared" si="37"/>
+        <v>0.49</v>
       </c>
       <c r="X23" s="10">
-        <f t="shared" ref="X23" si="35">X5/X3</f>
+        <f t="shared" ref="X23" si="38">X5/X3</f>
         <v>0.5</v>
       </c>
       <c r="Y23" s="10">
@@ -3953,56 +4030,56 @@
         <v>0.74107142857142849</v>
       </c>
       <c r="Z23" s="10">
-        <f t="shared" ref="Z23:AL23" si="36">Z5/Z3</f>
+        <f t="shared" ref="Z23:AL23" si="39">Z5/Z3</f>
         <v>0.63181818181818172</v>
       </c>
       <c r="AA23" s="10">
-        <f t="shared" si="36"/>
+        <f t="shared" si="39"/>
         <v>0.52436194895591637</v>
       </c>
       <c r="AB23" s="10">
-        <f t="shared" si="36"/>
+        <f t="shared" si="39"/>
         <v>0.5</v>
       </c>
       <c r="AC23" s="10">
-        <f t="shared" si="36"/>
+        <f t="shared" si="39"/>
         <v>0.51</v>
       </c>
       <c r="AD23" s="10">
-        <f t="shared" si="36"/>
+        <f t="shared" si="39"/>
         <v>0.52</v>
       </c>
       <c r="AE23" s="10">
-        <f t="shared" si="36"/>
+        <f t="shared" si="39"/>
         <v>0.52</v>
       </c>
       <c r="AF23" s="10">
-        <f t="shared" si="36"/>
+        <f t="shared" si="39"/>
         <v>0.54</v>
       </c>
       <c r="AG23" s="10">
-        <f t="shared" si="36"/>
+        <f t="shared" si="39"/>
         <v>0.56000000000000005</v>
       </c>
       <c r="AH23" s="10">
-        <f t="shared" si="36"/>
+        <f t="shared" si="39"/>
         <v>0.57999999999999996</v>
       </c>
       <c r="AI23" s="10">
-        <f t="shared" si="36"/>
+        <f t="shared" si="39"/>
         <v>0.6</v>
       </c>
       <c r="AJ23" s="10">
-        <f t="shared" si="36"/>
+        <f t="shared" si="39"/>
+        <v>0.61</v>
+      </c>
+      <c r="AK23" s="10">
+        <f t="shared" si="39"/>
         <v>0.62</v>
       </c>
-      <c r="AK23" s="10">
-        <f t="shared" si="36"/>
-        <v>0.63</v>
-      </c>
       <c r="AL23" s="10">
-        <f t="shared" si="36"/>
-        <v>0.64</v>
+        <f t="shared" si="39"/>
+        <v>0.62</v>
       </c>
       <c r="AO23" t="s">
         <v>52</v>
@@ -4020,43 +4097,43 @@
       <c r="E24" s="10"/>
       <c r="F24" s="10"/>
       <c r="G24" s="10">
-        <f t="shared" ref="G24:P24" si="37">G6/C6-1</f>
+        <f t="shared" ref="G24:P24" si="40">G6/C6-1</f>
         <v>0.9729729729729728</v>
       </c>
       <c r="H24" s="10">
-        <f t="shared" si="37"/>
+        <f t="shared" si="40"/>
         <v>0.76363636363636345</v>
       </c>
       <c r="I24" s="10">
-        <f t="shared" si="37"/>
+        <f t="shared" si="40"/>
         <v>1.1451612903225805</v>
       </c>
       <c r="J24" s="10">
-        <f t="shared" si="37"/>
+        <f t="shared" si="40"/>
         <v>1.7959183673469385</v>
       </c>
       <c r="K24" s="10">
-        <f t="shared" si="37"/>
+        <f t="shared" si="40"/>
         <v>1.2191780821917808</v>
       </c>
       <c r="L24" s="10">
-        <f t="shared" si="37"/>
+        <f t="shared" si="40"/>
         <v>1.0515463917525771</v>
       </c>
       <c r="M24" s="10">
-        <f t="shared" si="37"/>
+        <f t="shared" si="40"/>
         <v>0.84962406015037595</v>
       </c>
       <c r="N24" s="10">
-        <f t="shared" si="37"/>
+        <f t="shared" si="40"/>
         <v>1.3065693430656937</v>
       </c>
       <c r="O24" s="10">
-        <f t="shared" si="37"/>
+        <f t="shared" si="40"/>
         <v>1</v>
       </c>
       <c r="P24" s="10">
-        <f t="shared" si="37"/>
+        <f t="shared" si="40"/>
         <v>0.56783919597989962</v>
       </c>
       <c r="Q24" s="10">
@@ -4068,20 +4145,20 @@
         <v>0.26898734177215178</v>
       </c>
       <c r="S24" s="10">
-        <f t="shared" ref="S24:V24" si="38">S6/O6-1</f>
+        <f t="shared" ref="S24:V24" si="41">S6/O6-1</f>
         <v>0.23456790123456805</v>
       </c>
       <c r="T24" s="10">
-        <f t="shared" si="38"/>
+        <f t="shared" si="41"/>
         <v>2.3141025641025643</v>
       </c>
       <c r="U24" s="10">
-        <f t="shared" si="38"/>
-        <v>-1</v>
+        <f t="shared" si="41"/>
+        <v>0.99698795180722866</v>
       </c>
       <c r="V24" s="10">
-        <f t="shared" si="38"/>
-        <v>-1</v>
+        <f t="shared" si="41"/>
+        <v>0.99501246882793004</v>
       </c>
       <c r="X24" s="10"/>
       <c r="Y24" s="10">
@@ -4089,62 +4166,62 @@
         <v>1.1674876847290645</v>
       </c>
       <c r="Z24" s="10">
-        <f t="shared" ref="Z24:AL24" si="39">Z6/Y6-1</f>
+        <f t="shared" ref="Z24:AL24" si="42">Z6/Y6-1</f>
         <v>1.0977272727272727</v>
       </c>
       <c r="AA24" s="10">
-        <f t="shared" si="39"/>
+        <f t="shared" si="42"/>
         <v>0.48320693391115932</v>
       </c>
       <c r="AB24" s="10">
-        <f t="shared" si="39"/>
+        <f t="shared" si="42"/>
         <v>0.17999999999999994</v>
       </c>
       <c r="AC24" s="10">
-        <f t="shared" si="39"/>
+        <f t="shared" si="42"/>
         <v>0.12000000000000011</v>
       </c>
       <c r="AD24" s="10">
-        <f t="shared" si="39"/>
+        <f t="shared" si="42"/>
         <v>7.0000000000000062E-2</v>
       </c>
       <c r="AE24" s="10">
-        <f t="shared" si="39"/>
+        <f t="shared" si="42"/>
         <v>5.0000000000000044E-2</v>
       </c>
       <c r="AF24" s="10">
-        <f t="shared" si="39"/>
+        <f t="shared" si="42"/>
         <v>5.0000000000000044E-2</v>
       </c>
       <c r="AG24" s="10">
-        <f t="shared" si="39"/>
+        <f t="shared" si="42"/>
         <v>5.0000000000000044E-2</v>
       </c>
       <c r="AH24" s="10">
-        <f t="shared" si="39"/>
+        <f t="shared" si="42"/>
         <v>5.0000000000000044E-2</v>
       </c>
       <c r="AI24" s="10">
-        <f t="shared" si="39"/>
+        <f t="shared" si="42"/>
         <v>5.0000000000000044E-2</v>
       </c>
       <c r="AJ24" s="10">
-        <f t="shared" si="39"/>
+        <f t="shared" si="42"/>
         <v>5.0000000000000044E-2</v>
       </c>
       <c r="AK24" s="10">
-        <f t="shared" si="39"/>
+        <f t="shared" si="42"/>
         <v>5.0000000000000044E-2</v>
       </c>
       <c r="AL24" s="10">
-        <f t="shared" si="39"/>
+        <f t="shared" si="42"/>
         <v>5.0000000000000044E-2</v>
       </c>
       <c r="AO24" t="s">
         <v>53</v>
       </c>
       <c r="AP24" s="10">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="25" spans="2:156" x14ac:dyDescent="0.3">
@@ -4152,59 +4229,59 @@
         <v>47</v>
       </c>
       <c r="C25" s="10">
-        <f t="shared" ref="C25:P25" si="40">C7/C3</f>
+        <f t="shared" ref="C25:P25" si="43">C7/C3</f>
         <v>2</v>
       </c>
       <c r="D25" s="10">
-        <f t="shared" si="40"/>
+        <f t="shared" si="43"/>
         <v>9</v>
       </c>
       <c r="E25" s="10">
-        <f t="shared" si="40"/>
+        <f t="shared" si="43"/>
         <v>6.5</v>
       </c>
       <c r="F25" s="10">
-        <f t="shared" si="40"/>
+        <f t="shared" si="43"/>
         <v>0.5</v>
       </c>
       <c r="G25" s="10">
-        <f t="shared" si="40"/>
+        <f t="shared" si="43"/>
         <v>0.95</v>
       </c>
       <c r="H25" s="10">
-        <f t="shared" si="40"/>
+        <f t="shared" si="43"/>
         <v>0.80769230769230771</v>
       </c>
       <c r="I25" s="10">
-        <f t="shared" si="40"/>
+        <f t="shared" si="43"/>
         <v>0.7142857142857143</v>
       </c>
       <c r="J25" s="10">
-        <f t="shared" si="40"/>
+        <f t="shared" si="43"/>
         <v>0.63157894736842102</v>
       </c>
       <c r="K25" s="10">
-        <f t="shared" si="40"/>
+        <f t="shared" si="43"/>
         <v>0.62790697674418616</v>
       </c>
       <c r="L25" s="10">
-        <f t="shared" si="40"/>
+        <f t="shared" si="43"/>
         <v>0.65454545454545454</v>
       </c>
       <c r="M25" s="10">
-        <f t="shared" si="40"/>
+        <f t="shared" si="43"/>
         <v>0.81967213114754101</v>
       </c>
       <c r="N25" s="10">
-        <f t="shared" si="40"/>
+        <f t="shared" si="43"/>
         <v>1.1475409836065575</v>
       </c>
       <c r="O25" s="10">
-        <f t="shared" si="40"/>
+        <f t="shared" si="43"/>
         <v>0.88157894736842113</v>
       </c>
       <c r="P25" s="10">
-        <f t="shared" si="40"/>
+        <f t="shared" si="43"/>
         <v>0.53508771929824561</v>
       </c>
       <c r="Q25" s="10">
@@ -4216,23 +4293,23 @@
         <v>0.76068376068376076</v>
       </c>
       <c r="S25" s="10">
-        <f t="shared" ref="S25:V25" si="41">S7/S3</f>
+        <f t="shared" ref="S25:V25" si="44">S7/S3</f>
         <v>1.131578947368421</v>
       </c>
       <c r="T25" s="10">
-        <f t="shared" si="41"/>
+        <f t="shared" si="44"/>
         <v>0.52657004830917875</v>
       </c>
       <c r="U25" s="10">
-        <f t="shared" si="41"/>
-        <v>0</v>
+        <f t="shared" si="44"/>
+        <v>0.36090225563909778</v>
       </c>
       <c r="V25" s="10">
-        <f t="shared" si="41"/>
-        <v>0</v>
+        <f t="shared" si="44"/>
+        <v>0.39999999999999997</v>
       </c>
       <c r="X25" s="10">
-        <f t="shared" ref="X25" si="42">X7/X3</f>
+        <f t="shared" ref="X25" si="45">X7/X3</f>
         <v>1.6</v>
       </c>
       <c r="Y25" s="10">
@@ -4240,55 +4317,55 @@
         <v>0.75000000000000011</v>
       </c>
       <c r="Z25" s="10">
-        <f t="shared" ref="Z25:AL25" si="43">Z7/Z3</f>
+        <f t="shared" ref="Z25:AL25" si="46">Z7/Z3</f>
         <v>0.8318181818181819</v>
       </c>
       <c r="AA25" s="10">
-        <f t="shared" si="43"/>
+        <f t="shared" si="46"/>
         <v>0.65661252900232026</v>
       </c>
       <c r="AB25" s="10">
-        <f t="shared" si="43"/>
+        <f t="shared" si="46"/>
         <v>0.4</v>
       </c>
       <c r="AC25" s="10">
-        <f t="shared" si="43"/>
+        <f t="shared" si="46"/>
         <v>0.3</v>
       </c>
       <c r="AD25" s="10">
-        <f t="shared" si="43"/>
+        <f t="shared" si="46"/>
         <v>0.26</v>
       </c>
       <c r="AE25" s="10">
-        <f t="shared" si="43"/>
+        <f t="shared" si="46"/>
         <v>0.24</v>
       </c>
       <c r="AF25" s="10">
-        <f t="shared" si="43"/>
-        <v>0.21999999999999997</v>
+        <f t="shared" si="46"/>
+        <v>0.22000000000000003</v>
       </c>
       <c r="AG25" s="10">
-        <f t="shared" si="43"/>
-        <v>0.2</v>
+        <f t="shared" si="46"/>
+        <v>0.20000000000000004</v>
       </c>
       <c r="AH25" s="10">
-        <f t="shared" si="43"/>
+        <f t="shared" si="46"/>
         <v>0.18</v>
       </c>
       <c r="AI25" s="10">
-        <f t="shared" si="43"/>
+        <f t="shared" si="46"/>
         <v>0.17</v>
       </c>
       <c r="AJ25" s="10">
-        <f t="shared" si="43"/>
+        <f t="shared" si="46"/>
         <v>0.16</v>
       </c>
       <c r="AK25" s="10">
-        <f t="shared" si="43"/>
+        <f t="shared" si="46"/>
         <v>0.15</v>
       </c>
       <c r="AL25" s="10">
-        <f t="shared" si="43"/>
+        <f t="shared" si="46"/>
         <v>0.14000000000000001</v>
       </c>
       <c r="AO25" t="s">
@@ -4296,7 +4373,7 @@
       </c>
       <c r="AP25" s="5">
         <f>NPV(AP24,AA18:EZ18)</f>
-        <v>1071.9648925424406</v>
+        <v>3936.6052737763594</v>
       </c>
     </row>
     <row r="26" spans="2:156" x14ac:dyDescent="0.3">
@@ -4308,43 +4385,43 @@
       <c r="E26" s="10"/>
       <c r="F26" s="10"/>
       <c r="G26" s="10">
-        <f t="shared" ref="G26:P26" si="44">G8/C8-1</f>
+        <f t="shared" ref="G26:P26" si="47">G8/C8-1</f>
         <v>2.0666666666666664</v>
       </c>
       <c r="H26" s="10">
-        <f t="shared" si="44"/>
+        <f t="shared" si="47"/>
         <v>1.6206896551724137</v>
       </c>
       <c r="I26" s="10">
-        <f t="shared" si="44"/>
+        <f t="shared" si="47"/>
         <v>3.04</v>
       </c>
       <c r="J26" s="10">
-        <f t="shared" si="44"/>
+        <f t="shared" si="47"/>
         <v>0.68518518518518512</v>
       </c>
       <c r="K26" s="10">
-        <f t="shared" si="44"/>
+        <f t="shared" si="47"/>
         <v>0.15217391304347827</v>
       </c>
       <c r="L26" s="10">
-        <f t="shared" si="44"/>
+        <f t="shared" si="47"/>
         <v>0.4342105263157896</v>
       </c>
       <c r="M26" s="10">
-        <f t="shared" si="44"/>
+        <f t="shared" si="47"/>
         <v>0.37623762376237635</v>
       </c>
       <c r="N26" s="10">
-        <f t="shared" si="44"/>
+        <f t="shared" si="47"/>
         <v>0.68131868131868156</v>
       </c>
       <c r="O26" s="10">
-        <f t="shared" si="44"/>
+        <f t="shared" si="47"/>
         <v>0.32075471698113223</v>
       </c>
       <c r="P26" s="10">
-        <f t="shared" si="44"/>
+        <f t="shared" si="47"/>
         <v>0.201834862385321</v>
       </c>
       <c r="Q26" s="10">
@@ -4356,20 +4433,20 @@
         <v>0.94117647058823506</v>
       </c>
       <c r="S26" s="10">
-        <f t="shared" ref="S26:V26" si="45">S8/O8-1</f>
+        <f t="shared" ref="S26:V26" si="48">S8/O8-1</f>
         <v>0.7</v>
       </c>
       <c r="T26" s="10">
-        <f t="shared" si="45"/>
+        <f t="shared" si="48"/>
         <v>2.6717557251908399</v>
       </c>
       <c r="U26" s="10">
-        <f t="shared" si="45"/>
-        <v>-1</v>
+        <f t="shared" si="48"/>
+        <v>4.7692307692307692</v>
       </c>
       <c r="V26" s="10">
-        <f t="shared" si="45"/>
-        <v>-1</v>
+        <f t="shared" si="48"/>
+        <v>2.3670033670033672</v>
       </c>
       <c r="X26" s="10"/>
       <c r="Y26" s="10">
@@ -4377,55 +4454,55 @@
         <v>1.6086956521739131</v>
       </c>
       <c r="Z26" s="10">
-        <f t="shared" ref="Z26:AL26" si="46">Z8/Y8-1</f>
+        <f t="shared" ref="Z26:AL26" si="49">Z8/Y8-1</f>
         <v>0.40833333333333344</v>
       </c>
       <c r="AA26" s="10">
-        <f t="shared" si="46"/>
+        <f t="shared" si="49"/>
         <v>0.4023668639053255</v>
       </c>
       <c r="AB26" s="10">
-        <f t="shared" si="46"/>
+        <f t="shared" si="49"/>
         <v>0.10000000000000009</v>
       </c>
       <c r="AC26" s="10">
-        <f t="shared" si="46"/>
+        <f t="shared" si="49"/>
         <v>8.0000000000000071E-2</v>
       </c>
       <c r="AD26" s="10">
-        <f t="shared" si="46"/>
+        <f t="shared" si="49"/>
         <v>6.0000000000000053E-2</v>
       </c>
       <c r="AE26" s="10">
-        <f t="shared" si="46"/>
+        <f t="shared" si="49"/>
         <v>4.0000000000000036E-2</v>
       </c>
       <c r="AF26" s="10">
-        <f t="shared" si="46"/>
+        <f t="shared" si="49"/>
         <v>3.0000000000000027E-2</v>
       </c>
       <c r="AG26" s="10">
-        <f t="shared" si="46"/>
+        <f t="shared" si="49"/>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="AH26" s="10">
-        <f t="shared" si="46"/>
+        <f t="shared" si="49"/>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="AI26" s="10">
-        <f t="shared" si="46"/>
+        <f t="shared" si="49"/>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="AJ26" s="10">
-        <f t="shared" si="46"/>
+        <f t="shared" si="49"/>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="AK26" s="10">
-        <f t="shared" si="46"/>
+        <f t="shared" si="49"/>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="AL26" s="10">
-        <f t="shared" si="46"/>
+        <f t="shared" si="49"/>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="AO26" t="s">
@@ -4433,7 +4510,7 @@
       </c>
       <c r="AP26" s="5">
         <f>Main!D8</f>
-        <v>655.9</v>
+        <v>-283.29999999999995</v>
       </c>
     </row>
     <row r="27" spans="2:156" x14ac:dyDescent="0.3">
@@ -4445,43 +4522,43 @@
       <c r="E27" s="10"/>
       <c r="F27" s="10"/>
       <c r="G27" s="10">
-        <f t="shared" ref="G27:P27" si="47">G9/C9-1</f>
+        <f t="shared" ref="G27:P27" si="50">G9/C9-1</f>
         <v>2.25</v>
       </c>
       <c r="H27" s="10">
-        <f t="shared" si="47"/>
+        <f t="shared" si="50"/>
         <v>2</v>
       </c>
       <c r="I27" s="10">
-        <f t="shared" si="47"/>
+        <f t="shared" si="50"/>
         <v>1.5</v>
       </c>
       <c r="J27" s="10">
-        <f t="shared" si="47"/>
+        <f t="shared" si="50"/>
         <v>0.39999999999999991</v>
       </c>
       <c r="K27" s="10">
-        <f t="shared" si="47"/>
+        <f t="shared" si="50"/>
         <v>0.38461538461538458</v>
       </c>
       <c r="L27" s="10">
-        <f t="shared" si="47"/>
+        <f t="shared" si="50"/>
         <v>0.53333333333333321</v>
       </c>
       <c r="M27" s="10">
-        <f t="shared" si="47"/>
+        <f t="shared" si="50"/>
         <v>0.8</v>
       </c>
       <c r="N27" s="10">
-        <f t="shared" si="47"/>
+        <f t="shared" si="50"/>
         <v>1.5</v>
       </c>
       <c r="O27" s="10">
-        <f t="shared" si="47"/>
+        <f t="shared" si="50"/>
         <v>1.2222222222222223</v>
       </c>
       <c r="P27" s="10">
-        <f t="shared" si="47"/>
+        <f t="shared" si="50"/>
         <v>0.86956521739130443</v>
       </c>
       <c r="Q27" s="10">
@@ -4493,20 +4570,20 @@
         <v>0.5714285714285714</v>
       </c>
       <c r="S27" s="10">
-        <f t="shared" ref="S27:V27" si="48">S9/O9-1</f>
+        <f t="shared" ref="S27:V27" si="51">S9/O9-1</f>
         <v>0.64999999999999991</v>
       </c>
       <c r="T27" s="10">
-        <f t="shared" si="48"/>
+        <f t="shared" si="51"/>
         <v>1.4651162790697674</v>
       </c>
       <c r="U27" s="10">
-        <f t="shared" si="48"/>
-        <v>-1</v>
+        <f t="shared" si="51"/>
+        <v>3.9387755102040813</v>
       </c>
       <c r="V27" s="10">
-        <f t="shared" si="48"/>
-        <v>-1</v>
+        <f t="shared" si="51"/>
+        <v>4.4545454545454541</v>
       </c>
       <c r="X27" s="10"/>
       <c r="Y27" s="10">
@@ -4514,55 +4591,55 @@
         <v>1.2799999999999998</v>
       </c>
       <c r="Z27" s="10">
-        <f t="shared" ref="Z27:AL27" si="49">Z9/Y9-1</f>
+        <f t="shared" ref="Z27:AL27" si="52">Z9/Y9-1</f>
         <v>0.80701754385964941</v>
       </c>
       <c r="AA27" s="10">
-        <f t="shared" si="49"/>
+        <f t="shared" si="52"/>
         <v>0.81553398058252435</v>
       </c>
       <c r="AB27" s="10">
-        <f t="shared" si="49"/>
+        <f t="shared" si="52"/>
         <v>0.5</v>
       </c>
       <c r="AC27" s="10">
-        <f t="shared" si="49"/>
+        <f t="shared" si="52"/>
         <v>0.25</v>
       </c>
       <c r="AD27" s="10">
-        <f t="shared" si="49"/>
+        <f t="shared" si="52"/>
         <v>0.10000000000000009</v>
       </c>
       <c r="AE27" s="10">
-        <f t="shared" si="49"/>
+        <f t="shared" si="52"/>
         <v>7.0000000000000062E-2</v>
       </c>
       <c r="AF27" s="10">
-        <f t="shared" si="49"/>
+        <f t="shared" si="52"/>
         <v>3.0000000000000027E-2</v>
       </c>
       <c r="AG27" s="10">
-        <f t="shared" si="49"/>
+        <f t="shared" si="52"/>
         <v>3.0000000000000027E-2</v>
       </c>
       <c r="AH27" s="10">
-        <f t="shared" si="49"/>
+        <f t="shared" si="52"/>
         <v>3.0000000000000027E-2</v>
       </c>
       <c r="AI27" s="10">
-        <f t="shared" si="49"/>
+        <f t="shared" si="52"/>
         <v>3.0000000000000027E-2</v>
       </c>
       <c r="AJ27" s="10">
-        <f t="shared" si="49"/>
+        <f t="shared" si="52"/>
         <v>3.0000000000000027E-2</v>
       </c>
       <c r="AK27" s="10">
-        <f t="shared" si="49"/>
+        <f t="shared" si="52"/>
         <v>3.0000000000000027E-2</v>
       </c>
       <c r="AL27" s="10">
-        <f t="shared" si="49"/>
+        <f t="shared" si="52"/>
         <v>3.0000000000000027E-2</v>
       </c>
       <c r="AO27" t="s">
@@ -4570,7 +4647,7 @@
       </c>
       <c r="AP27" s="5">
         <f>AP25+AP26</f>
-        <v>1727.8648925424404</v>
+        <v>3653.3052737763592</v>
       </c>
     </row>
     <row r="28" spans="2:156" x14ac:dyDescent="0.3">
@@ -4578,59 +4655,59 @@
         <v>50</v>
       </c>
       <c r="C28" s="10">
-        <f t="shared" ref="C28:P28" si="50">C11/C3</f>
+        <f t="shared" ref="C28:P28" si="53">C11/C3</f>
         <v>-74</v>
       </c>
       <c r="D28" s="10">
-        <f t="shared" si="50"/>
+        <f t="shared" si="53"/>
         <v>-100</v>
       </c>
       <c r="E28" s="10">
-        <f t="shared" si="50"/>
+        <f t="shared" si="53"/>
         <v>-52.999999999999993</v>
       </c>
       <c r="F28" s="10">
-        <f t="shared" si="50"/>
+        <f t="shared" si="53"/>
         <v>-6.75</v>
       </c>
       <c r="G28" s="10">
-        <f t="shared" si="50"/>
+        <f t="shared" si="53"/>
         <v>-9.15</v>
       </c>
       <c r="H28" s="10">
-        <f t="shared" si="50"/>
+        <f t="shared" si="53"/>
         <v>-7.3076923076923075</v>
       </c>
       <c r="I28" s="10">
-        <f t="shared" si="50"/>
+        <f t="shared" si="53"/>
         <v>-8.8571428571428559</v>
       </c>
       <c r="J28" s="10">
-        <f t="shared" si="50"/>
+        <f t="shared" si="53"/>
         <v>-6.2368421052631566</v>
       </c>
       <c r="K28" s="10">
-        <f t="shared" si="50"/>
+        <f t="shared" si="53"/>
         <v>-6.5116279069767442</v>
       </c>
       <c r="L28" s="10">
-        <f t="shared" si="50"/>
+        <f t="shared" si="53"/>
         <v>-6.0181818181818167</v>
       </c>
       <c r="M28" s="10">
-        <f t="shared" si="50"/>
+        <f t="shared" si="53"/>
         <v>-6.9016393442622954</v>
       </c>
       <c r="N28" s="10">
-        <f t="shared" si="50"/>
+        <f t="shared" si="53"/>
         <v>-8.9344262295081975</v>
       </c>
       <c r="O28" s="10">
-        <f t="shared" si="50"/>
+        <f t="shared" si="53"/>
         <v>-6.9605263157894743</v>
       </c>
       <c r="P28" s="10">
-        <f t="shared" si="50"/>
+        <f t="shared" si="53"/>
         <v>-4.2894736842105257</v>
       </c>
       <c r="Q28" s="10">
@@ -4642,23 +4719,23 @@
         <v>-6.6239316239316244</v>
       </c>
       <c r="S28" s="10">
-        <f t="shared" ref="S28:V28" si="51">S11/S3</f>
+        <f t="shared" ref="S28:V28" si="54">S11/S3</f>
         <v>-9.9605263157894743</v>
       </c>
       <c r="T28" s="10">
-        <f t="shared" si="51"/>
+        <f t="shared" si="54"/>
         <v>-7.7584541062801931</v>
       </c>
       <c r="U28" s="10">
-        <f t="shared" si="51"/>
-        <v>0</v>
+        <f t="shared" si="54"/>
+        <v>-4.2305764411027562</v>
       </c>
       <c r="V28" s="10">
-        <f t="shared" si="51"/>
-        <v>0</v>
+        <f t="shared" si="54"/>
+        <v>-4.7937209302325581</v>
       </c>
       <c r="X28" s="10">
-        <f t="shared" ref="X28" si="52">X11/X3</f>
+        <f t="shared" ref="X28" si="55">X11/X3</f>
         <v>-19.399999999999999</v>
       </c>
       <c r="Y28" s="10">
@@ -4666,63 +4743,63 @@
         <v>-7.6607142857142874</v>
       </c>
       <c r="Z28" s="10">
-        <f t="shared" ref="Z28:AL28" si="53">Z11/Z3</f>
+        <f t="shared" ref="Z28:AL28" si="56">Z11/Z3</f>
         <v>-7.1681818181818189</v>
       </c>
       <c r="AA28" s="10">
-        <f t="shared" si="53"/>
+        <f t="shared" si="56"/>
         <v>-5.3921113689095135</v>
       </c>
       <c r="AB28" s="10">
-        <f t="shared" si="53"/>
-        <v>-3.1539732685297701</v>
+        <f t="shared" si="56"/>
+        <v>-2.3082913669064751</v>
       </c>
       <c r="AC28" s="10">
-        <f t="shared" si="53"/>
-        <v>-1.8181918455515056</v>
+        <f t="shared" si="56"/>
+        <v>-1.2120765808405911</v>
       </c>
       <c r="AD28" s="10">
-        <f t="shared" si="53"/>
-        <v>-1.0173905875999656</v>
+        <f t="shared" si="56"/>
+        <v>-0.61005866500784378</v>
       </c>
       <c r="AE28" s="10">
-        <f t="shared" si="53"/>
-        <v>-0.55797990240750028</v>
+        <f t="shared" si="56"/>
+        <v>-0.29076643766565713</v>
       </c>
       <c r="AF28" s="10">
-        <f t="shared" si="53"/>
-        <v>-0.26213913245916043</v>
+        <f t="shared" si="56"/>
+        <v>-7.6507694164142465E-2</v>
       </c>
       <c r="AG28" s="10">
-        <f t="shared" si="53"/>
-        <v>-5.7295901703140674E-2</v>
+        <f t="shared" si="56"/>
+        <v>7.5770635329919497E-2</v>
       </c>
       <c r="AH28" s="10">
-        <f t="shared" si="53"/>
-        <v>5.2949753029306837E-2</v>
+        <f t="shared" si="56"/>
+        <v>0.16361648700003939</v>
       </c>
       <c r="AI28" s="10">
-        <f t="shared" si="53"/>
-        <v>0.12929425867791872</v>
+        <f t="shared" si="56"/>
+        <v>0.22518274332484903</v>
       </c>
       <c r="AJ28" s="10">
-        <f t="shared" si="53"/>
-        <v>0.18807680138917118</v>
+        <f t="shared" si="56"/>
+        <v>0.2647871626230488</v>
       </c>
       <c r="AK28" s="10">
-        <f t="shared" si="53"/>
-        <v>0.22288517090685361</v>
+        <f t="shared" si="56"/>
+        <v>0.29487346695202088</v>
       </c>
       <c r="AL28" s="10">
-        <f t="shared" si="53"/>
-        <v>0.24526892556182686</v>
+        <f t="shared" si="56"/>
+        <v>0.30649709437885903</v>
       </c>
       <c r="AO28" t="s">
         <v>57</v>
       </c>
       <c r="AP28" s="4">
         <f>AP27/AL19</f>
-        <v>5.821647212070217</v>
+        <v>10.311332977071293</v>
       </c>
     </row>
     <row r="29" spans="2:156" x14ac:dyDescent="0.3">
@@ -4730,59 +4807,59 @@
         <v>36</v>
       </c>
       <c r="C29" s="10">
-        <f t="shared" ref="C29:P29" si="54">C17/C16</f>
+        <f t="shared" ref="C29:P29" si="57">C17/C16</f>
         <v>0</v>
       </c>
       <c r="D29" s="10">
-        <f t="shared" si="54"/>
+        <f t="shared" si="57"/>
         <v>0</v>
       </c>
       <c r="E29" s="10">
-        <f t="shared" si="54"/>
+        <f t="shared" si="57"/>
         <v>0</v>
       </c>
       <c r="F29" s="10">
-        <f t="shared" si="54"/>
+        <f t="shared" si="57"/>
         <v>0</v>
       </c>
       <c r="G29" s="10">
-        <f t="shared" si="54"/>
+        <f t="shared" si="57"/>
         <v>0</v>
       </c>
       <c r="H29" s="10">
-        <f t="shared" si="54"/>
+        <f t="shared" si="57"/>
         <v>0</v>
       </c>
       <c r="I29" s="10">
-        <f t="shared" si="54"/>
+        <f t="shared" si="57"/>
         <v>0</v>
       </c>
       <c r="J29" s="10">
-        <f t="shared" si="54"/>
+        <f t="shared" si="57"/>
         <v>0</v>
       </c>
       <c r="K29" s="10">
-        <f t="shared" si="54"/>
+        <f t="shared" si="57"/>
         <v>0</v>
       </c>
       <c r="L29" s="10">
-        <f t="shared" si="54"/>
+        <f t="shared" si="57"/>
         <v>0</v>
       </c>
       <c r="M29" s="10">
-        <f t="shared" si="54"/>
+        <f t="shared" si="57"/>
         <v>0</v>
       </c>
       <c r="N29" s="10">
-        <f t="shared" si="54"/>
+        <f t="shared" si="57"/>
         <v>0</v>
       </c>
       <c r="O29" s="10">
-        <f t="shared" si="54"/>
+        <f t="shared" si="57"/>
         <v>0</v>
       </c>
       <c r="P29" s="10">
-        <f t="shared" si="54"/>
+        <f t="shared" si="57"/>
         <v>0</v>
       </c>
       <c r="Q29" s="10">
@@ -4794,23 +4871,23 @@
         <v>0</v>
       </c>
       <c r="S29" s="10">
-        <f t="shared" ref="S29:V29" si="55">S17/S16</f>
+        <f t="shared" ref="S29:V29" si="58">S17/S16</f>
         <v>0</v>
       </c>
       <c r="T29" s="10">
-        <f t="shared" si="55"/>
+        <f t="shared" si="58"/>
         <v>7.931570762052878E-2</v>
       </c>
-      <c r="U29" s="10" t="e">
-        <f t="shared" si="55"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="V29" s="10" t="e">
-        <f t="shared" si="55"/>
-        <v>#DIV/0!</v>
+      <c r="U29" s="10">
+        <f t="shared" si="58"/>
+        <v>4.1509433962264152E-3</v>
+      </c>
+      <c r="V29" s="10">
+        <f t="shared" si="58"/>
+        <v>0.05</v>
       </c>
       <c r="X29" s="10">
-        <f t="shared" ref="X29" si="56">X17/X16</f>
+        <f t="shared" ref="X29" si="59">X17/X16</f>
         <v>0</v>
       </c>
       <c r="Y29" s="10">
@@ -4818,55 +4895,55 @@
         <v>0</v>
       </c>
       <c r="Z29" s="10">
-        <f t="shared" ref="Z29:AL29" si="57">Z17/Z16</f>
+        <f t="shared" ref="Z29:AL29" si="60">Z17/Z16</f>
         <v>0</v>
       </c>
       <c r="AA29" s="10">
-        <f t="shared" si="57"/>
+        <f t="shared" si="60"/>
         <v>0</v>
       </c>
       <c r="AB29" s="10">
-        <f t="shared" si="57"/>
+        <f t="shared" si="60"/>
         <v>0</v>
       </c>
       <c r="AC29" s="10">
-        <f t="shared" si="57"/>
+        <f t="shared" si="60"/>
         <v>0</v>
       </c>
       <c r="AD29" s="10">
-        <f t="shared" si="57"/>
+        <f t="shared" si="60"/>
         <v>0</v>
       </c>
       <c r="AE29" s="10">
-        <f t="shared" si="57"/>
+        <f t="shared" si="60"/>
         <v>0</v>
       </c>
       <c r="AF29" s="10">
-        <f t="shared" si="57"/>
+        <f t="shared" si="60"/>
         <v>0</v>
       </c>
       <c r="AG29" s="10">
-        <f t="shared" si="57"/>
+        <f t="shared" si="60"/>
         <v>0</v>
       </c>
       <c r="AH29" s="10">
-        <f t="shared" si="57"/>
+        <f t="shared" si="60"/>
         <v>0</v>
       </c>
       <c r="AI29" s="10">
-        <f t="shared" si="57"/>
+        <f t="shared" si="60"/>
         <v>0</v>
       </c>
       <c r="AJ29" s="10">
-        <f t="shared" si="57"/>
+        <f t="shared" si="60"/>
         <v>0</v>
       </c>
       <c r="AK29" s="10">
-        <f t="shared" si="57"/>
+        <f t="shared" si="60"/>
         <v>0</v>
       </c>
       <c r="AL29" s="10">
-        <f t="shared" si="57"/>
+        <f t="shared" si="60"/>
         <v>0</v>
       </c>
       <c r="AO29" t="s">
@@ -4874,7 +4951,7 @@
       </c>
       <c r="AP29" s="4">
         <f>Main!D3</f>
-        <v>75.069999999999993</v>
+        <v>57.7</v>
       </c>
     </row>
     <row r="30" spans="2:156" x14ac:dyDescent="0.3">
@@ -4882,59 +4959,59 @@
         <v>51</v>
       </c>
       <c r="C30" s="10">
-        <f t="shared" ref="C30:P30" si="58">C18/C3</f>
+        <f t="shared" ref="C30:P30" si="61">C18/C3</f>
         <v>-74</v>
       </c>
       <c r="D30" s="10">
-        <f t="shared" si="58"/>
+        <f t="shared" si="61"/>
         <v>-100</v>
       </c>
       <c r="E30" s="10">
-        <f t="shared" si="58"/>
+        <f t="shared" si="61"/>
         <v>-74.499999999999986</v>
       </c>
       <c r="F30" s="10">
-        <f t="shared" si="58"/>
+        <f t="shared" si="61"/>
         <v>-46.25</v>
       </c>
       <c r="G30" s="10">
-        <f t="shared" si="58"/>
+        <f t="shared" si="61"/>
         <v>-2.1500000000000004</v>
       </c>
       <c r="H30" s="10">
-        <f t="shared" si="58"/>
+        <f t="shared" si="61"/>
         <v>-0.57692307692307554</v>
       </c>
       <c r="I30" s="10">
-        <f t="shared" si="58"/>
+        <f t="shared" si="61"/>
         <v>-8.5357142857142865</v>
       </c>
       <c r="J30" s="10">
-        <f t="shared" si="58"/>
+        <f t="shared" si="61"/>
         <v>-4.9210526315789469</v>
       </c>
       <c r="K30" s="10">
-        <f t="shared" si="58"/>
+        <f t="shared" si="61"/>
         <v>-6.3488372093023262</v>
       </c>
       <c r="L30" s="10">
-        <f t="shared" si="58"/>
+        <f t="shared" si="61"/>
         <v>-7.9454545454545444</v>
       </c>
       <c r="M30" s="10">
-        <f t="shared" si="58"/>
+        <f t="shared" si="61"/>
         <v>-7.3114754098360661</v>
       </c>
       <c r="N30" s="10">
-        <f t="shared" si="58"/>
+        <f t="shared" si="61"/>
         <v>-6.8688524590163951</v>
       </c>
       <c r="O30" s="10">
-        <f t="shared" si="58"/>
+        <f t="shared" si="61"/>
         <v>-5.2105263157894752</v>
       </c>
       <c r="P30" s="10">
-        <f t="shared" si="58"/>
+        <f t="shared" si="61"/>
         <v>-3.2982456140350873</v>
       </c>
       <c r="Q30" s="10">
@@ -4946,23 +5023,23 @@
         <v>-17.264957264957268</v>
       </c>
       <c r="S30" s="10">
-        <f t="shared" ref="S30:V30" si="59">S18/S3</f>
+        <f t="shared" ref="S30:V30" si="62">S18/S3</f>
         <v>-4.2368421052631584</v>
       </c>
       <c r="T30" s="10">
-        <f t="shared" si="59"/>
+        <f t="shared" si="62"/>
         <v>-8.5797101449275353</v>
       </c>
       <c r="U30" s="10">
-        <f t="shared" si="59"/>
-        <v>0</v>
+        <f t="shared" si="62"/>
+        <v>-26.456140350877192</v>
       </c>
       <c r="V30" s="10">
-        <f t="shared" si="59"/>
-        <v>0</v>
+        <f t="shared" si="62"/>
+        <v>-6.3656627906976748</v>
       </c>
       <c r="X30" s="10">
-        <f t="shared" ref="X30" si="60">X18/X3</f>
+        <f t="shared" ref="X30" si="63">X18/X3</f>
         <v>-53.15</v>
       </c>
       <c r="Y30" s="10">
@@ -4970,63 +5047,63 @@
         <v>-4.3214285714285721</v>
       </c>
       <c r="Z30" s="10">
-        <f t="shared" ref="Z30:AL30" si="61">Z18/Z3</f>
+        <f t="shared" ref="Z30:AL30" si="64">Z18/Z3</f>
         <v>-7.1590909090909101</v>
       </c>
       <c r="AA30" s="10">
-        <f t="shared" si="61"/>
+        <f t="shared" si="64"/>
         <v>-7.6960556844547572</v>
       </c>
       <c r="AB30" s="10">
-        <f t="shared" si="61"/>
-        <v>-2.926196840826246</v>
+        <f t="shared" si="64"/>
+        <v>-2.1397122302158276</v>
       </c>
       <c r="AC30" s="10">
-        <f t="shared" si="61"/>
-        <v>-1.6878531119211559</v>
+        <f t="shared" si="64"/>
+        <v>-1.1206889435819769</v>
       </c>
       <c r="AD30" s="10">
-        <f t="shared" si="61"/>
-        <v>-0.93842064898863609</v>
+        <f t="shared" si="64"/>
+        <v>-0.55627051279277362</v>
       </c>
       <c r="AE30" s="10">
-        <f t="shared" si="61"/>
-        <v>-0.50714300442645699</v>
+        <f t="shared" si="64"/>
+        <v>-0.25614031467720577</v>
       </c>
       <c r="AF30" s="10">
-        <f t="shared" si="61"/>
-        <v>-0.22723112917884397</v>
+        <f t="shared" si="64"/>
+        <v>-5.2731089712072542E-2</v>
       </c>
       <c r="AG30" s="10">
-        <f t="shared" si="61"/>
-        <v>-3.249918213160554E-2</v>
+        <f t="shared" si="64"/>
+        <v>9.266022332001056E-2</v>
       </c>
       <c r="AH30" s="10">
-        <f t="shared" si="61"/>
-        <v>7.3382249956251783E-2</v>
+        <f t="shared" si="64"/>
+        <v>0.17753350750387439</v>
       </c>
       <c r="AI30" s="10">
-        <f t="shared" si="61"/>
-        <v>0.14683215187354648</v>
+        <f t="shared" si="64"/>
+        <v>0.23712818592397408</v>
       </c>
       <c r="AJ30" s="10">
-        <f t="shared" si="61"/>
-        <v>0.20378465355568995</v>
+        <f t="shared" si="64"/>
+        <v>0.27548612425530866</v>
       </c>
       <c r="AK30" s="10">
-        <f t="shared" si="61"/>
-        <v>0.23759343248095752</v>
+        <f t="shared" si="64"/>
+        <v>0.30489158557131874</v>
       </c>
       <c r="AL30" s="10">
-        <f t="shared" si="61"/>
-        <v>0.25969702977261455</v>
+        <f t="shared" si="64"/>
+        <v>0.31632439169112264</v>
       </c>
       <c r="AO30" s="1" t="s">
         <v>59</v>
       </c>
       <c r="AP30" s="9">
         <f>AP28/AP29-1</f>
-        <v>-0.92245041678339923</v>
+        <v>-0.82129405585665005</v>
       </c>
     </row>
     <row r="31" spans="2:156" x14ac:dyDescent="0.3">

--- a/Financial Analysis/IONQ.xlsx
+++ b/Financial Analysis/IONQ.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\antos\Documents\GitHub\FinanceModels\Financial Analysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3A62E678-3586-499E-BB3F-A412B97D508D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{48472CF0-E9EA-4C22-B39E-4F937EBCE448}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{054FC3C2-46E6-4A64-A90B-FD32B5955AC0}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="67">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="71">
   <si>
     <t>IONQ</t>
   </si>
@@ -227,6 +227,18 @@
   </si>
   <si>
     <t>Q425</t>
+  </si>
+  <si>
+    <t>Q126</t>
+  </si>
+  <si>
+    <t>Q226</t>
+  </si>
+  <si>
+    <t>Q326</t>
+  </si>
+  <si>
+    <t>Q426</t>
   </si>
 </sst>
 </file>
@@ -287,7 +299,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -305,6 +317,7 @@
     <xf numFmtId="3" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -326,13 +339,13 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>27</xdr:col>
+      <xdr:col>31</xdr:col>
       <xdr:colOff>38100</xdr:colOff>
       <xdr:row>0</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>27</xdr:col>
+      <xdr:col>31</xdr:col>
       <xdr:colOff>38100</xdr:colOff>
       <xdr:row>33</xdr:row>
       <xdr:rowOff>83820</xdr:rowOff>
@@ -376,14 +389,14 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>21</xdr:col>
-      <xdr:colOff>30480</xdr:colOff>
+      <xdr:col>22</xdr:col>
+      <xdr:colOff>38100</xdr:colOff>
       <xdr:row>0</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>21</xdr:col>
-      <xdr:colOff>30480</xdr:colOff>
+      <xdr:col>22</xdr:col>
+      <xdr:colOff>38100</xdr:colOff>
       <xdr:row>33</xdr:row>
       <xdr:rowOff>91440</xdr:rowOff>
     </xdr:to>
@@ -400,7 +413,7 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="13708380" y="0"/>
+          <a:off x="14325600" y="0"/>
           <a:ext cx="0" cy="6126480"/>
         </a:xfrm>
         <a:prstGeom prst="line">
@@ -749,17 +762,17 @@
         <v>1</v>
       </c>
       <c r="D3" s="4">
-        <v>57.7</v>
+        <v>38.46</v>
       </c>
       <c r="E3" s="3">
-        <v>45967</v>
+        <v>46079</v>
       </c>
       <c r="F3" s="3">
         <f ca="1">TODAY()</f>
-        <v>45967</v>
+        <v>46079</v>
       </c>
       <c r="G3" s="3">
-        <v>46026</v>
+        <v>46155</v>
       </c>
     </row>
     <row r="4" spans="2:11" x14ac:dyDescent="0.3">
@@ -767,11 +780,11 @@
         <v>2</v>
       </c>
       <c r="D4" s="5">
-        <f>354.3</f>
-        <v>354.3</v>
+        <f>366.6</f>
+        <v>366.6</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="5" spans="2:11" x14ac:dyDescent="0.3">
@@ -780,7 +793,7 @@
       </c>
       <c r="D5" s="5">
         <f>D3*D4</f>
-        <v>20443.11</v>
+        <v>14099.436000000002</v>
       </c>
     </row>
     <row r="6" spans="2:11" x14ac:dyDescent="0.3">
@@ -788,11 +801,11 @@
         <v>4</v>
       </c>
       <c r="D6" s="5">
-        <f>346+736.3+402.6</f>
-        <v>1484.9</v>
+        <f>1030.9+1361.3+944.6</f>
+        <v>3336.7999999999997</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="7" spans="2:11" x14ac:dyDescent="0.3">
@@ -800,11 +813,10 @@
         <v>5</v>
       </c>
       <c r="D7" s="5">
-        <f>1768.2</f>
-        <v>1768.2</v>
+        <v>0</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="8" spans="2:11" x14ac:dyDescent="0.3">
@@ -813,7 +825,7 @@
       </c>
       <c r="D8" s="5">
         <f>D6-D7</f>
-        <v>-283.29999999999995</v>
+        <v>3336.7999999999997</v>
       </c>
     </row>
     <row r="9" spans="2:11" x14ac:dyDescent="0.3">
@@ -822,7 +834,7 @@
       </c>
       <c r="D9" s="5">
         <f>D5-D8</f>
-        <v>20726.41</v>
+        <v>10762.636000000002</v>
       </c>
     </row>
     <row r="10" spans="2:11" x14ac:dyDescent="0.3">
@@ -837,16 +849,16 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00069D86-50D1-4FDE-B373-2512B05FF677}">
-  <dimension ref="B2:EZ31"/>
+  <dimension ref="B2:FD31"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="21.6640625" bestFit="1" customWidth="1"/>
     <col min="3" max="6" width="8.88671875" customWidth="1"/>
-    <col min="41" max="41" width="13.109375" customWidth="1"/>
-    <col min="42" max="42" width="16.44140625" bestFit="1" customWidth="1"/>
+    <col min="45" max="45" width="13.109375" customWidth="1"/>
+    <col min="46" max="46" width="16.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:38" x14ac:dyDescent="0.3">
+    <row r="2" spans="2:42" x14ac:dyDescent="0.3">
       <c r="C2" s="6" t="s">
         <v>40</v>
       </c>
@@ -907,53 +919,65 @@
       <c r="V2" s="6" t="s">
         <v>66</v>
       </c>
-      <c r="X2">
+      <c r="W2" s="6" t="s">
+        <v>67</v>
+      </c>
+      <c r="X2" s="6" t="s">
+        <v>68</v>
+      </c>
+      <c r="Y2" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="Z2" s="6" t="s">
+        <v>70</v>
+      </c>
+      <c r="AB2">
         <v>2021</v>
       </c>
-      <c r="Y2">
+      <c r="AC2">
         <v>2022</v>
       </c>
-      <c r="Z2">
+      <c r="AD2">
         <v>2023</v>
       </c>
-      <c r="AA2">
+      <c r="AE2">
         <v>2024</v>
       </c>
-      <c r="AB2">
+      <c r="AF2">
         <v>2025</v>
       </c>
-      <c r="AC2">
+      <c r="AG2">
         <v>2026</v>
       </c>
-      <c r="AD2">
+      <c r="AH2">
         <v>2027</v>
       </c>
-      <c r="AE2">
+      <c r="AI2">
         <v>2028</v>
       </c>
-      <c r="AF2">
+      <c r="AJ2">
         <v>2029</v>
       </c>
-      <c r="AG2">
+      <c r="AK2">
         <v>2030</v>
       </c>
-      <c r="AH2">
+      <c r="AL2">
         <v>2031</v>
       </c>
-      <c r="AI2">
+      <c r="AM2">
         <v>2032</v>
       </c>
-      <c r="AJ2">
+      <c r="AN2">
         <v>2033</v>
       </c>
-      <c r="AK2">
+      <c r="AO2">
         <v>2034</v>
       </c>
-      <c r="AL2">
+      <c r="AP2">
         <v>2035</v>
       </c>
     </row>
-    <row r="3" spans="2:38" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="2:42" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B3" s="1" t="s">
         <v>11</v>
       </c>
@@ -1015,71 +1039,77 @@
         <v>39.9</v>
       </c>
       <c r="V3" s="8">
-        <v>43</v>
-      </c>
-      <c r="W3" s="8"/>
-      <c r="X3" s="8">
+        <v>61.9</v>
+      </c>
+      <c r="W3" s="8">
+        <v>49</v>
+      </c>
+      <c r="X3" s="8"/>
+      <c r="Y3" s="8"/>
+      <c r="Z3" s="8"/>
+      <c r="AA3" s="8"/>
+      <c r="AB3" s="8">
         <f>SUM(C3:F3)</f>
         <v>2</v>
       </c>
-      <c r="Y3" s="8">
+      <c r="AC3" s="8">
         <f>SUM(G3:J3)</f>
         <v>11.2</v>
       </c>
-      <c r="Z3" s="8">
+      <c r="AD3" s="8">
         <f>SUM(K3:N3)</f>
         <v>22</v>
       </c>
-      <c r="AA3" s="8">
+      <c r="AE3" s="8">
         <f>SUM(O3:R3)</f>
         <v>43.099999999999994</v>
       </c>
-      <c r="AB3" s="8">
+      <c r="AF3" s="8">
         <f>SUM(S3:V3)</f>
-        <v>111.19999999999999</v>
-      </c>
-      <c r="AC3" s="8">
-        <f>AB3*1.9</f>
-        <v>211.27999999999997</v>
-      </c>
-      <c r="AD3" s="8">
-        <f>AC3*1.75</f>
-        <v>369.73999999999995</v>
-      </c>
-      <c r="AE3" s="8">
-        <f>AD3*1.6</f>
-        <v>591.58399999999995</v>
-      </c>
-      <c r="AF3" s="8">
-        <f>AE3*1.5</f>
-        <v>887.37599999999998</v>
+        <v>130.1</v>
       </c>
       <c r="AG3" s="8">
-        <f>AF3*1.45</f>
-        <v>1286.6951999999999</v>
+        <f>AF3*1.9</f>
+        <v>247.18999999999997</v>
       </c>
       <c r="AH3" s="8">
-        <f>AG3*1.25</f>
-        <v>1608.3689999999999</v>
+        <f>AG3*1.75</f>
+        <v>432.58249999999992</v>
       </c>
       <c r="AI3" s="8">
-        <f>AH3*1.2</f>
-        <v>1930.0427999999997</v>
+        <f>AH3*1.6</f>
+        <v>692.13199999999995</v>
       </c>
       <c r="AJ3" s="8">
-        <f>AI3*1.15</f>
-        <v>2219.5492199999994</v>
+        <f>AI3*1.5</f>
+        <v>1038.1979999999999</v>
       </c>
       <c r="AK3" s="8">
-        <f>AJ3*1.1</f>
-        <v>2441.5041419999998</v>
+        <f>AJ3*1.45</f>
+        <v>1505.3870999999997</v>
       </c>
       <c r="AL3" s="8">
-        <f>AK3*1.05</f>
-        <v>2563.5793490999999</v>
+        <f>AK3*1.25</f>
+        <v>1881.7338749999997</v>
+      </c>
+      <c r="AM3" s="8">
+        <f>AL3*1.2</f>
+        <v>2258.0806499999994</v>
+      </c>
+      <c r="AN3" s="8">
+        <f>AM3*1.15</f>
+        <v>2596.7927474999992</v>
+      </c>
+      <c r="AO3" s="8">
+        <f>AN3*1.1</f>
+        <v>2856.4720222499996</v>
+      </c>
+      <c r="AP3" s="8">
+        <f>AO3*1.05</f>
+        <v>2999.2956233624996</v>
       </c>
     </row>
-    <row r="4" spans="2:38" x14ac:dyDescent="0.3">
+    <row r="4" spans="2:42" x14ac:dyDescent="0.3">
       <c r="B4" t="s">
         <v>24</v>
       </c>
@@ -1141,216 +1171,223 @@
         <v>21.3</v>
       </c>
       <c r="V4" s="5">
-        <f t="shared" ref="V4" si="0">V3-V5</f>
-        <v>21.93</v>
-      </c>
-      <c r="X4" s="5">
+        <v>43.6</v>
+      </c>
+      <c r="W4" s="5"/>
+      <c r="X4" s="5"/>
+      <c r="Y4" s="5"/>
+      <c r="Z4" s="5"/>
+      <c r="AB4" s="5">
         <f>SUM(C4:F4)</f>
         <v>1</v>
       </c>
-      <c r="Y4" s="5">
+      <c r="AC4" s="5">
         <f>SUM(G4:J4)</f>
         <v>2.9</v>
       </c>
-      <c r="Z4" s="5">
+      <c r="AD4" s="5">
         <f>SUM(K4:N4)</f>
         <v>8.1000000000000014</v>
       </c>
-      <c r="AA4" s="5">
+      <c r="AE4" s="5">
         <f>SUM(O4:R4)</f>
         <v>20.5</v>
       </c>
-      <c r="AB4" s="5">
-        <f>AB3-AB5</f>
-        <v>55.599999999999994</v>
-      </c>
-      <c r="AC4" s="5">
-        <f t="shared" ref="AC4:AL4" si="1">AC3-AC5</f>
-        <v>103.52719999999998</v>
-      </c>
-      <c r="AD4" s="5">
-        <f t="shared" si="1"/>
-        <v>177.47519999999997</v>
-      </c>
-      <c r="AE4" s="5">
-        <f t="shared" si="1"/>
-        <v>283.96031999999997</v>
-      </c>
-      <c r="AF4" s="5">
-        <f t="shared" si="1"/>
-        <v>408.19295999999997</v>
+      <c r="AF4" s="11">
+        <f>SUM(S4:V4)</f>
+        <v>77.5</v>
       </c>
       <c r="AG4" s="5">
-        <f t="shared" si="1"/>
-        <v>566.1458879999999</v>
+        <f t="shared" ref="AG4:AP4" si="0">AG3-AG5</f>
+        <v>121.12309999999998</v>
       </c>
       <c r="AH4" s="5">
-        <f t="shared" si="1"/>
-        <v>675.51498000000004</v>
+        <f t="shared" si="0"/>
+        <v>207.63959999999994</v>
       </c>
       <c r="AI4" s="5">
-        <f t="shared" si="1"/>
-        <v>772.01711999999998</v>
+        <f t="shared" si="0"/>
+        <v>332.22335999999996</v>
       </c>
       <c r="AJ4" s="5">
-        <f t="shared" si="1"/>
-        <v>865.62419579999982</v>
+        <f t="shared" si="0"/>
+        <v>477.57107999999994</v>
       </c>
       <c r="AK4" s="5">
-        <f t="shared" si="1"/>
-        <v>927.77157395999984</v>
+        <f t="shared" si="0"/>
+        <v>662.37032399999975</v>
       </c>
       <c r="AL4" s="5">
-        <f t="shared" si="1"/>
-        <v>974.16015265800002</v>
+        <f t="shared" si="0"/>
+        <v>790.32822749999991</v>
+      </c>
+      <c r="AM4" s="5">
+        <f t="shared" si="0"/>
+        <v>903.23225999999977</v>
+      </c>
+      <c r="AN4" s="5">
+        <f t="shared" si="0"/>
+        <v>1012.7491715249998</v>
+      </c>
+      <c r="AO4" s="5">
+        <f t="shared" si="0"/>
+        <v>1085.4593684549998</v>
+      </c>
+      <c r="AP4" s="5">
+        <f t="shared" si="0"/>
+        <v>1139.7323368777497</v>
       </c>
     </row>
-    <row r="5" spans="2:38" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="2:42" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B5" s="1" t="s">
         <v>25</v>
       </c>
       <c r="C5" s="8">
-        <f t="shared" ref="C5:U5" si="2">C3-C4</f>
+        <f t="shared" ref="C5:V5" si="1">C3-C4</f>
         <v>-0.1</v>
       </c>
       <c r="D5" s="8">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>-0.19999999999999998</v>
       </c>
       <c r="E5" s="8">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="F5" s="8">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>1.3</v>
       </c>
       <c r="G5" s="8">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>1.4</v>
       </c>
       <c r="H5" s="8">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>1.9000000000000001</v>
       </c>
       <c r="I5" s="8">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>2.0999999999999996</v>
       </c>
       <c r="J5" s="8">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>2.9</v>
       </c>
       <c r="K5" s="8">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>3.3</v>
       </c>
       <c r="L5" s="8">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>3.6</v>
       </c>
       <c r="M5" s="8">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>4.0999999999999996</v>
       </c>
       <c r="N5" s="8">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>2.8999999999999995</v>
       </c>
       <c r="O5" s="8">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>4.1999999999999993</v>
       </c>
       <c r="P5" s="8">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>5.8000000000000007</v>
       </c>
       <c r="Q5" s="8">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>5.9</v>
       </c>
       <c r="R5" s="8">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>6.6999999999999993</v>
       </c>
       <c r="S5" s="8">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>3.3</v>
       </c>
       <c r="T5" s="8">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>12.399999999999999</v>
       </c>
       <c r="U5" s="8">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>18.599999999999998</v>
       </c>
       <c r="V5" s="8">
-        <f>V3*0.49</f>
-        <v>21.07</v>
-      </c>
-      <c r="X5" s="8">
-        <f>X3-X4</f>
+        <f t="shared" si="1"/>
+        <v>18.299999999999997</v>
+      </c>
+      <c r="W5" s="8"/>
+      <c r="X5" s="8"/>
+      <c r="Y5" s="8"/>
+      <c r="Z5" s="8"/>
+      <c r="AB5" s="8">
+        <f>AB3-AB4</f>
         <v>1</v>
       </c>
-      <c r="Y5" s="8">
-        <f>Y3-Y4</f>
+      <c r="AC5" s="8">
+        <f>AC3-AC4</f>
         <v>8.2999999999999989</v>
       </c>
-      <c r="Z5" s="8">
-        <f>Z3-Z4</f>
+      <c r="AD5" s="8">
+        <f>AD3-AD4</f>
         <v>13.899999999999999</v>
       </c>
-      <c r="AA5" s="8">
-        <f>AA3-AA4</f>
+      <c r="AE5" s="8">
+        <f>AE3-AE4</f>
         <v>22.599999999999994</v>
       </c>
-      <c r="AB5" s="8">
-        <f>AB3*0.5</f>
-        <v>55.599999999999994</v>
-      </c>
-      <c r="AC5" s="8">
-        <f>AC3*0.51</f>
-        <v>107.75279999999999</v>
-      </c>
-      <c r="AD5" s="8">
-        <f>AD3*0.52</f>
-        <v>192.26479999999998</v>
-      </c>
-      <c r="AE5" s="8">
-        <f>AE3*0.52</f>
-        <v>307.62367999999998</v>
-      </c>
       <c r="AF5" s="8">
-        <f>AF3*0.54</f>
-        <v>479.18304000000001</v>
+        <f>AF3-AF4</f>
+        <v>52.599999999999994</v>
       </c>
       <c r="AG5" s="8">
-        <f>AG3*0.56</f>
-        <v>720.54931199999999</v>
+        <f>AG3*0.51</f>
+        <v>126.06689999999999</v>
       </c>
       <c r="AH5" s="8">
-        <f>AH3*0.58</f>
-        <v>932.85401999999988</v>
+        <f>AH3*0.52</f>
+        <v>224.94289999999998</v>
       </c>
       <c r="AI5" s="8">
-        <f>AI3*0.6</f>
-        <v>1158.0256799999997</v>
+        <f>AI3*0.52</f>
+        <v>359.90863999999999</v>
       </c>
       <c r="AJ5" s="8">
-        <f>AJ3*0.61</f>
-        <v>1353.9250241999996</v>
+        <f>AJ3*0.54</f>
+        <v>560.62691999999993</v>
       </c>
       <c r="AK5" s="8">
-        <f>AK3*0.62</f>
-        <v>1513.7325680399999</v>
+        <f>AK3*0.56</f>
+        <v>843.01677599999994</v>
       </c>
       <c r="AL5" s="8">
-        <f>AL3*0.62</f>
-        <v>1589.4191964419999</v>
+        <f>AL3*0.58</f>
+        <v>1091.4056474999998</v>
+      </c>
+      <c r="AM5" s="8">
+        <f>AM3*0.6</f>
+        <v>1354.8483899999997</v>
+      </c>
+      <c r="AN5" s="8">
+        <f>AN3*0.61</f>
+        <v>1584.0435759749994</v>
+      </c>
+      <c r="AO5" s="8">
+        <f>AO3*0.62</f>
+        <v>1771.0126537949998</v>
+      </c>
+      <c r="AP5" s="8">
+        <f>AP3*0.62</f>
+        <v>1859.5632864847498</v>
       </c>
     </row>
-    <row r="6" spans="2:38" x14ac:dyDescent="0.3">
+    <row r="6" spans="2:42" x14ac:dyDescent="0.3">
       <c r="B6" t="s">
         <v>26</v>
       </c>
@@ -1412,70 +1449,74 @@
         <v>66.3</v>
       </c>
       <c r="V6" s="5">
-        <v>80</v>
-      </c>
-      <c r="X6" s="5">
+        <v>96.1</v>
+      </c>
+      <c r="W6" s="5"/>
+      <c r="X6" s="5"/>
+      <c r="Y6" s="5"/>
+      <c r="Z6" s="5"/>
+      <c r="AB6" s="5">
         <f>SUM(C6:F6)</f>
         <v>20.299999999999997</v>
       </c>
-      <c r="Y6" s="5">
+      <c r="AC6" s="5">
         <f>SUM(G6:J6)</f>
         <v>44</v>
       </c>
-      <c r="Z6" s="5">
+      <c r="AD6" s="5">
         <f>SUM(K6:N6)</f>
         <v>92.3</v>
       </c>
-      <c r="AA6" s="5">
+      <c r="AE6" s="5">
         <f>SUM(O6:R6)</f>
         <v>136.9</v>
       </c>
-      <c r="AB6" s="5">
-        <f>AA6*1.18</f>
-        <v>161.542</v>
-      </c>
-      <c r="AC6" s="5">
-        <f>AB6*1.12</f>
-        <v>180.92704000000001</v>
-      </c>
-      <c r="AD6" s="5">
-        <f>AC6*1.07</f>
-        <v>193.59193280000002</v>
-      </c>
-      <c r="AE6" s="5">
-        <f>AD6*1.05</f>
-        <v>203.27152944000002</v>
-      </c>
-      <c r="AF6" s="5">
-        <f t="shared" ref="AF6:AL6" si="3">AE6*1.05</f>
-        <v>213.43510591200004</v>
+      <c r="AF6" s="11">
+        <f t="shared" ref="AF6:AF9" si="2">SUM(S6:V6)</f>
+        <v>305.79999999999995</v>
       </c>
       <c r="AG6" s="5">
-        <f t="shared" si="3"/>
-        <v>224.10686120760005</v>
+        <f>AF6*1.12</f>
+        <v>342.49599999999998</v>
       </c>
       <c r="AH6" s="5">
-        <f t="shared" si="3"/>
-        <v>235.31220426798006</v>
+        <f>AG6*1.07</f>
+        <v>366.47072000000003</v>
       </c>
       <c r="AI6" s="5">
-        <f t="shared" si="3"/>
-        <v>247.07781448137908</v>
+        <f>AH6*1.05</f>
+        <v>384.79425600000002</v>
       </c>
       <c r="AJ6" s="5">
-        <f t="shared" si="3"/>
-        <v>259.43170520544805</v>
+        <f t="shared" ref="AJ6:AP6" si="3">AI6*1.05</f>
+        <v>404.03396880000003</v>
       </c>
       <c r="AK6" s="5">
         <f t="shared" si="3"/>
-        <v>272.40329046572049</v>
+        <v>424.23566724000005</v>
       </c>
       <c r="AL6" s="5">
         <f t="shared" si="3"/>
-        <v>286.02345498900655</v>
+        <v>445.44745060200006</v>
+      </c>
+      <c r="AM6" s="5">
+        <f t="shared" si="3"/>
+        <v>467.71982313210009</v>
+      </c>
+      <c r="AN6" s="5">
+        <f t="shared" si="3"/>
+        <v>491.10581428870512</v>
+      </c>
+      <c r="AO6" s="5">
+        <f t="shared" si="3"/>
+        <v>515.66110500314039</v>
+      </c>
+      <c r="AP6" s="5">
+        <f t="shared" si="3"/>
+        <v>541.44416025329747</v>
       </c>
     </row>
-    <row r="7" spans="2:38" x14ac:dyDescent="0.3">
+    <row r="7" spans="2:42" x14ac:dyDescent="0.3">
       <c r="B7" t="s">
         <v>27</v>
       </c>
@@ -1537,71 +1578,74 @@
         <v>14.4</v>
       </c>
       <c r="V7" s="5">
-        <f>V3*0.4</f>
-        <v>17.2</v>
-      </c>
-      <c r="X7" s="5">
+        <v>19.5</v>
+      </c>
+      <c r="W7" s="5"/>
+      <c r="X7" s="5"/>
+      <c r="Y7" s="5"/>
+      <c r="Z7" s="5"/>
+      <c r="AB7" s="5">
         <f>SUM(C7:F7)</f>
         <v>3.2</v>
       </c>
-      <c r="Y7" s="5">
+      <c r="AC7" s="5">
         <f>SUM(G7:J7)</f>
         <v>8.4</v>
       </c>
-      <c r="Z7" s="5">
+      <c r="AD7" s="5">
         <f>SUM(K7:N7)</f>
         <v>18.3</v>
       </c>
-      <c r="AA7" s="5">
+      <c r="AE7" s="5">
         <f>SUM(O7:R7)</f>
         <v>28.299999999999997</v>
       </c>
-      <c r="AB7" s="5">
-        <f>AB3*0.4</f>
-        <v>44.48</v>
-      </c>
-      <c r="AC7" s="5">
-        <f>AC3*0.3</f>
-        <v>63.383999999999986</v>
-      </c>
-      <c r="AD7" s="5">
-        <f>AD3*0.26</f>
-        <v>96.13239999999999</v>
-      </c>
-      <c r="AE7" s="5">
-        <f>AE3*0.24</f>
-        <v>141.98015999999998</v>
-      </c>
-      <c r="AF7" s="5">
-        <f>AF3*0.22</f>
-        <v>195.22272000000001</v>
+      <c r="AF7" s="11">
+        <f t="shared" si="2"/>
+        <v>53.4</v>
       </c>
       <c r="AG7" s="5">
-        <f>AG3*0.2</f>
-        <v>257.33904000000001</v>
+        <f>AG3*0.3</f>
+        <v>74.156999999999982</v>
       </c>
       <c r="AH7" s="5">
-        <f>AH3*0.18</f>
-        <v>289.50641999999999</v>
+        <f>AH3*0.26</f>
+        <v>112.47144999999999</v>
       </c>
       <c r="AI7" s="5">
-        <f>AI3*0.17</f>
-        <v>328.10727599999996</v>
+        <f>AI3*0.24</f>
+        <v>166.11167999999998</v>
       </c>
       <c r="AJ7" s="5">
-        <f>AJ3*0.16</f>
-        <v>355.12787519999989</v>
+        <f>AJ3*0.22</f>
+        <v>228.40355999999997</v>
       </c>
       <c r="AK7" s="5">
-        <f>AK3*0.15</f>
-        <v>366.22562129999994</v>
+        <f>AK3*0.2</f>
+        <v>301.07741999999996</v>
       </c>
       <c r="AL7" s="5">
-        <f>AL3*0.14</f>
-        <v>358.90110887400004</v>
+        <f>AL3*0.18</f>
+        <v>338.71209749999991</v>
+      </c>
+      <c r="AM7" s="5">
+        <f>AM3*0.17</f>
+        <v>383.8737104999999</v>
+      </c>
+      <c r="AN7" s="5">
+        <f>AN3*0.16</f>
+        <v>415.48683959999988</v>
+      </c>
+      <c r="AO7" s="5">
+        <f>AO3*0.15</f>
+        <v>428.47080333749994</v>
+      </c>
+      <c r="AP7" s="5">
+        <f>AP3*0.14</f>
+        <v>419.90138727074998</v>
       </c>
     </row>
-    <row r="8" spans="2:38" x14ac:dyDescent="0.3">
+    <row r="8" spans="2:42" x14ac:dyDescent="0.3">
       <c r="B8" t="s">
         <v>28</v>
       </c>
@@ -1663,70 +1707,74 @@
         <v>82.5</v>
       </c>
       <c r="V8" s="5">
-        <v>100</v>
-      </c>
-      <c r="X8" s="5">
+        <v>90.7</v>
+      </c>
+      <c r="W8" s="5"/>
+      <c r="X8" s="5"/>
+      <c r="Y8" s="5"/>
+      <c r="Z8" s="5"/>
+      <c r="AB8" s="5">
         <f>SUM(C8:F8)</f>
         <v>13.8</v>
       </c>
-      <c r="Y8" s="5">
+      <c r="AC8" s="5">
         <f>SUM(G8:J8)</f>
         <v>36</v>
       </c>
-      <c r="Z8" s="5">
+      <c r="AD8" s="5">
         <f>SUM(K8:N8)</f>
         <v>50.7</v>
       </c>
-      <c r="AA8" s="5">
+      <c r="AE8" s="5">
         <f>SUM(O8:R8)</f>
         <v>71.100000000000009</v>
       </c>
-      <c r="AB8" s="5">
-        <f>AA8*1.1</f>
-        <v>78.210000000000022</v>
-      </c>
-      <c r="AC8" s="5">
-        <f>AB8*1.08</f>
-        <v>84.466800000000035</v>
-      </c>
-      <c r="AD8" s="5">
-        <f>AC8*1.06</f>
-        <v>89.534808000000041</v>
-      </c>
-      <c r="AE8" s="5">
-        <f>AD8*1.04</f>
-        <v>93.116200320000047</v>
-      </c>
-      <c r="AF8" s="5">
-        <f>AE8*1.03</f>
-        <v>95.909686329600049</v>
+      <c r="AF8" s="11">
+        <f t="shared" si="2"/>
+        <v>245.10000000000002</v>
       </c>
       <c r="AG8" s="5">
-        <f>AF8*1.02</f>
-        <v>97.827880056192058</v>
+        <f>AF8*1.08</f>
+        <v>264.70800000000003</v>
       </c>
       <c r="AH8" s="5">
-        <f t="shared" ref="AH8:AL8" si="4">AG8*1.02</f>
-        <v>99.784437657315905</v>
+        <f>AG8*1.06</f>
+        <v>280.59048000000007</v>
       </c>
       <c r="AI8" s="5">
+        <f>AH8*1.04</f>
+        <v>291.8140992000001</v>
+      </c>
+      <c r="AJ8" s="5">
+        <f>AI8*1.03</f>
+        <v>300.5685221760001</v>
+      </c>
+      <c r="AK8" s="5">
+        <f>AJ8*1.02</f>
+        <v>306.57989261952008</v>
+      </c>
+      <c r="AL8" s="5">
+        <f t="shared" ref="AL8:AP8" si="4">AK8*1.02</f>
+        <v>312.71149047191051</v>
+      </c>
+      <c r="AM8" s="5">
         <f t="shared" si="4"/>
-        <v>101.78012641046223</v>
-      </c>
-      <c r="AJ8" s="5">
+        <v>318.96572028134875</v>
+      </c>
+      <c r="AN8" s="5">
         <f t="shared" si="4"/>
-        <v>103.81572893867148</v>
-      </c>
-      <c r="AK8" s="5">
+        <v>325.34503468697574</v>
+      </c>
+      <c r="AO8" s="5">
         <f t="shared" si="4"/>
-        <v>105.89204351744492</v>
-      </c>
-      <c r="AL8" s="5">
+        <v>331.85193538071525</v>
+      </c>
+      <c r="AP8" s="5">
         <f t="shared" si="4"/>
-        <v>108.00988438779382</v>
+        <v>338.48897408832954</v>
       </c>
     </row>
-    <row r="9" spans="2:38" x14ac:dyDescent="0.3">
+    <row r="9" spans="2:42" x14ac:dyDescent="0.3">
       <c r="B9" t="s">
         <v>29</v>
       </c>
@@ -1788,70 +1836,74 @@
         <v>24.2</v>
       </c>
       <c r="V9" s="5">
-        <v>30</v>
-      </c>
-      <c r="X9" s="5">
+        <v>40.6</v>
+      </c>
+      <c r="W9" s="5"/>
+      <c r="X9" s="5"/>
+      <c r="Y9" s="5"/>
+      <c r="Z9" s="5"/>
+      <c r="AB9" s="5">
         <f>SUM(C9:F9)</f>
         <v>2.5</v>
       </c>
-      <c r="Y9" s="5">
+      <c r="AC9" s="5">
         <f>SUM(G9:J9)</f>
         <v>5.6999999999999993</v>
       </c>
-      <c r="Z9" s="5">
+      <c r="AD9" s="5">
         <f>SUM(K9:N9)</f>
         <v>10.3</v>
       </c>
-      <c r="AA9" s="5">
+      <c r="AE9" s="5">
         <f>SUM(O9:R9)</f>
         <v>18.700000000000003</v>
       </c>
-      <c r="AB9" s="5">
-        <f>AA9*1.5</f>
-        <v>28.050000000000004</v>
-      </c>
-      <c r="AC9" s="5">
-        <f>AB9*1.25</f>
-        <v>35.062500000000007</v>
-      </c>
-      <c r="AD9" s="5">
-        <f>AC9*1.1</f>
-        <v>38.568750000000009</v>
-      </c>
-      <c r="AE9" s="5">
-        <f>AD9*1.07</f>
-        <v>41.268562500000009</v>
-      </c>
-      <c r="AF9" s="5">
-        <f>AE9*1.03</f>
-        <v>42.506619375000007</v>
+      <c r="AF9" s="11">
+        <f t="shared" si="2"/>
+        <v>82</v>
       </c>
       <c r="AG9" s="5">
-        <f t="shared" ref="AG9:AL9" si="5">AF9*1.03</f>
-        <v>43.781817956250009</v>
+        <f>AF9*1.25</f>
+        <v>102.5</v>
       </c>
       <c r="AH9" s="5">
-        <f t="shared" si="5"/>
-        <v>45.095272494937511</v>
+        <f>AG9*1.1</f>
+        <v>112.75000000000001</v>
       </c>
       <c r="AI9" s="5">
-        <f t="shared" si="5"/>
-        <v>46.448130669785634</v>
+        <f>AH9*1.07</f>
+        <v>120.64250000000003</v>
       </c>
       <c r="AJ9" s="5">
-        <f t="shared" si="5"/>
-        <v>47.841574589879201</v>
+        <f>AI9*1.03</f>
+        <v>124.26177500000003</v>
       </c>
       <c r="AK9" s="5">
-        <f t="shared" si="5"/>
-        <v>49.276821827575581</v>
+        <f t="shared" ref="AK9:AP9" si="5">AJ9*1.03</f>
+        <v>127.98962825000004</v>
       </c>
       <c r="AL9" s="5">
         <f t="shared" si="5"/>
-        <v>50.755126482402851</v>
+        <v>131.82931709750005</v>
+      </c>
+      <c r="AM9" s="5">
+        <f t="shared" si="5"/>
+        <v>135.78419661042506</v>
+      </c>
+      <c r="AN9" s="5">
+        <f t="shared" si="5"/>
+        <v>139.85772250873782</v>
+      </c>
+      <c r="AO9" s="5">
+        <f t="shared" si="5"/>
+        <v>144.05345418399997</v>
+      </c>
+      <c r="AP9" s="5">
+        <f t="shared" si="5"/>
+        <v>148.37505780951997</v>
       </c>
     </row>
-    <row r="10" spans="2:38" x14ac:dyDescent="0.3">
+    <row r="10" spans="2:42" x14ac:dyDescent="0.3">
       <c r="B10" t="s">
         <v>30</v>
       </c>
@@ -1933,70 +1985,74 @@
       </c>
       <c r="V10" s="5">
         <f t="shared" si="8"/>
-        <v>227.2</v>
-      </c>
-      <c r="X10" s="5">
-        <f>SUM(X6:X9)</f>
+        <v>246.9</v>
+      </c>
+      <c r="W10" s="5"/>
+      <c r="X10" s="5"/>
+      <c r="Y10" s="5"/>
+      <c r="Z10" s="5"/>
+      <c r="AB10" s="5">
+        <f>SUM(AB6:AB9)</f>
         <v>39.799999999999997</v>
       </c>
-      <c r="Y10" s="5">
-        <f>SUM(Y6:Y9)</f>
+      <c r="AC10" s="5">
+        <f>SUM(AC6:AC9)</f>
         <v>94.100000000000009</v>
       </c>
-      <c r="Z10" s="5">
-        <f>SUM(Z6:Z9)</f>
+      <c r="AD10" s="5">
+        <f>SUM(AD6:AD9)</f>
         <v>171.60000000000002</v>
       </c>
-      <c r="AA10" s="5">
-        <f>SUM(AA6:AA9)</f>
+      <c r="AE10" s="5">
+        <f>SUM(AE6:AE9)</f>
         <v>255</v>
       </c>
-      <c r="AB10" s="5">
-        <f t="shared" ref="AB10:AL10" si="9">SUM(AB6:AB9)</f>
-        <v>312.28200000000004</v>
-      </c>
-      <c r="AC10" s="5">
-        <f t="shared" si="9"/>
-        <v>363.84034000000003</v>
-      </c>
-      <c r="AD10" s="5">
-        <f t="shared" si="9"/>
-        <v>417.82789080000009</v>
-      </c>
-      <c r="AE10" s="5">
-        <f t="shared" si="9"/>
-        <v>479.63645226000006</v>
-      </c>
       <c r="AF10" s="5">
-        <f t="shared" si="9"/>
-        <v>547.07413161660008</v>
+        <f t="shared" ref="AF10:AP10" si="9">SUM(AF6:AF9)</f>
+        <v>686.3</v>
       </c>
       <c r="AG10" s="5">
         <f t="shared" si="9"/>
-        <v>623.05559922004215</v>
+        <v>783.86099999999999</v>
       </c>
       <c r="AH10" s="5">
         <f t="shared" si="9"/>
-        <v>669.69833442023355</v>
+        <v>872.2826500000001</v>
       </c>
       <c r="AI10" s="5">
         <f t="shared" si="9"/>
-        <v>723.41334756162689</v>
+        <v>963.36253520000014</v>
       </c>
       <c r="AJ10" s="5">
         <f t="shared" si="9"/>
-        <v>766.21688393399859</v>
+        <v>1057.267825976</v>
       </c>
       <c r="AK10" s="5">
         <f t="shared" si="9"/>
-        <v>793.79777711074087</v>
+        <v>1159.8826081095201</v>
       </c>
       <c r="AL10" s="5">
         <f t="shared" si="9"/>
-        <v>803.68957473320324</v>
+        <v>1228.7003556714105</v>
+      </c>
+      <c r="AM10" s="5">
+        <f t="shared" si="9"/>
+        <v>1306.3434505238738</v>
+      </c>
+      <c r="AN10" s="5">
+        <f t="shared" si="9"/>
+        <v>1371.7954110844184</v>
+      </c>
+      <c r="AO10" s="5">
+        <f t="shared" si="9"/>
+        <v>1420.0372979053557</v>
+      </c>
+      <c r="AP10" s="5">
+        <f t="shared" si="9"/>
+        <v>1448.2095794218972</v>
       </c>
     </row>
-    <row r="11" spans="2:38" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="2:42" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B11" s="1" t="s">
         <v>31</v>
       </c>
@@ -2078,70 +2134,74 @@
       </c>
       <c r="V11" s="8">
         <f t="shared" si="12"/>
-        <v>-206.13</v>
-      </c>
-      <c r="X11" s="8">
-        <f>X5-X10</f>
+        <v>-228.60000000000002</v>
+      </c>
+      <c r="W11" s="8"/>
+      <c r="X11" s="8"/>
+      <c r="Y11" s="8"/>
+      <c r="Z11" s="8"/>
+      <c r="AB11" s="8">
+        <f>AB5-AB10</f>
         <v>-38.799999999999997</v>
       </c>
-      <c r="Y11" s="8">
-        <f>Y5-Y10</f>
+      <c r="AC11" s="8">
+        <f>AC5-AC10</f>
         <v>-85.800000000000011</v>
       </c>
-      <c r="Z11" s="8">
-        <f>Z5-Z10</f>
+      <c r="AD11" s="8">
+        <f>AD5-AD10</f>
         <v>-157.70000000000002</v>
       </c>
-      <c r="AA11" s="8">
-        <f>AA5-AA10</f>
+      <c r="AE11" s="8">
+        <f>AE5-AE10</f>
         <v>-232.4</v>
       </c>
-      <c r="AB11" s="8">
-        <f t="shared" ref="AB11:AL11" si="13">AB5-AB10</f>
-        <v>-256.68200000000002</v>
-      </c>
-      <c r="AC11" s="8">
-        <f t="shared" si="13"/>
-        <v>-256.08754000000005</v>
-      </c>
-      <c r="AD11" s="8">
-        <f t="shared" si="13"/>
-        <v>-225.56309080000011</v>
-      </c>
-      <c r="AE11" s="8">
-        <f t="shared" si="13"/>
-        <v>-172.01277226000008</v>
-      </c>
       <c r="AF11" s="8">
-        <f t="shared" si="13"/>
-        <v>-67.891091616600079</v>
+        <f t="shared" ref="AF11:AP11" si="13">AF5-AF10</f>
+        <v>-633.69999999999993</v>
       </c>
       <c r="AG11" s="8">
         <f t="shared" si="13"/>
-        <v>97.493712779957832</v>
+        <v>-657.79409999999996</v>
       </c>
       <c r="AH11" s="8">
         <f t="shared" si="13"/>
-        <v>263.15568557976633</v>
+        <v>-647.33975000000009</v>
       </c>
       <c r="AI11" s="8">
         <f t="shared" si="13"/>
-        <v>434.61233243837285</v>
+        <v>-603.45389520000015</v>
       </c>
       <c r="AJ11" s="8">
         <f t="shared" si="13"/>
-        <v>587.70814026600101</v>
+        <v>-496.64090597600011</v>
       </c>
       <c r="AK11" s="8">
         <f t="shared" si="13"/>
-        <v>719.93479092925907</v>
+        <v>-316.86583210952017</v>
       </c>
       <c r="AL11" s="8">
         <f t="shared" si="13"/>
-        <v>785.72962170879669</v>
+        <v>-137.29470817141078</v>
+      </c>
+      <c r="AM11" s="8">
+        <f t="shared" si="13"/>
+        <v>48.504939476125855</v>
+      </c>
+      <c r="AN11" s="8">
+        <f t="shared" si="13"/>
+        <v>212.24816489058094</v>
+      </c>
+      <c r="AO11" s="8">
+        <f t="shared" si="13"/>
+        <v>350.97535588964411</v>
+      </c>
+      <c r="AP11" s="8">
+        <f t="shared" si="13"/>
+        <v>411.35370706285266</v>
       </c>
     </row>
-    <row r="12" spans="2:38" x14ac:dyDescent="0.3">
+    <row r="12" spans="2:42" x14ac:dyDescent="0.3">
       <c r="B12" t="s">
         <v>32</v>
       </c>
@@ -2203,38 +2263,31 @@
         <v>881.8</v>
       </c>
       <c r="V12" s="5">
-        <v>100</v>
-      </c>
-      <c r="X12" s="5">
+        <v>-949.6</v>
+      </c>
+      <c r="W12" s="5"/>
+      <c r="X12" s="5"/>
+      <c r="Y12" s="5"/>
+      <c r="Z12" s="5"/>
+      <c r="AB12" s="5">
         <f>SUM(C12:F12)</f>
         <v>63.3</v>
       </c>
-      <c r="Y12" s="5">
+      <c r="AC12" s="5">
         <f>SUM(G12:J12)</f>
         <v>-30.1</v>
       </c>
-      <c r="Z12" s="5">
+      <c r="AD12" s="5">
         <f>SUM(K12:N12)</f>
         <v>19.100000000000001</v>
       </c>
-      <c r="AA12" s="5">
+      <c r="AE12" s="5">
         <f>SUM(O12:R12)</f>
         <v>117.2</v>
       </c>
-      <c r="AB12" s="5">
-        <v>0</v>
-      </c>
-      <c r="AC12" s="5">
-        <v>0</v>
-      </c>
-      <c r="AD12" s="5">
-        <v>0</v>
-      </c>
-      <c r="AE12" s="5">
-        <v>0</v>
-      </c>
-      <c r="AF12" s="5">
-        <v>0</v>
+      <c r="AF12" s="11">
+        <f t="shared" ref="AF12:AF14" si="14">SUM(S12:V12)</f>
+        <v>-66.700000000000045</v>
       </c>
       <c r="AG12" s="5">
         <v>0</v>
@@ -2254,8 +2307,20 @@
       <c r="AL12" s="5">
         <v>0</v>
       </c>
+      <c r="AM12" s="5">
+        <v>0</v>
+      </c>
+      <c r="AN12" s="5">
+        <v>0</v>
+      </c>
+      <c r="AO12" s="5">
+        <v>0</v>
+      </c>
+      <c r="AP12" s="5">
+        <v>0</v>
+      </c>
     </row>
-    <row r="13" spans="2:38" x14ac:dyDescent="0.3">
+    <row r="13" spans="2:42" x14ac:dyDescent="0.3">
       <c r="B13" t="s">
         <v>33</v>
       </c>
@@ -2317,70 +2382,74 @@
         <v>-14.4</v>
       </c>
       <c r="V13" s="5">
-        <v>-18</v>
-      </c>
-      <c r="X13" s="5">
+        <v>-29.5</v>
+      </c>
+      <c r="W13" s="5"/>
+      <c r="X13" s="5"/>
+      <c r="Y13" s="5"/>
+      <c r="Z13" s="5"/>
+      <c r="AB13" s="5">
         <f>SUM(C13:F13)</f>
         <v>-0.1</v>
       </c>
-      <c r="Y13" s="5">
+      <c r="AC13" s="5">
         <f>SUM(G13:J13)</f>
         <v>-7.2</v>
       </c>
-      <c r="Z13" s="5">
+      <c r="AD13" s="5">
         <f>SUM(K13:N13)</f>
         <v>-19.3</v>
       </c>
-      <c r="AA13" s="5">
+      <c r="AE13" s="5">
         <f>SUM(O13:R13)</f>
         <v>-18.2</v>
       </c>
-      <c r="AB13" s="5">
-        <f>AA13*1.03</f>
-        <v>-18.745999999999999</v>
-      </c>
-      <c r="AC13" s="5">
-        <f t="shared" ref="AC13:AL13" si="14">AB13*1.03</f>
-        <v>-19.30838</v>
-      </c>
-      <c r="AD13" s="5">
+      <c r="AF13" s="11">
         <f t="shared" si="14"/>
-        <v>-19.8876314</v>
-      </c>
-      <c r="AE13" s="5">
-        <f t="shared" si="14"/>
-        <v>-20.484260341999999</v>
-      </c>
-      <c r="AF13" s="5">
-        <f t="shared" si="14"/>
-        <v>-21.098788152259999</v>
+        <v>-55.9</v>
       </c>
       <c r="AG13" s="5">
-        <f t="shared" si="14"/>
-        <v>-21.731751796827801</v>
+        <f t="shared" ref="AG13:AP13" si="15">AF13*1.03</f>
+        <v>-57.576999999999998</v>
       </c>
       <c r="AH13" s="5">
-        <f t="shared" si="14"/>
-        <v>-22.383704350732636</v>
+        <f t="shared" si="15"/>
+        <v>-59.304310000000001</v>
       </c>
       <c r="AI13" s="5">
-        <f t="shared" si="14"/>
-        <v>-23.055215481254617</v>
+        <f t="shared" si="15"/>
+        <v>-61.083439300000002</v>
       </c>
       <c r="AJ13" s="5">
-        <f t="shared" si="14"/>
-        <v>-23.746871945692256</v>
+        <f t="shared" si="15"/>
+        <v>-62.915942479000002</v>
       </c>
       <c r="AK13" s="5">
-        <f t="shared" si="14"/>
-        <v>-24.459278104063024</v>
+        <f t="shared" si="15"/>
+        <v>-64.803420753370006</v>
       </c>
       <c r="AL13" s="5">
-        <f t="shared" si="14"/>
-        <v>-25.193056447184915</v>
+        <f t="shared" si="15"/>
+        <v>-66.747523375971113</v>
+      </c>
+      <c r="AM13" s="5">
+        <f t="shared" si="15"/>
+        <v>-68.74994907725025</v>
+      </c>
+      <c r="AN13" s="5">
+        <f t="shared" si="15"/>
+        <v>-70.812447549567764</v>
+      </c>
+      <c r="AO13" s="5">
+        <f t="shared" si="15"/>
+        <v>-72.936820976054804</v>
+      </c>
+      <c r="AP13" s="5">
+        <f t="shared" si="15"/>
+        <v>-75.124925605336443</v>
       </c>
     </row>
-    <row r="14" spans="2:38" x14ac:dyDescent="0.3">
+    <row r="14" spans="2:42" x14ac:dyDescent="0.3">
       <c r="B14" t="s">
         <v>34</v>
       </c>
@@ -2443,38 +2512,32 @@
         <v>23.8</v>
       </c>
       <c r="V14" s="5">
-        <v>0</v>
-      </c>
-      <c r="X14" s="5">
+        <f>22.9-0.7</f>
+        <v>22.2</v>
+      </c>
+      <c r="W14" s="5"/>
+      <c r="X14" s="5"/>
+      <c r="Y14" s="5"/>
+      <c r="Z14" s="5"/>
+      <c r="AB14" s="5">
         <f>SUM(C14:F14)</f>
         <v>4.3</v>
       </c>
-      <c r="Y14" s="5">
+      <c r="AC14" s="5">
         <f>SUM(G14:J14)</f>
         <v>-0.1</v>
       </c>
-      <c r="Z14" s="5">
+      <c r="AD14" s="5">
         <f>SUM(K14:N14)</f>
         <v>0</v>
       </c>
-      <c r="AA14" s="5">
+      <c r="AE14" s="5">
         <f>SUM(O14:R14)</f>
         <v>0.30000000000000004</v>
       </c>
-      <c r="AB14" s="5">
-        <v>0</v>
-      </c>
-      <c r="AC14" s="5">
-        <v>0</v>
-      </c>
-      <c r="AD14" s="5">
-        <v>0</v>
-      </c>
-      <c r="AE14" s="5">
-        <v>0</v>
-      </c>
-      <c r="AF14" s="5">
-        <v>0</v>
+      <c r="AF14" s="11">
+        <f t="shared" si="14"/>
+        <v>45.7</v>
       </c>
       <c r="AG14" s="5">
         <v>0</v>
@@ -2494,298 +2557,318 @@
       <c r="AL14" s="5">
         <v>0</v>
       </c>
+      <c r="AM14" s="5">
+        <v>0</v>
+      </c>
+      <c r="AN14" s="5">
+        <v>0</v>
+      </c>
+      <c r="AO14" s="5">
+        <v>0</v>
+      </c>
+      <c r="AP14" s="5">
+        <v>0</v>
+      </c>
     </row>
-    <row r="15" spans="2:38" x14ac:dyDescent="0.3">
+    <row r="15" spans="2:42" x14ac:dyDescent="0.3">
       <c r="B15" t="s">
         <v>39</v>
       </c>
       <c r="C15" s="5">
-        <f t="shared" ref="C15:R15" si="15">SUM(C12:C14)</f>
+        <f t="shared" ref="C15:R15" si="16">SUM(C12:C14)</f>
         <v>0</v>
       </c>
       <c r="D15" s="5">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="E15" s="5">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>4.3</v>
       </c>
       <c r="F15" s="5">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>63.199999999999996</v>
       </c>
       <c r="G15" s="5">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>-14</v>
       </c>
       <c r="H15" s="5">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>-17.500000000000004</v>
       </c>
       <c r="I15" s="5">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>-0.90000000000000013</v>
       </c>
       <c r="J15" s="5">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>-5</v>
       </c>
       <c r="K15" s="5">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>-0.70000000000000007</v>
       </c>
       <c r="L15" s="5">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>10.6</v>
       </c>
       <c r="M15" s="5">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>2.4999999999999996</v>
       </c>
       <c r="N15" s="5">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>-12.600000000000001</v>
       </c>
       <c r="O15" s="5">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>-13.299999999999999</v>
       </c>
       <c r="P15" s="5">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>-11.299999999999999</v>
       </c>
       <c r="Q15" s="5">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>-0.60000000000000009</v>
       </c>
       <c r="R15" s="5">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>124.5</v>
       </c>
       <c r="S15" s="5">
-        <f t="shared" ref="S15:T15" si="16">SUM(S12:S14)</f>
+        <f t="shared" ref="S15:T15" si="17">SUM(S12:S14)</f>
         <v>-43.5</v>
       </c>
       <c r="T15" s="5">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>32.299999999999997</v>
       </c>
       <c r="U15" s="5">
-        <f t="shared" ref="U15:V15" si="17">SUM(U12:U14)</f>
+        <f t="shared" ref="U15:V15" si="18">SUM(U12:U14)</f>
         <v>891.19999999999993</v>
       </c>
       <c r="V15" s="5">
-        <f t="shared" si="17"/>
-        <v>82</v>
-      </c>
-      <c r="X15" s="5">
-        <f>SUM(X12:X14)</f>
+        <f t="shared" si="18"/>
+        <v>-956.9</v>
+      </c>
+      <c r="W15" s="5"/>
+      <c r="X15" s="5"/>
+      <c r="Y15" s="5"/>
+      <c r="Z15" s="5"/>
+      <c r="AB15" s="5">
+        <f>SUM(AB12:AB14)</f>
         <v>67.5</v>
       </c>
-      <c r="Y15" s="5">
-        <f>SUM(Y12:Y14)</f>
+      <c r="AC15" s="5">
+        <f>SUM(AC12:AC14)</f>
         <v>-37.400000000000006</v>
       </c>
-      <c r="Z15" s="5">
-        <f>SUM(Z12:Z14)</f>
+      <c r="AD15" s="5">
+        <f>SUM(AD12:AD14)</f>
         <v>-0.19999999999999929</v>
       </c>
-      <c r="AA15" s="5">
-        <f>SUM(AA12:AA14)</f>
+      <c r="AE15" s="5">
+        <f>SUM(AE12:AE14)</f>
         <v>99.3</v>
       </c>
-      <c r="AB15" s="5">
-        <f t="shared" ref="AB15:AL15" si="18">SUM(AB12:AB14)</f>
-        <v>-18.745999999999999</v>
-      </c>
-      <c r="AC15" s="5">
-        <f t="shared" si="18"/>
-        <v>-19.30838</v>
-      </c>
-      <c r="AD15" s="5">
-        <f t="shared" si="18"/>
-        <v>-19.8876314</v>
-      </c>
-      <c r="AE15" s="5">
-        <f t="shared" si="18"/>
-        <v>-20.484260341999999</v>
-      </c>
       <c r="AF15" s="5">
-        <f t="shared" si="18"/>
-        <v>-21.098788152259999</v>
+        <f t="shared" ref="AF15:AP15" si="19">SUM(AF12:AF14)</f>
+        <v>-76.900000000000048</v>
       </c>
       <c r="AG15" s="5">
-        <f t="shared" si="18"/>
-        <v>-21.731751796827801</v>
+        <f t="shared" si="19"/>
+        <v>-57.576999999999998</v>
       </c>
       <c r="AH15" s="5">
-        <f t="shared" si="18"/>
-        <v>-22.383704350732636</v>
+        <f t="shared" si="19"/>
+        <v>-59.304310000000001</v>
       </c>
       <c r="AI15" s="5">
-        <f t="shared" si="18"/>
-        <v>-23.055215481254617</v>
+        <f t="shared" si="19"/>
+        <v>-61.083439300000002</v>
       </c>
       <c r="AJ15" s="5">
-        <f t="shared" si="18"/>
-        <v>-23.746871945692256</v>
+        <f t="shared" si="19"/>
+        <v>-62.915942479000002</v>
       </c>
       <c r="AK15" s="5">
-        <f t="shared" si="18"/>
-        <v>-24.459278104063024</v>
+        <f t="shared" si="19"/>
+        <v>-64.803420753370006</v>
       </c>
       <c r="AL15" s="5">
-        <f t="shared" si="18"/>
-        <v>-25.193056447184915</v>
+        <f t="shared" si="19"/>
+        <v>-66.747523375971113</v>
+      </c>
+      <c r="AM15" s="5">
+        <f t="shared" si="19"/>
+        <v>-68.74994907725025</v>
+      </c>
+      <c r="AN15" s="5">
+        <f t="shared" si="19"/>
+        <v>-70.812447549567764</v>
+      </c>
+      <c r="AO15" s="5">
+        <f t="shared" si="19"/>
+        <v>-72.936820976054804</v>
+      </c>
+      <c r="AP15" s="5">
+        <f t="shared" si="19"/>
+        <v>-75.124925605336443</v>
       </c>
     </row>
-    <row r="16" spans="2:38" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="2:42" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B16" s="1" t="s">
         <v>35</v>
       </c>
       <c r="C16" s="8">
-        <f t="shared" ref="C16:R16" si="19">C11-C15</f>
+        <f t="shared" ref="C16:R16" si="20">C11-C15</f>
         <v>-7.4</v>
       </c>
       <c r="D16" s="8">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>-10</v>
       </c>
       <c r="E16" s="8">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>-14.899999999999999</v>
       </c>
       <c r="F16" s="8">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>-74</v>
       </c>
       <c r="G16" s="8">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>-4.3000000000000007</v>
       </c>
       <c r="H16" s="8">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>-1.4999999999999964</v>
       </c>
       <c r="I16" s="8">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>-23.9</v>
       </c>
       <c r="J16" s="8">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>-18.699999999999996</v>
       </c>
       <c r="K16" s="8">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>-27.3</v>
       </c>
       <c r="L16" s="8">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>-43.699999999999996</v>
       </c>
       <c r="M16" s="8">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>-44.6</v>
       </c>
       <c r="N16" s="8">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>-41.900000000000006</v>
       </c>
       <c r="O16" s="8">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>-39.600000000000009</v>
       </c>
       <c r="P16" s="8">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>-37.599999999999994</v>
       </c>
       <c r="Q16" s="8">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>-52.500000000000007</v>
       </c>
       <c r="R16" s="8">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>-202</v>
       </c>
       <c r="S16" s="8">
-        <f t="shared" ref="S16:T16" si="20">S11-S15</f>
+        <f t="shared" ref="S16:T16" si="21">S11-S15</f>
         <v>-32.200000000000003</v>
       </c>
       <c r="T16" s="8">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>-192.89999999999998</v>
       </c>
       <c r="U16" s="8">
-        <f t="shared" ref="U16:V16" si="21">U11-U15</f>
+        <f t="shared" ref="U16:V16" si="22">U11-U15</f>
         <v>-1060</v>
       </c>
       <c r="V16" s="8">
-        <f t="shared" si="21"/>
-        <v>-288.13</v>
-      </c>
-      <c r="X16" s="8">
-        <f>X11-X15</f>
+        <f t="shared" si="22"/>
+        <v>728.3</v>
+      </c>
+      <c r="W16" s="8"/>
+      <c r="X16" s="8"/>
+      <c r="Y16" s="8"/>
+      <c r="Z16" s="8"/>
+      <c r="AB16" s="8">
+        <f>AB11-AB15</f>
         <v>-106.3</v>
       </c>
-      <c r="Y16" s="8">
-        <f>Y11-Y15</f>
+      <c r="AC16" s="8">
+        <f>AC11-AC15</f>
         <v>-48.400000000000006</v>
       </c>
-      <c r="Z16" s="8">
-        <f>Z11-Z15</f>
+      <c r="AD16" s="8">
+        <f>AD11-AD15</f>
         <v>-157.50000000000003</v>
       </c>
-      <c r="AA16" s="8">
-        <f>AA11-AA15</f>
+      <c r="AE16" s="8">
+        <f>AE11-AE15</f>
         <v>-331.7</v>
       </c>
-      <c r="AB16" s="8">
-        <f t="shared" ref="AB16:AL16" si="22">AB11-AB15</f>
-        <v>-237.93600000000001</v>
-      </c>
-      <c r="AC16" s="8">
-        <f t="shared" si="22"/>
-        <v>-236.77916000000005</v>
-      </c>
-      <c r="AD16" s="8">
-        <f t="shared" si="22"/>
-        <v>-205.67545940000011</v>
-      </c>
-      <c r="AE16" s="8">
-        <f t="shared" si="22"/>
-        <v>-151.52851191800008</v>
-      </c>
       <c r="AF16" s="8">
-        <f t="shared" si="22"/>
-        <v>-46.79230346434008</v>
+        <f t="shared" ref="AF16:AP16" si="23">AF11-AF15</f>
+        <v>-556.79999999999984</v>
       </c>
       <c r="AG16" s="8">
-        <f t="shared" si="22"/>
-        <v>119.22546457678564</v>
+        <f t="shared" si="23"/>
+        <v>-600.21709999999996</v>
       </c>
       <c r="AH16" s="8">
-        <f t="shared" si="22"/>
-        <v>285.53938993049894</v>
+        <f t="shared" si="23"/>
+        <v>-588.03544000000011</v>
       </c>
       <c r="AI16" s="8">
-        <f t="shared" si="22"/>
-        <v>457.66754791962745</v>
+        <f t="shared" si="23"/>
+        <v>-542.37045590000014</v>
       </c>
       <c r="AJ16" s="8">
-        <f t="shared" si="22"/>
-        <v>611.45501221169332</v>
+        <f t="shared" si="23"/>
+        <v>-433.72496349700009</v>
       </c>
       <c r="AK16" s="8">
-        <f t="shared" si="22"/>
-        <v>744.39406903332213</v>
+        <f t="shared" si="23"/>
+        <v>-252.06241135615016</v>
       </c>
       <c r="AL16" s="8">
-        <f t="shared" si="22"/>
-        <v>810.92267815598166</v>
+        <f t="shared" si="23"/>
+        <v>-70.547184795439662</v>
+      </c>
+      <c r="AM16" s="8">
+        <f t="shared" si="23"/>
+        <v>117.25488855337611</v>
+      </c>
+      <c r="AN16" s="8">
+        <f t="shared" si="23"/>
+        <v>283.0606124401487</v>
+      </c>
+      <c r="AO16" s="8">
+        <f t="shared" si="23"/>
+        <v>423.91217686569894</v>
+      </c>
+      <c r="AP16" s="8">
+        <f t="shared" si="23"/>
+        <v>486.47863266818911</v>
       </c>
     </row>
-    <row r="17" spans="2:156" x14ac:dyDescent="0.3">
+    <row r="17" spans="2:160" x14ac:dyDescent="0.3">
       <c r="B17" t="s">
         <v>36</v>
       </c>
@@ -2847,39 +2930,31 @@
         <v>-4.4000000000000004</v>
       </c>
       <c r="V17" s="5">
-        <f>V16*0.05</f>
-        <v>-14.406500000000001</v>
-      </c>
-      <c r="X17" s="5">
+        <v>-24.9</v>
+      </c>
+      <c r="W17" s="5"/>
+      <c r="X17" s="5"/>
+      <c r="Y17" s="5"/>
+      <c r="Z17" s="5"/>
+      <c r="AB17" s="5">
         <f>SUM(C17:F17)</f>
         <v>0</v>
       </c>
-      <c r="Y17" s="5">
+      <c r="AC17" s="5">
         <f>SUM(G17:J17)</f>
         <v>0</v>
       </c>
-      <c r="Z17" s="5">
+      <c r="AD17" s="5">
         <f>SUM(K17:N17)</f>
         <v>0</v>
       </c>
-      <c r="AA17" s="5">
+      <c r="AE17" s="5">
         <f>SUM(O17:R17)</f>
         <v>0</v>
       </c>
-      <c r="AB17" s="5">
-        <v>0</v>
-      </c>
-      <c r="AC17" s="5">
-        <v>0</v>
-      </c>
-      <c r="AD17" s="5">
-        <v>0</v>
-      </c>
-      <c r="AE17" s="5">
-        <v>0</v>
-      </c>
-      <c r="AF17" s="5">
-        <v>0</v>
+      <c r="AF17" s="11">
+        <f>SUM(S17:V17)</f>
+        <v>-44.6</v>
       </c>
       <c r="AG17" s="5">
         <v>0</v>
@@ -2899,694 +2974,710 @@
       <c r="AL17" s="5">
         <v>0</v>
       </c>
+      <c r="AM17" s="5">
+        <v>0</v>
+      </c>
+      <c r="AN17" s="5">
+        <v>0</v>
+      </c>
+      <c r="AO17" s="5">
+        <v>0</v>
+      </c>
+      <c r="AP17" s="5">
+        <v>0</v>
+      </c>
     </row>
-    <row r="18" spans="2:156" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="2:160" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B18" s="1" t="s">
         <v>37</v>
       </c>
       <c r="C18" s="8">
-        <f t="shared" ref="C18:R18" si="23">C16-C17</f>
+        <f t="shared" ref="C18:R18" si="24">C16-C17</f>
         <v>-7.4</v>
       </c>
       <c r="D18" s="8">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>-10</v>
       </c>
       <c r="E18" s="8">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>-14.899999999999999</v>
       </c>
       <c r="F18" s="8">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>-74</v>
       </c>
       <c r="G18" s="8">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>-4.3000000000000007</v>
       </c>
       <c r="H18" s="8">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>-1.4999999999999964</v>
       </c>
       <c r="I18" s="8">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>-23.9</v>
       </c>
       <c r="J18" s="8">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>-18.699999999999996</v>
       </c>
       <c r="K18" s="8">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>-27.3</v>
       </c>
       <c r="L18" s="8">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>-43.699999999999996</v>
       </c>
       <c r="M18" s="8">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>-44.6</v>
       </c>
       <c r="N18" s="8">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>-41.900000000000006</v>
       </c>
       <c r="O18" s="8">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>-39.600000000000009</v>
       </c>
       <c r="P18" s="8">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>-37.599999999999994</v>
       </c>
       <c r="Q18" s="8">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>-52.500000000000007</v>
       </c>
       <c r="R18" s="8">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>-202</v>
       </c>
       <c r="S18" s="8">
-        <f t="shared" ref="S18:V18" si="24">S16-S17</f>
+        <f t="shared" ref="S18:V18" si="25">S16-S17</f>
         <v>-32.200000000000003</v>
       </c>
       <c r="T18" s="8">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>-177.59999999999997</v>
       </c>
       <c r="U18" s="8">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>-1055.5999999999999</v>
       </c>
       <c r="V18" s="8">
-        <f t="shared" si="24"/>
-        <v>-273.7235</v>
-      </c>
-      <c r="X18" s="8">
-        <f>X16-X17</f>
-        <v>-106.3</v>
-      </c>
-      <c r="Y18" s="8">
-        <f>Y16-Y17</f>
-        <v>-48.400000000000006</v>
-      </c>
-      <c r="Z18" s="8">
-        <f>Z16-Z17</f>
-        <v>-157.50000000000003</v>
-      </c>
-      <c r="AA18" s="8">
-        <f>AA16-AA17</f>
-        <v>-331.7</v>
-      </c>
+        <f t="shared" si="25"/>
+        <v>753.19999999999993</v>
+      </c>
+      <c r="W18" s="8"/>
+      <c r="X18" s="8"/>
+      <c r="Y18" s="8"/>
+      <c r="Z18" s="8"/>
       <c r="AB18" s="8">
         <f>AB16-AB17</f>
-        <v>-237.93600000000001</v>
+        <v>-106.3</v>
       </c>
       <c r="AC18" s="8">
-        <f t="shared" ref="AC18:AL18" si="25">AC16-AC17</f>
-        <v>-236.77916000000005</v>
+        <f>AC16-AC17</f>
+        <v>-48.400000000000006</v>
       </c>
       <c r="AD18" s="8">
-        <f t="shared" si="25"/>
-        <v>-205.67545940000011</v>
+        <f>AD16-AD17</f>
+        <v>-157.50000000000003</v>
       </c>
       <c r="AE18" s="8">
-        <f t="shared" si="25"/>
-        <v>-151.52851191800008</v>
+        <f>AE16-AE17</f>
+        <v>-331.7</v>
       </c>
       <c r="AF18" s="8">
-        <f t="shared" si="25"/>
-        <v>-46.79230346434008</v>
+        <f>AF16-AF17</f>
+        <v>-512.19999999999982</v>
       </c>
       <c r="AG18" s="8">
-        <f t="shared" si="25"/>
-        <v>119.22546457678564</v>
+        <f t="shared" ref="AG18:AP18" si="26">AG16-AG17</f>
+        <v>-600.21709999999996</v>
       </c>
       <c r="AH18" s="8">
-        <f t="shared" si="25"/>
-        <v>285.53938993049894</v>
+        <f t="shared" si="26"/>
+        <v>-588.03544000000011</v>
       </c>
       <c r="AI18" s="8">
-        <f t="shared" si="25"/>
-        <v>457.66754791962745</v>
+        <f t="shared" si="26"/>
+        <v>-542.37045590000014</v>
       </c>
       <c r="AJ18" s="8">
-        <f t="shared" si="25"/>
-        <v>611.45501221169332</v>
+        <f t="shared" si="26"/>
+        <v>-433.72496349700009</v>
       </c>
       <c r="AK18" s="8">
-        <f t="shared" si="25"/>
-        <v>744.39406903332213</v>
+        <f t="shared" si="26"/>
+        <v>-252.06241135615016</v>
       </c>
       <c r="AL18" s="8">
-        <f t="shared" si="25"/>
-        <v>810.92267815598166</v>
-      </c>
-      <c r="AM18" s="1">
-        <f>AL18*(1+$AP$23)</f>
-        <v>802.81345137442179</v>
-      </c>
-      <c r="AN18" s="1">
-        <f t="shared" ref="AN18:CY18" si="26">AM18*(1+$AP$23)</f>
-        <v>794.78531686067754</v>
-      </c>
-      <c r="AO18" s="1">
         <f t="shared" si="26"/>
-        <v>786.83746369207074</v>
-      </c>
-      <c r="AP18" s="1">
+        <v>-70.547184795439662</v>
+      </c>
+      <c r="AM18" s="8">
         <f t="shared" si="26"/>
-        <v>778.96908905514999</v>
+        <v>117.25488855337611</v>
+      </c>
+      <c r="AN18" s="8">
+        <f t="shared" si="26"/>
+        <v>283.0606124401487</v>
+      </c>
+      <c r="AO18" s="8">
+        <f t="shared" si="26"/>
+        <v>423.91217686569894</v>
+      </c>
+      <c r="AP18" s="8">
+        <f t="shared" si="26"/>
+        <v>486.47863266818911</v>
       </c>
       <c r="AQ18" s="1">
-        <f t="shared" si="26"/>
-        <v>771.17939816459852</v>
+        <f>AP18*(1+$AT$23)</f>
+        <v>481.61384634150721</v>
       </c>
       <c r="AR18" s="1">
-        <f t="shared" si="26"/>
-        <v>763.46760418295253</v>
+        <f t="shared" ref="AR18:DC18" si="27">AQ18*(1+$AT$23)</f>
+        <v>476.79770787809213</v>
       </c>
       <c r="AS18" s="1">
-        <f t="shared" si="26"/>
-        <v>755.83292814112303</v>
+        <f t="shared" si="27"/>
+        <v>472.02973079931121</v>
       </c>
       <c r="AT18" s="1">
-        <f t="shared" si="26"/>
-        <v>748.27459885971177</v>
+        <f t="shared" si="27"/>
+        <v>467.30943349131809</v>
       </c>
       <c r="AU18" s="1">
-        <f t="shared" si="26"/>
-        <v>740.79185287111466</v>
+        <f t="shared" si="27"/>
+        <v>462.63633915640492</v>
       </c>
       <c r="AV18" s="1">
-        <f t="shared" si="26"/>
-        <v>733.38393434240345</v>
+        <f t="shared" si="27"/>
+        <v>458.00997576484087</v>
       </c>
       <c r="AW18" s="1">
-        <f t="shared" si="26"/>
-        <v>726.05009499897938</v>
+        <f t="shared" si="27"/>
+        <v>453.42987600719243</v>
       </c>
       <c r="AX18" s="1">
-        <f t="shared" si="26"/>
-        <v>718.78959404898956</v>
+        <f t="shared" si="27"/>
+        <v>448.89557724712051</v>
       </c>
       <c r="AY18" s="1">
-        <f t="shared" si="26"/>
-        <v>711.6016981084997</v>
+        <f t="shared" si="27"/>
+        <v>444.40662147464928</v>
       </c>
       <c r="AZ18" s="1">
-        <f t="shared" si="26"/>
-        <v>704.48568112741475</v>
+        <f t="shared" si="27"/>
+        <v>439.96255525990279</v>
       </c>
       <c r="BA18" s="1">
-        <f t="shared" si="26"/>
-        <v>697.44082431614061</v>
+        <f t="shared" si="27"/>
+        <v>435.56292970730374</v>
       </c>
       <c r="BB18" s="1">
-        <f t="shared" si="26"/>
-        <v>690.4664160729792</v>
+        <f t="shared" si="27"/>
+        <v>431.20730041023069</v>
       </c>
       <c r="BC18" s="1">
-        <f t="shared" si="26"/>
-        <v>683.56175191224941</v>
+        <f t="shared" si="27"/>
+        <v>426.89522740612836</v>
       </c>
       <c r="BD18" s="1">
-        <f t="shared" si="26"/>
-        <v>676.72613439312693</v>
+        <f t="shared" si="27"/>
+        <v>422.62627513206706</v>
       </c>
       <c r="BE18" s="1">
-        <f t="shared" si="26"/>
-        <v>669.95887304919563</v>
+        <f t="shared" si="27"/>
+        <v>418.40001238074638</v>
       </c>
       <c r="BF18" s="1">
-        <f t="shared" si="26"/>
-        <v>663.25928431870364</v>
+        <f t="shared" si="27"/>
+        <v>414.21601225693888</v>
       </c>
       <c r="BG18" s="1">
-        <f t="shared" si="26"/>
-        <v>656.62669147551662</v>
+        <f t="shared" si="27"/>
+        <v>410.07385213436947</v>
       </c>
       <c r="BH18" s="1">
-        <f t="shared" si="26"/>
-        <v>650.06042456076148</v>
+        <f t="shared" si="27"/>
+        <v>405.97311361302576</v>
       </c>
       <c r="BI18" s="1">
-        <f t="shared" si="26"/>
-        <v>643.55982031515384</v>
+        <f t="shared" si="27"/>
+        <v>401.91338247689549</v>
       </c>
       <c r="BJ18" s="1">
-        <f t="shared" si="26"/>
-        <v>637.12422211200226</v>
+        <f t="shared" si="27"/>
+        <v>397.89424865212652</v>
       </c>
       <c r="BK18" s="1">
-        <f t="shared" si="26"/>
-        <v>630.75297989088222</v>
+        <f t="shared" si="27"/>
+        <v>393.91530616560527</v>
       </c>
       <c r="BL18" s="1">
-        <f t="shared" si="26"/>
-        <v>624.44545009197338</v>
+        <f t="shared" si="27"/>
+        <v>389.97615310394923</v>
       </c>
       <c r="BM18" s="1">
-        <f t="shared" si="26"/>
-        <v>618.2009955910537</v>
+        <f t="shared" si="27"/>
+        <v>386.07639157290976</v>
       </c>
       <c r="BN18" s="1">
-        <f t="shared" si="26"/>
-        <v>612.01898563514317</v>
+        <f t="shared" si="27"/>
+        <v>382.21562765718068</v>
       </c>
       <c r="BO18" s="1">
-        <f t="shared" si="26"/>
-        <v>605.89879577879174</v>
+        <f t="shared" si="27"/>
+        <v>378.39347138060884</v>
       </c>
       <c r="BP18" s="1">
-        <f t="shared" si="26"/>
-        <v>599.83980782100377</v>
+        <f t="shared" si="27"/>
+        <v>374.60953666680274</v>
       </c>
       <c r="BQ18" s="1">
-        <f t="shared" si="26"/>
-        <v>593.84140974279376</v>
+        <f t="shared" si="27"/>
+        <v>370.8634413001347</v>
       </c>
       <c r="BR18" s="1">
-        <f t="shared" si="26"/>
-        <v>587.90299564536576</v>
+        <f t="shared" si="27"/>
+        <v>367.15480688713336</v>
       </c>
       <c r="BS18" s="1">
-        <f t="shared" si="26"/>
-        <v>582.02396568891209</v>
+        <f t="shared" si="27"/>
+        <v>363.48325881826202</v>
       </c>
       <c r="BT18" s="1">
-        <f t="shared" si="26"/>
-        <v>576.20372603202293</v>
+        <f t="shared" si="27"/>
+        <v>359.84842623007938</v>
       </c>
       <c r="BU18" s="1">
-        <f t="shared" si="26"/>
-        <v>570.44168877170273</v>
+        <f t="shared" si="27"/>
+        <v>356.24994196777857</v>
       </c>
       <c r="BV18" s="1">
-        <f t="shared" si="26"/>
-        <v>564.73727188398573</v>
+        <f t="shared" si="27"/>
+        <v>352.68744254810076</v>
       </c>
       <c r="BW18" s="1">
-        <f t="shared" si="26"/>
-        <v>559.08989916514588</v>
+        <f t="shared" si="27"/>
+        <v>349.16056812261974</v>
       </c>
       <c r="BX18" s="1">
-        <f t="shared" si="26"/>
-        <v>553.49900017349444</v>
+        <f t="shared" si="27"/>
+        <v>345.66896244139355</v>
       </c>
       <c r="BY18" s="1">
-        <f t="shared" si="26"/>
-        <v>547.96401017175947</v>
+        <f t="shared" si="27"/>
+        <v>342.21227281697963</v>
       </c>
       <c r="BZ18" s="1">
-        <f t="shared" si="26"/>
-        <v>542.4843700700419</v>
+        <f t="shared" si="27"/>
+        <v>338.79015008880981</v>
       </c>
       <c r="CA18" s="1">
-        <f t="shared" si="26"/>
-        <v>537.05952636934148</v>
+        <f t="shared" si="27"/>
+        <v>335.40224858792169</v>
       </c>
       <c r="CB18" s="1">
-        <f t="shared" si="26"/>
-        <v>531.68893110564807</v>
+        <f t="shared" si="27"/>
+        <v>332.04822610204246</v>
       </c>
       <c r="CC18" s="1">
-        <f t="shared" si="26"/>
-        <v>526.37204179459161</v>
+        <f t="shared" si="27"/>
+        <v>328.72774384102206</v>
       </c>
       <c r="CD18" s="1">
-        <f t="shared" si="26"/>
-        <v>521.10832137664568</v>
+        <f t="shared" si="27"/>
+        <v>325.44046640261183</v>
       </c>
       <c r="CE18" s="1">
-        <f t="shared" si="26"/>
-        <v>515.89723816287926</v>
+        <f t="shared" si="27"/>
+        <v>322.18606173858569</v>
       </c>
       <c r="CF18" s="1">
-        <f t="shared" si="26"/>
-        <v>510.73826578125045</v>
+        <f t="shared" si="27"/>
+        <v>318.96420112119984</v>
       </c>
       <c r="CG18" s="1">
-        <f t="shared" si="26"/>
-        <v>505.63088312343791</v>
+        <f t="shared" si="27"/>
+        <v>315.77455910998782</v>
       </c>
       <c r="CH18" s="1">
-        <f t="shared" si="26"/>
-        <v>500.57457429220352</v>
+        <f t="shared" si="27"/>
+        <v>312.61681351888797</v>
       </c>
       <c r="CI18" s="1">
-        <f t="shared" si="26"/>
-        <v>495.56882854928148</v>
+        <f t="shared" si="27"/>
+        <v>309.49064538369907</v>
       </c>
       <c r="CJ18" s="1">
-        <f t="shared" si="26"/>
-        <v>490.61314026378864</v>
+        <f t="shared" si="27"/>
+        <v>306.39573892986209</v>
       </c>
       <c r="CK18" s="1">
-        <f t="shared" si="26"/>
-        <v>485.70700886115077</v>
+        <f t="shared" si="27"/>
+        <v>303.33178154056344</v>
       </c>
       <c r="CL18" s="1">
-        <f t="shared" si="26"/>
-        <v>480.84993877253925</v>
+        <f t="shared" si="27"/>
+        <v>300.29846372515783</v>
       </c>
       <c r="CM18" s="1">
-        <f t="shared" si="26"/>
-        <v>476.04143938481383</v>
+        <f t="shared" si="27"/>
+        <v>297.29547908790624</v>
       </c>
       <c r="CN18" s="1">
-        <f t="shared" si="26"/>
-        <v>471.2810249909657</v>
+        <f t="shared" si="27"/>
+        <v>294.3225242970272</v>
       </c>
       <c r="CO18" s="1">
-        <f t="shared" si="26"/>
-        <v>466.56821474105607</v>
+        <f t="shared" si="27"/>
+        <v>291.3792990540569</v>
       </c>
       <c r="CP18" s="1">
-        <f t="shared" si="26"/>
-        <v>461.9025325936455</v>
+        <f t="shared" si="27"/>
+        <v>288.46550606351633</v>
       </c>
       <c r="CQ18" s="1">
-        <f t="shared" si="26"/>
-        <v>457.28350726770907</v>
+        <f t="shared" si="27"/>
+        <v>285.58085100288116</v>
       </c>
       <c r="CR18" s="1">
-        <f t="shared" si="26"/>
-        <v>452.71067219503198</v>
+        <f t="shared" si="27"/>
+        <v>282.72504249285237</v>
       </c>
       <c r="CS18" s="1">
-        <f t="shared" si="26"/>
-        <v>448.18356547308167</v>
+        <f t="shared" si="27"/>
+        <v>279.89779206792383</v>
       </c>
       <c r="CT18" s="1">
-        <f t="shared" si="26"/>
-        <v>443.70172981835083</v>
+        <f t="shared" si="27"/>
+        <v>277.09881414724458</v>
       </c>
       <c r="CU18" s="1">
-        <f t="shared" si="26"/>
-        <v>439.26471252016734</v>
+        <f t="shared" si="27"/>
+        <v>274.32782600577212</v>
       </c>
       <c r="CV18" s="1">
-        <f t="shared" si="26"/>
-        <v>434.87206539496566</v>
+        <f t="shared" si="27"/>
+        <v>271.58454774571442</v>
       </c>
       <c r="CW18" s="1">
-        <f t="shared" si="26"/>
-        <v>430.52334474101599</v>
+        <f t="shared" si="27"/>
+        <v>268.86870226825727</v>
       </c>
       <c r="CX18" s="1">
-        <f t="shared" si="26"/>
-        <v>426.21811129360583</v>
+        <f t="shared" si="27"/>
+        <v>266.18001524557468</v>
       </c>
       <c r="CY18" s="1">
-        <f t="shared" si="26"/>
-        <v>421.95593018066978</v>
+        <f t="shared" si="27"/>
+        <v>263.51821509311895</v>
       </c>
       <c r="CZ18" s="1">
-        <f t="shared" ref="CZ18:EZ18" si="27">CY18*(1+$AP$23)</f>
-        <v>417.73637087886306</v>
+        <f t="shared" si="27"/>
+        <v>260.88303294218775</v>
       </c>
       <c r="DA18" s="1">
         <f t="shared" si="27"/>
-        <v>413.55900717007444</v>
+        <v>258.27420261276586</v>
       </c>
       <c r="DB18" s="1">
         <f t="shared" si="27"/>
-        <v>409.4234170983737</v>
+        <v>255.69146058663821</v>
       </c>
       <c r="DC18" s="1">
         <f t="shared" si="27"/>
-        <v>405.32918292738998</v>
+        <v>253.13454598077183</v>
       </c>
       <c r="DD18" s="1">
-        <f t="shared" si="27"/>
-        <v>401.27589109811606</v>
+        <f t="shared" ref="DD18:FD18" si="28">DC18*(1+$AT$23)</f>
+        <v>250.60320052096412</v>
       </c>
       <c r="DE18" s="1">
-        <f t="shared" si="27"/>
-        <v>397.26313218713489</v>
+        <f t="shared" si="28"/>
+        <v>248.09716851575448</v>
       </c>
       <c r="DF18" s="1">
-        <f t="shared" si="27"/>
-        <v>393.29050086526354</v>
+        <f t="shared" si="28"/>
+        <v>245.61619683059692</v>
       </c>
       <c r="DG18" s="1">
-        <f t="shared" si="27"/>
-        <v>389.35759585661089</v>
+        <f t="shared" si="28"/>
+        <v>243.16003486229096</v>
       </c>
       <c r="DH18" s="1">
-        <f t="shared" si="27"/>
-        <v>385.4640198980448</v>
+        <f t="shared" si="28"/>
+        <v>240.72843451366805</v>
       </c>
       <c r="DI18" s="1">
-        <f t="shared" si="27"/>
-        <v>381.60937969906433</v>
+        <f t="shared" si="28"/>
+        <v>238.32115016853137</v>
       </c>
       <c r="DJ18" s="1">
-        <f t="shared" si="27"/>
-        <v>377.79328590207371</v>
+        <f t="shared" si="28"/>
+        <v>235.93793866684607</v>
       </c>
       <c r="DK18" s="1">
-        <f t="shared" si="27"/>
-        <v>374.01535304305298</v>
+        <f t="shared" si="28"/>
+        <v>233.57855928017761</v>
       </c>
       <c r="DL18" s="1">
-        <f t="shared" si="27"/>
-        <v>370.27519951262246</v>
+        <f t="shared" si="28"/>
+        <v>231.24277368737583</v>
       </c>
       <c r="DM18" s="1">
-        <f t="shared" si="27"/>
-        <v>366.57244751749624</v>
+        <f t="shared" si="28"/>
+        <v>228.93034595050207</v>
       </c>
       <c r="DN18" s="1">
-        <f t="shared" si="27"/>
-        <v>362.90672304232129</v>
+        <f t="shared" si="28"/>
+        <v>226.64104249099705</v>
       </c>
       <c r="DO18" s="1">
-        <f t="shared" si="27"/>
-        <v>359.27765581189806</v>
+        <f t="shared" si="28"/>
+        <v>224.37463206608709</v>
       </c>
       <c r="DP18" s="1">
-        <f t="shared" si="27"/>
-        <v>355.68487925377906</v>
+        <f t="shared" si="28"/>
+        <v>222.13088574542621</v>
       </c>
       <c r="DQ18" s="1">
-        <f t="shared" si="27"/>
-        <v>352.12803046124128</v>
+        <f t="shared" si="28"/>
+        <v>219.90957688797195</v>
       </c>
       <c r="DR18" s="1">
-        <f t="shared" si="27"/>
-        <v>348.60675015662889</v>
+        <f t="shared" si="28"/>
+        <v>217.71048111909224</v>
       </c>
       <c r="DS18" s="1">
-        <f t="shared" si="27"/>
-        <v>345.12068265506258</v>
+        <f t="shared" si="28"/>
+        <v>215.53337630790131</v>
       </c>
       <c r="DT18" s="1">
-        <f t="shared" si="27"/>
-        <v>341.66947582851196</v>
+        <f t="shared" si="28"/>
+        <v>213.37804254482228</v>
       </c>
       <c r="DU18" s="1">
-        <f t="shared" si="27"/>
-        <v>338.25278107022683</v>
+        <f t="shared" si="28"/>
+        <v>211.24426211937404</v>
       </c>
       <c r="DV18" s="1">
-        <f t="shared" si="27"/>
-        <v>334.87025325952453</v>
+        <f t="shared" si="28"/>
+        <v>209.13181949818031</v>
       </c>
       <c r="DW18" s="1">
-        <f t="shared" si="27"/>
-        <v>331.52155072692926</v>
+        <f t="shared" si="28"/>
+        <v>207.04050130319851</v>
       </c>
       <c r="DX18" s="1">
-        <f t="shared" si="27"/>
-        <v>328.20633521965999</v>
+        <f t="shared" si="28"/>
+        <v>204.97009629016654</v>
       </c>
       <c r="DY18" s="1">
-        <f t="shared" si="27"/>
-        <v>324.9242718674634</v>
+        <f t="shared" si="28"/>
+        <v>202.92039532726488</v>
       </c>
       <c r="DZ18" s="1">
-        <f t="shared" si="27"/>
-        <v>321.67502914878878</v>
+        <f t="shared" si="28"/>
+        <v>200.89119137399223</v>
       </c>
       <c r="EA18" s="1">
-        <f t="shared" si="27"/>
-        <v>318.45827885730091</v>
+        <f t="shared" si="28"/>
+        <v>198.88227946025231</v>
       </c>
       <c r="EB18" s="1">
-        <f t="shared" si="27"/>
-        <v>315.27369606872787</v>
+        <f t="shared" si="28"/>
+        <v>196.89345666564978</v>
       </c>
       <c r="EC18" s="1">
-        <f t="shared" si="27"/>
-        <v>312.12095910804061</v>
+        <f t="shared" si="28"/>
+        <v>194.92452209899329</v>
       </c>
       <c r="ED18" s="1">
-        <f t="shared" si="27"/>
-        <v>308.99974951696021</v>
+        <f t="shared" si="28"/>
+        <v>192.97527687800337</v>
       </c>
       <c r="EE18" s="1">
-        <f t="shared" si="27"/>
-        <v>305.90975202179061</v>
+        <f t="shared" si="28"/>
+        <v>191.04552410922332</v>
       </c>
       <c r="EF18" s="1">
-        <f t="shared" si="27"/>
-        <v>302.85065450157271</v>
+        <f t="shared" si="28"/>
+        <v>189.1350688681311</v>
       </c>
       <c r="EG18" s="1">
-        <f t="shared" si="27"/>
-        <v>299.82214795655699</v>
+        <f t="shared" si="28"/>
+        <v>187.24371817944979</v>
       </c>
       <c r="EH18" s="1">
-        <f t="shared" si="27"/>
-        <v>296.8239264769914</v>
+        <f t="shared" si="28"/>
+        <v>185.37128099765528</v>
       </c>
       <c r="EI18" s="1">
-        <f t="shared" si="27"/>
-        <v>293.85568721222148</v>
+        <f t="shared" si="28"/>
+        <v>183.51756818767873</v>
       </c>
       <c r="EJ18" s="1">
-        <f t="shared" si="27"/>
-        <v>290.91713034009928</v>
+        <f t="shared" si="28"/>
+        <v>181.68239250580194</v>
       </c>
       <c r="EK18" s="1">
-        <f t="shared" si="27"/>
-        <v>288.00795903669831</v>
+        <f t="shared" si="28"/>
+        <v>179.86556858074391</v>
       </c>
       <c r="EL18" s="1">
-        <f t="shared" si="27"/>
-        <v>285.12787944633135</v>
+        <f t="shared" si="28"/>
+        <v>178.06691289493648</v>
       </c>
       <c r="EM18" s="1">
-        <f t="shared" si="27"/>
-        <v>282.27660065186802</v>
+        <f t="shared" si="28"/>
+        <v>176.28624376598711</v>
       </c>
       <c r="EN18" s="1">
-        <f t="shared" si="27"/>
-        <v>279.45383464534933</v>
+        <f t="shared" si="28"/>
+        <v>174.52338132832725</v>
       </c>
       <c r="EO18" s="1">
-        <f t="shared" si="27"/>
-        <v>276.65929629889581</v>
+        <f t="shared" si="28"/>
+        <v>172.77814751504397</v>
       </c>
       <c r="EP18" s="1">
-        <f t="shared" si="27"/>
-        <v>273.89270333590684</v>
+        <f t="shared" si="28"/>
+        <v>171.05036603989353</v>
       </c>
       <c r="EQ18" s="1">
-        <f t="shared" si="27"/>
-        <v>271.15377630254778</v>
+        <f t="shared" si="28"/>
+        <v>169.3398623794946</v>
       </c>
       <c r="ER18" s="1">
-        <f t="shared" si="27"/>
-        <v>268.44223853952229</v>
+        <f t="shared" si="28"/>
+        <v>167.64646375569967</v>
       </c>
       <c r="ES18" s="1">
-        <f t="shared" si="27"/>
-        <v>265.75781615412706</v>
+        <f t="shared" si="28"/>
+        <v>165.96999911814268</v>
       </c>
       <c r="ET18" s="1">
-        <f t="shared" si="27"/>
-        <v>263.10023799258579</v>
+        <f t="shared" si="28"/>
+        <v>164.31029912696124</v>
       </c>
       <c r="EU18" s="1">
-        <f t="shared" si="27"/>
-        <v>260.46923561265993</v>
+        <f t="shared" si="28"/>
+        <v>162.66719613569163</v>
       </c>
       <c r="EV18" s="1">
-        <f t="shared" si="27"/>
-        <v>257.86454325653335</v>
+        <f t="shared" si="28"/>
+        <v>161.04052417433471</v>
       </c>
       <c r="EW18" s="1">
-        <f t="shared" si="27"/>
-        <v>255.28589782396801</v>
+        <f t="shared" si="28"/>
+        <v>159.43011893259137</v>
       </c>
       <c r="EX18" s="1">
-        <f t="shared" si="27"/>
-        <v>252.73303884572834</v>
+        <f t="shared" si="28"/>
+        <v>157.83581774326547</v>
       </c>
       <c r="EY18" s="1">
-        <f t="shared" si="27"/>
-        <v>250.20570845727107</v>
+        <f t="shared" si="28"/>
+        <v>156.25745956583282</v>
       </c>
       <c r="EZ18" s="1">
-        <f t="shared" si="27"/>
-        <v>247.70365137269835</v>
+        <f t="shared" si="28"/>
+        <v>154.69488497017448</v>
+      </c>
+      <c r="FA18" s="1">
+        <f t="shared" si="28"/>
+        <v>153.14793612047274</v>
+      </c>
+      <c r="FB18" s="1">
+        <f t="shared" si="28"/>
+        <v>151.616456759268</v>
+      </c>
+      <c r="FC18" s="1">
+        <f t="shared" si="28"/>
+        <v>150.10029219167532</v>
+      </c>
+      <c r="FD18" s="1">
+        <f t="shared" si="28"/>
+        <v>148.59928926975857</v>
       </c>
     </row>
-    <row r="19" spans="2:156" x14ac:dyDescent="0.3">
+    <row r="19" spans="2:160" x14ac:dyDescent="0.3">
       <c r="B19" t="s">
         <v>2</v>
       </c>
       <c r="C19" s="5">
-        <f t="shared" ref="C19:S19" si="28">216.4</f>
+        <f t="shared" ref="C19:S19" si="29">216.4</f>
         <v>216.4</v>
       </c>
       <c r="D19" s="5">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>216.4</v>
       </c>
       <c r="E19" s="5">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>216.4</v>
       </c>
       <c r="F19" s="5">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>216.4</v>
       </c>
       <c r="G19" s="5">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>216.4</v>
       </c>
       <c r="H19" s="5">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>216.4</v>
       </c>
       <c r="I19" s="5">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>216.4</v>
       </c>
       <c r="J19" s="5">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>216.4</v>
       </c>
       <c r="K19" s="5">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>216.4</v>
       </c>
       <c r="L19" s="5">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>216.4</v>
       </c>
       <c r="M19" s="5">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>216.4</v>
       </c>
       <c r="N19" s="5">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>216.4</v>
       </c>
       <c r="O19" s="5">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>216.4</v>
       </c>
       <c r="P19" s="5">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>216.4</v>
       </c>
       <c r="Q19" s="5">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>216.4</v>
       </c>
       <c r="R19" s="5">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>216.4</v>
       </c>
       <c r="S19" s="5">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>216.4</v>
       </c>
       <c r="T19" s="5">
@@ -3598,71 +3689,75 @@
         <v>354.3</v>
       </c>
       <c r="V19" s="5">
-        <f>354.3</f>
-        <v>354.3</v>
-      </c>
-      <c r="X19" s="5">
+        <f>366.6</f>
+        <v>366.6</v>
+      </c>
+      <c r="W19" s="5"/>
+      <c r="X19" s="5"/>
+      <c r="Y19" s="5"/>
+      <c r="Z19" s="5"/>
+      <c r="AB19" s="5">
         <f>216.4</f>
         <v>216.4</v>
       </c>
-      <c r="Y19" s="5">
+      <c r="AC19" s="5">
         <f>216.4</f>
         <v>216.4</v>
       </c>
-      <c r="Z19" s="5">
+      <c r="AD19" s="5">
         <f>216.4</f>
         <v>216.4</v>
       </c>
-      <c r="AA19" s="5">
+      <c r="AE19" s="5">
         <f>216.4</f>
         <v>216.4</v>
       </c>
-      <c r="AB19" s="5">
-        <f t="shared" ref="AB19:AL19" si="29">354.3</f>
-        <v>354.3</v>
-      </c>
-      <c r="AC19" s="5">
-        <f t="shared" si="29"/>
-        <v>354.3</v>
-      </c>
-      <c r="AD19" s="5">
-        <f t="shared" si="29"/>
-        <v>354.3</v>
-      </c>
-      <c r="AE19" s="5">
-        <f t="shared" si="29"/>
-        <v>354.3</v>
-      </c>
       <c r="AF19" s="5">
-        <f t="shared" si="29"/>
-        <v>354.3</v>
+        <f>366.6</f>
+        <v>366.6</v>
       </c>
       <c r="AG19" s="5">
-        <f t="shared" si="29"/>
-        <v>354.3</v>
+        <f>366.6</f>
+        <v>366.6</v>
       </c>
       <c r="AH19" s="5">
-        <f t="shared" si="29"/>
-        <v>354.3</v>
+        <f>366.6</f>
+        <v>366.6</v>
       </c>
       <c r="AI19" s="5">
-        <f t="shared" si="29"/>
-        <v>354.3</v>
+        <f>366.6</f>
+        <v>366.6</v>
       </c>
       <c r="AJ19" s="5">
-        <f t="shared" si="29"/>
-        <v>354.3</v>
+        <f>366.6</f>
+        <v>366.6</v>
       </c>
       <c r="AK19" s="5">
-        <f t="shared" si="29"/>
-        <v>354.3</v>
+        <f>366.6</f>
+        <v>366.6</v>
       </c>
       <c r="AL19" s="5">
-        <f t="shared" si="29"/>
-        <v>354.3</v>
+        <f>366.6</f>
+        <v>366.6</v>
+      </c>
+      <c r="AM19" s="5">
+        <f>366.6</f>
+        <v>366.6</v>
+      </c>
+      <c r="AN19" s="5">
+        <f>366.6</f>
+        <v>366.6</v>
+      </c>
+      <c r="AO19" s="5">
+        <f>366.6</f>
+        <v>366.6</v>
+      </c>
+      <c r="AP19" s="5">
+        <f>366.6</f>
+        <v>366.6</v>
       </c>
     </row>
-    <row r="20" spans="2:156" x14ac:dyDescent="0.3">
+    <row r="20" spans="2:160" x14ac:dyDescent="0.3">
       <c r="B20" t="s">
         <v>38</v>
       </c>
@@ -3744,70 +3839,74 @@
       </c>
       <c r="V20" s="7">
         <f t="shared" si="31"/>
-        <v>-0.77257550098786332</v>
-      </c>
-      <c r="X20" s="7">
-        <f>X18/X19</f>
-        <v>-0.49121996303142329</v>
-      </c>
-      <c r="Y20" s="7">
-        <f>Y18/Y19</f>
-        <v>-0.2236598890942699</v>
-      </c>
-      <c r="Z20" s="7">
-        <f>Z18/Z19</f>
-        <v>-0.72781885397412216</v>
-      </c>
-      <c r="AA20" s="7">
-        <f>AA18/AA19</f>
-        <v>-1.5328096118299444</v>
-      </c>
+        <v>2.0545553737043094</v>
+      </c>
+      <c r="W20" s="7"/>
+      <c r="X20" s="7"/>
+      <c r="Y20" s="7"/>
+      <c r="Z20" s="7"/>
       <c r="AB20" s="7">
         <f>AB18/AB19</f>
-        <v>-0.67156646909398809</v>
+        <v>-0.49121996303142329</v>
       </c>
       <c r="AC20" s="7">
-        <f t="shared" ref="AC20:AL20" si="32">AC18/AC19</f>
-        <v>-0.66830132655941299</v>
+        <f>AC18/AC19</f>
+        <v>-0.2236598890942699</v>
       </c>
       <c r="AD20" s="7">
-        <f t="shared" si="32"/>
-        <v>-0.58051216313858345</v>
+        <f>AD18/AD19</f>
+        <v>-0.72781885397412216</v>
       </c>
       <c r="AE20" s="7">
-        <f t="shared" si="32"/>
-        <v>-0.42768419959920989</v>
+        <f>AE18/AE19</f>
+        <v>-1.5328096118299444</v>
       </c>
       <c r="AF20" s="7">
-        <f t="shared" si="32"/>
-        <v>-0.13206972470883455</v>
+        <f>AF18/AF19</f>
+        <v>-1.3971631205673753</v>
       </c>
       <c r="AG20" s="7">
-        <f t="shared" si="32"/>
-        <v>0.33650991977642009</v>
+        <f t="shared" ref="AG20:AP20" si="32">AG18/AG19</f>
+        <v>-1.6372534097108562</v>
       </c>
       <c r="AH20" s="7">
         <f t="shared" si="32"/>
-        <v>0.80592545845469643</v>
+        <v>-1.6040246590289144</v>
       </c>
       <c r="AI20" s="7">
         <f t="shared" si="32"/>
-        <v>1.2917514759233064</v>
+        <v>-1.4794611453900712</v>
       </c>
       <c r="AJ20" s="7">
         <f t="shared" si="32"/>
-        <v>1.7258114936824536</v>
+        <v>-1.18310137342335</v>
       </c>
       <c r="AK20" s="7">
         <f t="shared" si="32"/>
-        <v>2.1010275727725714</v>
+        <v>-0.68756795241721258</v>
       </c>
       <c r="AL20" s="7">
         <f t="shared" si="32"/>
-        <v>2.2888023656674616</v>
+        <v>-0.19243640151511091</v>
+      </c>
+      <c r="AM20" s="7">
+        <f t="shared" si="32"/>
+        <v>0.31984421318433198</v>
+      </c>
+      <c r="AN20" s="7">
+        <f t="shared" si="32"/>
+        <v>0.77212387463215681</v>
+      </c>
+      <c r="AO20" s="7">
+        <f t="shared" si="32"/>
+        <v>1.1563343613357853</v>
+      </c>
+      <c r="AP20" s="7">
+        <f t="shared" si="32"/>
+        <v>1.3270011802187371</v>
       </c>
     </row>
-    <row r="22" spans="2:156" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="2:160" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B22" s="1" t="s">
         <v>44</v>
       </c>
@@ -3877,67 +3976,71 @@
       </c>
       <c r="V22" s="9">
         <f t="shared" si="34"/>
-        <v>2.6752136752136755</v>
-      </c>
+        <v>4.2905982905982905</v>
+      </c>
+      <c r="W22" s="9"/>
       <c r="X22" s="9"/>
-      <c r="Y22" s="9">
-        <f>Y3/X3-1</f>
+      <c r="Y22" s="9"/>
+      <c r="Z22" s="9"/>
+      <c r="AB22" s="9"/>
+      <c r="AC22" s="9">
+        <f>AC3/AB3-1</f>
         <v>4.5999999999999996</v>
       </c>
-      <c r="Z22" s="9">
-        <f t="shared" ref="Z22:AL22" si="35">Z3/Y3-1</f>
+      <c r="AD22" s="9">
+        <f t="shared" ref="AD22:AP22" si="35">AD3/AC3-1</f>
         <v>0.96428571428571441</v>
       </c>
-      <c r="AA22" s="9">
+      <c r="AE22" s="9">
         <f t="shared" si="35"/>
         <v>0.95909090909090877</v>
       </c>
-      <c r="AB22" s="9">
+      <c r="AF22" s="9">
         <f t="shared" si="35"/>
-        <v>1.5800464037122972</v>
-      </c>
-      <c r="AC22" s="9">
+        <v>2.0185614849187936</v>
+      </c>
+      <c r="AG22" s="9">
         <f t="shared" si="35"/>
         <v>0.89999999999999991</v>
       </c>
-      <c r="AD22" s="9">
+      <c r="AH22" s="9">
         <f t="shared" si="35"/>
         <v>0.75</v>
       </c>
-      <c r="AE22" s="9">
+      <c r="AI22" s="9">
         <f t="shared" si="35"/>
         <v>0.60000000000000009</v>
       </c>
-      <c r="AF22" s="9">
+      <c r="AJ22" s="9">
         <f t="shared" si="35"/>
         <v>0.5</v>
       </c>
-      <c r="AG22" s="9">
+      <c r="AK22" s="9">
         <f t="shared" si="35"/>
         <v>0.44999999999999996</v>
       </c>
-      <c r="AH22" s="9">
+      <c r="AL22" s="9">
         <f t="shared" si="35"/>
         <v>0.25</v>
       </c>
-      <c r="AI22" s="9">
+      <c r="AM22" s="9">
         <f t="shared" si="35"/>
         <v>0.19999999999999996</v>
       </c>
-      <c r="AJ22" s="9">
+      <c r="AN22" s="9">
         <f t="shared" si="35"/>
         <v>0.14999999999999991</v>
       </c>
-      <c r="AK22" s="9">
+      <c r="AO22" s="9">
         <f t="shared" si="35"/>
         <v>0.10000000000000009</v>
       </c>
-      <c r="AL22" s="9">
+      <c r="AP22" s="9">
         <f t="shared" si="35"/>
         <v>5.0000000000000044E-2</v>
       </c>
     </row>
-    <row r="23" spans="2:156" x14ac:dyDescent="0.3">
+    <row r="23" spans="2:160" x14ac:dyDescent="0.3">
       <c r="B23" t="s">
         <v>45</v>
       </c>
@@ -4019,76 +4122,80 @@
       </c>
       <c r="V23" s="10">
         <f t="shared" si="37"/>
-        <v>0.49</v>
-      </c>
-      <c r="X23" s="10">
-        <f t="shared" ref="X23" si="38">X5/X3</f>
+        <v>0.29563812600969303</v>
+      </c>
+      <c r="W23" s="10"/>
+      <c r="X23" s="10"/>
+      <c r="Y23" s="10"/>
+      <c r="Z23" s="10"/>
+      <c r="AB23" s="10">
+        <f t="shared" ref="AB23" si="38">AB5/AB3</f>
         <v>0.5</v>
       </c>
-      <c r="Y23" s="10">
-        <f>Y5/Y3</f>
+      <c r="AC23" s="10">
+        <f>AC5/AC3</f>
         <v>0.74107142857142849</v>
       </c>
-      <c r="Z23" s="10">
-        <f t="shared" ref="Z23:AL23" si="39">Z5/Z3</f>
+      <c r="AD23" s="10">
+        <f t="shared" ref="AD23:AP23" si="39">AD5/AD3</f>
         <v>0.63181818181818172</v>
       </c>
-      <c r="AA23" s="10">
+      <c r="AE23" s="10">
         <f t="shared" si="39"/>
         <v>0.52436194895591637</v>
       </c>
-      <c r="AB23" s="10">
+      <c r="AF23" s="10">
         <f t="shared" si="39"/>
-        <v>0.5</v>
-      </c>
-      <c r="AC23" s="10">
+        <v>0.40430438124519597</v>
+      </c>
+      <c r="AG23" s="10">
         <f t="shared" si="39"/>
         <v>0.51</v>
       </c>
-      <c r="AD23" s="10">
+      <c r="AH23" s="10">
         <f t="shared" si="39"/>
         <v>0.52</v>
       </c>
-      <c r="AE23" s="10">
+      <c r="AI23" s="10">
         <f t="shared" si="39"/>
         <v>0.52</v>
       </c>
-      <c r="AF23" s="10">
+      <c r="AJ23" s="10">
         <f t="shared" si="39"/>
         <v>0.54</v>
       </c>
-      <c r="AG23" s="10">
+      <c r="AK23" s="10">
         <f t="shared" si="39"/>
         <v>0.56000000000000005</v>
       </c>
-      <c r="AH23" s="10">
+      <c r="AL23" s="10">
         <f t="shared" si="39"/>
         <v>0.57999999999999996</v>
       </c>
-      <c r="AI23" s="10">
+      <c r="AM23" s="10">
         <f t="shared" si="39"/>
         <v>0.6</v>
       </c>
-      <c r="AJ23" s="10">
+      <c r="AN23" s="10">
         <f t="shared" si="39"/>
         <v>0.61</v>
       </c>
-      <c r="AK23" s="10">
+      <c r="AO23" s="10">
         <f t="shared" si="39"/>
         <v>0.62</v>
       </c>
-      <c r="AL23" s="10">
+      <c r="AP23" s="10">
         <f t="shared" si="39"/>
         <v>0.62</v>
       </c>
-      <c r="AO23" t="s">
+      <c r="AS23" t="s">
         <v>52</v>
       </c>
-      <c r="AP23" s="10">
+      <c r="AT23" s="10">
         <v>-0.01</v>
       </c>
     </row>
-    <row r="24" spans="2:156" x14ac:dyDescent="0.3">
+    <row r="24" spans="2:160" x14ac:dyDescent="0.3">
       <c r="B24" t="s">
         <v>46</v>
       </c>
@@ -4158,48 +4265,36 @@
       </c>
       <c r="V24" s="10">
         <f t="shared" si="41"/>
-        <v>0.99501246882793004</v>
-      </c>
+        <v>1.3965087281795507</v>
+      </c>
+      <c r="W24" s="10"/>
       <c r="X24" s="10"/>
-      <c r="Y24" s="10">
-        <f>Y6/X6-1</f>
+      <c r="Y24" s="10"/>
+      <c r="Z24" s="10"/>
+      <c r="AB24" s="10"/>
+      <c r="AC24" s="10">
+        <f>AC6/AB6-1</f>
         <v>1.1674876847290645</v>
       </c>
-      <c r="Z24" s="10">
-        <f t="shared" ref="Z24:AL24" si="42">Z6/Y6-1</f>
+      <c r="AD24" s="10">
+        <f t="shared" ref="AD24:AP24" si="42">AD6/AC6-1</f>
         <v>1.0977272727272727</v>
       </c>
-      <c r="AA24" s="10">
+      <c r="AE24" s="10">
         <f t="shared" si="42"/>
         <v>0.48320693391115932</v>
       </c>
-      <c r="AB24" s="10">
+      <c r="AF24" s="10">
         <f t="shared" si="42"/>
-        <v>0.17999999999999994</v>
-      </c>
-      <c r="AC24" s="10">
+        <v>1.2337472607742872</v>
+      </c>
+      <c r="AG24" s="10">
         <f t="shared" si="42"/>
         <v>0.12000000000000011</v>
       </c>
-      <c r="AD24" s="10">
+      <c r="AH24" s="10">
         <f t="shared" si="42"/>
         <v>7.0000000000000062E-2</v>
-      </c>
-      <c r="AE24" s="10">
-        <f t="shared" si="42"/>
-        <v>5.0000000000000044E-2</v>
-      </c>
-      <c r="AF24" s="10">
-        <f t="shared" si="42"/>
-        <v>5.0000000000000044E-2</v>
-      </c>
-      <c r="AG24" s="10">
-        <f t="shared" si="42"/>
-        <v>5.0000000000000044E-2</v>
-      </c>
-      <c r="AH24" s="10">
-        <f t="shared" si="42"/>
-        <v>5.0000000000000044E-2</v>
       </c>
       <c r="AI24" s="10">
         <f t="shared" si="42"/>
@@ -4217,14 +4312,30 @@
         <f t="shared" si="42"/>
         <v>5.0000000000000044E-2</v>
       </c>
-      <c r="AO24" t="s">
+      <c r="AM24" s="10">
+        <f t="shared" si="42"/>
+        <v>5.0000000000000044E-2</v>
+      </c>
+      <c r="AN24" s="10">
+        <f t="shared" si="42"/>
+        <v>5.0000000000000044E-2</v>
+      </c>
+      <c r="AO24" s="10">
+        <f t="shared" si="42"/>
+        <v>5.0000000000000044E-2</v>
+      </c>
+      <c r="AP24" s="10">
+        <f t="shared" si="42"/>
+        <v>5.0000000000000044E-2</v>
+      </c>
+      <c r="AS24" t="s">
         <v>53</v>
       </c>
-      <c r="AP24" s="10">
+      <c r="AT24" s="10">
         <v>0.08</v>
       </c>
     </row>
-    <row r="25" spans="2:156" x14ac:dyDescent="0.3">
+    <row r="25" spans="2:160" x14ac:dyDescent="0.3">
       <c r="B25" t="s">
         <v>47</v>
       </c>
@@ -4306,77 +4417,81 @@
       </c>
       <c r="V25" s="10">
         <f t="shared" si="44"/>
-        <v>0.39999999999999997</v>
-      </c>
-      <c r="X25" s="10">
-        <f t="shared" ref="X25" si="45">X7/X3</f>
+        <v>0.3150242326332795</v>
+      </c>
+      <c r="W25" s="10"/>
+      <c r="X25" s="10"/>
+      <c r="Y25" s="10"/>
+      <c r="Z25" s="10"/>
+      <c r="AB25" s="10">
+        <f t="shared" ref="AB25" si="45">AB7/AB3</f>
         <v>1.6</v>
       </c>
-      <c r="Y25" s="10">
-        <f>Y7/Y3</f>
+      <c r="AC25" s="10">
+        <f>AC7/AC3</f>
         <v>0.75000000000000011</v>
       </c>
-      <c r="Z25" s="10">
-        <f t="shared" ref="Z25:AL25" si="46">Z7/Z3</f>
+      <c r="AD25" s="10">
+        <f t="shared" ref="AD25:AP25" si="46">AD7/AD3</f>
         <v>0.8318181818181819</v>
       </c>
-      <c r="AA25" s="10">
+      <c r="AE25" s="10">
         <f t="shared" si="46"/>
         <v>0.65661252900232026</v>
       </c>
-      <c r="AB25" s="10">
+      <c r="AF25" s="10">
         <f t="shared" si="46"/>
-        <v>0.4</v>
-      </c>
-      <c r="AC25" s="10">
+        <v>0.41045349730976172</v>
+      </c>
+      <c r="AG25" s="10">
         <f t="shared" si="46"/>
         <v>0.3</v>
       </c>
-      <c r="AD25" s="10">
+      <c r="AH25" s="10">
         <f t="shared" si="46"/>
         <v>0.26</v>
       </c>
-      <c r="AE25" s="10">
+      <c r="AI25" s="10">
         <f t="shared" si="46"/>
         <v>0.24</v>
       </c>
-      <c r="AF25" s="10">
+      <c r="AJ25" s="10">
         <f t="shared" si="46"/>
-        <v>0.22000000000000003</v>
-      </c>
-      <c r="AG25" s="10">
+        <v>0.22</v>
+      </c>
+      <c r="AK25" s="10">
         <f t="shared" si="46"/>
-        <v>0.20000000000000004</v>
-      </c>
-      <c r="AH25" s="10">
+        <v>0.2</v>
+      </c>
+      <c r="AL25" s="10">
         <f t="shared" si="46"/>
         <v>0.18</v>
       </c>
-      <c r="AI25" s="10">
+      <c r="AM25" s="10">
         <f t="shared" si="46"/>
         <v>0.17</v>
       </c>
-      <c r="AJ25" s="10">
+      <c r="AN25" s="10">
         <f t="shared" si="46"/>
         <v>0.16</v>
       </c>
-      <c r="AK25" s="10">
+      <c r="AO25" s="10">
         <f t="shared" si="46"/>
         <v>0.15</v>
       </c>
-      <c r="AL25" s="10">
+      <c r="AP25" s="10">
         <f t="shared" si="46"/>
         <v>0.14000000000000001</v>
       </c>
-      <c r="AO25" t="s">
+      <c r="AS25" t="s">
         <v>54</v>
       </c>
-      <c r="AP25" s="5">
-        <f>NPV(AP24,AA18:EZ18)</f>
-        <v>3936.6052737763594</v>
+      <c r="AT25" s="5">
+        <f>NPV(AT24,AE18:FD18)</f>
+        <v>207.1587666279265</v>
       </c>
     </row>
-    <row r="26" spans="2:156" x14ac:dyDescent="0.3">
+    <row r="26" spans="2:160" x14ac:dyDescent="0.3">
       <c r="B26" t="s">
         <v>48</v>
       </c>
@@ -4446,56 +4561,44 @@
       </c>
       <c r="V26" s="10">
         <f t="shared" si="48"/>
-        <v>2.3670033670033672</v>
-      </c>
+        <v>2.0538720538720541</v>
+      </c>
+      <c r="W26" s="10"/>
       <c r="X26" s="10"/>
-      <c r="Y26" s="10">
-        <f>Y8/X8-1</f>
+      <c r="Y26" s="10"/>
+      <c r="Z26" s="10"/>
+      <c r="AB26" s="10"/>
+      <c r="AC26" s="10">
+        <f>AC8/AB8-1</f>
         <v>1.6086956521739131</v>
       </c>
-      <c r="Z26" s="10">
-        <f t="shared" ref="Z26:AL26" si="49">Z8/Y8-1</f>
+      <c r="AD26" s="10">
+        <f t="shared" ref="AD26:AP26" si="49">AD8/AC8-1</f>
         <v>0.40833333333333344</v>
       </c>
-      <c r="AA26" s="10">
+      <c r="AE26" s="10">
         <f t="shared" si="49"/>
         <v>0.4023668639053255</v>
       </c>
-      <c r="AB26" s="10">
+      <c r="AF26" s="10">
         <f t="shared" si="49"/>
-        <v>0.10000000000000009</v>
-      </c>
-      <c r="AC26" s="10">
+        <v>2.4472573839662446</v>
+      </c>
+      <c r="AG26" s="10">
         <f t="shared" si="49"/>
         <v>8.0000000000000071E-2</v>
       </c>
-      <c r="AD26" s="10">
+      <c r="AH26" s="10">
         <f t="shared" si="49"/>
         <v>6.0000000000000053E-2</v>
       </c>
-      <c r="AE26" s="10">
+      <c r="AI26" s="10">
         <f t="shared" si="49"/>
         <v>4.0000000000000036E-2</v>
       </c>
-      <c r="AF26" s="10">
+      <c r="AJ26" s="10">
         <f t="shared" si="49"/>
         <v>3.0000000000000027E-2</v>
-      </c>
-      <c r="AG26" s="10">
-        <f t="shared" si="49"/>
-        <v>2.0000000000000018E-2</v>
-      </c>
-      <c r="AH26" s="10">
-        <f t="shared" si="49"/>
-        <v>2.0000000000000018E-2</v>
-      </c>
-      <c r="AI26" s="10">
-        <f t="shared" si="49"/>
-        <v>2.0000000000000018E-2</v>
-      </c>
-      <c r="AJ26" s="10">
-        <f t="shared" si="49"/>
-        <v>2.0000000000000018E-2</v>
       </c>
       <c r="AK26" s="10">
         <f t="shared" si="49"/>
@@ -4505,15 +4608,31 @@
         <f t="shared" si="49"/>
         <v>2.0000000000000018E-2</v>
       </c>
-      <c r="AO26" t="s">
+      <c r="AM26" s="10">
+        <f t="shared" si="49"/>
+        <v>2.0000000000000018E-2</v>
+      </c>
+      <c r="AN26" s="10">
+        <f t="shared" si="49"/>
+        <v>2.0000000000000018E-2</v>
+      </c>
+      <c r="AO26" s="10">
+        <f t="shared" si="49"/>
+        <v>2.0000000000000018E-2</v>
+      </c>
+      <c r="AP26" s="10">
+        <f t="shared" si="49"/>
+        <v>2.0000000000000018E-2</v>
+      </c>
+      <c r="AS26" t="s">
         <v>55</v>
       </c>
-      <c r="AP26" s="5">
+      <c r="AT26" s="5">
         <f>Main!D8</f>
-        <v>-283.29999999999995</v>
+        <v>3336.7999999999997</v>
       </c>
     </row>
-    <row r="27" spans="2:156" x14ac:dyDescent="0.3">
+    <row r="27" spans="2:160" x14ac:dyDescent="0.3">
       <c r="B27" t="s">
         <v>49</v>
       </c>
@@ -4583,52 +4702,40 @@
       </c>
       <c r="V27" s="10">
         <f t="shared" si="51"/>
-        <v>4.4545454545454541</v>
-      </c>
+        <v>6.3818181818181818</v>
+      </c>
+      <c r="W27" s="10"/>
       <c r="X27" s="10"/>
-      <c r="Y27" s="10">
-        <f>Y9/X9-1</f>
+      <c r="Y27" s="10"/>
+      <c r="Z27" s="10"/>
+      <c r="AB27" s="10"/>
+      <c r="AC27" s="10">
+        <f>AC9/AB9-1</f>
         <v>1.2799999999999998</v>
       </c>
-      <c r="Z27" s="10">
-        <f t="shared" ref="Z27:AL27" si="52">Z9/Y9-1</f>
+      <c r="AD27" s="10">
+        <f t="shared" ref="AD27:AP27" si="52">AD9/AC9-1</f>
         <v>0.80701754385964941</v>
       </c>
-      <c r="AA27" s="10">
+      <c r="AE27" s="10">
         <f t="shared" si="52"/>
         <v>0.81553398058252435</v>
       </c>
-      <c r="AB27" s="10">
+      <c r="AF27" s="10">
         <f t="shared" si="52"/>
-        <v>0.5</v>
-      </c>
-      <c r="AC27" s="10">
+        <v>3.3850267379679142</v>
+      </c>
+      <c r="AG27" s="10">
         <f t="shared" si="52"/>
         <v>0.25</v>
       </c>
-      <c r="AD27" s="10">
+      <c r="AH27" s="10">
         <f t="shared" si="52"/>
         <v>0.10000000000000009</v>
       </c>
-      <c r="AE27" s="10">
+      <c r="AI27" s="10">
         <f t="shared" si="52"/>
         <v>7.0000000000000062E-2</v>
-      </c>
-      <c r="AF27" s="10">
-        <f t="shared" si="52"/>
-        <v>3.0000000000000027E-2</v>
-      </c>
-      <c r="AG27" s="10">
-        <f t="shared" si="52"/>
-        <v>3.0000000000000027E-2</v>
-      </c>
-      <c r="AH27" s="10">
-        <f t="shared" si="52"/>
-        <v>3.0000000000000027E-2</v>
-      </c>
-      <c r="AI27" s="10">
-        <f t="shared" si="52"/>
-        <v>3.0000000000000027E-2</v>
       </c>
       <c r="AJ27" s="10">
         <f t="shared" si="52"/>
@@ -4642,15 +4749,31 @@
         <f t="shared" si="52"/>
         <v>3.0000000000000027E-2</v>
       </c>
-      <c r="AO27" t="s">
+      <c r="AM27" s="10">
+        <f t="shared" si="52"/>
+        <v>3.0000000000000027E-2</v>
+      </c>
+      <c r="AN27" s="10">
+        <f t="shared" si="52"/>
+        <v>3.0000000000000027E-2</v>
+      </c>
+      <c r="AO27" s="10">
+        <f t="shared" si="52"/>
+        <v>3.0000000000000027E-2</v>
+      </c>
+      <c r="AP27" s="10">
+        <f t="shared" si="52"/>
+        <v>3.0000000000000027E-2</v>
+      </c>
+      <c r="AS27" t="s">
         <v>56</v>
       </c>
-      <c r="AP27" s="5">
-        <f>AP25+AP26</f>
-        <v>3653.3052737763592</v>
+      <c r="AT27" s="5">
+        <f>AT25+AT26</f>
+        <v>3543.9587666279263</v>
       </c>
     </row>
-    <row r="28" spans="2:156" x14ac:dyDescent="0.3">
+    <row r="28" spans="2:160" x14ac:dyDescent="0.3">
       <c r="B28" t="s">
         <v>50</v>
       </c>
@@ -4732,77 +4855,81 @@
       </c>
       <c r="V28" s="10">
         <f t="shared" si="54"/>
-        <v>-4.7937209302325581</v>
-      </c>
-      <c r="X28" s="10">
-        <f t="shared" ref="X28" si="55">X11/X3</f>
+        <v>-3.6930533117932152</v>
+      </c>
+      <c r="W28" s="10"/>
+      <c r="X28" s="10"/>
+      <c r="Y28" s="10"/>
+      <c r="Z28" s="10"/>
+      <c r="AB28" s="10">
+        <f t="shared" ref="AB28" si="55">AB11/AB3</f>
         <v>-19.399999999999999</v>
       </c>
-      <c r="Y28" s="10">
-        <f>Y11/Y3</f>
+      <c r="AC28" s="10">
+        <f>AC11/AC3</f>
         <v>-7.6607142857142874</v>
       </c>
-      <c r="Z28" s="10">
-        <f t="shared" ref="Z28:AL28" si="56">Z11/Z3</f>
+      <c r="AD28" s="10">
+        <f t="shared" ref="AD28:AP28" si="56">AD11/AD3</f>
         <v>-7.1681818181818189</v>
       </c>
-      <c r="AA28" s="10">
+      <c r="AE28" s="10">
         <f t="shared" si="56"/>
         <v>-5.3921113689095135</v>
       </c>
-      <c r="AB28" s="10">
-        <f t="shared" si="56"/>
-        <v>-2.3082913669064751</v>
-      </c>
-      <c r="AC28" s="10">
-        <f t="shared" si="56"/>
-        <v>-1.2120765808405911</v>
-      </c>
-      <c r="AD28" s="10">
-        <f t="shared" si="56"/>
-        <v>-0.61005866500784378</v>
-      </c>
-      <c r="AE28" s="10">
-        <f t="shared" si="56"/>
-        <v>-0.29076643766565713</v>
-      </c>
       <c r="AF28" s="10">
         <f t="shared" si="56"/>
-        <v>-7.6507694164142465E-2</v>
+        <v>-4.8708685626441195</v>
       </c>
       <c r="AG28" s="10">
         <f t="shared" si="56"/>
-        <v>7.5770635329919497E-2</v>
+        <v>-2.661087018083256</v>
       </c>
       <c r="AH28" s="10">
         <f t="shared" si="56"/>
-        <v>0.16361648700003939</v>
+        <v>-1.4964538556229163</v>
       </c>
       <c r="AI28" s="10">
         <f t="shared" si="56"/>
-        <v>0.22518274332484903</v>
+        <v>-0.87187688937948282</v>
       </c>
       <c r="AJ28" s="10">
         <f t="shared" si="56"/>
-        <v>0.2647871626230488</v>
+        <v>-0.47836819756539711</v>
       </c>
       <c r="AK28" s="10">
         <f t="shared" si="56"/>
-        <v>0.29487346695202088</v>
+        <v>-0.21048794167926657</v>
       </c>
       <c r="AL28" s="10">
         <f t="shared" si="56"/>
-        <v>0.30649709437885903</v>
-      </c>
-      <c r="AO28" t="s">
+        <v>-7.2961809316107892E-2</v>
+      </c>
+      <c r="AM28" s="10">
+        <f t="shared" si="56"/>
+        <v>2.1480605431929929E-2</v>
+      </c>
+      <c r="AN28" s="10">
+        <f t="shared" si="56"/>
+        <v>8.1734734161945669E-2</v>
+      </c>
+      <c r="AO28" s="10">
+        <f t="shared" si="56"/>
+        <v>0.12287022353300914</v>
+      </c>
+      <c r="AP28" s="10">
+        <f t="shared" si="56"/>
+        <v>0.13715010413067769</v>
+      </c>
+      <c r="AS28" t="s">
         <v>57</v>
       </c>
-      <c r="AP28" s="4">
-        <f>AP27/AL19</f>
-        <v>10.311332977071293</v>
+      <c r="AT28" s="4">
+        <f>AT27/AP19</f>
+        <v>9.6670997453025809</v>
       </c>
     </row>
-    <row r="29" spans="2:156" x14ac:dyDescent="0.3">
+    <row r="29" spans="2:160" x14ac:dyDescent="0.3">
       <c r="B29" t="s">
         <v>36</v>
       </c>
@@ -4884,34 +5011,22 @@
       </c>
       <c r="V29" s="10">
         <f t="shared" si="58"/>
-        <v>0.05</v>
-      </c>
-      <c r="X29" s="10">
-        <f t="shared" ref="X29" si="59">X17/X16</f>
-        <v>0</v>
-      </c>
-      <c r="Y29" s="10">
-        <f>Y17/Y16</f>
-        <v>0</v>
-      </c>
-      <c r="Z29" s="10">
-        <f t="shared" ref="Z29:AL29" si="60">Z17/Z16</f>
-        <v>0</v>
-      </c>
-      <c r="AA29" s="10">
-        <f t="shared" si="60"/>
-        <v>0</v>
-      </c>
+        <v>-3.4189207744061513E-2</v>
+      </c>
+      <c r="W29" s="10"/>
+      <c r="X29" s="10"/>
+      <c r="Y29" s="10"/>
+      <c r="Z29" s="10"/>
       <c r="AB29" s="10">
-        <f t="shared" si="60"/>
+        <f t="shared" ref="AB29" si="59">AB17/AB16</f>
         <v>0</v>
       </c>
       <c r="AC29" s="10">
-        <f t="shared" si="60"/>
+        <f>AC17/AC16</f>
         <v>0</v>
       </c>
       <c r="AD29" s="10">
-        <f t="shared" si="60"/>
+        <f t="shared" ref="AD29:AP29" si="60">AD17/AD16</f>
         <v>0</v>
       </c>
       <c r="AE29" s="10">
@@ -4920,7 +5035,7 @@
       </c>
       <c r="AF29" s="10">
         <f t="shared" si="60"/>
-        <v>0</v>
+        <v>8.0100574712643702E-2</v>
       </c>
       <c r="AG29" s="10">
         <f t="shared" si="60"/>
@@ -4946,15 +5061,31 @@
         <f t="shared" si="60"/>
         <v>0</v>
       </c>
-      <c r="AO29" t="s">
+      <c r="AM29" s="10">
+        <f t="shared" si="60"/>
+        <v>0</v>
+      </c>
+      <c r="AN29" s="10">
+        <f t="shared" si="60"/>
+        <v>0</v>
+      </c>
+      <c r="AO29" s="10">
+        <f t="shared" si="60"/>
+        <v>0</v>
+      </c>
+      <c r="AP29" s="10">
+        <f t="shared" si="60"/>
+        <v>0</v>
+      </c>
+      <c r="AS29" t="s">
         <v>58</v>
       </c>
-      <c r="AP29" s="4">
+      <c r="AT29" s="4">
         <f>Main!D3</f>
-        <v>57.7</v>
+        <v>38.46</v>
       </c>
     </row>
-    <row r="30" spans="2:156" x14ac:dyDescent="0.3">
+    <row r="30" spans="2:160" x14ac:dyDescent="0.3">
       <c r="B30" t="s">
         <v>51</v>
       </c>
@@ -5036,81 +5167,85 @@
       </c>
       <c r="V30" s="10">
         <f t="shared" si="62"/>
-        <v>-6.3656627906976748</v>
-      </c>
-      <c r="X30" s="10">
-        <f t="shared" ref="X30" si="63">X18/X3</f>
+        <v>12.168012924071082</v>
+      </c>
+      <c r="W30" s="10"/>
+      <c r="X30" s="10"/>
+      <c r="Y30" s="10"/>
+      <c r="Z30" s="10"/>
+      <c r="AB30" s="10">
+        <f t="shared" ref="AB30" si="63">AB18/AB3</f>
         <v>-53.15</v>
       </c>
-      <c r="Y30" s="10">
-        <f>Y18/Y3</f>
+      <c r="AC30" s="10">
+        <f>AC18/AC3</f>
         <v>-4.3214285714285721</v>
       </c>
-      <c r="Z30" s="10">
-        <f t="shared" ref="Z30:AL30" si="64">Z18/Z3</f>
+      <c r="AD30" s="10">
+        <f t="shared" ref="AD30:AP30" si="64">AD18/AD3</f>
         <v>-7.1590909090909101</v>
       </c>
-      <c r="AA30" s="10">
+      <c r="AE30" s="10">
         <f t="shared" si="64"/>
         <v>-7.6960556844547572</v>
       </c>
-      <c r="AB30" s="10">
-        <f t="shared" si="64"/>
-        <v>-2.1397122302158276</v>
-      </c>
-      <c r="AC30" s="10">
-        <f t="shared" si="64"/>
-        <v>-1.1206889435819769</v>
-      </c>
-      <c r="AD30" s="10">
-        <f t="shared" si="64"/>
-        <v>-0.55627051279277362</v>
-      </c>
-      <c r="AE30" s="10">
-        <f t="shared" si="64"/>
-        <v>-0.25614031467720577</v>
-      </c>
       <c r="AF30" s="10">
         <f t="shared" si="64"/>
-        <v>-5.2731089712072542E-2</v>
+        <v>-3.9369715603382001</v>
       </c>
       <c r="AG30" s="10">
         <f t="shared" si="64"/>
-        <v>9.266022332001056E-2</v>
+        <v>-2.4281609288401635</v>
       </c>
       <c r="AH30" s="10">
         <f t="shared" si="64"/>
-        <v>0.17753350750387439</v>
+        <v>-1.3593602145255534</v>
       </c>
       <c r="AI30" s="10">
         <f t="shared" si="64"/>
-        <v>0.23712818592397408</v>
+        <v>-0.78362285792305542</v>
       </c>
       <c r="AJ30" s="10">
         <f t="shared" si="64"/>
-        <v>0.27548612425530866</v>
+        <v>-0.41776709596531697</v>
       </c>
       <c r="AK30" s="10">
         <f t="shared" si="64"/>
-        <v>0.30489158557131874</v>
+        <v>-0.16744026261162342</v>
       </c>
       <c r="AL30" s="10">
         <f t="shared" si="64"/>
-        <v>0.31632439169112264</v>
-      </c>
-      <c r="AO30" s="1" t="s">
+        <v>-3.7490521764369934E-2</v>
+      </c>
+      <c r="AM30" s="10">
+        <f t="shared" si="64"/>
+        <v>5.1926793913838344E-2</v>
+      </c>
+      <c r="AN30" s="10">
+        <f t="shared" si="64"/>
+        <v>0.10900392906313321</v>
+      </c>
+      <c r="AO30" s="10">
+        <f t="shared" si="64"/>
+        <v>0.14840410603139384</v>
+      </c>
+      <c r="AP30" s="10">
+        <f t="shared" si="64"/>
+        <v>0.16219762696242648</v>
+      </c>
+      <c r="AS30" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="AP30" s="9">
-        <f>AP28/AP29-1</f>
-        <v>-0.82129405585665005</v>
+      <c r="AT30" s="9">
+        <f>AT28/AT29-1</f>
+        <v>-0.74864535243623043</v>
       </c>
     </row>
-    <row r="31" spans="2:156" x14ac:dyDescent="0.3">
-      <c r="AO31" t="s">
+    <row r="31" spans="2:160" x14ac:dyDescent="0.3">
+      <c r="AS31" t="s">
         <v>60</v>
       </c>
-      <c r="AP31" s="6" t="s">
+      <c r="AT31" s="6" t="s">
         <v>61</v>
       </c>
     </row>
